--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(バッチ)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(バッチ)_サンプル.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C753FA7F-ADC9-49E3-9C06-78EF01F999B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E23CA8B-A29B-4064-9D31-5AFCB8A02CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="1770" windowWidth="33090" windowHeight="18225" tabRatio="619" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="619" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
-    <sheet name="【テストターゲット名】_クラス単体" sheetId="25" r:id="rId3"/>
-    <sheet name="【バッチ処理ID】_リクエスト単体" sheetId="26" r:id="rId4"/>
-    <sheet name="取引単体" sheetId="17" r:id="rId5"/>
+    <sheet name="【バッチ処理ID】_クラス単体テスト" sheetId="25" r:id="rId3"/>
+    <sheet name="【バッチ処理ID】_リクエスト単体テスト" sheetId="26" r:id="rId4"/>
+    <sheet name="取引単体テスト" sheetId="17" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【テストターゲット名】_クラス単体!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【バッチ処理ID】_リクエスト単体!$A$10:$R$329</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">【テストターゲット名】_クラス単体!$A$1:$R$304</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">【バッチ処理ID】_リクエスト単体!$A$1:$R$329</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$P$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【バッチ処理ID】_クラス単体テスト!$A$10:$R$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【バッチ処理ID】_リクエスト単体テスト!$A$10:$R$329</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">【バッチ処理ID】_クラス単体テスト!$A$1:$R$304</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">【バッチ処理ID】_リクエスト単体テスト!$A$1:$R$329</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体テスト!$A$1:$P$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">【テストターゲット名】_クラス単体!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">【バッチ処理ID】_リクエスト単体!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">【バッチ処理ID】_クラス単体テスト!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">【バッチ処理ID】_リクエスト単体テスト!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体テスト!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1898" uniqueCount="649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1897" uniqueCount="648">
   <si>
     <t>正常取引</t>
     <rPh sb="0" eb="2">
@@ -7655,13 +7655,6 @@
     <t>テストターゲット名：XxxAction</t>
     <rPh sb="8" eb="9">
       <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>バッチ処理ID：XXX</t>
-    <rPh sb="3" eb="5">
-      <t>ショリ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -9912,6 +9905,72 @@
     <xf numFmtId="31" fontId="13" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="6" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -10018,72 +10077,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10218,8 +10211,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7953375" y="285750"/>
-          <a:ext cx="1400175" cy="590550"/>
+          <a:off x="7905750" y="285750"/>
+          <a:ext cx="1390650" cy="590550"/>
           <a:chOff x="591" y="61"/>
           <a:chExt cx="147" cy="62"/>
         </a:xfrm>
@@ -11960,8 +11953,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="16259175" y="1676400"/>
-          <a:ext cx="4914900" cy="2733675"/>
+          <a:off x="16224250" y="1644650"/>
+          <a:ext cx="4899025" cy="2670175"/>
           <a:chOff x="16335375" y="4752975"/>
           <a:chExt cx="4914900" cy="2733675"/>
         </a:xfrm>
@@ -13357,9 +13350,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -13397,9 +13390,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -13432,26 +13425,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -13484,26 +13460,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -13681,9 +13640,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K513"/>
-  <sheetFormatPr defaultColWidth="6.625" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="6.58203125" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="16384" width="6.625" style="1"/>
+    <col min="1" max="16384" width="6.58203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="13.5" customHeight="1">
@@ -13769,18 +13728,18 @@
       <c r="G31" s="5"/>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" spans="6:11" ht="18.75">
+    <row r="32" spans="6:11" ht="19">
       <c r="F32" s="3"/>
       <c r="G32" s="5"/>
       <c r="H32" s="3"/>
       <c r="J32" s="2"/>
     </row>
-    <row r="33" spans="6:10" ht="18.75">
+    <row r="33" spans="6:10" ht="19">
       <c r="F33" s="3"/>
       <c r="H33" s="3"/>
       <c r="J33" s="4"/>
     </row>
-    <row r="34" spans="6:10" ht="18.75">
+    <row r="34" spans="6:10" ht="19">
       <c r="F34" s="3"/>
       <c r="H34" s="3"/>
       <c r="J34" s="2"/>
@@ -14283,63 +14242,63 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN34"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="11.25"/>
+  <sheetFormatPr defaultColWidth="3.58203125" defaultRowHeight="11"/>
   <cols>
-    <col min="1" max="16384" width="3.625" style="22"/>
+    <col min="1" max="16384" width="3.58203125" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="171" t="s">
+      <c r="A1" s="193" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="172"/>
-      <c r="C1" s="172"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="174" t="s">
+      <c r="B1" s="194"/>
+      <c r="C1" s="194"/>
+      <c r="D1" s="195"/>
+      <c r="E1" s="196" t="s">
         <v>85</v>
       </c>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
-      <c r="H1" s="175"/>
-      <c r="I1" s="175"/>
-      <c r="J1" s="175"/>
-      <c r="K1" s="175"/>
-      <c r="L1" s="175"/>
-      <c r="M1" s="175"/>
-      <c r="N1" s="176"/>
-      <c r="O1" s="180" t="s">
+      <c r="F1" s="197"/>
+      <c r="G1" s="197"/>
+      <c r="H1" s="197"/>
+      <c r="I1" s="197"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="197"/>
+      <c r="N1" s="198"/>
+      <c r="O1" s="202" t="s">
         <v>66</v>
       </c>
-      <c r="P1" s="181"/>
-      <c r="Q1" s="181"/>
-      <c r="R1" s="182"/>
-      <c r="S1" s="189" t="s">
-        <v>648</v>
-      </c>
-      <c r="T1" s="190"/>
-      <c r="U1" s="190"/>
-      <c r="V1" s="190"/>
-      <c r="W1" s="190"/>
-      <c r="X1" s="190"/>
-      <c r="Y1" s="190"/>
-      <c r="Z1" s="191"/>
-      <c r="AA1" s="171" t="s">
+      <c r="P1" s="203"/>
+      <c r="Q1" s="203"/>
+      <c r="R1" s="204"/>
+      <c r="S1" s="211" t="s">
+        <v>647</v>
+      </c>
+      <c r="T1" s="212"/>
+      <c r="U1" s="212"/>
+      <c r="V1" s="212"/>
+      <c r="W1" s="212"/>
+      <c r="X1" s="212"/>
+      <c r="Y1" s="212"/>
+      <c r="Z1" s="213"/>
+      <c r="AA1" s="193" t="s">
         <v>67</v>
       </c>
-      <c r="AB1" s="173"/>
-      <c r="AC1" s="198" t="str">
+      <c r="AB1" s="195"/>
+      <c r="AC1" s="220" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="199"/>
-      <c r="AE1" s="199"/>
-      <c r="AF1" s="200"/>
-      <c r="AG1" s="165">
+      <c r="AD1" s="221"/>
+      <c r="AE1" s="221"/>
+      <c r="AF1" s="222"/>
+      <c r="AG1" s="187">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="166"/>
-      <c r="AI1" s="167"/>
+      <c r="AH1" s="188"/>
+      <c r="AI1" s="189"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -14347,53 +14306,53 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="171" t="s">
+      <c r="A2" s="193" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="172"/>
-      <c r="C2" s="172"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="174" t="s">
+      <c r="B2" s="194"/>
+      <c r="C2" s="194"/>
+      <c r="D2" s="195"/>
+      <c r="E2" s="196" t="s">
         <v>86</v>
       </c>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
-      <c r="H2" s="175"/>
-      <c r="I2" s="175"/>
-      <c r="J2" s="175"/>
-      <c r="K2" s="175"/>
-      <c r="L2" s="175"/>
-      <c r="M2" s="175"/>
-      <c r="N2" s="176"/>
-      <c r="O2" s="183"/>
-      <c r="P2" s="184"/>
-      <c r="Q2" s="184"/>
-      <c r="R2" s="185"/>
-      <c r="S2" s="192"/>
-      <c r="T2" s="193"/>
-      <c r="U2" s="193"/>
-      <c r="V2" s="193"/>
-      <c r="W2" s="193"/>
-      <c r="X2" s="193"/>
-      <c r="Y2" s="193"/>
-      <c r="Z2" s="194"/>
-      <c r="AA2" s="171" t="s">
+      <c r="F2" s="197"/>
+      <c r="G2" s="197"/>
+      <c r="H2" s="197"/>
+      <c r="I2" s="197"/>
+      <c r="J2" s="197"/>
+      <c r="K2" s="197"/>
+      <c r="L2" s="197"/>
+      <c r="M2" s="197"/>
+      <c r="N2" s="198"/>
+      <c r="O2" s="205"/>
+      <c r="P2" s="206"/>
+      <c r="Q2" s="206"/>
+      <c r="R2" s="207"/>
+      <c r="S2" s="214"/>
+      <c r="T2" s="215"/>
+      <c r="U2" s="215"/>
+      <c r="V2" s="215"/>
+      <c r="W2" s="215"/>
+      <c r="X2" s="215"/>
+      <c r="Y2" s="215"/>
+      <c r="Z2" s="216"/>
+      <c r="AA2" s="193" t="s">
         <v>69</v>
       </c>
-      <c r="AB2" s="173"/>
-      <c r="AC2" s="177" t="str">
+      <c r="AB2" s="195"/>
+      <c r="AC2" s="199" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="178"/>
-      <c r="AE2" s="178"/>
-      <c r="AF2" s="179"/>
-      <c r="AG2" s="165">
+      <c r="AD2" s="200"/>
+      <c r="AE2" s="200"/>
+      <c r="AF2" s="201"/>
+      <c r="AG2" s="187">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44852</v>
       </c>
-      <c r="AH2" s="166"/>
-      <c r="AI2" s="167"/>
+      <c r="AH2" s="188"/>
+      <c r="AI2" s="189"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -14401,45 +14360,45 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="193" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="172"/>
-      <c r="C3" s="172"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="174" t="s">
+      <c r="B3" s="194"/>
+      <c r="C3" s="194"/>
+      <c r="D3" s="195"/>
+      <c r="E3" s="196" t="s">
         <v>87</v>
       </c>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="175"/>
-      <c r="I3" s="175"/>
-      <c r="J3" s="175"/>
-      <c r="K3" s="175"/>
-      <c r="L3" s="175"/>
-      <c r="M3" s="175"/>
-      <c r="N3" s="176"/>
-      <c r="O3" s="186"/>
-      <c r="P3" s="187"/>
-      <c r="Q3" s="187"/>
-      <c r="R3" s="188"/>
-      <c r="S3" s="195"/>
-      <c r="T3" s="196"/>
-      <c r="U3" s="196"/>
-      <c r="V3" s="196"/>
-      <c r="W3" s="196"/>
-      <c r="X3" s="196"/>
-      <c r="Y3" s="196"/>
-      <c r="Z3" s="197"/>
-      <c r="AA3" s="171"/>
-      <c r="AB3" s="173"/>
-      <c r="AC3" s="198"/>
-      <c r="AD3" s="199"/>
-      <c r="AE3" s="199"/>
-      <c r="AF3" s="200"/>
-      <c r="AG3" s="165"/>
-      <c r="AH3" s="166"/>
-      <c r="AI3" s="167"/>
+      <c r="F3" s="197"/>
+      <c r="G3" s="197"/>
+      <c r="H3" s="197"/>
+      <c r="I3" s="197"/>
+      <c r="J3" s="197"/>
+      <c r="K3" s="197"/>
+      <c r="L3" s="197"/>
+      <c r="M3" s="197"/>
+      <c r="N3" s="198"/>
+      <c r="O3" s="208"/>
+      <c r="P3" s="209"/>
+      <c r="Q3" s="209"/>
+      <c r="R3" s="210"/>
+      <c r="S3" s="217"/>
+      <c r="T3" s="218"/>
+      <c r="U3" s="218"/>
+      <c r="V3" s="218"/>
+      <c r="W3" s="218"/>
+      <c r="X3" s="218"/>
+      <c r="Y3" s="218"/>
+      <c r="Z3" s="219"/>
+      <c r="AA3" s="193"/>
+      <c r="AB3" s="195"/>
+      <c r="AC3" s="220"/>
+      <c r="AD3" s="221"/>
+      <c r="AE3" s="221"/>
+      <c r="AF3" s="222"/>
+      <c r="AG3" s="187"/>
+      <c r="AH3" s="188"/>
+      <c r="AI3" s="189"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -14476,97 +14435,97 @@
       <c r="A7" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="168" t="s">
+      <c r="B7" s="190" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="169"/>
-      <c r="D7" s="168" t="s">
+      <c r="C7" s="191"/>
+      <c r="D7" s="190" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="170"/>
-      <c r="F7" s="169"/>
-      <c r="G7" s="168" t="s">
+      <c r="E7" s="192"/>
+      <c r="F7" s="191"/>
+      <c r="G7" s="190" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="170"/>
-      <c r="I7" s="169"/>
-      <c r="J7" s="168" t="s">
+      <c r="H7" s="192"/>
+      <c r="I7" s="191"/>
+      <c r="J7" s="190" t="s">
         <v>75</v>
       </c>
-      <c r="K7" s="170"/>
-      <c r="L7" s="170"/>
-      <c r="M7" s="170"/>
-      <c r="N7" s="170"/>
-      <c r="O7" s="170"/>
-      <c r="P7" s="169"/>
-      <c r="Q7" s="168" t="s">
+      <c r="K7" s="192"/>
+      <c r="L7" s="192"/>
+      <c r="M7" s="192"/>
+      <c r="N7" s="192"/>
+      <c r="O7" s="192"/>
+      <c r="P7" s="191"/>
+      <c r="Q7" s="190" t="s">
         <v>76</v>
       </c>
-      <c r="R7" s="170"/>
-      <c r="S7" s="170"/>
-      <c r="T7" s="170"/>
-      <c r="U7" s="170"/>
-      <c r="V7" s="170"/>
-      <c r="W7" s="170"/>
-      <c r="X7" s="170"/>
-      <c r="Y7" s="170"/>
-      <c r="Z7" s="170"/>
-      <c r="AA7" s="170"/>
-      <c r="AB7" s="170"/>
-      <c r="AC7" s="170"/>
-      <c r="AD7" s="170"/>
-      <c r="AE7" s="169"/>
-      <c r="AF7" s="168" t="s">
+      <c r="R7" s="192"/>
+      <c r="S7" s="192"/>
+      <c r="T7" s="192"/>
+      <c r="U7" s="192"/>
+      <c r="V7" s="192"/>
+      <c r="W7" s="192"/>
+      <c r="X7" s="192"/>
+      <c r="Y7" s="192"/>
+      <c r="Z7" s="192"/>
+      <c r="AA7" s="192"/>
+      <c r="AB7" s="192"/>
+      <c r="AC7" s="192"/>
+      <c r="AD7" s="192"/>
+      <c r="AE7" s="191"/>
+      <c r="AF7" s="190" t="s">
         <v>77</v>
       </c>
-      <c r="AG7" s="170"/>
-      <c r="AH7" s="170"/>
-      <c r="AI7" s="169"/>
+      <c r="AG7" s="192"/>
+      <c r="AH7" s="192"/>
+      <c r="AI7" s="191"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="24">
         <v>1</v>
       </c>
-      <c r="B8" s="213" t="s">
+      <c r="B8" s="178" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="214"/>
-      <c r="D8" s="215">
+      <c r="C8" s="179"/>
+      <c r="D8" s="180">
         <v>43336</v>
       </c>
-      <c r="E8" s="216"/>
-      <c r="F8" s="217"/>
-      <c r="G8" s="213" t="s">
+      <c r="E8" s="181"/>
+      <c r="F8" s="182"/>
+      <c r="G8" s="178" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="218"/>
-      <c r="I8" s="214"/>
-      <c r="J8" s="219" t="s">
+      <c r="H8" s="183"/>
+      <c r="I8" s="179"/>
+      <c r="J8" s="184" t="s">
         <v>80</v>
       </c>
-      <c r="K8" s="220"/>
-      <c r="L8" s="220"/>
-      <c r="M8" s="220"/>
-      <c r="N8" s="220"/>
-      <c r="O8" s="220"/>
-      <c r="P8" s="221"/>
-      <c r="Q8" s="219" t="s">
+      <c r="K8" s="185"/>
+      <c r="L8" s="185"/>
+      <c r="M8" s="185"/>
+      <c r="N8" s="185"/>
+      <c r="O8" s="185"/>
+      <c r="P8" s="186"/>
+      <c r="Q8" s="184" t="s">
         <v>81</v>
       </c>
-      <c r="R8" s="220"/>
-      <c r="S8" s="220"/>
-      <c r="T8" s="220"/>
-      <c r="U8" s="220"/>
-      <c r="V8" s="220"/>
-      <c r="W8" s="220"/>
-      <c r="X8" s="220"/>
-      <c r="Y8" s="220"/>
-      <c r="Z8" s="220"/>
-      <c r="AA8" s="220"/>
-      <c r="AB8" s="220"/>
-      <c r="AC8" s="220"/>
-      <c r="AD8" s="220"/>
-      <c r="AE8" s="221"/>
+      <c r="R8" s="185"/>
+      <c r="S8" s="185"/>
+      <c r="T8" s="185"/>
+      <c r="U8" s="185"/>
+      <c r="V8" s="185"/>
+      <c r="W8" s="185"/>
+      <c r="X8" s="185"/>
+      <c r="Y8" s="185"/>
+      <c r="Z8" s="185"/>
+      <c r="AA8" s="185"/>
+      <c r="AB8" s="185"/>
+      <c r="AC8" s="185"/>
+      <c r="AD8" s="185"/>
+      <c r="AE8" s="186"/>
       <c r="AF8" s="25" t="s">
         <v>82</v>
       </c>
@@ -14578,1101 +14537,946 @@
       <c r="A9" s="24">
         <v>2</v>
       </c>
-      <c r="B9" s="201" t="s">
+      <c r="B9" s="165" t="s">
         <v>549</v>
       </c>
-      <c r="C9" s="202"/>
-      <c r="D9" s="203">
+      <c r="C9" s="166"/>
+      <c r="D9" s="167">
         <v>44852</v>
       </c>
-      <c r="E9" s="204"/>
-      <c r="F9" s="205"/>
-      <c r="G9" s="203" t="s">
+      <c r="E9" s="168"/>
+      <c r="F9" s="169"/>
+      <c r="G9" s="167" t="s">
         <v>550</v>
       </c>
-      <c r="H9" s="206"/>
-      <c r="I9" s="202"/>
-      <c r="J9" s="207" t="s">
+      <c r="H9" s="170"/>
+      <c r="I9" s="166"/>
+      <c r="J9" s="174" t="s">
         <v>552</v>
       </c>
-      <c r="K9" s="208"/>
-      <c r="L9" s="208"/>
-      <c r="M9" s="208"/>
-      <c r="N9" s="208"/>
-      <c r="O9" s="208"/>
-      <c r="P9" s="209"/>
-      <c r="Q9" s="207" t="s">
+      <c r="K9" s="172"/>
+      <c r="L9" s="172"/>
+      <c r="M9" s="172"/>
+      <c r="N9" s="172"/>
+      <c r="O9" s="172"/>
+      <c r="P9" s="173"/>
+      <c r="Q9" s="174" t="s">
         <v>551</v>
       </c>
-      <c r="R9" s="210"/>
-      <c r="S9" s="210"/>
-      <c r="T9" s="210"/>
-      <c r="U9" s="210"/>
-      <c r="V9" s="210"/>
-      <c r="W9" s="210"/>
-      <c r="X9" s="210"/>
-      <c r="Y9" s="210"/>
-      <c r="Z9" s="210"/>
-      <c r="AA9" s="210"/>
-      <c r="AB9" s="210"/>
-      <c r="AC9" s="210"/>
-      <c r="AD9" s="210"/>
-      <c r="AE9" s="211"/>
-      <c r="AF9" s="212" t="s">
+      <c r="R9" s="175"/>
+      <c r="S9" s="175"/>
+      <c r="T9" s="175"/>
+      <c r="U9" s="175"/>
+      <c r="V9" s="175"/>
+      <c r="W9" s="175"/>
+      <c r="X9" s="175"/>
+      <c r="Y9" s="175"/>
+      <c r="Z9" s="175"/>
+      <c r="AA9" s="175"/>
+      <c r="AB9" s="175"/>
+      <c r="AC9" s="175"/>
+      <c r="AD9" s="175"/>
+      <c r="AE9" s="176"/>
+      <c r="AF9" s="171" t="s">
         <v>82</v>
       </c>
-      <c r="AG9" s="208"/>
-      <c r="AH9" s="208"/>
-      <c r="AI9" s="209"/>
+      <c r="AG9" s="172"/>
+      <c r="AH9" s="172"/>
+      <c r="AI9" s="173"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="21"/>
-      <c r="B10" s="201"/>
-      <c r="C10" s="202"/>
-      <c r="D10" s="203"/>
-      <c r="E10" s="204"/>
-      <c r="F10" s="205"/>
-      <c r="G10" s="201"/>
-      <c r="H10" s="206"/>
-      <c r="I10" s="202"/>
-      <c r="J10" s="212"/>
-      <c r="K10" s="208"/>
-      <c r="L10" s="208"/>
-      <c r="M10" s="208"/>
-      <c r="N10" s="208"/>
-      <c r="O10" s="208"/>
-      <c r="P10" s="209"/>
-      <c r="Q10" s="207"/>
-      <c r="R10" s="210"/>
-      <c r="S10" s="210"/>
-      <c r="T10" s="210"/>
-      <c r="U10" s="210"/>
-      <c r="V10" s="210"/>
-      <c r="W10" s="210"/>
-      <c r="X10" s="210"/>
-      <c r="Y10" s="210"/>
-      <c r="Z10" s="210"/>
-      <c r="AA10" s="210"/>
-      <c r="AB10" s="210"/>
-      <c r="AC10" s="210"/>
-      <c r="AD10" s="210"/>
-      <c r="AE10" s="211"/>
-      <c r="AF10" s="212"/>
-      <c r="AG10" s="208"/>
-      <c r="AH10" s="208"/>
-      <c r="AI10" s="209"/>
+      <c r="B10" s="165"/>
+      <c r="C10" s="166"/>
+      <c r="D10" s="167"/>
+      <c r="E10" s="168"/>
+      <c r="F10" s="169"/>
+      <c r="G10" s="165"/>
+      <c r="H10" s="170"/>
+      <c r="I10" s="166"/>
+      <c r="J10" s="171"/>
+      <c r="K10" s="172"/>
+      <c r="L10" s="172"/>
+      <c r="M10" s="172"/>
+      <c r="N10" s="172"/>
+      <c r="O10" s="172"/>
+      <c r="P10" s="173"/>
+      <c r="Q10" s="174"/>
+      <c r="R10" s="175"/>
+      <c r="S10" s="175"/>
+      <c r="T10" s="175"/>
+      <c r="U10" s="175"/>
+      <c r="V10" s="175"/>
+      <c r="W10" s="175"/>
+      <c r="X10" s="175"/>
+      <c r="Y10" s="175"/>
+      <c r="Z10" s="175"/>
+      <c r="AA10" s="175"/>
+      <c r="AB10" s="175"/>
+      <c r="AC10" s="175"/>
+      <c r="AD10" s="175"/>
+      <c r="AE10" s="176"/>
+      <c r="AF10" s="171"/>
+      <c r="AG10" s="172"/>
+      <c r="AH10" s="172"/>
+      <c r="AI10" s="173"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="21"/>
-      <c r="B11" s="201"/>
-      <c r="C11" s="202"/>
-      <c r="D11" s="203"/>
-      <c r="E11" s="204"/>
-      <c r="F11" s="205"/>
-      <c r="G11" s="201"/>
-      <c r="H11" s="206"/>
-      <c r="I11" s="202"/>
-      <c r="J11" s="212"/>
-      <c r="K11" s="208"/>
-      <c r="L11" s="208"/>
-      <c r="M11" s="208"/>
-      <c r="N11" s="208"/>
-      <c r="O11" s="208"/>
-      <c r="P11" s="209"/>
-      <c r="Q11" s="207"/>
-      <c r="R11" s="210"/>
-      <c r="S11" s="210"/>
-      <c r="T11" s="210"/>
-      <c r="U11" s="210"/>
-      <c r="V11" s="210"/>
-      <c r="W11" s="210"/>
-      <c r="X11" s="210"/>
-      <c r="Y11" s="210"/>
-      <c r="Z11" s="210"/>
-      <c r="AA11" s="210"/>
-      <c r="AB11" s="210"/>
-      <c r="AC11" s="210"/>
-      <c r="AD11" s="210"/>
-      <c r="AE11" s="211"/>
-      <c r="AF11" s="212"/>
-      <c r="AG11" s="208"/>
-      <c r="AH11" s="208"/>
-      <c r="AI11" s="209"/>
+      <c r="B11" s="165"/>
+      <c r="C11" s="166"/>
+      <c r="D11" s="167"/>
+      <c r="E11" s="168"/>
+      <c r="F11" s="169"/>
+      <c r="G11" s="165"/>
+      <c r="H11" s="170"/>
+      <c r="I11" s="166"/>
+      <c r="J11" s="171"/>
+      <c r="K11" s="172"/>
+      <c r="L11" s="172"/>
+      <c r="M11" s="172"/>
+      <c r="N11" s="172"/>
+      <c r="O11" s="172"/>
+      <c r="P11" s="173"/>
+      <c r="Q11" s="174"/>
+      <c r="R11" s="175"/>
+      <c r="S11" s="175"/>
+      <c r="T11" s="175"/>
+      <c r="U11" s="175"/>
+      <c r="V11" s="175"/>
+      <c r="W11" s="175"/>
+      <c r="X11" s="175"/>
+      <c r="Y11" s="175"/>
+      <c r="Z11" s="175"/>
+      <c r="AA11" s="175"/>
+      <c r="AB11" s="175"/>
+      <c r="AC11" s="175"/>
+      <c r="AD11" s="175"/>
+      <c r="AE11" s="176"/>
+      <c r="AF11" s="171"/>
+      <c r="AG11" s="172"/>
+      <c r="AH11" s="172"/>
+      <c r="AI11" s="173"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="21"/>
-      <c r="B12" s="201"/>
-      <c r="C12" s="202"/>
-      <c r="D12" s="203"/>
-      <c r="E12" s="204"/>
-      <c r="F12" s="205"/>
-      <c r="G12" s="201"/>
-      <c r="H12" s="206"/>
-      <c r="I12" s="202"/>
-      <c r="J12" s="212"/>
-      <c r="K12" s="208"/>
-      <c r="L12" s="208"/>
-      <c r="M12" s="208"/>
-      <c r="N12" s="208"/>
-      <c r="O12" s="208"/>
-      <c r="P12" s="209"/>
-      <c r="Q12" s="207"/>
-      <c r="R12" s="210"/>
-      <c r="S12" s="210"/>
-      <c r="T12" s="210"/>
-      <c r="U12" s="210"/>
-      <c r="V12" s="210"/>
-      <c r="W12" s="210"/>
-      <c r="X12" s="210"/>
-      <c r="Y12" s="210"/>
-      <c r="Z12" s="210"/>
-      <c r="AA12" s="210"/>
-      <c r="AB12" s="210"/>
-      <c r="AC12" s="210"/>
-      <c r="AD12" s="210"/>
-      <c r="AE12" s="211"/>
-      <c r="AF12" s="212"/>
-      <c r="AG12" s="208"/>
-      <c r="AH12" s="208"/>
-      <c r="AI12" s="209"/>
+      <c r="B12" s="165"/>
+      <c r="C12" s="166"/>
+      <c r="D12" s="167"/>
+      <c r="E12" s="168"/>
+      <c r="F12" s="169"/>
+      <c r="G12" s="165"/>
+      <c r="H12" s="170"/>
+      <c r="I12" s="166"/>
+      <c r="J12" s="171"/>
+      <c r="K12" s="172"/>
+      <c r="L12" s="172"/>
+      <c r="M12" s="172"/>
+      <c r="N12" s="172"/>
+      <c r="O12" s="172"/>
+      <c r="P12" s="173"/>
+      <c r="Q12" s="174"/>
+      <c r="R12" s="175"/>
+      <c r="S12" s="175"/>
+      <c r="T12" s="175"/>
+      <c r="U12" s="175"/>
+      <c r="V12" s="175"/>
+      <c r="W12" s="175"/>
+      <c r="X12" s="175"/>
+      <c r="Y12" s="175"/>
+      <c r="Z12" s="175"/>
+      <c r="AA12" s="175"/>
+      <c r="AB12" s="175"/>
+      <c r="AC12" s="175"/>
+      <c r="AD12" s="175"/>
+      <c r="AE12" s="176"/>
+      <c r="AF12" s="171"/>
+      <c r="AG12" s="172"/>
+      <c r="AH12" s="172"/>
+      <c r="AI12" s="173"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="21"/>
-      <c r="B13" s="201"/>
-      <c r="C13" s="202"/>
-      <c r="D13" s="203"/>
-      <c r="E13" s="204"/>
-      <c r="F13" s="205"/>
-      <c r="G13" s="201"/>
-      <c r="H13" s="206"/>
-      <c r="I13" s="202"/>
-      <c r="J13" s="212"/>
-      <c r="K13" s="208"/>
-      <c r="L13" s="208"/>
-      <c r="M13" s="208"/>
-      <c r="N13" s="208"/>
-      <c r="O13" s="208"/>
-      <c r="P13" s="209"/>
-      <c r="Q13" s="207"/>
-      <c r="R13" s="210"/>
-      <c r="S13" s="210"/>
-      <c r="T13" s="210"/>
-      <c r="U13" s="210"/>
-      <c r="V13" s="210"/>
-      <c r="W13" s="210"/>
-      <c r="X13" s="210"/>
-      <c r="Y13" s="210"/>
-      <c r="Z13" s="210"/>
-      <c r="AA13" s="210"/>
-      <c r="AB13" s="210"/>
-      <c r="AC13" s="210"/>
-      <c r="AD13" s="210"/>
-      <c r="AE13" s="211"/>
-      <c r="AF13" s="212"/>
-      <c r="AG13" s="208"/>
-      <c r="AH13" s="208"/>
-      <c r="AI13" s="209"/>
+      <c r="B13" s="165"/>
+      <c r="C13" s="166"/>
+      <c r="D13" s="167"/>
+      <c r="E13" s="168"/>
+      <c r="F13" s="169"/>
+      <c r="G13" s="165"/>
+      <c r="H13" s="170"/>
+      <c r="I13" s="166"/>
+      <c r="J13" s="171"/>
+      <c r="K13" s="172"/>
+      <c r="L13" s="172"/>
+      <c r="M13" s="172"/>
+      <c r="N13" s="172"/>
+      <c r="O13" s="172"/>
+      <c r="P13" s="173"/>
+      <c r="Q13" s="174"/>
+      <c r="R13" s="175"/>
+      <c r="S13" s="175"/>
+      <c r="T13" s="175"/>
+      <c r="U13" s="175"/>
+      <c r="V13" s="175"/>
+      <c r="W13" s="175"/>
+      <c r="X13" s="175"/>
+      <c r="Y13" s="175"/>
+      <c r="Z13" s="175"/>
+      <c r="AA13" s="175"/>
+      <c r="AB13" s="175"/>
+      <c r="AC13" s="175"/>
+      <c r="AD13" s="175"/>
+      <c r="AE13" s="176"/>
+      <c r="AF13" s="171"/>
+      <c r="AG13" s="172"/>
+      <c r="AH13" s="172"/>
+      <c r="AI13" s="173"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="201"/>
-      <c r="C14" s="202"/>
-      <c r="D14" s="203"/>
-      <c r="E14" s="204"/>
-      <c r="F14" s="205"/>
-      <c r="G14" s="201"/>
-      <c r="H14" s="206"/>
-      <c r="I14" s="202"/>
-      <c r="J14" s="212"/>
-      <c r="K14" s="208"/>
-      <c r="L14" s="208"/>
-      <c r="M14" s="208"/>
-      <c r="N14" s="208"/>
-      <c r="O14" s="208"/>
-      <c r="P14" s="209"/>
-      <c r="Q14" s="207"/>
-      <c r="R14" s="210"/>
-      <c r="S14" s="210"/>
-      <c r="T14" s="210"/>
-      <c r="U14" s="210"/>
-      <c r="V14" s="210"/>
-      <c r="W14" s="210"/>
-      <c r="X14" s="210"/>
-      <c r="Y14" s="210"/>
-      <c r="Z14" s="210"/>
-      <c r="AA14" s="210"/>
-      <c r="AB14" s="210"/>
-      <c r="AC14" s="210"/>
-      <c r="AD14" s="210"/>
-      <c r="AE14" s="211"/>
-      <c r="AF14" s="212"/>
-      <c r="AG14" s="208"/>
-      <c r="AH14" s="208"/>
-      <c r="AI14" s="209"/>
+      <c r="B14" s="165"/>
+      <c r="C14" s="166"/>
+      <c r="D14" s="167"/>
+      <c r="E14" s="168"/>
+      <c r="F14" s="169"/>
+      <c r="G14" s="165"/>
+      <c r="H14" s="170"/>
+      <c r="I14" s="166"/>
+      <c r="J14" s="171"/>
+      <c r="K14" s="172"/>
+      <c r="L14" s="172"/>
+      <c r="M14" s="172"/>
+      <c r="N14" s="172"/>
+      <c r="O14" s="172"/>
+      <c r="P14" s="173"/>
+      <c r="Q14" s="174"/>
+      <c r="R14" s="175"/>
+      <c r="S14" s="175"/>
+      <c r="T14" s="175"/>
+      <c r="U14" s="175"/>
+      <c r="V14" s="175"/>
+      <c r="W14" s="175"/>
+      <c r="X14" s="175"/>
+      <c r="Y14" s="175"/>
+      <c r="Z14" s="175"/>
+      <c r="AA14" s="175"/>
+      <c r="AB14" s="175"/>
+      <c r="AC14" s="175"/>
+      <c r="AD14" s="175"/>
+      <c r="AE14" s="176"/>
+      <c r="AF14" s="171"/>
+      <c r="AG14" s="172"/>
+      <c r="AH14" s="172"/>
+      <c r="AI14" s="173"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="21"/>
-      <c r="B15" s="201"/>
-      <c r="C15" s="202"/>
-      <c r="D15" s="203"/>
-      <c r="E15" s="204"/>
-      <c r="F15" s="205"/>
-      <c r="G15" s="201"/>
-      <c r="H15" s="206"/>
-      <c r="I15" s="202"/>
-      <c r="J15" s="212"/>
-      <c r="K15" s="208"/>
-      <c r="L15" s="208"/>
-      <c r="M15" s="208"/>
-      <c r="N15" s="208"/>
-      <c r="O15" s="208"/>
-      <c r="P15" s="209"/>
-      <c r="Q15" s="207"/>
-      <c r="R15" s="210"/>
-      <c r="S15" s="210"/>
-      <c r="T15" s="210"/>
-      <c r="U15" s="210"/>
-      <c r="V15" s="210"/>
-      <c r="W15" s="210"/>
-      <c r="X15" s="210"/>
-      <c r="Y15" s="210"/>
-      <c r="Z15" s="210"/>
-      <c r="AA15" s="210"/>
-      <c r="AB15" s="210"/>
-      <c r="AC15" s="210"/>
-      <c r="AD15" s="210"/>
-      <c r="AE15" s="211"/>
-      <c r="AF15" s="212"/>
-      <c r="AG15" s="208"/>
-      <c r="AH15" s="208"/>
-      <c r="AI15" s="209"/>
+      <c r="B15" s="165"/>
+      <c r="C15" s="166"/>
+      <c r="D15" s="167"/>
+      <c r="E15" s="168"/>
+      <c r="F15" s="169"/>
+      <c r="G15" s="165"/>
+      <c r="H15" s="170"/>
+      <c r="I15" s="166"/>
+      <c r="J15" s="171"/>
+      <c r="K15" s="172"/>
+      <c r="L15" s="172"/>
+      <c r="M15" s="172"/>
+      <c r="N15" s="172"/>
+      <c r="O15" s="172"/>
+      <c r="P15" s="173"/>
+      <c r="Q15" s="174"/>
+      <c r="R15" s="175"/>
+      <c r="S15" s="175"/>
+      <c r="T15" s="175"/>
+      <c r="U15" s="175"/>
+      <c r="V15" s="175"/>
+      <c r="W15" s="175"/>
+      <c r="X15" s="175"/>
+      <c r="Y15" s="175"/>
+      <c r="Z15" s="175"/>
+      <c r="AA15" s="175"/>
+      <c r="AB15" s="175"/>
+      <c r="AC15" s="175"/>
+      <c r="AD15" s="175"/>
+      <c r="AE15" s="176"/>
+      <c r="AF15" s="171"/>
+      <c r="AG15" s="172"/>
+      <c r="AH15" s="172"/>
+      <c r="AI15" s="173"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="21"/>
-      <c r="B16" s="201"/>
-      <c r="C16" s="202"/>
-      <c r="D16" s="203"/>
-      <c r="E16" s="204"/>
-      <c r="F16" s="205"/>
-      <c r="G16" s="201"/>
-      <c r="H16" s="206"/>
-      <c r="I16" s="202"/>
-      <c r="J16" s="212"/>
-      <c r="K16" s="208"/>
-      <c r="L16" s="208"/>
-      <c r="M16" s="208"/>
-      <c r="N16" s="208"/>
-      <c r="O16" s="208"/>
-      <c r="P16" s="209"/>
-      <c r="Q16" s="207"/>
-      <c r="R16" s="210"/>
-      <c r="S16" s="210"/>
-      <c r="T16" s="210"/>
-      <c r="U16" s="210"/>
-      <c r="V16" s="210"/>
-      <c r="W16" s="210"/>
-      <c r="X16" s="210"/>
-      <c r="Y16" s="210"/>
-      <c r="Z16" s="210"/>
-      <c r="AA16" s="210"/>
-      <c r="AB16" s="210"/>
-      <c r="AC16" s="210"/>
-      <c r="AD16" s="210"/>
-      <c r="AE16" s="211"/>
-      <c r="AF16" s="212"/>
-      <c r="AG16" s="208"/>
-      <c r="AH16" s="208"/>
-      <c r="AI16" s="209"/>
+      <c r="B16" s="165"/>
+      <c r="C16" s="166"/>
+      <c r="D16" s="167"/>
+      <c r="E16" s="168"/>
+      <c r="F16" s="169"/>
+      <c r="G16" s="165"/>
+      <c r="H16" s="170"/>
+      <c r="I16" s="166"/>
+      <c r="J16" s="171"/>
+      <c r="K16" s="172"/>
+      <c r="L16" s="172"/>
+      <c r="M16" s="172"/>
+      <c r="N16" s="172"/>
+      <c r="O16" s="172"/>
+      <c r="P16" s="173"/>
+      <c r="Q16" s="174"/>
+      <c r="R16" s="175"/>
+      <c r="S16" s="175"/>
+      <c r="T16" s="175"/>
+      <c r="U16" s="175"/>
+      <c r="V16" s="175"/>
+      <c r="W16" s="175"/>
+      <c r="X16" s="175"/>
+      <c r="Y16" s="175"/>
+      <c r="Z16" s="175"/>
+      <c r="AA16" s="175"/>
+      <c r="AB16" s="175"/>
+      <c r="AC16" s="175"/>
+      <c r="AD16" s="175"/>
+      <c r="AE16" s="176"/>
+      <c r="AF16" s="171"/>
+      <c r="AG16" s="172"/>
+      <c r="AH16" s="172"/>
+      <c r="AI16" s="173"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="21"/>
-      <c r="B17" s="201"/>
-      <c r="C17" s="202"/>
-      <c r="D17" s="203"/>
-      <c r="E17" s="204"/>
-      <c r="F17" s="205"/>
-      <c r="G17" s="201"/>
-      <c r="H17" s="206"/>
-      <c r="I17" s="202"/>
-      <c r="J17" s="212"/>
-      <c r="K17" s="208"/>
-      <c r="L17" s="208"/>
-      <c r="M17" s="208"/>
-      <c r="N17" s="208"/>
-      <c r="O17" s="208"/>
-      <c r="P17" s="209"/>
-      <c r="Q17" s="207"/>
-      <c r="R17" s="210"/>
-      <c r="S17" s="210"/>
-      <c r="T17" s="210"/>
-      <c r="U17" s="210"/>
-      <c r="V17" s="210"/>
-      <c r="W17" s="210"/>
-      <c r="X17" s="210"/>
-      <c r="Y17" s="210"/>
-      <c r="Z17" s="210"/>
-      <c r="AA17" s="210"/>
-      <c r="AB17" s="210"/>
-      <c r="AC17" s="210"/>
-      <c r="AD17" s="210"/>
-      <c r="AE17" s="211"/>
-      <c r="AF17" s="212"/>
-      <c r="AG17" s="208"/>
-      <c r="AH17" s="208"/>
-      <c r="AI17" s="209"/>
+      <c r="B17" s="165"/>
+      <c r="C17" s="166"/>
+      <c r="D17" s="167"/>
+      <c r="E17" s="168"/>
+      <c r="F17" s="169"/>
+      <c r="G17" s="165"/>
+      <c r="H17" s="170"/>
+      <c r="I17" s="166"/>
+      <c r="J17" s="171"/>
+      <c r="K17" s="172"/>
+      <c r="L17" s="172"/>
+      <c r="M17" s="172"/>
+      <c r="N17" s="172"/>
+      <c r="O17" s="172"/>
+      <c r="P17" s="173"/>
+      <c r="Q17" s="174"/>
+      <c r="R17" s="175"/>
+      <c r="S17" s="175"/>
+      <c r="T17" s="175"/>
+      <c r="U17" s="175"/>
+      <c r="V17" s="175"/>
+      <c r="W17" s="175"/>
+      <c r="X17" s="175"/>
+      <c r="Y17" s="175"/>
+      <c r="Z17" s="175"/>
+      <c r="AA17" s="175"/>
+      <c r="AB17" s="175"/>
+      <c r="AC17" s="175"/>
+      <c r="AD17" s="175"/>
+      <c r="AE17" s="176"/>
+      <c r="AF17" s="171"/>
+      <c r="AG17" s="172"/>
+      <c r="AH17" s="172"/>
+      <c r="AI17" s="173"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="21"/>
-      <c r="B18" s="201"/>
-      <c r="C18" s="202"/>
-      <c r="D18" s="203"/>
-      <c r="E18" s="204"/>
-      <c r="F18" s="205"/>
-      <c r="G18" s="201"/>
-      <c r="H18" s="206"/>
-      <c r="I18" s="202"/>
-      <c r="J18" s="212"/>
-      <c r="K18" s="208"/>
-      <c r="L18" s="208"/>
-      <c r="M18" s="208"/>
-      <c r="N18" s="208"/>
-      <c r="O18" s="208"/>
-      <c r="P18" s="209"/>
-      <c r="Q18" s="207"/>
-      <c r="R18" s="210"/>
-      <c r="S18" s="210"/>
-      <c r="T18" s="210"/>
-      <c r="U18" s="210"/>
-      <c r="V18" s="210"/>
-      <c r="W18" s="210"/>
-      <c r="X18" s="210"/>
-      <c r="Y18" s="210"/>
-      <c r="Z18" s="210"/>
-      <c r="AA18" s="210"/>
-      <c r="AB18" s="210"/>
-      <c r="AC18" s="210"/>
-      <c r="AD18" s="210"/>
-      <c r="AE18" s="211"/>
-      <c r="AF18" s="212"/>
-      <c r="AG18" s="208"/>
-      <c r="AH18" s="208"/>
-      <c r="AI18" s="209"/>
+      <c r="B18" s="165"/>
+      <c r="C18" s="166"/>
+      <c r="D18" s="167"/>
+      <c r="E18" s="168"/>
+      <c r="F18" s="169"/>
+      <c r="G18" s="165"/>
+      <c r="H18" s="170"/>
+      <c r="I18" s="166"/>
+      <c r="J18" s="171"/>
+      <c r="K18" s="172"/>
+      <c r="L18" s="172"/>
+      <c r="M18" s="172"/>
+      <c r="N18" s="172"/>
+      <c r="O18" s="172"/>
+      <c r="P18" s="173"/>
+      <c r="Q18" s="174"/>
+      <c r="R18" s="175"/>
+      <c r="S18" s="175"/>
+      <c r="T18" s="175"/>
+      <c r="U18" s="175"/>
+      <c r="V18" s="175"/>
+      <c r="W18" s="175"/>
+      <c r="X18" s="175"/>
+      <c r="Y18" s="175"/>
+      <c r="Z18" s="175"/>
+      <c r="AA18" s="175"/>
+      <c r="AB18" s="175"/>
+      <c r="AC18" s="175"/>
+      <c r="AD18" s="175"/>
+      <c r="AE18" s="176"/>
+      <c r="AF18" s="171"/>
+      <c r="AG18" s="172"/>
+      <c r="AH18" s="172"/>
+      <c r="AI18" s="173"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="21"/>
-      <c r="B19" s="201"/>
-      <c r="C19" s="202"/>
-      <c r="D19" s="203"/>
-      <c r="E19" s="204"/>
-      <c r="F19" s="205"/>
-      <c r="G19" s="201"/>
-      <c r="H19" s="206"/>
-      <c r="I19" s="202"/>
-      <c r="J19" s="212"/>
-      <c r="K19" s="208"/>
-      <c r="L19" s="208"/>
-      <c r="M19" s="208"/>
-      <c r="N19" s="208"/>
-      <c r="O19" s="208"/>
-      <c r="P19" s="209"/>
-      <c r="Q19" s="207"/>
-      <c r="R19" s="210"/>
-      <c r="S19" s="210"/>
-      <c r="T19" s="210"/>
-      <c r="U19" s="210"/>
-      <c r="V19" s="210"/>
-      <c r="W19" s="210"/>
-      <c r="X19" s="210"/>
-      <c r="Y19" s="210"/>
-      <c r="Z19" s="210"/>
-      <c r="AA19" s="210"/>
-      <c r="AB19" s="210"/>
-      <c r="AC19" s="210"/>
-      <c r="AD19" s="210"/>
-      <c r="AE19" s="211"/>
-      <c r="AF19" s="212"/>
-      <c r="AG19" s="208"/>
-      <c r="AH19" s="208"/>
-      <c r="AI19" s="209"/>
+      <c r="B19" s="165"/>
+      <c r="C19" s="166"/>
+      <c r="D19" s="167"/>
+      <c r="E19" s="168"/>
+      <c r="F19" s="169"/>
+      <c r="G19" s="165"/>
+      <c r="H19" s="170"/>
+      <c r="I19" s="166"/>
+      <c r="J19" s="171"/>
+      <c r="K19" s="172"/>
+      <c r="L19" s="172"/>
+      <c r="M19" s="172"/>
+      <c r="N19" s="172"/>
+      <c r="O19" s="172"/>
+      <c r="P19" s="173"/>
+      <c r="Q19" s="174"/>
+      <c r="R19" s="175"/>
+      <c r="S19" s="175"/>
+      <c r="T19" s="175"/>
+      <c r="U19" s="175"/>
+      <c r="V19" s="175"/>
+      <c r="W19" s="175"/>
+      <c r="X19" s="175"/>
+      <c r="Y19" s="175"/>
+      <c r="Z19" s="175"/>
+      <c r="AA19" s="175"/>
+      <c r="AB19" s="175"/>
+      <c r="AC19" s="175"/>
+      <c r="AD19" s="175"/>
+      <c r="AE19" s="176"/>
+      <c r="AF19" s="171"/>
+      <c r="AG19" s="172"/>
+      <c r="AH19" s="172"/>
+      <c r="AI19" s="173"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="21"/>
-      <c r="B20" s="201"/>
-      <c r="C20" s="202"/>
-      <c r="D20" s="203"/>
-      <c r="E20" s="204"/>
-      <c r="F20" s="205"/>
-      <c r="G20" s="201"/>
-      <c r="H20" s="206"/>
-      <c r="I20" s="202"/>
-      <c r="J20" s="212"/>
-      <c r="K20" s="208"/>
-      <c r="L20" s="208"/>
-      <c r="M20" s="208"/>
-      <c r="N20" s="208"/>
-      <c r="O20" s="208"/>
-      <c r="P20" s="209"/>
-      <c r="Q20" s="207"/>
-      <c r="R20" s="210"/>
-      <c r="S20" s="210"/>
-      <c r="T20" s="210"/>
-      <c r="U20" s="210"/>
-      <c r="V20" s="210"/>
-      <c r="W20" s="210"/>
-      <c r="X20" s="210"/>
-      <c r="Y20" s="210"/>
-      <c r="Z20" s="210"/>
-      <c r="AA20" s="210"/>
-      <c r="AB20" s="210"/>
-      <c r="AC20" s="210"/>
-      <c r="AD20" s="210"/>
-      <c r="AE20" s="211"/>
-      <c r="AF20" s="212"/>
-      <c r="AG20" s="208"/>
-      <c r="AH20" s="208"/>
-      <c r="AI20" s="209"/>
+      <c r="B20" s="165"/>
+      <c r="C20" s="166"/>
+      <c r="D20" s="167"/>
+      <c r="E20" s="168"/>
+      <c r="F20" s="169"/>
+      <c r="G20" s="165"/>
+      <c r="H20" s="170"/>
+      <c r="I20" s="166"/>
+      <c r="J20" s="171"/>
+      <c r="K20" s="172"/>
+      <c r="L20" s="172"/>
+      <c r="M20" s="172"/>
+      <c r="N20" s="172"/>
+      <c r="O20" s="172"/>
+      <c r="P20" s="173"/>
+      <c r="Q20" s="174"/>
+      <c r="R20" s="175"/>
+      <c r="S20" s="175"/>
+      <c r="T20" s="175"/>
+      <c r="U20" s="175"/>
+      <c r="V20" s="175"/>
+      <c r="W20" s="175"/>
+      <c r="X20" s="175"/>
+      <c r="Y20" s="175"/>
+      <c r="Z20" s="175"/>
+      <c r="AA20" s="175"/>
+      <c r="AB20" s="175"/>
+      <c r="AC20" s="175"/>
+      <c r="AD20" s="175"/>
+      <c r="AE20" s="176"/>
+      <c r="AF20" s="171"/>
+      <c r="AG20" s="172"/>
+      <c r="AH20" s="172"/>
+      <c r="AI20" s="173"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="21"/>
-      <c r="B21" s="201"/>
-      <c r="C21" s="202"/>
-      <c r="D21" s="203"/>
-      <c r="E21" s="204"/>
-      <c r="F21" s="205"/>
-      <c r="G21" s="201"/>
-      <c r="H21" s="206"/>
-      <c r="I21" s="202"/>
-      <c r="J21" s="212"/>
-      <c r="K21" s="208"/>
-      <c r="L21" s="208"/>
-      <c r="M21" s="208"/>
-      <c r="N21" s="208"/>
-      <c r="O21" s="208"/>
-      <c r="P21" s="209"/>
-      <c r="Q21" s="207"/>
-      <c r="R21" s="210"/>
-      <c r="S21" s="210"/>
-      <c r="T21" s="210"/>
-      <c r="U21" s="210"/>
-      <c r="V21" s="210"/>
-      <c r="W21" s="210"/>
-      <c r="X21" s="210"/>
-      <c r="Y21" s="210"/>
-      <c r="Z21" s="210"/>
-      <c r="AA21" s="210"/>
-      <c r="AB21" s="210"/>
-      <c r="AC21" s="210"/>
-      <c r="AD21" s="210"/>
-      <c r="AE21" s="211"/>
-      <c r="AF21" s="212"/>
-      <c r="AG21" s="208"/>
-      <c r="AH21" s="208"/>
-      <c r="AI21" s="209"/>
+      <c r="B21" s="165"/>
+      <c r="C21" s="166"/>
+      <c r="D21" s="167"/>
+      <c r="E21" s="168"/>
+      <c r="F21" s="169"/>
+      <c r="G21" s="165"/>
+      <c r="H21" s="170"/>
+      <c r="I21" s="166"/>
+      <c r="J21" s="171"/>
+      <c r="K21" s="172"/>
+      <c r="L21" s="172"/>
+      <c r="M21" s="172"/>
+      <c r="N21" s="172"/>
+      <c r="O21" s="172"/>
+      <c r="P21" s="173"/>
+      <c r="Q21" s="174"/>
+      <c r="R21" s="175"/>
+      <c r="S21" s="175"/>
+      <c r="T21" s="175"/>
+      <c r="U21" s="175"/>
+      <c r="V21" s="175"/>
+      <c r="W21" s="175"/>
+      <c r="X21" s="175"/>
+      <c r="Y21" s="175"/>
+      <c r="Z21" s="175"/>
+      <c r="AA21" s="175"/>
+      <c r="AB21" s="175"/>
+      <c r="AC21" s="175"/>
+      <c r="AD21" s="175"/>
+      <c r="AE21" s="176"/>
+      <c r="AF21" s="171"/>
+      <c r="AG21" s="172"/>
+      <c r="AH21" s="172"/>
+      <c r="AI21" s="173"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="21"/>
-      <c r="B22" s="201"/>
-      <c r="C22" s="202"/>
-      <c r="D22" s="203"/>
-      <c r="E22" s="204"/>
-      <c r="F22" s="205"/>
-      <c r="G22" s="201"/>
-      <c r="H22" s="206"/>
-      <c r="I22" s="202"/>
-      <c r="J22" s="212"/>
-      <c r="K22" s="208"/>
-      <c r="L22" s="208"/>
-      <c r="M22" s="208"/>
-      <c r="N22" s="208"/>
-      <c r="O22" s="208"/>
-      <c r="P22" s="209"/>
-      <c r="Q22" s="207"/>
-      <c r="R22" s="210"/>
-      <c r="S22" s="210"/>
-      <c r="T22" s="210"/>
-      <c r="U22" s="210"/>
-      <c r="V22" s="210"/>
-      <c r="W22" s="210"/>
-      <c r="X22" s="210"/>
-      <c r="Y22" s="210"/>
-      <c r="Z22" s="210"/>
-      <c r="AA22" s="210"/>
-      <c r="AB22" s="210"/>
-      <c r="AC22" s="210"/>
-      <c r="AD22" s="210"/>
-      <c r="AE22" s="211"/>
-      <c r="AF22" s="212"/>
-      <c r="AG22" s="208"/>
-      <c r="AH22" s="208"/>
-      <c r="AI22" s="209"/>
+      <c r="B22" s="165"/>
+      <c r="C22" s="166"/>
+      <c r="D22" s="167"/>
+      <c r="E22" s="168"/>
+      <c r="F22" s="169"/>
+      <c r="G22" s="165"/>
+      <c r="H22" s="170"/>
+      <c r="I22" s="166"/>
+      <c r="J22" s="171"/>
+      <c r="K22" s="172"/>
+      <c r="L22" s="172"/>
+      <c r="M22" s="172"/>
+      <c r="N22" s="172"/>
+      <c r="O22" s="172"/>
+      <c r="P22" s="173"/>
+      <c r="Q22" s="174"/>
+      <c r="R22" s="175"/>
+      <c r="S22" s="175"/>
+      <c r="T22" s="175"/>
+      <c r="U22" s="175"/>
+      <c r="V22" s="175"/>
+      <c r="W22" s="175"/>
+      <c r="X22" s="175"/>
+      <c r="Y22" s="175"/>
+      <c r="Z22" s="175"/>
+      <c r="AA22" s="175"/>
+      <c r="AB22" s="175"/>
+      <c r="AC22" s="175"/>
+      <c r="AD22" s="175"/>
+      <c r="AE22" s="176"/>
+      <c r="AF22" s="171"/>
+      <c r="AG22" s="172"/>
+      <c r="AH22" s="172"/>
+      <c r="AI22" s="173"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="21"/>
-      <c r="B23" s="201"/>
-      <c r="C23" s="202"/>
-      <c r="D23" s="203"/>
-      <c r="E23" s="204"/>
-      <c r="F23" s="205"/>
-      <c r="G23" s="201"/>
-      <c r="H23" s="206"/>
-      <c r="I23" s="202"/>
-      <c r="J23" s="212"/>
-      <c r="K23" s="208"/>
-      <c r="L23" s="208"/>
-      <c r="M23" s="208"/>
-      <c r="N23" s="208"/>
-      <c r="O23" s="208"/>
-      <c r="P23" s="209"/>
-      <c r="Q23" s="207"/>
-      <c r="R23" s="210"/>
-      <c r="S23" s="210"/>
-      <c r="T23" s="210"/>
-      <c r="U23" s="210"/>
-      <c r="V23" s="210"/>
-      <c r="W23" s="210"/>
-      <c r="X23" s="210"/>
-      <c r="Y23" s="210"/>
-      <c r="Z23" s="210"/>
-      <c r="AA23" s="210"/>
-      <c r="AB23" s="210"/>
-      <c r="AC23" s="210"/>
-      <c r="AD23" s="210"/>
-      <c r="AE23" s="211"/>
-      <c r="AF23" s="212"/>
-      <c r="AG23" s="208"/>
-      <c r="AH23" s="208"/>
-      <c r="AI23" s="209"/>
+      <c r="B23" s="165"/>
+      <c r="C23" s="166"/>
+      <c r="D23" s="167"/>
+      <c r="E23" s="168"/>
+      <c r="F23" s="169"/>
+      <c r="G23" s="165"/>
+      <c r="H23" s="170"/>
+      <c r="I23" s="166"/>
+      <c r="J23" s="171"/>
+      <c r="K23" s="172"/>
+      <c r="L23" s="172"/>
+      <c r="M23" s="172"/>
+      <c r="N23" s="172"/>
+      <c r="O23" s="172"/>
+      <c r="P23" s="173"/>
+      <c r="Q23" s="174"/>
+      <c r="R23" s="175"/>
+      <c r="S23" s="175"/>
+      <c r="T23" s="175"/>
+      <c r="U23" s="175"/>
+      <c r="V23" s="175"/>
+      <c r="W23" s="175"/>
+      <c r="X23" s="175"/>
+      <c r="Y23" s="175"/>
+      <c r="Z23" s="175"/>
+      <c r="AA23" s="175"/>
+      <c r="AB23" s="175"/>
+      <c r="AC23" s="175"/>
+      <c r="AD23" s="175"/>
+      <c r="AE23" s="176"/>
+      <c r="AF23" s="171"/>
+      <c r="AG23" s="172"/>
+      <c r="AH23" s="172"/>
+      <c r="AI23" s="173"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="21"/>
-      <c r="B24" s="201"/>
-      <c r="C24" s="202"/>
-      <c r="D24" s="203"/>
-      <c r="E24" s="204"/>
-      <c r="F24" s="205"/>
-      <c r="G24" s="201"/>
-      <c r="H24" s="206"/>
-      <c r="I24" s="202"/>
-      <c r="J24" s="212"/>
-      <c r="K24" s="208"/>
-      <c r="L24" s="208"/>
-      <c r="M24" s="208"/>
-      <c r="N24" s="208"/>
-      <c r="O24" s="208"/>
-      <c r="P24" s="209"/>
-      <c r="Q24" s="207"/>
-      <c r="R24" s="210"/>
-      <c r="S24" s="210"/>
-      <c r="T24" s="210"/>
-      <c r="U24" s="210"/>
-      <c r="V24" s="210"/>
-      <c r="W24" s="210"/>
-      <c r="X24" s="210"/>
-      <c r="Y24" s="210"/>
-      <c r="Z24" s="210"/>
-      <c r="AA24" s="210"/>
-      <c r="AB24" s="210"/>
-      <c r="AC24" s="210"/>
-      <c r="AD24" s="210"/>
-      <c r="AE24" s="211"/>
-      <c r="AF24" s="212"/>
-      <c r="AG24" s="208"/>
-      <c r="AH24" s="208"/>
-      <c r="AI24" s="209"/>
+      <c r="B24" s="165"/>
+      <c r="C24" s="166"/>
+      <c r="D24" s="167"/>
+      <c r="E24" s="168"/>
+      <c r="F24" s="169"/>
+      <c r="G24" s="165"/>
+      <c r="H24" s="170"/>
+      <c r="I24" s="166"/>
+      <c r="J24" s="171"/>
+      <c r="K24" s="172"/>
+      <c r="L24" s="172"/>
+      <c r="M24" s="172"/>
+      <c r="N24" s="172"/>
+      <c r="O24" s="172"/>
+      <c r="P24" s="173"/>
+      <c r="Q24" s="174"/>
+      <c r="R24" s="175"/>
+      <c r="S24" s="175"/>
+      <c r="T24" s="175"/>
+      <c r="U24" s="175"/>
+      <c r="V24" s="175"/>
+      <c r="W24" s="175"/>
+      <c r="X24" s="175"/>
+      <c r="Y24" s="175"/>
+      <c r="Z24" s="175"/>
+      <c r="AA24" s="175"/>
+      <c r="AB24" s="175"/>
+      <c r="AC24" s="175"/>
+      <c r="AD24" s="175"/>
+      <c r="AE24" s="176"/>
+      <c r="AF24" s="171"/>
+      <c r="AG24" s="172"/>
+      <c r="AH24" s="172"/>
+      <c r="AI24" s="173"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="21"/>
-      <c r="B25" s="201"/>
-      <c r="C25" s="202"/>
-      <c r="D25" s="203"/>
-      <c r="E25" s="204"/>
-      <c r="F25" s="205"/>
-      <c r="G25" s="201"/>
-      <c r="H25" s="206"/>
-      <c r="I25" s="202"/>
-      <c r="J25" s="212"/>
-      <c r="K25" s="208"/>
-      <c r="L25" s="208"/>
-      <c r="M25" s="208"/>
-      <c r="N25" s="208"/>
-      <c r="O25" s="208"/>
-      <c r="P25" s="209"/>
-      <c r="Q25" s="207"/>
-      <c r="R25" s="210"/>
-      <c r="S25" s="210"/>
-      <c r="T25" s="210"/>
-      <c r="U25" s="210"/>
-      <c r="V25" s="210"/>
-      <c r="W25" s="210"/>
-      <c r="X25" s="210"/>
-      <c r="Y25" s="210"/>
-      <c r="Z25" s="210"/>
-      <c r="AA25" s="210"/>
-      <c r="AB25" s="210"/>
-      <c r="AC25" s="210"/>
-      <c r="AD25" s="210"/>
-      <c r="AE25" s="211"/>
-      <c r="AF25" s="212"/>
-      <c r="AG25" s="208"/>
-      <c r="AH25" s="208"/>
-      <c r="AI25" s="209"/>
+      <c r="B25" s="165"/>
+      <c r="C25" s="166"/>
+      <c r="D25" s="167"/>
+      <c r="E25" s="168"/>
+      <c r="F25" s="169"/>
+      <c r="G25" s="165"/>
+      <c r="H25" s="170"/>
+      <c r="I25" s="166"/>
+      <c r="J25" s="171"/>
+      <c r="K25" s="172"/>
+      <c r="L25" s="172"/>
+      <c r="M25" s="172"/>
+      <c r="N25" s="172"/>
+      <c r="O25" s="172"/>
+      <c r="P25" s="173"/>
+      <c r="Q25" s="174"/>
+      <c r="R25" s="175"/>
+      <c r="S25" s="175"/>
+      <c r="T25" s="175"/>
+      <c r="U25" s="175"/>
+      <c r="V25" s="175"/>
+      <c r="W25" s="175"/>
+      <c r="X25" s="175"/>
+      <c r="Y25" s="175"/>
+      <c r="Z25" s="175"/>
+      <c r="AA25" s="175"/>
+      <c r="AB25" s="175"/>
+      <c r="AC25" s="175"/>
+      <c r="AD25" s="175"/>
+      <c r="AE25" s="176"/>
+      <c r="AF25" s="171"/>
+      <c r="AG25" s="172"/>
+      <c r="AH25" s="172"/>
+      <c r="AI25" s="173"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="21"/>
-      <c r="B26" s="201"/>
-      <c r="C26" s="202"/>
-      <c r="D26" s="203"/>
-      <c r="E26" s="204"/>
-      <c r="F26" s="205"/>
-      <c r="G26" s="201"/>
-      <c r="H26" s="206"/>
-      <c r="I26" s="202"/>
-      <c r="J26" s="212"/>
-      <c r="K26" s="208"/>
-      <c r="L26" s="208"/>
-      <c r="M26" s="208"/>
-      <c r="N26" s="208"/>
-      <c r="O26" s="208"/>
-      <c r="P26" s="209"/>
-      <c r="Q26" s="207"/>
-      <c r="R26" s="210"/>
-      <c r="S26" s="210"/>
-      <c r="T26" s="210"/>
-      <c r="U26" s="210"/>
-      <c r="V26" s="210"/>
-      <c r="W26" s="210"/>
-      <c r="X26" s="210"/>
-      <c r="Y26" s="210"/>
-      <c r="Z26" s="210"/>
-      <c r="AA26" s="210"/>
-      <c r="AB26" s="210"/>
-      <c r="AC26" s="210"/>
-      <c r="AD26" s="210"/>
-      <c r="AE26" s="211"/>
-      <c r="AF26" s="212"/>
-      <c r="AG26" s="208"/>
-      <c r="AH26" s="208"/>
-      <c r="AI26" s="209"/>
+      <c r="B26" s="165"/>
+      <c r="C26" s="166"/>
+      <c r="D26" s="167"/>
+      <c r="E26" s="168"/>
+      <c r="F26" s="169"/>
+      <c r="G26" s="165"/>
+      <c r="H26" s="170"/>
+      <c r="I26" s="166"/>
+      <c r="J26" s="171"/>
+      <c r="K26" s="172"/>
+      <c r="L26" s="172"/>
+      <c r="M26" s="172"/>
+      <c r="N26" s="172"/>
+      <c r="O26" s="172"/>
+      <c r="P26" s="173"/>
+      <c r="Q26" s="174"/>
+      <c r="R26" s="175"/>
+      <c r="S26" s="175"/>
+      <c r="T26" s="175"/>
+      <c r="U26" s="175"/>
+      <c r="V26" s="175"/>
+      <c r="W26" s="175"/>
+      <c r="X26" s="175"/>
+      <c r="Y26" s="175"/>
+      <c r="Z26" s="175"/>
+      <c r="AA26" s="175"/>
+      <c r="AB26" s="175"/>
+      <c r="AC26" s="175"/>
+      <c r="AD26" s="175"/>
+      <c r="AE26" s="176"/>
+      <c r="AF26" s="171"/>
+      <c r="AG26" s="172"/>
+      <c r="AH26" s="172"/>
+      <c r="AI26" s="173"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="21"/>
-      <c r="B27" s="201"/>
-      <c r="C27" s="202"/>
-      <c r="D27" s="203"/>
-      <c r="E27" s="204"/>
-      <c r="F27" s="205"/>
-      <c r="G27" s="201"/>
-      <c r="H27" s="206"/>
-      <c r="I27" s="202"/>
-      <c r="J27" s="212"/>
-      <c r="K27" s="208"/>
-      <c r="L27" s="208"/>
-      <c r="M27" s="208"/>
-      <c r="N27" s="208"/>
-      <c r="O27" s="208"/>
-      <c r="P27" s="209"/>
-      <c r="Q27" s="207"/>
-      <c r="R27" s="210"/>
-      <c r="S27" s="210"/>
-      <c r="T27" s="210"/>
-      <c r="U27" s="210"/>
-      <c r="V27" s="210"/>
-      <c r="W27" s="210"/>
-      <c r="X27" s="210"/>
-      <c r="Y27" s="210"/>
-      <c r="Z27" s="210"/>
-      <c r="AA27" s="210"/>
-      <c r="AB27" s="210"/>
-      <c r="AC27" s="210"/>
-      <c r="AD27" s="210"/>
-      <c r="AE27" s="211"/>
-      <c r="AF27" s="212"/>
-      <c r="AG27" s="208"/>
-      <c r="AH27" s="208"/>
-      <c r="AI27" s="209"/>
+      <c r="B27" s="165"/>
+      <c r="C27" s="166"/>
+      <c r="D27" s="167"/>
+      <c r="E27" s="168"/>
+      <c r="F27" s="169"/>
+      <c r="G27" s="165"/>
+      <c r="H27" s="170"/>
+      <c r="I27" s="166"/>
+      <c r="J27" s="171"/>
+      <c r="K27" s="172"/>
+      <c r="L27" s="172"/>
+      <c r="M27" s="172"/>
+      <c r="N27" s="172"/>
+      <c r="O27" s="172"/>
+      <c r="P27" s="173"/>
+      <c r="Q27" s="174"/>
+      <c r="R27" s="175"/>
+      <c r="S27" s="175"/>
+      <c r="T27" s="175"/>
+      <c r="U27" s="175"/>
+      <c r="V27" s="175"/>
+      <c r="W27" s="175"/>
+      <c r="X27" s="175"/>
+      <c r="Y27" s="175"/>
+      <c r="Z27" s="175"/>
+      <c r="AA27" s="175"/>
+      <c r="AB27" s="175"/>
+      <c r="AC27" s="175"/>
+      <c r="AD27" s="175"/>
+      <c r="AE27" s="176"/>
+      <c r="AF27" s="171"/>
+      <c r="AG27" s="172"/>
+      <c r="AH27" s="172"/>
+      <c r="AI27" s="173"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="21"/>
-      <c r="B28" s="201"/>
-      <c r="C28" s="202"/>
-      <c r="D28" s="203"/>
-      <c r="E28" s="204"/>
-      <c r="F28" s="205"/>
-      <c r="G28" s="201"/>
-      <c r="H28" s="206"/>
-      <c r="I28" s="202"/>
-      <c r="J28" s="212"/>
-      <c r="K28" s="208"/>
-      <c r="L28" s="208"/>
-      <c r="M28" s="208"/>
-      <c r="N28" s="208"/>
-      <c r="O28" s="208"/>
-      <c r="P28" s="209"/>
-      <c r="Q28" s="207"/>
-      <c r="R28" s="210"/>
-      <c r="S28" s="210"/>
-      <c r="T28" s="210"/>
-      <c r="U28" s="210"/>
-      <c r="V28" s="210"/>
-      <c r="W28" s="210"/>
-      <c r="X28" s="210"/>
-      <c r="Y28" s="210"/>
-      <c r="Z28" s="210"/>
-      <c r="AA28" s="210"/>
-      <c r="AB28" s="210"/>
-      <c r="AC28" s="210"/>
-      <c r="AD28" s="210"/>
-      <c r="AE28" s="211"/>
-      <c r="AF28" s="212"/>
-      <c r="AG28" s="208"/>
-      <c r="AH28" s="208"/>
-      <c r="AI28" s="209"/>
+      <c r="B28" s="165"/>
+      <c r="C28" s="166"/>
+      <c r="D28" s="167"/>
+      <c r="E28" s="168"/>
+      <c r="F28" s="169"/>
+      <c r="G28" s="165"/>
+      <c r="H28" s="170"/>
+      <c r="I28" s="166"/>
+      <c r="J28" s="171"/>
+      <c r="K28" s="172"/>
+      <c r="L28" s="172"/>
+      <c r="M28" s="172"/>
+      <c r="N28" s="172"/>
+      <c r="O28" s="172"/>
+      <c r="P28" s="173"/>
+      <c r="Q28" s="174"/>
+      <c r="R28" s="175"/>
+      <c r="S28" s="175"/>
+      <c r="T28" s="175"/>
+      <c r="U28" s="175"/>
+      <c r="V28" s="175"/>
+      <c r="W28" s="175"/>
+      <c r="X28" s="175"/>
+      <c r="Y28" s="175"/>
+      <c r="Z28" s="175"/>
+      <c r="AA28" s="175"/>
+      <c r="AB28" s="175"/>
+      <c r="AC28" s="175"/>
+      <c r="AD28" s="175"/>
+      <c r="AE28" s="176"/>
+      <c r="AF28" s="171"/>
+      <c r="AG28" s="172"/>
+      <c r="AH28" s="172"/>
+      <c r="AI28" s="173"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="21"/>
-      <c r="B29" s="201"/>
-      <c r="C29" s="202"/>
-      <c r="D29" s="203"/>
-      <c r="E29" s="204"/>
-      <c r="F29" s="205"/>
-      <c r="G29" s="201"/>
-      <c r="H29" s="206"/>
-      <c r="I29" s="202"/>
-      <c r="J29" s="212"/>
-      <c r="K29" s="208"/>
-      <c r="L29" s="208"/>
-      <c r="M29" s="208"/>
-      <c r="N29" s="208"/>
-      <c r="O29" s="208"/>
-      <c r="P29" s="209"/>
-      <c r="Q29" s="207"/>
-      <c r="R29" s="210"/>
-      <c r="S29" s="210"/>
-      <c r="T29" s="210"/>
-      <c r="U29" s="210"/>
-      <c r="V29" s="210"/>
-      <c r="W29" s="210"/>
-      <c r="X29" s="210"/>
-      <c r="Y29" s="210"/>
-      <c r="Z29" s="210"/>
-      <c r="AA29" s="210"/>
-      <c r="AB29" s="210"/>
-      <c r="AC29" s="210"/>
-      <c r="AD29" s="210"/>
-      <c r="AE29" s="211"/>
-      <c r="AF29" s="212"/>
-      <c r="AG29" s="208"/>
-      <c r="AH29" s="208"/>
-      <c r="AI29" s="209"/>
+      <c r="B29" s="165"/>
+      <c r="C29" s="166"/>
+      <c r="D29" s="167"/>
+      <c r="E29" s="168"/>
+      <c r="F29" s="169"/>
+      <c r="G29" s="165"/>
+      <c r="H29" s="170"/>
+      <c r="I29" s="166"/>
+      <c r="J29" s="171"/>
+      <c r="K29" s="172"/>
+      <c r="L29" s="172"/>
+      <c r="M29" s="172"/>
+      <c r="N29" s="172"/>
+      <c r="O29" s="172"/>
+      <c r="P29" s="173"/>
+      <c r="Q29" s="174"/>
+      <c r="R29" s="175"/>
+      <c r="S29" s="175"/>
+      <c r="T29" s="175"/>
+      <c r="U29" s="175"/>
+      <c r="V29" s="175"/>
+      <c r="W29" s="175"/>
+      <c r="X29" s="175"/>
+      <c r="Y29" s="175"/>
+      <c r="Z29" s="175"/>
+      <c r="AA29" s="175"/>
+      <c r="AB29" s="175"/>
+      <c r="AC29" s="175"/>
+      <c r="AD29" s="175"/>
+      <c r="AE29" s="176"/>
+      <c r="AF29" s="171"/>
+      <c r="AG29" s="172"/>
+      <c r="AH29" s="172"/>
+      <c r="AI29" s="173"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="21"/>
-      <c r="B30" s="201"/>
-      <c r="C30" s="202"/>
-      <c r="D30" s="203"/>
-      <c r="E30" s="204"/>
-      <c r="F30" s="205"/>
-      <c r="G30" s="201"/>
-      <c r="H30" s="206"/>
-      <c r="I30" s="202"/>
-      <c r="J30" s="212"/>
-      <c r="K30" s="208"/>
-      <c r="L30" s="208"/>
-      <c r="M30" s="208"/>
-      <c r="N30" s="208"/>
-      <c r="O30" s="208"/>
-      <c r="P30" s="209"/>
-      <c r="Q30" s="207"/>
-      <c r="R30" s="210"/>
-      <c r="S30" s="210"/>
-      <c r="T30" s="210"/>
-      <c r="U30" s="210"/>
-      <c r="V30" s="210"/>
-      <c r="W30" s="210"/>
-      <c r="X30" s="210"/>
-      <c r="Y30" s="210"/>
-      <c r="Z30" s="210"/>
-      <c r="AA30" s="210"/>
-      <c r="AB30" s="210"/>
-      <c r="AC30" s="210"/>
-      <c r="AD30" s="210"/>
-      <c r="AE30" s="211"/>
-      <c r="AF30" s="212"/>
-      <c r="AG30" s="208"/>
-      <c r="AH30" s="208"/>
-      <c r="AI30" s="209"/>
+      <c r="B30" s="165"/>
+      <c r="C30" s="166"/>
+      <c r="D30" s="167"/>
+      <c r="E30" s="168"/>
+      <c r="F30" s="169"/>
+      <c r="G30" s="165"/>
+      <c r="H30" s="170"/>
+      <c r="I30" s="166"/>
+      <c r="J30" s="171"/>
+      <c r="K30" s="172"/>
+      <c r="L30" s="172"/>
+      <c r="M30" s="172"/>
+      <c r="N30" s="172"/>
+      <c r="O30" s="172"/>
+      <c r="P30" s="173"/>
+      <c r="Q30" s="174"/>
+      <c r="R30" s="175"/>
+      <c r="S30" s="175"/>
+      <c r="T30" s="175"/>
+      <c r="U30" s="175"/>
+      <c r="V30" s="175"/>
+      <c r="W30" s="175"/>
+      <c r="X30" s="175"/>
+      <c r="Y30" s="175"/>
+      <c r="Z30" s="175"/>
+      <c r="AA30" s="175"/>
+      <c r="AB30" s="175"/>
+      <c r="AC30" s="175"/>
+      <c r="AD30" s="175"/>
+      <c r="AE30" s="176"/>
+      <c r="AF30" s="171"/>
+      <c r="AG30" s="172"/>
+      <c r="AH30" s="172"/>
+      <c r="AI30" s="173"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="201"/>
-      <c r="C31" s="202"/>
-      <c r="D31" s="203"/>
-      <c r="E31" s="204"/>
-      <c r="F31" s="205"/>
-      <c r="G31" s="201"/>
-      <c r="H31" s="206"/>
-      <c r="I31" s="202"/>
-      <c r="J31" s="212"/>
-      <c r="K31" s="208"/>
-      <c r="L31" s="208"/>
-      <c r="M31" s="208"/>
-      <c r="N31" s="208"/>
-      <c r="O31" s="208"/>
-      <c r="P31" s="209"/>
-      <c r="Q31" s="207"/>
-      <c r="R31" s="210"/>
-      <c r="S31" s="210"/>
-      <c r="T31" s="210"/>
-      <c r="U31" s="210"/>
-      <c r="V31" s="210"/>
-      <c r="W31" s="210"/>
-      <c r="X31" s="210"/>
-      <c r="Y31" s="210"/>
-      <c r="Z31" s="210"/>
-      <c r="AA31" s="210"/>
-      <c r="AB31" s="210"/>
-      <c r="AC31" s="210"/>
-      <c r="AD31" s="210"/>
-      <c r="AE31" s="211"/>
-      <c r="AF31" s="212"/>
-      <c r="AG31" s="208"/>
-      <c r="AH31" s="208"/>
-      <c r="AI31" s="209"/>
+      <c r="B31" s="165"/>
+      <c r="C31" s="166"/>
+      <c r="D31" s="167"/>
+      <c r="E31" s="168"/>
+      <c r="F31" s="169"/>
+      <c r="G31" s="165"/>
+      <c r="H31" s="170"/>
+      <c r="I31" s="166"/>
+      <c r="J31" s="171"/>
+      <c r="K31" s="172"/>
+      <c r="L31" s="172"/>
+      <c r="M31" s="172"/>
+      <c r="N31" s="172"/>
+      <c r="O31" s="172"/>
+      <c r="P31" s="173"/>
+      <c r="Q31" s="174"/>
+      <c r="R31" s="175"/>
+      <c r="S31" s="175"/>
+      <c r="T31" s="175"/>
+      <c r="U31" s="175"/>
+      <c r="V31" s="175"/>
+      <c r="W31" s="175"/>
+      <c r="X31" s="175"/>
+      <c r="Y31" s="175"/>
+      <c r="Z31" s="175"/>
+      <c r="AA31" s="175"/>
+      <c r="AB31" s="175"/>
+      <c r="AC31" s="175"/>
+      <c r="AD31" s="175"/>
+      <c r="AE31" s="176"/>
+      <c r="AF31" s="171"/>
+      <c r="AG31" s="172"/>
+      <c r="AH31" s="172"/>
+      <c r="AI31" s="173"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="21"/>
-      <c r="B32" s="201"/>
-      <c r="C32" s="202"/>
-      <c r="D32" s="203"/>
-      <c r="E32" s="204"/>
-      <c r="F32" s="205"/>
-      <c r="G32" s="201"/>
-      <c r="H32" s="206"/>
-      <c r="I32" s="202"/>
-      <c r="J32" s="212"/>
-      <c r="K32" s="222"/>
-      <c r="L32" s="208"/>
-      <c r="M32" s="208"/>
-      <c r="N32" s="208"/>
-      <c r="O32" s="208"/>
-      <c r="P32" s="209"/>
-      <c r="Q32" s="207"/>
-      <c r="R32" s="210"/>
-      <c r="S32" s="210"/>
-      <c r="T32" s="210"/>
-      <c r="U32" s="210"/>
-      <c r="V32" s="210"/>
-      <c r="W32" s="210"/>
-      <c r="X32" s="210"/>
-      <c r="Y32" s="210"/>
-      <c r="Z32" s="210"/>
-      <c r="AA32" s="210"/>
-      <c r="AB32" s="210"/>
-      <c r="AC32" s="210"/>
-      <c r="AD32" s="210"/>
-      <c r="AE32" s="211"/>
-      <c r="AF32" s="212"/>
-      <c r="AG32" s="208"/>
-      <c r="AH32" s="208"/>
-      <c r="AI32" s="209"/>
+      <c r="B32" s="165"/>
+      <c r="C32" s="166"/>
+      <c r="D32" s="167"/>
+      <c r="E32" s="168"/>
+      <c r="F32" s="169"/>
+      <c r="G32" s="165"/>
+      <c r="H32" s="170"/>
+      <c r="I32" s="166"/>
+      <c r="J32" s="171"/>
+      <c r="K32" s="177"/>
+      <c r="L32" s="172"/>
+      <c r="M32" s="172"/>
+      <c r="N32" s="172"/>
+      <c r="O32" s="172"/>
+      <c r="P32" s="173"/>
+      <c r="Q32" s="174"/>
+      <c r="R32" s="175"/>
+      <c r="S32" s="175"/>
+      <c r="T32" s="175"/>
+      <c r="U32" s="175"/>
+      <c r="V32" s="175"/>
+      <c r="W32" s="175"/>
+      <c r="X32" s="175"/>
+      <c r="Y32" s="175"/>
+      <c r="Z32" s="175"/>
+      <c r="AA32" s="175"/>
+      <c r="AB32" s="175"/>
+      <c r="AC32" s="175"/>
+      <c r="AD32" s="175"/>
+      <c r="AE32" s="176"/>
+      <c r="AF32" s="171"/>
+      <c r="AG32" s="172"/>
+      <c r="AH32" s="172"/>
+      <c r="AI32" s="173"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="21"/>
-      <c r="B33" s="201"/>
-      <c r="C33" s="202"/>
-      <c r="D33" s="203"/>
-      <c r="E33" s="204"/>
-      <c r="F33" s="205"/>
-      <c r="G33" s="201"/>
-      <c r="H33" s="206"/>
-      <c r="I33" s="202"/>
-      <c r="J33" s="212"/>
-      <c r="K33" s="208"/>
-      <c r="L33" s="208"/>
-      <c r="M33" s="208"/>
-      <c r="N33" s="208"/>
-      <c r="O33" s="208"/>
-      <c r="P33" s="209"/>
-      <c r="Q33" s="207"/>
-      <c r="R33" s="210"/>
-      <c r="S33" s="210"/>
-      <c r="T33" s="210"/>
-      <c r="U33" s="210"/>
-      <c r="V33" s="210"/>
-      <c r="W33" s="210"/>
-      <c r="X33" s="210"/>
-      <c r="Y33" s="210"/>
-      <c r="Z33" s="210"/>
-      <c r="AA33" s="210"/>
-      <c r="AB33" s="210"/>
-      <c r="AC33" s="210"/>
-      <c r="AD33" s="210"/>
-      <c r="AE33" s="211"/>
-      <c r="AF33" s="212"/>
-      <c r="AG33" s="208"/>
-      <c r="AH33" s="208"/>
-      <c r="AI33" s="209"/>
-    </row>
-    <row r="34" spans="1:35" ht="14.25">
+      <c r="B33" s="165"/>
+      <c r="C33" s="166"/>
+      <c r="D33" s="167"/>
+      <c r="E33" s="168"/>
+      <c r="F33" s="169"/>
+      <c r="G33" s="165"/>
+      <c r="H33" s="170"/>
+      <c r="I33" s="166"/>
+      <c r="J33" s="171"/>
+      <c r="K33" s="172"/>
+      <c r="L33" s="172"/>
+      <c r="M33" s="172"/>
+      <c r="N33" s="172"/>
+      <c r="O33" s="172"/>
+      <c r="P33" s="173"/>
+      <c r="Q33" s="174"/>
+      <c r="R33" s="175"/>
+      <c r="S33" s="175"/>
+      <c r="T33" s="175"/>
+      <c r="U33" s="175"/>
+      <c r="V33" s="175"/>
+      <c r="W33" s="175"/>
+      <c r="X33" s="175"/>
+      <c r="Y33" s="175"/>
+      <c r="Z33" s="175"/>
+      <c r="AA33" s="175"/>
+      <c r="AB33" s="175"/>
+      <c r="AC33" s="175"/>
+      <c r="AD33" s="175"/>
+      <c r="AE33" s="176"/>
+      <c r="AF33" s="171"/>
+      <c r="AG33" s="172"/>
+      <c r="AH33" s="172"/>
+      <c r="AI33" s="173"/>
+    </row>
+    <row r="34" spans="1:35" ht="14">
       <c r="K34" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="178">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -15696,6 +15500,161 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -15712,18 +15671,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R304"/>
-  <sheetFormatPr defaultRowHeight="11.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="2" width="8.625" style="28" customWidth="1"/>
-    <col min="3" max="3" width="8.625" style="29" customWidth="1"/>
-    <col min="4" max="5" width="8.625" style="28" customWidth="1"/>
-    <col min="6" max="6" width="40.625" style="28" customWidth="1"/>
-    <col min="7" max="7" width="40.625" style="28" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="9" width="15.625" style="28" customWidth="1"/>
-    <col min="10" max="11" width="25.625" style="28" customWidth="1"/>
+    <col min="1" max="2" width="8.58203125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="8.58203125" style="29" customWidth="1"/>
+    <col min="4" max="5" width="8.58203125" style="28" customWidth="1"/>
+    <col min="6" max="6" width="40.58203125" style="28" customWidth="1"/>
+    <col min="7" max="7" width="40.58203125" style="28" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="9" width="15.58203125" style="28" customWidth="1"/>
+    <col min="10" max="11" width="25.58203125" style="28" customWidth="1"/>
     <col min="12" max="12" width="19.25" style="28" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.625" style="28" customWidth="1"/>
-    <col min="14" max="18" width="8.625" style="28" customWidth="1"/>
+    <col min="13" max="13" width="12.58203125" style="28" customWidth="1"/>
+    <col min="14" max="18" width="8.58203125" style="28" customWidth="1"/>
     <col min="19" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
@@ -15769,7 +15728,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="12" thickBot="1">
+    <row r="8" spans="1:18" ht="11.5" thickBot="1">
       <c r="A8" s="30"/>
       <c r="B8" s="30"/>
       <c r="C8" s="31"/>
@@ -15846,7 +15805,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="22.5">
+    <row r="11" spans="1:18" ht="22">
       <c r="A11" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A11" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E11),
@@ -15875,7 +15834,7 @@
         <v>104</v>
       </c>
       <c r="G11" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H11" s="76"/>
       <c r="I11" s="76"/>
@@ -15889,7 +15848,7 @@
       <c r="Q11" s="79"/>
       <c r="R11" s="80"/>
     </row>
-    <row r="12" spans="1:18" ht="22.5">
+    <row r="12" spans="1:18" ht="22">
       <c r="A12" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A12" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E12),
@@ -15912,7 +15871,7 @@
         <v>106</v>
       </c>
       <c r="G12" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H12" s="61"/>
       <c r="I12" s="61"/>
@@ -15926,7 +15885,7 @@
       <c r="Q12" s="63"/>
       <c r="R12" s="65"/>
     </row>
-    <row r="13" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="13" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A13" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A13" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E13),
@@ -15951,7 +15910,7 @@
         <v>108</v>
       </c>
       <c r="G13" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H13" s="61"/>
       <c r="I13" s="61"/>
@@ -15965,7 +15924,7 @@
       <c r="Q13" s="64"/>
       <c r="R13" s="63"/>
     </row>
-    <row r="14" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="14" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A14" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E14),
@@ -15986,7 +15945,7 @@
         <v>109</v>
       </c>
       <c r="G14" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H14" s="61"/>
       <c r="I14" s="61"/>
@@ -16000,7 +15959,7 @@
       <c r="Q14" s="64"/>
       <c r="R14" s="63"/>
     </row>
-    <row r="15" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="15" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A15" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A15" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E15),
@@ -16021,7 +15980,7 @@
         <v>110</v>
       </c>
       <c r="G15" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H15" s="61"/>
       <c r="I15" s="68"/>
@@ -16035,7 +15994,7 @@
       <c r="Q15" s="64"/>
       <c r="R15" s="63"/>
     </row>
-    <row r="16" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="16" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A16" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A16" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E16),
@@ -16056,7 +16015,7 @@
         <v>111</v>
       </c>
       <c r="G16" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H16" s="61"/>
       <c r="I16" s="68"/>
@@ -16070,7 +16029,7 @@
       <c r="Q16" s="63"/>
       <c r="R16" s="65"/>
     </row>
-    <row r="17" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="17" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A17" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E17),
@@ -16091,7 +16050,7 @@
         <v>112</v>
       </c>
       <c r="G17" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H17" s="61"/>
       <c r="I17" s="68"/>
@@ -16105,7 +16064,7 @@
       <c r="Q17" s="63"/>
       <c r="R17" s="65"/>
     </row>
-    <row r="18" spans="1:18" ht="22.5">
+    <row r="18" spans="1:18" ht="22">
       <c r="A18" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A18" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E18),
@@ -16130,7 +16089,7 @@
         <v>115</v>
       </c>
       <c r="G18" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H18" s="61"/>
       <c r="I18" s="61"/>
@@ -16144,7 +16103,7 @@
       <c r="Q18" s="63"/>
       <c r="R18" s="65"/>
     </row>
-    <row r="19" spans="1:18" ht="22.5">
+    <row r="19" spans="1:18" ht="22">
       <c r="A19" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A19" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E19),
@@ -16165,7 +16124,7 @@
         <v>116</v>
       </c>
       <c r="G19" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H19" s="61"/>
       <c r="I19" s="61"/>
@@ -16179,7 +16138,7 @@
       <c r="Q19" s="63"/>
       <c r="R19" s="65"/>
     </row>
-    <row r="20" spans="1:18" ht="22.5">
+    <row r="20" spans="1:18" ht="22">
       <c r="A20" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A20" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E20),
@@ -16200,7 +16159,7 @@
         <v>117</v>
       </c>
       <c r="G20" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H20" s="61"/>
       <c r="I20" s="68"/>
@@ -16214,7 +16173,7 @@
       <c r="Q20" s="63"/>
       <c r="R20" s="65"/>
     </row>
-    <row r="21" spans="1:18" ht="22.5">
+    <row r="21" spans="1:18" ht="22">
       <c r="A21" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A21" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E21),
@@ -16237,7 +16196,7 @@
         <v>119</v>
       </c>
       <c r="G21" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H21" s="61"/>
       <c r="I21" s="61"/>
@@ -16251,7 +16210,7 @@
       <c r="Q21" s="63"/>
       <c r="R21" s="65"/>
     </row>
-    <row r="22" spans="1:18" ht="22.5">
+    <row r="22" spans="1:18" ht="22">
       <c r="A22" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A22" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E22),
@@ -16272,7 +16231,7 @@
         <v>120</v>
       </c>
       <c r="G22" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H22" s="61"/>
       <c r="I22" s="61"/>
@@ -16286,7 +16245,7 @@
       <c r="Q22" s="63"/>
       <c r="R22" s="65"/>
     </row>
-    <row r="23" spans="1:18" ht="22.5">
+    <row r="23" spans="1:18" ht="22">
       <c r="A23" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A23" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E23),
@@ -16307,7 +16266,7 @@
         <v>121</v>
       </c>
       <c r="G23" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H23" s="61"/>
       <c r="I23" s="61"/>
@@ -16321,7 +16280,7 @@
       <c r="Q23" s="63"/>
       <c r="R23" s="65"/>
     </row>
-    <row r="24" spans="1:18" ht="22.5">
+    <row r="24" spans="1:18" ht="22">
       <c r="A24" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A24" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E24),
@@ -16342,7 +16301,7 @@
         <v>122</v>
       </c>
       <c r="G24" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H24" s="61"/>
       <c r="I24" s="61"/>
@@ -16356,7 +16315,7 @@
       <c r="Q24" s="63"/>
       <c r="R24" s="65"/>
     </row>
-    <row r="25" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="25" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A25" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A25" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E25),
@@ -16381,7 +16340,7 @@
         <v>124</v>
       </c>
       <c r="G25" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H25" s="61"/>
       <c r="I25" s="61"/>
@@ -16416,7 +16375,7 @@
         <v>125</v>
       </c>
       <c r="G26" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -16430,7 +16389,7 @@
       <c r="Q26" s="64"/>
       <c r="R26" s="63"/>
     </row>
-    <row r="27" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="27" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A27" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A27" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E27),
@@ -16455,7 +16414,7 @@
         <v>128</v>
       </c>
       <c r="G27" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H27" s="61"/>
       <c r="I27" s="61"/>
@@ -16469,7 +16428,7 @@
       <c r="Q27" s="64"/>
       <c r="R27" s="63"/>
     </row>
-    <row r="28" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="28" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A28" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A28" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E28),
@@ -16490,7 +16449,7 @@
         <v>129</v>
       </c>
       <c r="G28" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H28" s="61"/>
       <c r="I28" s="61"/>
@@ -16504,7 +16463,7 @@
       <c r="Q28" s="64"/>
       <c r="R28" s="63"/>
     </row>
-    <row r="29" spans="1:18" ht="22.5">
+    <row r="29" spans="1:18" ht="22">
       <c r="A29" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A29" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E29),
@@ -16527,7 +16486,7 @@
         <v>131</v>
       </c>
       <c r="G29" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H29" s="61"/>
       <c r="I29" s="61"/>
@@ -16541,7 +16500,7 @@
       <c r="Q29" s="65"/>
       <c r="R29" s="65"/>
     </row>
-    <row r="30" spans="1:18" ht="22.5">
+    <row r="30" spans="1:18" ht="22">
       <c r="A30" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A30" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E30),
@@ -16562,7 +16521,7 @@
         <v>132</v>
       </c>
       <c r="G30" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -16576,7 +16535,7 @@
       <c r="Q30" s="65"/>
       <c r="R30" s="65"/>
     </row>
-    <row r="31" spans="1:18" ht="22.5">
+    <row r="31" spans="1:18" ht="22">
       <c r="A31" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A31" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E31),
@@ -16597,7 +16556,7 @@
         <v>133</v>
       </c>
       <c r="G31" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H31" s="61"/>
       <c r="I31" s="61"/>
@@ -16611,7 +16570,7 @@
       <c r="Q31" s="65"/>
       <c r="R31" s="65"/>
     </row>
-    <row r="32" spans="1:18" ht="22.5">
+    <row r="32" spans="1:18" ht="22">
       <c r="A32" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A32" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E32),
@@ -16632,7 +16591,7 @@
         <v>134</v>
       </c>
       <c r="G32" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H32" s="61"/>
       <c r="I32" s="61"/>
@@ -16646,7 +16605,7 @@
       <c r="Q32" s="65"/>
       <c r="R32" s="65"/>
     </row>
-    <row r="33" spans="1:18" ht="22.5">
+    <row r="33" spans="1:18" ht="22">
       <c r="A33" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A33" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E33),
@@ -16669,7 +16628,7 @@
         <v>136</v>
       </c>
       <c r="G33" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H33" s="61"/>
       <c r="I33" s="68"/>
@@ -16683,7 +16642,7 @@
       <c r="Q33" s="65"/>
       <c r="R33" s="65"/>
     </row>
-    <row r="34" spans="1:18" ht="22.5">
+    <row r="34" spans="1:18" ht="22">
       <c r="A34" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A34" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E34),
@@ -16704,7 +16663,7 @@
         <v>137</v>
       </c>
       <c r="G34" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H34" s="61"/>
       <c r="I34" s="68"/>
@@ -16718,7 +16677,7 @@
       <c r="Q34" s="65"/>
       <c r="R34" s="65"/>
     </row>
-    <row r="35" spans="1:18" ht="45">
+    <row r="35" spans="1:18" ht="44">
       <c r="A35" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A35" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E35),
@@ -16741,7 +16700,7 @@
         <v>139</v>
       </c>
       <c r="G35" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H35" s="68"/>
       <c r="I35" s="68"/>
@@ -16755,7 +16714,7 @@
       <c r="Q35" s="65"/>
       <c r="R35" s="65"/>
     </row>
-    <row r="36" spans="1:18" ht="33.75">
+    <row r="36" spans="1:18" ht="33">
       <c r="A36" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A36" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E36),
@@ -16782,7 +16741,7 @@
         <v>141</v>
       </c>
       <c r="G36" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H36" s="67"/>
       <c r="I36" s="67"/>
@@ -16796,7 +16755,7 @@
       <c r="Q36" s="80"/>
       <c r="R36" s="80"/>
     </row>
-    <row r="37" spans="1:18" ht="33.75">
+    <row r="37" spans="1:18" ht="33">
       <c r="A37" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A37" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E37),
@@ -16817,7 +16776,7 @@
         <v>142</v>
       </c>
       <c r="G37" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H37" s="67"/>
       <c r="I37" s="67"/>
@@ -16831,7 +16790,7 @@
       <c r="Q37" s="80"/>
       <c r="R37" s="80"/>
     </row>
-    <row r="38" spans="1:18" ht="22.5">
+    <row r="38" spans="1:18" ht="22">
       <c r="A38" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A38" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E38),
@@ -16852,7 +16811,7 @@
         <v>143</v>
       </c>
       <c r="G38" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H38" s="67"/>
       <c r="I38" s="76"/>
@@ -16866,7 +16825,7 @@
       <c r="Q38" s="80"/>
       <c r="R38" s="80"/>
     </row>
-    <row r="39" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="39" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A39" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A39" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E39),
@@ -16887,7 +16846,7 @@
         <v>144</v>
       </c>
       <c r="G39" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H39" s="67"/>
       <c r="I39" s="76"/>
@@ -16901,7 +16860,7 @@
       <c r="Q39" s="79"/>
       <c r="R39" s="80"/>
     </row>
-    <row r="40" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="40" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A40" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A40" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E40),
@@ -16926,7 +16885,7 @@
         <v>146</v>
       </c>
       <c r="G40" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H40" s="67"/>
       <c r="I40" s="67"/>
@@ -16961,7 +16920,7 @@
         <v>147</v>
       </c>
       <c r="G41" s="67" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H41" s="67"/>
       <c r="I41" s="67"/>
@@ -16975,7 +16934,7 @@
       <c r="Q41" s="79"/>
       <c r="R41" s="80"/>
     </row>
-    <row r="42" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="42" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A42" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A42" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E42),
@@ -17018,7 +16977,7 @@
       <c r="Q42" s="63"/>
       <c r="R42" s="65"/>
     </row>
-    <row r="43" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="43" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A43" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A43" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E43),
@@ -17053,7 +17012,7 @@
       <c r="Q43" s="63"/>
       <c r="R43" s="65"/>
     </row>
-    <row r="44" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="44" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A44" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A44" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E44),
@@ -17088,7 +17047,7 @@
       <c r="Q44" s="63"/>
       <c r="R44" s="65"/>
     </row>
-    <row r="45" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="45" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A45" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A45" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E45),
@@ -17125,7 +17084,7 @@
       <c r="Q45" s="63"/>
       <c r="R45" s="65"/>
     </row>
-    <row r="46" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="46" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A46" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A46" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E46),
@@ -17160,7 +17119,7 @@
       <c r="Q46" s="63"/>
       <c r="R46" s="65"/>
     </row>
-    <row r="47" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="47" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A47" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A47" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E47),
@@ -17195,7 +17154,7 @@
       <c r="Q47" s="63"/>
       <c r="R47" s="65"/>
     </row>
-    <row r="48" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="48" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A48" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A48" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E48),
@@ -17232,7 +17191,7 @@
       <c r="Q48" s="63"/>
       <c r="R48" s="65"/>
     </row>
-    <row r="49" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="49" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A49" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A49" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E49),
@@ -17267,7 +17226,7 @@
       <c r="Q49" s="63"/>
       <c r="R49" s="65"/>
     </row>
-    <row r="50" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="50" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A50" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A50" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E50),
@@ -17304,7 +17263,7 @@
       <c r="Q50" s="63"/>
       <c r="R50" s="65"/>
     </row>
-    <row r="51" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="51" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A51" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A51" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E51),
@@ -17339,7 +17298,7 @@
       <c r="Q51" s="63"/>
       <c r="R51" s="65"/>
     </row>
-    <row r="52" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="52" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A52" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A52" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E52),
@@ -17374,7 +17333,7 @@
       <c r="Q52" s="63"/>
       <c r="R52" s="65"/>
     </row>
-    <row r="53" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="53" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A53" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A53" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E53),
@@ -17409,7 +17368,7 @@
       <c r="Q53" s="63"/>
       <c r="R53" s="65"/>
     </row>
-    <row r="54" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="54" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A54" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A54" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E54),
@@ -17444,7 +17403,7 @@
       <c r="Q54" s="63"/>
       <c r="R54" s="65"/>
     </row>
-    <row r="55" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="55" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A55" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A55" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E55),
@@ -17479,7 +17438,7 @@
       <c r="Q55" s="63"/>
       <c r="R55" s="65"/>
     </row>
-    <row r="56" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="56" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A56" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A56" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E56),
@@ -17516,7 +17475,7 @@
       <c r="Q56" s="63"/>
       <c r="R56" s="65"/>
     </row>
-    <row r="57" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="57" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A57" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A57" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E57),
@@ -17553,7 +17512,7 @@
       <c r="Q57" s="63"/>
       <c r="R57" s="65"/>
     </row>
-    <row r="58" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="58" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A58" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A58" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E58),
@@ -17590,7 +17549,7 @@
       <c r="Q58" s="63"/>
       <c r="R58" s="65"/>
     </row>
-    <row r="59" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="59" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A59" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A59" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E59),
@@ -17619,13 +17578,13 @@
         <v>555</v>
       </c>
       <c r="I59" s="114" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="J59" s="153" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="K59" s="115" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="L59" s="110" t="s">
         <v>554</v>
@@ -17639,7 +17598,7 @@
       <c r="Q59" s="118"/>
       <c r="R59" s="111"/>
     </row>
-    <row r="60" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="60" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A60" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A60" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E60),
@@ -17674,7 +17633,7 @@
       <c r="Q60" s="79"/>
       <c r="R60" s="80"/>
     </row>
-    <row r="61" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="61" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A61" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A61" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E61),
@@ -17709,7 +17668,7 @@
       <c r="Q61" s="79"/>
       <c r="R61" s="80"/>
     </row>
-    <row r="62" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="62" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A62" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A62" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E62),
@@ -17744,7 +17703,7 @@
       <c r="Q62" s="79"/>
       <c r="R62" s="80"/>
     </row>
-    <row r="63" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="63" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A63" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A63" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E63),
@@ -17779,7 +17738,7 @@
       <c r="Q63" s="79"/>
       <c r="R63" s="80"/>
     </row>
-    <row r="64" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="64" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A64" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A64" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E64),
@@ -17809,7 +17768,7 @@
         <v>556</v>
       </c>
       <c r="J64" s="37" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="K64" s="115" t="s">
         <v>558</v>
@@ -17826,7 +17785,7 @@
       <c r="Q64" s="118"/>
       <c r="R64" s="111"/>
     </row>
-    <row r="65" spans="1:18" s="35" customFormat="1" ht="78.75">
+    <row r="65" spans="1:18" s="35" customFormat="1" ht="77">
       <c r="A65" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A65" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E65),
@@ -17851,10 +17810,10 @@
         <v>555</v>
       </c>
       <c r="I65" s="114" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="J65" s="37" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="K65" s="115" t="s">
         <v>55</v>
@@ -17871,7 +17830,7 @@
       <c r="Q65" s="118"/>
       <c r="R65" s="111"/>
     </row>
-    <row r="66" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="66" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A66" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A66" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E66),
@@ -17897,7 +17856,7 @@
         <v>557</v>
       </c>
       <c r="J66" s="37" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="K66" s="115" t="s">
         <v>56</v>
@@ -17914,7 +17873,7 @@
       <c r="Q66" s="118"/>
       <c r="R66" s="111"/>
     </row>
-    <row r="67" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="67" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A67" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A67" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E67),
@@ -17949,7 +17908,7 @@
       <c r="Q67" s="79"/>
       <c r="R67" s="80"/>
     </row>
-    <row r="68" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="68" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A68" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A68" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E68),
@@ -17984,7 +17943,7 @@
       <c r="Q68" s="79"/>
       <c r="R68" s="80"/>
     </row>
-    <row r="69" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="69" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A69" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A69" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E69),
@@ -18019,7 +17978,7 @@
       <c r="Q69" s="79"/>
       <c r="R69" s="80"/>
     </row>
-    <row r="70" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="70" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A70" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A70" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E70),
@@ -18054,7 +18013,7 @@
       <c r="Q70" s="79"/>
       <c r="R70" s="80"/>
     </row>
-    <row r="71" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="71" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A71" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A71" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E71),
@@ -18089,7 +18048,7 @@
       <c r="Q71" s="79"/>
       <c r="R71" s="80"/>
     </row>
-    <row r="72" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="72" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A72" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A72" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E72),
@@ -18124,7 +18083,7 @@
       <c r="Q72" s="79"/>
       <c r="R72" s="80"/>
     </row>
-    <row r="73" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="73" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A73" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A73" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E73),
@@ -18151,13 +18110,13 @@
         <v>541</v>
       </c>
       <c r="I73" s="116" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="J73" s="37" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="K73" s="115" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L73" s="110" t="s">
         <v>54</v>
@@ -18171,7 +18130,7 @@
       <c r="Q73" s="118"/>
       <c r="R73" s="111"/>
     </row>
-    <row r="74" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="74" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A74" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A74" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E74),
@@ -18193,10 +18152,10 @@
       <c r="H74" s="121"/>
       <c r="I74" s="121"/>
       <c r="J74" s="37" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="K74" s="115" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="L74" s="110" t="s">
         <v>54</v>
@@ -18210,7 +18169,7 @@
       <c r="Q74" s="118"/>
       <c r="R74" s="111"/>
     </row>
-    <row r="75" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="75" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A75" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A75" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E75),
@@ -18232,10 +18191,10 @@
       <c r="H75" s="121"/>
       <c r="I75" s="121"/>
       <c r="J75" s="37" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="K75" s="115" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="L75" s="110" t="s">
         <v>54</v>
@@ -18249,7 +18208,7 @@
       <c r="Q75" s="118"/>
       <c r="R75" s="111"/>
     </row>
-    <row r="76" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="76" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A76" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A76" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E76),
@@ -18271,10 +18230,10 @@
       <c r="H76" s="121"/>
       <c r="I76" s="121"/>
       <c r="J76" s="37" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="K76" s="115" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="L76" s="110" t="s">
         <v>54</v>
@@ -18288,7 +18247,7 @@
       <c r="Q76" s="118"/>
       <c r="R76" s="111"/>
     </row>
-    <row r="77" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="77" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A77" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A77" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E77),
@@ -18310,10 +18269,10 @@
       <c r="H77" s="123"/>
       <c r="I77" s="123"/>
       <c r="J77" s="37" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="K77" s="115" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="L77" s="110" t="s">
         <v>54</v>
@@ -18327,7 +18286,7 @@
       <c r="Q77" s="118"/>
       <c r="R77" s="111"/>
     </row>
-    <row r="78" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="78" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A78" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A78" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E78),
@@ -18354,13 +18313,13 @@
         <v>541</v>
       </c>
       <c r="I78" s="116" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="J78" s="37" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K78" s="115" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L78" s="110" t="s">
         <v>54</v>
@@ -18374,7 +18333,7 @@
       <c r="Q78" s="118"/>
       <c r="R78" s="111"/>
     </row>
-    <row r="79" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="79" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A79" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A79" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E79),
@@ -18396,10 +18355,10 @@
       <c r="H79" s="121"/>
       <c r="I79" s="121"/>
       <c r="J79" s="37" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K79" s="115" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="L79" s="110" t="s">
         <v>54</v>
@@ -18413,7 +18372,7 @@
       <c r="Q79" s="118"/>
       <c r="R79" s="111"/>
     </row>
-    <row r="80" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="80" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A80" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A80" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E80),
@@ -18435,10 +18394,10 @@
       <c r="H80" s="121"/>
       <c r="I80" s="121"/>
       <c r="J80" s="37" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K80" s="115" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="L80" s="110" t="s">
         <v>54</v>
@@ -18452,7 +18411,7 @@
       <c r="Q80" s="118"/>
       <c r="R80" s="111"/>
     </row>
-    <row r="81" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="81" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A81" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A81" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E81),
@@ -18474,10 +18433,10 @@
       <c r="H81" s="121"/>
       <c r="I81" s="121"/>
       <c r="J81" s="37" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="K81" s="115" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="L81" s="110" t="s">
         <v>54</v>
@@ -18491,7 +18450,7 @@
       <c r="Q81" s="118"/>
       <c r="R81" s="111"/>
     </row>
-    <row r="82" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="82" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A82" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A82" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E82),
@@ -18513,10 +18472,10 @@
       <c r="H82" s="123"/>
       <c r="I82" s="123"/>
       <c r="J82" s="37" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K82" s="115" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="L82" s="110" t="s">
         <v>54</v>
@@ -18530,7 +18489,7 @@
       <c r="Q82" s="118"/>
       <c r="R82" s="111"/>
     </row>
-    <row r="83" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="83" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A83" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A83" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E83),
@@ -18635,7 +18594,7 @@
       <c r="Q85" s="80"/>
       <c r="R85" s="80"/>
     </row>
-    <row r="86" spans="1:18" ht="22.5">
+    <row r="86" spans="1:18" ht="22">
       <c r="A86" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A86" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E86),
@@ -18670,7 +18629,7 @@
       <c r="Q86" s="80"/>
       <c r="R86" s="80"/>
     </row>
-    <row r="87" spans="1:18" ht="22.5">
+    <row r="87" spans="1:18" ht="22">
       <c r="A87" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A87" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E87),
@@ -18711,7 +18670,7 @@
       <c r="Q87" s="65"/>
       <c r="R87" s="65"/>
     </row>
-    <row r="88" spans="1:18" ht="33.75">
+    <row r="88" spans="1:18" ht="33">
       <c r="A88" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A88" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E88),
@@ -18783,7 +18742,7 @@
       <c r="Q89" s="65"/>
       <c r="R89" s="65"/>
     </row>
-    <row r="90" spans="1:18" ht="33.75">
+    <row r="90" spans="1:18" ht="33">
       <c r="A90" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A90" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E90),
@@ -18820,7 +18779,7 @@
       <c r="Q90" s="65"/>
       <c r="R90" s="65"/>
     </row>
-    <row r="91" spans="1:18" ht="33.75">
+    <row r="91" spans="1:18" ht="33">
       <c r="A91" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A91" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E91),
@@ -18855,7 +18814,7 @@
       <c r="Q91" s="65"/>
       <c r="R91" s="65"/>
     </row>
-    <row r="92" spans="1:18" ht="22.5">
+    <row r="92" spans="1:18" ht="22">
       <c r="A92" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A92" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E92),
@@ -18892,7 +18851,7 @@
       <c r="Q92" s="65"/>
       <c r="R92" s="65"/>
     </row>
-    <row r="93" spans="1:18" ht="22.5">
+    <row r="93" spans="1:18" ht="22">
       <c r="A93" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A93" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E93),
@@ -18929,7 +18888,7 @@
       <c r="Q93" s="65"/>
       <c r="R93" s="65"/>
     </row>
-    <row r="94" spans="1:18" ht="33.75">
+    <row r="94" spans="1:18" ht="33">
       <c r="A94" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A94" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E94),
@@ -18960,13 +18919,13 @@
         <v>561</v>
       </c>
       <c r="I94" s="114" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="J94" s="37" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="K94" s="111" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="L94" s="110" t="s">
         <v>554</v>
@@ -18980,7 +18939,7 @@
       <c r="Q94" s="111"/>
       <c r="R94" s="111"/>
     </row>
-    <row r="95" spans="1:18" ht="33.75">
+    <row r="95" spans="1:18" ht="33">
       <c r="A95" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A95" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E95),
@@ -19007,13 +18966,13 @@
         <v>561</v>
       </c>
       <c r="I95" s="114" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="J95" s="37" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="K95" s="111" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="L95" s="110" t="s">
         <v>554</v>
@@ -19027,7 +18986,7 @@
       <c r="Q95" s="111"/>
       <c r="R95" s="111"/>
     </row>
-    <row r="96" spans="1:18" ht="33.75">
+    <row r="96" spans="1:18" ht="33">
       <c r="A96" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A96" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E96),
@@ -19064,7 +19023,7 @@
       <c r="Q96" s="80"/>
       <c r="R96" s="80"/>
     </row>
-    <row r="97" spans="1:18" ht="22.5">
+    <row r="97" spans="1:18" ht="22">
       <c r="A97" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A97" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E97),
@@ -19105,7 +19064,7 @@
       <c r="Q97" s="65"/>
       <c r="R97" s="65"/>
     </row>
-    <row r="98" spans="1:18" ht="33.75">
+    <row r="98" spans="1:18" ht="33">
       <c r="A98" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A98" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E98),
@@ -19177,7 +19136,7 @@
       <c r="Q99" s="65"/>
       <c r="R99" s="65"/>
     </row>
-    <row r="100" spans="1:18" ht="33.75">
+    <row r="100" spans="1:18" ht="33">
       <c r="A100" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A100" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E100),
@@ -19214,7 +19173,7 @@
       <c r="Q100" s="65"/>
       <c r="R100" s="65"/>
     </row>
-    <row r="101" spans="1:18" ht="33.75">
+    <row r="101" spans="1:18" ht="33">
       <c r="A101" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A101" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E101),
@@ -19249,7 +19208,7 @@
       <c r="Q101" s="65"/>
       <c r="R101" s="65"/>
     </row>
-    <row r="102" spans="1:18" ht="33.75">
+    <row r="102" spans="1:18" ht="33">
       <c r="A102" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A102" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E102),
@@ -19286,7 +19245,7 @@
       <c r="Q102" s="65"/>
       <c r="R102" s="65"/>
     </row>
-    <row r="103" spans="1:18" ht="22.5">
+    <row r="103" spans="1:18" ht="22">
       <c r="A103" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A103" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E103),
@@ -19327,7 +19286,7 @@
       <c r="Q103" s="65"/>
       <c r="R103" s="65"/>
     </row>
-    <row r="104" spans="1:18" ht="33.75">
+    <row r="104" spans="1:18" ht="33">
       <c r="A104" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A104" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E104),
@@ -19397,7 +19356,7 @@
       <c r="Q105" s="65"/>
       <c r="R105" s="65"/>
     </row>
-    <row r="106" spans="1:18" ht="33.75">
+    <row r="106" spans="1:18" ht="33">
       <c r="A106" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A106" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E106),
@@ -19432,7 +19391,7 @@
       <c r="Q106" s="65"/>
       <c r="R106" s="65"/>
     </row>
-    <row r="107" spans="1:18" ht="33.75">
+    <row r="107" spans="1:18" ht="33">
       <c r="A107" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A107" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E107),
@@ -19467,7 +19426,7 @@
       <c r="Q107" s="65"/>
       <c r="R107" s="65"/>
     </row>
-    <row r="108" spans="1:18" ht="22.5">
+    <row r="108" spans="1:18" ht="22">
       <c r="A108" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A108" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E108),
@@ -19504,7 +19463,7 @@
       <c r="Q108" s="65"/>
       <c r="R108" s="65"/>
     </row>
-    <row r="109" spans="1:18" ht="33.75">
+    <row r="109" spans="1:18" ht="33">
       <c r="A109" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A109" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E109),
@@ -19574,7 +19533,7 @@
       <c r="Q110" s="65"/>
       <c r="R110" s="65"/>
     </row>
-    <row r="111" spans="1:18" ht="33.75">
+    <row r="111" spans="1:18" ht="33">
       <c r="A111" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A111" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E111),
@@ -19609,7 +19568,7 @@
       <c r="Q111" s="65"/>
       <c r="R111" s="65"/>
     </row>
-    <row r="112" spans="1:18" ht="33.75">
+    <row r="112" spans="1:18" ht="33">
       <c r="A112" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A112" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E112),
@@ -19644,7 +19603,7 @@
       <c r="Q112" s="65"/>
       <c r="R112" s="65"/>
     </row>
-    <row r="113" spans="1:18" ht="33.75">
+    <row r="113" spans="1:18" ht="33">
       <c r="A113" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A113" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E113),
@@ -19681,7 +19640,7 @@
       <c r="Q113" s="65"/>
       <c r="R113" s="65"/>
     </row>
-    <row r="114" spans="1:18" ht="33.75">
+    <row r="114" spans="1:18" ht="33">
       <c r="A114" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A114" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E114),
@@ -19800,7 +19759,7 @@
       <c r="Q116" s="65"/>
       <c r="R116" s="65"/>
     </row>
-    <row r="117" spans="1:18" ht="22.5">
+    <row r="117" spans="1:18" ht="22">
       <c r="A117" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A117" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E117),
@@ -19841,7 +19800,7 @@
       <c r="Q117" s="65"/>
       <c r="R117" s="65"/>
     </row>
-    <row r="118" spans="1:18" ht="22.5">
+    <row r="118" spans="1:18" ht="22">
       <c r="A118" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A118" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E118),
@@ -19917,7 +19876,7 @@
       <c r="Q119" s="65"/>
       <c r="R119" s="65"/>
     </row>
-    <row r="120" spans="1:18" ht="22.5">
+    <row r="120" spans="1:18" ht="22">
       <c r="A120" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A120" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E120),
@@ -19960,7 +19919,7 @@
       <c r="Q120" s="80"/>
       <c r="R120" s="80"/>
     </row>
-    <row r="121" spans="1:18" ht="22.5">
+    <row r="121" spans="1:18" ht="22">
       <c r="A121" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A121" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E121),
@@ -19997,7 +19956,7 @@
       <c r="Q121" s="80"/>
       <c r="R121" s="80"/>
     </row>
-    <row r="122" spans="1:18" ht="22.5">
+    <row r="122" spans="1:18" ht="22">
       <c r="A122" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A122" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E122),
@@ -20032,7 +19991,7 @@
       <c r="Q122" s="80"/>
       <c r="R122" s="80"/>
     </row>
-    <row r="123" spans="1:18" ht="22.5">
+    <row r="123" spans="1:18" ht="22">
       <c r="A123" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A123" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E123),
@@ -20067,7 +20026,7 @@
       <c r="Q123" s="80"/>
       <c r="R123" s="80"/>
     </row>
-    <row r="124" spans="1:18" ht="22.5">
+    <row r="124" spans="1:18" ht="22">
       <c r="A124" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A124" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E124),
@@ -20104,7 +20063,7 @@
       <c r="Q124" s="80"/>
       <c r="R124" s="80"/>
     </row>
-    <row r="125" spans="1:18" ht="22.5">
+    <row r="125" spans="1:18" ht="22">
       <c r="A125" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A125" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E125),
@@ -20139,7 +20098,7 @@
       <c r="Q125" s="80"/>
       <c r="R125" s="80"/>
     </row>
-    <row r="126" spans="1:18" ht="22.5">
+    <row r="126" spans="1:18" ht="22">
       <c r="A126" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A126" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E126),
@@ -20174,7 +20133,7 @@
       <c r="Q126" s="80"/>
       <c r="R126" s="80"/>
     </row>
-    <row r="127" spans="1:18" ht="22.5">
+    <row r="127" spans="1:18" ht="22">
       <c r="A127" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A127" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E127),
@@ -20209,7 +20168,7 @@
       <c r="Q127" s="80"/>
       <c r="R127" s="80"/>
     </row>
-    <row r="128" spans="1:18" ht="33.75">
+    <row r="128" spans="1:18" ht="33">
       <c r="A128" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A128" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E128),
@@ -20244,7 +20203,7 @@
       <c r="Q128" s="80"/>
       <c r="R128" s="80"/>
     </row>
-    <row r="129" spans="1:18" ht="33.75">
+    <row r="129" spans="1:18" ht="33">
       <c r="A129" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A129" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E129),
@@ -20281,7 +20240,7 @@
       <c r="Q129" s="80"/>
       <c r="R129" s="80"/>
     </row>
-    <row r="130" spans="1:18" ht="33.75">
+    <row r="130" spans="1:18" ht="33">
       <c r="A130" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A130" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E130),
@@ -20316,7 +20275,7 @@
       <c r="Q130" s="80"/>
       <c r="R130" s="80"/>
     </row>
-    <row r="131" spans="1:18" ht="45">
+    <row r="131" spans="1:18" ht="44">
       <c r="A131" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A131" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E131),
@@ -20351,7 +20310,7 @@
       <c r="Q131" s="80"/>
       <c r="R131" s="80"/>
     </row>
-    <row r="132" spans="1:18" ht="45">
+    <row r="132" spans="1:18" ht="44">
       <c r="A132" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A132" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E132),
@@ -20386,7 +20345,7 @@
       <c r="Q132" s="80"/>
       <c r="R132" s="80"/>
     </row>
-    <row r="133" spans="1:18" ht="33.75">
+    <row r="133" spans="1:18" ht="33">
       <c r="A133" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A133" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E133),
@@ -20421,7 +20380,7 @@
       <c r="Q133" s="80"/>
       <c r="R133" s="80"/>
     </row>
-    <row r="134" spans="1:18" ht="33.75">
+    <row r="134" spans="1:18" ht="33">
       <c r="A134" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A134" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E134),
@@ -20458,7 +20417,7 @@
       <c r="Q134" s="80"/>
       <c r="R134" s="80"/>
     </row>
-    <row r="135" spans="1:18" ht="33.75">
+    <row r="135" spans="1:18" ht="33">
       <c r="A135" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A135" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E135),
@@ -20497,7 +20456,7 @@
       <c r="Q135" s="80"/>
       <c r="R135" s="80"/>
     </row>
-    <row r="136" spans="1:18" ht="33.75">
+    <row r="136" spans="1:18" ht="33">
       <c r="A136" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A136" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E136),
@@ -20538,7 +20497,7 @@
       <c r="Q136" s="80"/>
       <c r="R136" s="80"/>
     </row>
-    <row r="137" spans="1:18" ht="22.5">
+    <row r="137" spans="1:18" ht="22">
       <c r="A137" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A137" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E137),
@@ -20575,7 +20534,7 @@
       <c r="Q137" s="80"/>
       <c r="R137" s="80"/>
     </row>
-    <row r="138" spans="1:18" ht="22.5">
+    <row r="138" spans="1:18" ht="22">
       <c r="A138" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A138" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E138),
@@ -20610,7 +20569,7 @@
       <c r="Q138" s="80"/>
       <c r="R138" s="80"/>
     </row>
-    <row r="139" spans="1:18" ht="45">
+    <row r="139" spans="1:18" ht="44">
       <c r="A139" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A139" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E139),
@@ -20645,7 +20604,7 @@
       <c r="Q139" s="80"/>
       <c r="R139" s="80"/>
     </row>
-    <row r="140" spans="1:18" ht="22.5">
+    <row r="140" spans="1:18" ht="22">
       <c r="A140" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A140" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E140),
@@ -20688,7 +20647,7 @@
       <c r="Q140" s="80"/>
       <c r="R140" s="80"/>
     </row>
-    <row r="141" spans="1:18" ht="22.5">
+    <row r="141" spans="1:18" ht="22">
       <c r="A141" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A141" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E141),
@@ -20725,7 +20684,7 @@
       <c r="Q141" s="80"/>
       <c r="R141" s="80"/>
     </row>
-    <row r="142" spans="1:18" ht="22.5">
+    <row r="142" spans="1:18" ht="22">
       <c r="A142" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A142" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E142),
@@ -20760,7 +20719,7 @@
       <c r="Q142" s="80"/>
       <c r="R142" s="80"/>
     </row>
-    <row r="143" spans="1:18" ht="22.5">
+    <row r="143" spans="1:18" ht="22">
       <c r="A143" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A143" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E143),
@@ -20795,7 +20754,7 @@
       <c r="Q143" s="80"/>
       <c r="R143" s="80"/>
     </row>
-    <row r="144" spans="1:18" ht="22.5">
+    <row r="144" spans="1:18" ht="22">
       <c r="A144" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A144" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E144),
@@ -20832,7 +20791,7 @@
       <c r="Q144" s="80"/>
       <c r="R144" s="80"/>
     </row>
-    <row r="145" spans="1:18" ht="33.75">
+    <row r="145" spans="1:18" ht="33">
       <c r="A145" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A145" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E145),
@@ -20867,7 +20826,7 @@
       <c r="Q145" s="80"/>
       <c r="R145" s="80"/>
     </row>
-    <row r="146" spans="1:18" ht="33.75">
+    <row r="146" spans="1:18" ht="33">
       <c r="A146" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A146" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E146),
@@ -20906,7 +20865,7 @@
       <c r="Q146" s="80"/>
       <c r="R146" s="80"/>
     </row>
-    <row r="147" spans="1:18" ht="33.75">
+    <row r="147" spans="1:18" ht="33">
       <c r="A147" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A147" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E147),
@@ -20947,7 +20906,7 @@
       <c r="Q147" s="80"/>
       <c r="R147" s="80"/>
     </row>
-    <row r="148" spans="1:18" ht="33.75">
+    <row r="148" spans="1:18" ht="33">
       <c r="A148" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A148" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E148),
@@ -20984,7 +20943,7 @@
       <c r="Q148" s="80"/>
       <c r="R148" s="80"/>
     </row>
-    <row r="149" spans="1:18" ht="33.75">
+    <row r="149" spans="1:18" ht="33">
       <c r="A149" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A149" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E149),
@@ -21021,7 +20980,7 @@
       <c r="Q149" s="80"/>
       <c r="R149" s="80"/>
     </row>
-    <row r="150" spans="1:18" ht="33.75">
+    <row r="150" spans="1:18" ht="33">
       <c r="A150" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A150" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E150),
@@ -21058,7 +21017,7 @@
       <c r="Q150" s="80"/>
       <c r="R150" s="80"/>
     </row>
-    <row r="151" spans="1:18" ht="33.75">
+    <row r="151" spans="1:18" ht="33">
       <c r="A151" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A151" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E151),
@@ -21095,7 +21054,7 @@
       <c r="Q151" s="80"/>
       <c r="R151" s="80"/>
     </row>
-    <row r="152" spans="1:18" ht="22.5">
+    <row r="152" spans="1:18" ht="22">
       <c r="A152" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A152" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E152),
@@ -21132,7 +21091,7 @@
       <c r="Q152" s="80"/>
       <c r="R152" s="80"/>
     </row>
-    <row r="153" spans="1:18" ht="22.5">
+    <row r="153" spans="1:18" ht="22">
       <c r="A153" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A153" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E153),
@@ -21167,7 +21126,7 @@
       <c r="Q153" s="80"/>
       <c r="R153" s="80"/>
     </row>
-    <row r="154" spans="1:18" ht="22.5">
+    <row r="154" spans="1:18" ht="22">
       <c r="A154" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A154" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E154),
@@ -21202,7 +21161,7 @@
       <c r="Q154" s="80"/>
       <c r="R154" s="80"/>
     </row>
-    <row r="155" spans="1:18" ht="22.5">
+    <row r="155" spans="1:18" ht="22">
       <c r="A155" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A155" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E155),
@@ -21237,7 +21196,7 @@
       <c r="Q155" s="80"/>
       <c r="R155" s="80"/>
     </row>
-    <row r="156" spans="1:18" ht="22.5">
+    <row r="156" spans="1:18" ht="22">
       <c r="A156" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A156" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E156),
@@ -21272,7 +21231,7 @@
       <c r="Q156" s="80"/>
       <c r="R156" s="80"/>
     </row>
-    <row r="157" spans="1:18" ht="22.5">
+    <row r="157" spans="1:18" ht="22">
       <c r="A157" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A157" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E157),
@@ -21307,7 +21266,7 @@
       <c r="Q157" s="80"/>
       <c r="R157" s="80"/>
     </row>
-    <row r="158" spans="1:18" ht="22.5">
+    <row r="158" spans="1:18" ht="22">
       <c r="A158" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A158" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E158),
@@ -21346,7 +21305,7 @@
       <c r="Q158" s="80"/>
       <c r="R158" s="80"/>
     </row>
-    <row r="159" spans="1:18" ht="22.5">
+    <row r="159" spans="1:18" ht="22">
       <c r="A159" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A159" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E159),
@@ -21381,7 +21340,7 @@
       <c r="Q159" s="80"/>
       <c r="R159" s="80"/>
     </row>
-    <row r="160" spans="1:18" ht="33.75">
+    <row r="160" spans="1:18" ht="33">
       <c r="A160" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A160" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E160),
@@ -21418,7 +21377,7 @@
       <c r="Q160" s="80"/>
       <c r="R160" s="80"/>
     </row>
-    <row r="161" spans="1:18" ht="33.75">
+    <row r="161" spans="1:18" ht="33">
       <c r="A161" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A161" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E161),
@@ -21453,7 +21412,7 @@
       <c r="Q161" s="80"/>
       <c r="R161" s="80"/>
     </row>
-    <row r="162" spans="1:18" ht="33.75">
+    <row r="162" spans="1:18" ht="33">
       <c r="A162" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A162" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E162),
@@ -21488,7 +21447,7 @@
       <c r="Q162" s="80"/>
       <c r="R162" s="80"/>
     </row>
-    <row r="163" spans="1:18" ht="33.75">
+    <row r="163" spans="1:18" ht="33">
       <c r="A163" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A163" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E163),
@@ -21523,7 +21482,7 @@
       <c r="Q163" s="80"/>
       <c r="R163" s="80"/>
     </row>
-    <row r="164" spans="1:18" ht="33.75">
+    <row r="164" spans="1:18" ht="33">
       <c r="A164" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A164" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E164),
@@ -21558,7 +21517,7 @@
       <c r="Q164" s="80"/>
       <c r="R164" s="80"/>
     </row>
-    <row r="165" spans="1:18" ht="22.5">
+    <row r="165" spans="1:18" ht="22">
       <c r="A165" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A165" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E165),
@@ -21593,7 +21552,7 @@
       <c r="Q165" s="80"/>
       <c r="R165" s="80"/>
     </row>
-    <row r="166" spans="1:18" ht="22.5">
+    <row r="166" spans="1:18" ht="22">
       <c r="A166" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A166" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E166),
@@ -21628,7 +21587,7 @@
       <c r="Q166" s="80"/>
       <c r="R166" s="80"/>
     </row>
-    <row r="167" spans="1:18" ht="33.75">
+    <row r="167" spans="1:18" ht="33">
       <c r="A167" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A167" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E167),
@@ -21663,7 +21622,7 @@
       <c r="Q167" s="80"/>
       <c r="R167" s="80"/>
     </row>
-    <row r="168" spans="1:18" ht="33.75">
+    <row r="168" spans="1:18" ht="33">
       <c r="A168" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A168" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E168),
@@ -21698,7 +21657,7 @@
       <c r="Q168" s="80"/>
       <c r="R168" s="80"/>
     </row>
-    <row r="169" spans="1:18" ht="33.75">
+    <row r="169" spans="1:18" ht="33">
       <c r="A169" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A169" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E169),
@@ -21733,7 +21692,7 @@
       <c r="Q169" s="80"/>
       <c r="R169" s="80"/>
     </row>
-    <row r="170" spans="1:18" ht="33.75">
+    <row r="170" spans="1:18" ht="33">
       <c r="A170" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A170" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E170),
@@ -21840,7 +21799,7 @@
       <c r="Q172" s="80"/>
       <c r="R172" s="80"/>
     </row>
-    <row r="173" spans="1:18" ht="22.5">
+    <row r="173" spans="1:18" ht="22">
       <c r="A173" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A173" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E173),
@@ -21875,7 +21834,7 @@
       <c r="Q173" s="80"/>
       <c r="R173" s="80"/>
     </row>
-    <row r="174" spans="1:18" ht="22.5">
+    <row r="174" spans="1:18" ht="22">
       <c r="A174" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A174" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E174),
@@ -21910,7 +21869,7 @@
       <c r="Q174" s="80"/>
       <c r="R174" s="80"/>
     </row>
-    <row r="175" spans="1:18" ht="22.5">
+    <row r="175" spans="1:18" ht="22">
       <c r="A175" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A175" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E175),
@@ -21945,7 +21904,7 @@
       <c r="Q175" s="80"/>
       <c r="R175" s="80"/>
     </row>
-    <row r="176" spans="1:18" ht="33.75">
+    <row r="176" spans="1:18" ht="33">
       <c r="A176" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A176" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E176),
@@ -21980,7 +21939,7 @@
       <c r="Q176" s="80"/>
       <c r="R176" s="80"/>
     </row>
-    <row r="177" spans="1:18" ht="22.5">
+    <row r="177" spans="1:18" ht="22">
       <c r="A177" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A177" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E177),
@@ -22015,7 +21974,7 @@
       <c r="Q177" s="80"/>
       <c r="R177" s="80"/>
     </row>
-    <row r="178" spans="1:18" ht="22.5">
+    <row r="178" spans="1:18" ht="22">
       <c r="A178" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A178" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E178),
@@ -22052,7 +22011,7 @@
       <c r="Q178" s="80"/>
       <c r="R178" s="80"/>
     </row>
-    <row r="179" spans="1:18" ht="33.75">
+    <row r="179" spans="1:18" ht="33">
       <c r="A179" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A179" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E179),
@@ -22087,7 +22046,7 @@
       <c r="Q179" s="80"/>
       <c r="R179" s="80"/>
     </row>
-    <row r="180" spans="1:18" ht="33.75">
+    <row r="180" spans="1:18" ht="33">
       <c r="A180" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A180" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E180),
@@ -22122,7 +22081,7 @@
       <c r="Q180" s="80"/>
       <c r="R180" s="80"/>
     </row>
-    <row r="181" spans="1:18" ht="45">
+    <row r="181" spans="1:18" ht="44">
       <c r="A181" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A181" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E181),
@@ -22157,7 +22116,7 @@
       <c r="Q181" s="80"/>
       <c r="R181" s="80"/>
     </row>
-    <row r="182" spans="1:18" ht="45">
+    <row r="182" spans="1:18" ht="44">
       <c r="A182" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A182" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E182),
@@ -22192,7 +22151,7 @@
       <c r="Q182" s="80"/>
       <c r="R182" s="80"/>
     </row>
-    <row r="183" spans="1:18" ht="33.75">
+    <row r="183" spans="1:18" ht="33">
       <c r="A183" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A183" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E183),
@@ -22227,7 +22186,7 @@
       <c r="Q183" s="80"/>
       <c r="R183" s="80"/>
     </row>
-    <row r="184" spans="1:18" ht="45">
+    <row r="184" spans="1:18" ht="44">
       <c r="A184" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A184" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E184),
@@ -22262,7 +22221,7 @@
       <c r="Q184" s="80"/>
       <c r="R184" s="80"/>
     </row>
-    <row r="185" spans="1:18" ht="45">
+    <row r="185" spans="1:18" ht="44">
       <c r="A185" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A185" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E185),
@@ -22297,7 +22256,7 @@
       <c r="Q185" s="80"/>
       <c r="R185" s="80"/>
     </row>
-    <row r="186" spans="1:18" ht="22.5">
+    <row r="186" spans="1:18" ht="22">
       <c r="A186" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A186" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E186),
@@ -22332,7 +22291,7 @@
       <c r="Q186" s="80"/>
       <c r="R186" s="80"/>
     </row>
-    <row r="187" spans="1:18" ht="33.75">
+    <row r="187" spans="1:18" ht="33">
       <c r="A187" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A187" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E187),
@@ -22369,7 +22328,7 @@
       <c r="Q187" s="80"/>
       <c r="R187" s="80"/>
     </row>
-    <row r="188" spans="1:18" ht="22.5">
+    <row r="188" spans="1:18" ht="22">
       <c r="A188" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A188" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E188),
@@ -22406,7 +22365,7 @@
       <c r="Q188" s="80"/>
       <c r="R188" s="80"/>
     </row>
-    <row r="189" spans="1:18" ht="22.5">
+    <row r="189" spans="1:18" ht="22">
       <c r="A189" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A189" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E189),
@@ -22449,7 +22408,7 @@
       <c r="Q189" s="65"/>
       <c r="R189" s="65"/>
     </row>
-    <row r="190" spans="1:18" ht="22.5">
+    <row r="190" spans="1:18" ht="22">
       <c r="A190" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A190" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E190),
@@ -22527,7 +22486,7 @@
       <c r="Q191" s="65"/>
       <c r="R191" s="65"/>
     </row>
-    <row r="192" spans="1:18" ht="22.5">
+    <row r="192" spans="1:18" ht="22">
       <c r="A192" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A192" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E192),
@@ -22570,7 +22529,7 @@
       <c r="Q192" s="65"/>
       <c r="R192" s="65"/>
     </row>
-    <row r="193" spans="1:18" ht="22.5">
+    <row r="193" spans="1:18" ht="22">
       <c r="A193" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A193" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E193),
@@ -22607,7 +22566,7 @@
       <c r="Q193" s="65"/>
       <c r="R193" s="65"/>
     </row>
-    <row r="194" spans="1:18" ht="22.5">
+    <row r="194" spans="1:18" ht="22">
       <c r="A194" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A194" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E194),
@@ -22642,7 +22601,7 @@
       <c r="Q194" s="65"/>
       <c r="R194" s="65"/>
     </row>
-    <row r="195" spans="1:18" ht="22.5">
+    <row r="195" spans="1:18" ht="22">
       <c r="A195" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A195" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E195),
@@ -22679,7 +22638,7 @@
       <c r="Q195" s="65"/>
       <c r="R195" s="65"/>
     </row>
-    <row r="196" spans="1:18" ht="22.5">
+    <row r="196" spans="1:18" ht="22">
       <c r="A196" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A196" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E196),
@@ -22714,7 +22673,7 @@
       <c r="Q196" s="65"/>
       <c r="R196" s="65"/>
     </row>
-    <row r="197" spans="1:18" ht="33.75">
+    <row r="197" spans="1:18" ht="33">
       <c r="A197" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A197" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E197),
@@ -22753,7 +22712,7 @@
       <c r="Q197" s="65"/>
       <c r="R197" s="65"/>
     </row>
-    <row r="198" spans="1:18" ht="22.5">
+    <row r="198" spans="1:18" ht="22">
       <c r="A198" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A198" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E198),
@@ -22794,7 +22753,7 @@
       <c r="Q198" s="65"/>
       <c r="R198" s="65"/>
     </row>
-    <row r="199" spans="1:18" ht="22.5">
+    <row r="199" spans="1:18" ht="22">
       <c r="A199" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A199" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E199),
@@ -22829,7 +22788,7 @@
       <c r="Q199" s="65"/>
       <c r="R199" s="65"/>
     </row>
-    <row r="200" spans="1:18" ht="22.5">
+    <row r="200" spans="1:18" ht="22">
       <c r="A200" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A200" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E200),
@@ -22864,7 +22823,7 @@
       <c r="Q200" s="65"/>
       <c r="R200" s="65"/>
     </row>
-    <row r="201" spans="1:18" ht="22.5">
+    <row r="201" spans="1:18" ht="22">
       <c r="A201" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A201" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E201),
@@ -22899,7 +22858,7 @@
       <c r="Q201" s="65"/>
       <c r="R201" s="65"/>
     </row>
-    <row r="202" spans="1:18" ht="22.5">
+    <row r="202" spans="1:18" ht="22">
       <c r="A202" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A202" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E202),
@@ -22934,7 +22893,7 @@
       <c r="Q202" s="65"/>
       <c r="R202" s="65"/>
     </row>
-    <row r="203" spans="1:18" ht="22.5">
+    <row r="203" spans="1:18" ht="22">
       <c r="A203" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A203" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E203),
@@ -22969,7 +22928,7 @@
       <c r="Q203" s="65"/>
       <c r="R203" s="65"/>
     </row>
-    <row r="204" spans="1:18" ht="22.5">
+    <row r="204" spans="1:18" ht="22">
       <c r="A204" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A204" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E204),
@@ -23004,7 +22963,7 @@
       <c r="Q204" s="65"/>
       <c r="R204" s="65"/>
     </row>
-    <row r="205" spans="1:18" ht="22.5">
+    <row r="205" spans="1:18" ht="22">
       <c r="A205" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A205" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E205),
@@ -23041,7 +23000,7 @@
       <c r="Q205" s="65"/>
       <c r="R205" s="65"/>
     </row>
-    <row r="206" spans="1:18" ht="22.5">
+    <row r="206" spans="1:18" ht="22">
       <c r="A206" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A206" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E206),
@@ -23080,7 +23039,7 @@
       <c r="Q206" s="65"/>
       <c r="R206" s="65"/>
     </row>
-    <row r="207" spans="1:18" ht="22.5">
+    <row r="207" spans="1:18" ht="22">
       <c r="A207" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A207" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E207),
@@ -23150,7 +23109,7 @@
       <c r="Q208" s="65"/>
       <c r="R208" s="65"/>
     </row>
-    <row r="209" spans="1:18" ht="22.5">
+    <row r="209" spans="1:18" ht="22">
       <c r="A209" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A209" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E209),
@@ -23185,7 +23144,7 @@
       <c r="Q209" s="65"/>
       <c r="R209" s="65"/>
     </row>
-    <row r="210" spans="1:18" ht="33.75">
+    <row r="210" spans="1:18" ht="33">
       <c r="A210" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A210" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E210),
@@ -23220,7 +23179,7 @@
       <c r="Q210" s="65"/>
       <c r="R210" s="65"/>
     </row>
-    <row r="211" spans="1:18" ht="33.75">
+    <row r="211" spans="1:18" ht="33">
       <c r="A211" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A211" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E211),
@@ -23255,7 +23214,7 @@
       <c r="Q211" s="65"/>
       <c r="R211" s="65"/>
     </row>
-    <row r="212" spans="1:18" ht="45">
+    <row r="212" spans="1:18" ht="44">
       <c r="A212" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A212" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E212),
@@ -23290,7 +23249,7 @@
       <c r="Q212" s="65"/>
       <c r="R212" s="65"/>
     </row>
-    <row r="213" spans="1:18" ht="33.75">
+    <row r="213" spans="1:18" ht="33">
       <c r="A213" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A213" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E213),
@@ -23325,7 +23284,7 @@
       <c r="Q213" s="65"/>
       <c r="R213" s="65"/>
     </row>
-    <row r="214" spans="1:18" ht="33.75">
+    <row r="214" spans="1:18" ht="33">
       <c r="A214" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A214" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E214),
@@ -23360,7 +23319,7 @@
       <c r="Q214" s="65"/>
       <c r="R214" s="65"/>
     </row>
-    <row r="215" spans="1:18" ht="22.5">
+    <row r="215" spans="1:18" ht="22">
       <c r="A215" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A215" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E215),
@@ -23395,7 +23354,7 @@
       <c r="Q215" s="65"/>
       <c r="R215" s="65"/>
     </row>
-    <row r="216" spans="1:18" ht="22.5">
+    <row r="216" spans="1:18" ht="22">
       <c r="A216" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A216" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E216),
@@ -23430,7 +23389,7 @@
       <c r="Q216" s="65"/>
       <c r="R216" s="65"/>
     </row>
-    <row r="217" spans="1:18" ht="33.75">
+    <row r="217" spans="1:18" ht="33">
       <c r="A217" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A217" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E217),
@@ -23465,7 +23424,7 @@
       <c r="Q217" s="65"/>
       <c r="R217" s="65"/>
     </row>
-    <row r="218" spans="1:18" ht="22.5">
+    <row r="218" spans="1:18" ht="22">
       <c r="A218" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A218" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E218),
@@ -23500,7 +23459,7 @@
       <c r="Q218" s="65"/>
       <c r="R218" s="65"/>
     </row>
-    <row r="219" spans="1:18" ht="22.5">
+    <row r="219" spans="1:18" ht="22">
       <c r="A219" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A219" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E219),
@@ -23539,7 +23498,7 @@
       <c r="Q219" s="65"/>
       <c r="R219" s="65"/>
     </row>
-    <row r="220" spans="1:18" ht="22.5">
+    <row r="220" spans="1:18" ht="22">
       <c r="A220" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A220" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E220),
@@ -23574,7 +23533,7 @@
       <c r="Q220" s="65"/>
       <c r="R220" s="65"/>
     </row>
-    <row r="221" spans="1:18" ht="22.5">
+    <row r="221" spans="1:18" ht="22">
       <c r="A221" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A221" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E221),
@@ -23644,7 +23603,7 @@
       <c r="Q222" s="65"/>
       <c r="R222" s="65"/>
     </row>
-    <row r="223" spans="1:18" ht="22.5">
+    <row r="223" spans="1:18" ht="22">
       <c r="A223" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A223" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E223),
@@ -23679,7 +23638,7 @@
       <c r="Q223" s="65"/>
       <c r="R223" s="65"/>
     </row>
-    <row r="224" spans="1:18" ht="45">
+    <row r="224" spans="1:18" ht="44">
       <c r="A224" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A224" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E224),
@@ -23714,7 +23673,7 @@
       <c r="Q224" s="65"/>
       <c r="R224" s="65"/>
     </row>
-    <row r="225" spans="1:18" ht="33.75">
+    <row r="225" spans="1:18" ht="33">
       <c r="A225" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A225" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E225),
@@ -23749,7 +23708,7 @@
       <c r="Q225" s="65"/>
       <c r="R225" s="65"/>
     </row>
-    <row r="226" spans="1:18" ht="33.75">
+    <row r="226" spans="1:18" ht="33">
       <c r="A226" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A226" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E226),
@@ -23784,7 +23743,7 @@
       <c r="Q226" s="65"/>
       <c r="R226" s="65"/>
     </row>
-    <row r="227" spans="1:18" ht="45">
+    <row r="227" spans="1:18" ht="44">
       <c r="A227" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A227" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E227),
@@ -23819,7 +23778,7 @@
       <c r="Q227" s="65"/>
       <c r="R227" s="65"/>
     </row>
-    <row r="228" spans="1:18" ht="33.75">
+    <row r="228" spans="1:18" ht="33">
       <c r="A228" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A228" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E228),
@@ -23854,7 +23813,7 @@
       <c r="Q228" s="65"/>
       <c r="R228" s="65"/>
     </row>
-    <row r="229" spans="1:18" ht="33.75">
+    <row r="229" spans="1:18" ht="33">
       <c r="A229" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A229" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E229),
@@ -23889,7 +23848,7 @@
       <c r="Q229" s="65"/>
       <c r="R229" s="65"/>
     </row>
-    <row r="230" spans="1:18" ht="22.5">
+    <row r="230" spans="1:18" ht="22">
       <c r="A230" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A230" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E230),
@@ -23924,7 +23883,7 @@
       <c r="Q230" s="65"/>
       <c r="R230" s="65"/>
     </row>
-    <row r="231" spans="1:18" ht="22.5">
+    <row r="231" spans="1:18" ht="22">
       <c r="A231" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A231" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E231),
@@ -23959,7 +23918,7 @@
       <c r="Q231" s="65"/>
       <c r="R231" s="65"/>
     </row>
-    <row r="232" spans="1:18" ht="33.75">
+    <row r="232" spans="1:18" ht="33">
       <c r="A232" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A232" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E232),
@@ -23994,7 +23953,7 @@
       <c r="Q232" s="65"/>
       <c r="R232" s="65"/>
     </row>
-    <row r="233" spans="1:18" ht="22.5">
+    <row r="233" spans="1:18" ht="22">
       <c r="A233" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A233" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E233),
@@ -24029,7 +23988,7 @@
       <c r="Q233" s="65"/>
       <c r="R233" s="65"/>
     </row>
-    <row r="234" spans="1:18" ht="45">
+    <row r="234" spans="1:18" ht="44">
       <c r="A234" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A234" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E234),
@@ -24066,7 +24025,7 @@
       <c r="Q234" s="65"/>
       <c r="R234" s="65"/>
     </row>
-    <row r="235" spans="1:18" ht="45">
+    <row r="235" spans="1:18" ht="44">
       <c r="A235" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A235" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E235),
@@ -24101,7 +24060,7 @@
       <c r="Q235" s="65"/>
       <c r="R235" s="65"/>
     </row>
-    <row r="236" spans="1:18" ht="33.75">
+    <row r="236" spans="1:18" ht="33">
       <c r="A236" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A236" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E236),
@@ -24136,7 +24095,7 @@
       <c r="Q236" s="65"/>
       <c r="R236" s="65"/>
     </row>
-    <row r="237" spans="1:18" ht="33.75">
+    <row r="237" spans="1:18" ht="33">
       <c r="A237" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A237" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E237),
@@ -24173,7 +24132,7 @@
       <c r="Q237" s="65"/>
       <c r="R237" s="65"/>
     </row>
-    <row r="238" spans="1:18" ht="22.5">
+    <row r="238" spans="1:18" ht="22">
       <c r="A238" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A238" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E238),
@@ -24210,7 +24169,7 @@
       <c r="Q238" s="65"/>
       <c r="R238" s="65"/>
     </row>
-    <row r="239" spans="1:18" ht="22.5">
+    <row r="239" spans="1:18" ht="22">
       <c r="A239" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A239" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E239),
@@ -24253,7 +24212,7 @@
       <c r="Q239" s="65"/>
       <c r="R239" s="65"/>
     </row>
-    <row r="240" spans="1:18" ht="22.5">
+    <row r="240" spans="1:18" ht="22">
       <c r="A240" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A240" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E240),
@@ -24290,7 +24249,7 @@
       <c r="Q240" s="65"/>
       <c r="R240" s="65"/>
     </row>
-    <row r="241" spans="1:18" ht="22.5">
+    <row r="241" spans="1:18" ht="22">
       <c r="A241" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A241" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E241),
@@ -24325,7 +24284,7 @@
       <c r="Q241" s="65"/>
       <c r="R241" s="65"/>
     </row>
-    <row r="242" spans="1:18" ht="22.5">
+    <row r="242" spans="1:18" ht="22">
       <c r="A242" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A242" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E242),
@@ -24360,7 +24319,7 @@
       <c r="Q242" s="65"/>
       <c r="R242" s="65"/>
     </row>
-    <row r="243" spans="1:18" ht="22.5">
+    <row r="243" spans="1:18" ht="22">
       <c r="A243" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A243" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E243),
@@ -24395,7 +24354,7 @@
       <c r="Q243" s="65"/>
       <c r="R243" s="65"/>
     </row>
-    <row r="244" spans="1:18" ht="33.75">
+    <row r="244" spans="1:18" ht="33">
       <c r="A244" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A244" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E244),
@@ -24430,7 +24389,7 @@
       <c r="Q244" s="65"/>
       <c r="R244" s="65"/>
     </row>
-    <row r="245" spans="1:18" ht="33.75">
+    <row r="245" spans="1:18" ht="33">
       <c r="A245" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A245" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E245),
@@ -24467,7 +24426,7 @@
       <c r="Q245" s="65"/>
       <c r="R245" s="65"/>
     </row>
-    <row r="246" spans="1:18" ht="33.75">
+    <row r="246" spans="1:18" ht="33">
       <c r="A246" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A246" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E246),
@@ -24502,7 +24461,7 @@
       <c r="Q246" s="65"/>
       <c r="R246" s="65"/>
     </row>
-    <row r="247" spans="1:18" ht="45">
+    <row r="247" spans="1:18" ht="44">
       <c r="A247" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A247" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E247),
@@ -24537,7 +24496,7 @@
       <c r="Q247" s="65"/>
       <c r="R247" s="65"/>
     </row>
-    <row r="248" spans="1:18" ht="45">
+    <row r="248" spans="1:18" ht="44">
       <c r="A248" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A248" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E248),
@@ -24572,7 +24531,7 @@
       <c r="Q248" s="65"/>
       <c r="R248" s="65"/>
     </row>
-    <row r="249" spans="1:18" ht="33.75">
+    <row r="249" spans="1:18" ht="33">
       <c r="A249" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A249" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E249),
@@ -24607,7 +24566,7 @@
       <c r="Q249" s="65"/>
       <c r="R249" s="65"/>
     </row>
-    <row r="250" spans="1:18" ht="33.75">
+    <row r="250" spans="1:18" ht="33">
       <c r="A250" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A250" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E250),
@@ -24644,7 +24603,7 @@
       <c r="Q250" s="65"/>
       <c r="R250" s="65"/>
     </row>
-    <row r="251" spans="1:18" ht="33.75">
+    <row r="251" spans="1:18" ht="33">
       <c r="A251" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A251" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E251),
@@ -24685,7 +24644,7 @@
       <c r="Q251" s="65"/>
       <c r="R251" s="65"/>
     </row>
-    <row r="252" spans="1:18" ht="22.5">
+    <row r="252" spans="1:18" ht="22">
       <c r="A252" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A252" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E252),
@@ -24728,7 +24687,7 @@
       <c r="Q252" s="65"/>
       <c r="R252" s="65"/>
     </row>
-    <row r="253" spans="1:18" ht="22.5">
+    <row r="253" spans="1:18" ht="22">
       <c r="A253" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A253" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E253),
@@ -24763,7 +24722,7 @@
       <c r="Q253" s="65"/>
       <c r="R253" s="65"/>
     </row>
-    <row r="254" spans="1:18" ht="33.75">
+    <row r="254" spans="1:18" ht="33">
       <c r="A254" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A254" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E254),
@@ -24802,7 +24761,7 @@
       <c r="Q254" s="65"/>
       <c r="R254" s="65"/>
     </row>
-    <row r="255" spans="1:18" ht="33.75">
+    <row r="255" spans="1:18" ht="33">
       <c r="A255" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A255" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E255),
@@ -24837,7 +24796,7 @@
       <c r="Q255" s="65"/>
       <c r="R255" s="65"/>
     </row>
-    <row r="256" spans="1:18" ht="33.75">
+    <row r="256" spans="1:18" ht="33">
       <c r="A256" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A256" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E256),
@@ -24878,7 +24837,7 @@
       <c r="Q256" s="65"/>
       <c r="R256" s="65"/>
     </row>
-    <row r="257" spans="1:18" ht="33.75">
+    <row r="257" spans="1:18" ht="33">
       <c r="A257" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A257" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E257),
@@ -24915,7 +24874,7 @@
       <c r="Q257" s="65"/>
       <c r="R257" s="65"/>
     </row>
-    <row r="258" spans="1:18" ht="33.75">
+    <row r="258" spans="1:18" ht="33">
       <c r="A258" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A258" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E258),
@@ -24952,7 +24911,7 @@
       <c r="Q258" s="65"/>
       <c r="R258" s="65"/>
     </row>
-    <row r="259" spans="1:18" ht="33.75">
+    <row r="259" spans="1:18" ht="33">
       <c r="A259" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A259" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E259),
@@ -24989,7 +24948,7 @@
       <c r="Q259" s="65"/>
       <c r="R259" s="65"/>
     </row>
-    <row r="260" spans="1:18" ht="22.5">
+    <row r="260" spans="1:18" ht="22">
       <c r="A260" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A260" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E260),
@@ -25028,7 +24987,7 @@
       <c r="Q260" s="65"/>
       <c r="R260" s="65"/>
     </row>
-    <row r="261" spans="1:18" ht="22.5">
+    <row r="261" spans="1:18" ht="22">
       <c r="A261" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A261" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E261),
@@ -25063,7 +25022,7 @@
       <c r="Q261" s="65"/>
       <c r="R261" s="65"/>
     </row>
-    <row r="262" spans="1:18" ht="33.75">
+    <row r="262" spans="1:18" ht="33">
       <c r="A262" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A262" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E262),
@@ -25100,7 +25059,7 @@
       <c r="Q262" s="65"/>
       <c r="R262" s="65"/>
     </row>
-    <row r="263" spans="1:18" ht="33.75">
+    <row r="263" spans="1:18" ht="33">
       <c r="A263" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A263" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E263),
@@ -25135,7 +25094,7 @@
       <c r="Q263" s="65"/>
       <c r="R263" s="65"/>
     </row>
-    <row r="264" spans="1:18" ht="33.75">
+    <row r="264" spans="1:18" ht="33">
       <c r="A264" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A264" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E264),
@@ -25170,7 +25129,7 @@
       <c r="Q264" s="65"/>
       <c r="R264" s="65"/>
     </row>
-    <row r="265" spans="1:18" ht="33.75">
+    <row r="265" spans="1:18" ht="33">
       <c r="A265" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A265" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E265),
@@ -25205,7 +25164,7 @@
       <c r="Q265" s="65"/>
       <c r="R265" s="65"/>
     </row>
-    <row r="266" spans="1:18" ht="33.75">
+    <row r="266" spans="1:18" ht="33">
       <c r="A266" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A266" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E266),
@@ -25240,7 +25199,7 @@
       <c r="Q266" s="65"/>
       <c r="R266" s="65"/>
     </row>
-    <row r="267" spans="1:18" ht="22.5">
+    <row r="267" spans="1:18" ht="22">
       <c r="A267" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A267" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E267),
@@ -25275,7 +25234,7 @@
       <c r="Q267" s="65"/>
       <c r="R267" s="65"/>
     </row>
-    <row r="268" spans="1:18" ht="22.5">
+    <row r="268" spans="1:18" ht="22">
       <c r="A268" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A268" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E268),
@@ -25310,7 +25269,7 @@
       <c r="Q268" s="65"/>
       <c r="R268" s="65"/>
     </row>
-    <row r="269" spans="1:18" ht="33.75">
+    <row r="269" spans="1:18" ht="33">
       <c r="A269" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A269" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E269),
@@ -25345,7 +25304,7 @@
       <c r="Q269" s="65"/>
       <c r="R269" s="65"/>
     </row>
-    <row r="270" spans="1:18" ht="33.75">
+    <row r="270" spans="1:18" ht="33">
       <c r="A270" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A270" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E270),
@@ -25380,7 +25339,7 @@
       <c r="Q270" s="65"/>
       <c r="R270" s="65"/>
     </row>
-    <row r="271" spans="1:18" ht="33.75">
+    <row r="271" spans="1:18" ht="33">
       <c r="A271" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A271" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E271),
@@ -25415,7 +25374,7 @@
       <c r="Q271" s="65"/>
       <c r="R271" s="65"/>
     </row>
-    <row r="272" spans="1:18" ht="33.75">
+    <row r="272" spans="1:18" ht="33">
       <c r="A272" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A272" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E272),
@@ -25522,7 +25481,7 @@
       <c r="Q274" s="65"/>
       <c r="R274" s="65"/>
     </row>
-    <row r="275" spans="1:18" ht="22.5">
+    <row r="275" spans="1:18" ht="22">
       <c r="A275" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A275" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E275),
@@ -25557,7 +25516,7 @@
       <c r="Q275" s="65"/>
       <c r="R275" s="65"/>
     </row>
-    <row r="276" spans="1:18" ht="22.5">
+    <row r="276" spans="1:18" ht="22">
       <c r="A276" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A276" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E276),
@@ -25592,7 +25551,7 @@
       <c r="Q276" s="65"/>
       <c r="R276" s="65"/>
     </row>
-    <row r="277" spans="1:18" ht="22.5">
+    <row r="277" spans="1:18" ht="22">
       <c r="A277" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A277" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E277),
@@ -25627,7 +25586,7 @@
       <c r="Q277" s="65"/>
       <c r="R277" s="65"/>
     </row>
-    <row r="278" spans="1:18" ht="33.75">
+    <row r="278" spans="1:18" ht="33">
       <c r="A278" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A278" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E278),
@@ -25662,7 +25621,7 @@
       <c r="Q278" s="65"/>
       <c r="R278" s="65"/>
     </row>
-    <row r="279" spans="1:18" ht="22.5">
+    <row r="279" spans="1:18" ht="22">
       <c r="A279" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A279" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E279),
@@ -25699,7 +25658,7 @@
       <c r="Q279" s="65"/>
       <c r="R279" s="65"/>
     </row>
-    <row r="280" spans="1:18" ht="33.75">
+    <row r="280" spans="1:18" ht="33">
       <c r="A280" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A280" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E280),
@@ -25734,7 +25693,7 @@
       <c r="Q280" s="65"/>
       <c r="R280" s="65"/>
     </row>
-    <row r="281" spans="1:18" ht="45">
+    <row r="281" spans="1:18" ht="44">
       <c r="A281" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A281" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E281),
@@ -25769,7 +25728,7 @@
       <c r="Q281" s="65"/>
       <c r="R281" s="65"/>
     </row>
-    <row r="282" spans="1:18" ht="45">
+    <row r="282" spans="1:18" ht="44">
       <c r="A282" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A282" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E282),
@@ -25804,7 +25763,7 @@
       <c r="Q282" s="65"/>
       <c r="R282" s="65"/>
     </row>
-    <row r="283" spans="1:18" ht="22.5">
+    <row r="283" spans="1:18" ht="22">
       <c r="A283" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A283" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E283),
@@ -25839,7 +25798,7 @@
       <c r="Q283" s="65"/>
       <c r="R283" s="65"/>
     </row>
-    <row r="284" spans="1:18" ht="45">
+    <row r="284" spans="1:18" ht="44">
       <c r="A284" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A284" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E284),
@@ -25874,7 +25833,7 @@
       <c r="Q284" s="65"/>
       <c r="R284" s="65"/>
     </row>
-    <row r="285" spans="1:18" ht="45">
+    <row r="285" spans="1:18" ht="44">
       <c r="A285" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A285" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E285),
@@ -25909,7 +25868,7 @@
       <c r="Q285" s="65"/>
       <c r="R285" s="65"/>
     </row>
-    <row r="286" spans="1:18" ht="22.5">
+    <row r="286" spans="1:18" ht="22">
       <c r="A286" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A286" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E286),
@@ -25944,7 +25903,7 @@
       <c r="Q286" s="65"/>
       <c r="R286" s="65"/>
     </row>
-    <row r="287" spans="1:18" ht="22.5">
+    <row r="287" spans="1:18" ht="22">
       <c r="A287" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A287" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E287),
@@ -25981,7 +25940,7 @@
       <c r="Q287" s="65"/>
       <c r="R287" s="65"/>
     </row>
-    <row r="288" spans="1:18" ht="22.5">
+    <row r="288" spans="1:18" ht="22">
       <c r="A288" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A288" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E288),
@@ -26024,7 +25983,7 @@
       <c r="Q288" s="80"/>
       <c r="R288" s="80"/>
     </row>
-    <row r="289" spans="1:18" ht="22.5">
+    <row r="289" spans="1:18" ht="22">
       <c r="A289" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A289" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E289),
@@ -26059,7 +26018,7 @@
       <c r="Q289" s="80"/>
       <c r="R289" s="80"/>
     </row>
-    <row r="290" spans="1:18" ht="22.5">
+    <row r="290" spans="1:18" ht="22">
       <c r="A290" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A290" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E290),
@@ -26094,7 +26053,7 @@
       <c r="Q290" s="80"/>
       <c r="R290" s="80"/>
     </row>
-    <row r="291" spans="1:18" ht="22.5">
+    <row r="291" spans="1:18" ht="22">
       <c r="A291" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A291" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E291),
@@ -26129,7 +26088,7 @@
       <c r="Q291" s="80"/>
       <c r="R291" s="80"/>
     </row>
-    <row r="292" spans="1:18" ht="22.5">
+    <row r="292" spans="1:18" ht="22">
       <c r="A292" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A292" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E292),
@@ -26170,7 +26129,7 @@
       <c r="Q292" s="80"/>
       <c r="R292" s="80"/>
     </row>
-    <row r="293" spans="1:18" ht="22.5">
+    <row r="293" spans="1:18" ht="22">
       <c r="A293" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A293" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E293),
@@ -26207,7 +26166,7 @@
       <c r="Q293" s="80"/>
       <c r="R293" s="80"/>
     </row>
-    <row r="294" spans="1:18" ht="22.5">
+    <row r="294" spans="1:18" ht="22">
       <c r="A294" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A294" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E294),
@@ -26244,7 +26203,7 @@
       <c r="Q294" s="80"/>
       <c r="R294" s="80"/>
     </row>
-    <row r="295" spans="1:18" ht="22.5">
+    <row r="295" spans="1:18" ht="22">
       <c r="A295" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A295" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E295),
@@ -26281,7 +26240,7 @@
       <c r="Q295" s="80"/>
       <c r="R295" s="80"/>
     </row>
-    <row r="296" spans="1:18" ht="22.5">
+    <row r="296" spans="1:18" ht="22">
       <c r="A296" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A296" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E296),
@@ -26320,7 +26279,7 @@
       <c r="Q296" s="80"/>
       <c r="R296" s="80"/>
     </row>
-    <row r="297" spans="1:18" ht="22.5">
+    <row r="297" spans="1:18" ht="22">
       <c r="A297" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A297" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E297),
@@ -26355,7 +26314,7 @@
       <c r="Q297" s="80"/>
       <c r="R297" s="80"/>
     </row>
-    <row r="298" spans="1:18" ht="33.75">
+    <row r="298" spans="1:18" ht="33">
       <c r="A298" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A298" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E298),
@@ -26390,7 +26349,7 @@
       <c r="Q298" s="80"/>
       <c r="R298" s="80"/>
     </row>
-    <row r="299" spans="1:18" ht="33.75">
+    <row r="299" spans="1:18" ht="33">
       <c r="A299" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A299" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E299),
@@ -26425,7 +26384,7 @@
       <c r="Q299" s="80"/>
       <c r="R299" s="80"/>
     </row>
-    <row r="300" spans="1:18" ht="33.75">
+    <row r="300" spans="1:18" ht="33">
       <c r="A300" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A300" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E300),
@@ -26460,7 +26419,7 @@
       <c r="Q300" s="80"/>
       <c r="R300" s="80"/>
     </row>
-    <row r="301" spans="1:18" ht="33.75">
+    <row r="301" spans="1:18" ht="33">
       <c r="A301" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A301" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E301),
@@ -26495,7 +26454,7 @@
       <c r="Q301" s="80"/>
       <c r="R301" s="80"/>
     </row>
-    <row r="302" spans="1:18" ht="33.75">
+    <row r="302" spans="1:18" ht="33">
       <c r="A302" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A302" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E302),
@@ -26530,7 +26489,7 @@
       <c r="Q302" s="80"/>
       <c r="R302" s="80"/>
     </row>
-    <row r="303" spans="1:18" ht="22.5">
+    <row r="303" spans="1:18" ht="22">
       <c r="A303" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A303" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E303),
@@ -26565,7 +26524,7 @@
       <c r="Q303" s="80"/>
       <c r="R303" s="80"/>
     </row>
-    <row r="304" spans="1:18" ht="22.5">
+    <row r="304" spans="1:18" ht="22">
       <c r="A304" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A304" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E304),
@@ -26632,16 +26591,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R329"/>
-  <sheetFormatPr defaultRowHeight="11.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="3" width="8.625" style="28" customWidth="1"/>
-    <col min="4" max="5" width="8.625" style="29" customWidth="1"/>
-    <col min="6" max="6" width="37.625" style="29" customWidth="1"/>
-    <col min="7" max="7" width="40.625" style="103" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="9" width="16.375" style="28" customWidth="1"/>
-    <col min="10" max="11" width="23.625" style="28" customWidth="1"/>
-    <col min="12" max="12" width="15.625" style="28" customWidth="1"/>
-    <col min="13" max="18" width="8.625" style="28" customWidth="1"/>
+    <col min="1" max="3" width="8.58203125" style="28" customWidth="1"/>
+    <col min="4" max="5" width="8.58203125" style="29" customWidth="1"/>
+    <col min="6" max="6" width="37.58203125" style="29" customWidth="1"/>
+    <col min="7" max="7" width="40.58203125" style="103" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="9" width="16.33203125" style="28" customWidth="1"/>
+    <col min="10" max="11" width="23.58203125" style="28" customWidth="1"/>
+    <col min="12" max="12" width="15.58203125" style="28" customWidth="1"/>
+    <col min="13" max="18" width="8.58203125" style="28" customWidth="1"/>
     <col min="19" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
@@ -26687,10 +26646,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="12" thickBot="1">
-      <c r="A8" s="30" t="s">
-        <v>581</v>
-      </c>
+    <row r="8" spans="1:18" ht="11.5" thickBot="1">
+      <c r="A8" s="30"/>
       <c r="B8" s="30"/>
       <c r="C8" s="30"/>
       <c r="D8" s="31"/>
@@ -26766,7 +26723,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="22.5">
+    <row r="11" spans="1:18" ht="22">
       <c r="A11" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A11" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E11),
@@ -26809,7 +26766,7 @@
       <c r="Q11" s="136"/>
       <c r="R11" s="78"/>
     </row>
-    <row r="12" spans="1:18" ht="22.5">
+    <row r="12" spans="1:18" ht="22">
       <c r="A12" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A12" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E12),
@@ -26846,7 +26803,7 @@
       <c r="Q12" s="136"/>
       <c r="R12" s="78"/>
     </row>
-    <row r="13" spans="1:18" ht="33.75">
+    <row r="13" spans="1:18" ht="33">
       <c r="A13" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A13" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E13),
@@ -26885,7 +26842,7 @@
       <c r="Q13" s="136"/>
       <c r="R13" s="78"/>
     </row>
-    <row r="14" spans="1:18" ht="22.5">
+    <row r="14" spans="1:18" ht="22">
       <c r="A14" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E14),
@@ -26920,7 +26877,7 @@
       <c r="Q14" s="136"/>
       <c r="R14" s="78"/>
     </row>
-    <row r="15" spans="1:18" ht="22.5">
+    <row r="15" spans="1:18" ht="22">
       <c r="A15" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A15" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E15),
@@ -26955,7 +26912,7 @@
       <c r="Q15" s="136"/>
       <c r="R15" s="78"/>
     </row>
-    <row r="16" spans="1:18" ht="22.5">
+    <row r="16" spans="1:18" ht="22">
       <c r="A16" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A16" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E16),
@@ -26990,7 +26947,7 @@
       <c r="Q16" s="136"/>
       <c r="R16" s="78"/>
     </row>
-    <row r="17" spans="1:18" ht="33.75">
+    <row r="17" spans="1:18" ht="33">
       <c r="A17" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E17),
@@ -27025,7 +26982,7 @@
       <c r="Q17" s="136"/>
       <c r="R17" s="78"/>
     </row>
-    <row r="18" spans="1:18" ht="22.5">
+    <row r="18" spans="1:18" ht="22">
       <c r="A18" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A18" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E18),
@@ -27064,7 +27021,7 @@
       <c r="Q18" s="136"/>
       <c r="R18" s="78"/>
     </row>
-    <row r="19" spans="1:18" ht="22.5">
+    <row r="19" spans="1:18" ht="22">
       <c r="A19" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A19" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E19),
@@ -27099,7 +27056,7 @@
       <c r="Q19" s="136"/>
       <c r="R19" s="78"/>
     </row>
-    <row r="20" spans="1:18" ht="22.5">
+    <row r="20" spans="1:18" ht="22">
       <c r="A20" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A20" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E20),
@@ -27134,7 +27091,7 @@
       <c r="Q20" s="136"/>
       <c r="R20" s="78"/>
     </row>
-    <row r="21" spans="1:18" ht="22.5">
+    <row r="21" spans="1:18" ht="22">
       <c r="A21" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A21" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E21),
@@ -27171,7 +27128,7 @@
       <c r="Q21" s="136"/>
       <c r="R21" s="78"/>
     </row>
-    <row r="22" spans="1:18" ht="22.5">
+    <row r="22" spans="1:18" ht="22">
       <c r="A22" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A22" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E22),
@@ -27206,7 +27163,7 @@
       <c r="Q22" s="136"/>
       <c r="R22" s="78"/>
     </row>
-    <row r="23" spans="1:18" ht="22.5">
+    <row r="23" spans="1:18" ht="22">
       <c r="A23" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A23" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E23),
@@ -27241,7 +27198,7 @@
       <c r="Q23" s="136"/>
       <c r="R23" s="78"/>
     </row>
-    <row r="24" spans="1:18" ht="22.5">
+    <row r="24" spans="1:18" ht="22">
       <c r="A24" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A24" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E24),
@@ -27276,7 +27233,7 @@
       <c r="Q24" s="136"/>
       <c r="R24" s="78"/>
     </row>
-    <row r="25" spans="1:18" ht="22.5">
+    <row r="25" spans="1:18" ht="22">
       <c r="A25" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A25" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E25),
@@ -27315,7 +27272,7 @@
       <c r="Q25" s="136"/>
       <c r="R25" s="78"/>
     </row>
-    <row r="26" spans="1:18" ht="22.5">
+    <row r="26" spans="1:18" ht="22">
       <c r="A26" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A26" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E26),
@@ -27350,7 +27307,7 @@
       <c r="Q26" s="136"/>
       <c r="R26" s="78"/>
     </row>
-    <row r="27" spans="1:18" ht="33.75">
+    <row r="27" spans="1:18" ht="33">
       <c r="A27" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A27" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E27),
@@ -27389,7 +27346,7 @@
       <c r="Q27" s="136"/>
       <c r="R27" s="78"/>
     </row>
-    <row r="28" spans="1:18" ht="22.5">
+    <row r="28" spans="1:18" ht="22">
       <c r="A28" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A28" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E28),
@@ -27424,7 +27381,7 @@
       <c r="Q28" s="136"/>
       <c r="R28" s="78"/>
     </row>
-    <row r="29" spans="1:18" ht="22.5">
+    <row r="29" spans="1:18" ht="22">
       <c r="A29" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A29" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E29),
@@ -27461,7 +27418,7 @@
       <c r="Q29" s="136"/>
       <c r="R29" s="78"/>
     </row>
-    <row r="30" spans="1:18" ht="22.5">
+    <row r="30" spans="1:18" ht="22">
       <c r="A30" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A30" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E30),
@@ -27496,7 +27453,7 @@
       <c r="Q30" s="136"/>
       <c r="R30" s="78"/>
     </row>
-    <row r="31" spans="1:18" ht="22.5">
+    <row r="31" spans="1:18" ht="22">
       <c r="A31" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A31" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E31),
@@ -27531,7 +27488,7 @@
       <c r="Q31" s="136"/>
       <c r="R31" s="78"/>
     </row>
-    <row r="32" spans="1:18" ht="22.5">
+    <row r="32" spans="1:18" ht="22">
       <c r="A32" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A32" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E32),
@@ -27566,7 +27523,7 @@
       <c r="Q32" s="136"/>
       <c r="R32" s="78"/>
     </row>
-    <row r="33" spans="1:18" ht="22.5">
+    <row r="33" spans="1:18" ht="22">
       <c r="A33" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A33" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E33),
@@ -27603,7 +27560,7 @@
       <c r="Q33" s="136"/>
       <c r="R33" s="78"/>
     </row>
-    <row r="34" spans="1:18" ht="22.5">
+    <row r="34" spans="1:18" ht="22">
       <c r="A34" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A34" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E34),
@@ -27638,7 +27595,7 @@
       <c r="Q34" s="136"/>
       <c r="R34" s="78"/>
     </row>
-    <row r="35" spans="1:18" ht="45">
+    <row r="35" spans="1:18" ht="44">
       <c r="A35" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A35" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E35),
@@ -27675,7 +27632,7 @@
       <c r="Q35" s="136"/>
       <c r="R35" s="78"/>
     </row>
-    <row r="36" spans="1:18" ht="33.75">
+    <row r="36" spans="1:18" ht="33">
       <c r="A36" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A36" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E36),
@@ -27716,7 +27673,7 @@
       <c r="Q36" s="136"/>
       <c r="R36" s="78"/>
     </row>
-    <row r="37" spans="1:18" ht="33.75">
+    <row r="37" spans="1:18" ht="33">
       <c r="A37" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A37" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E37),
@@ -27751,7 +27708,7 @@
       <c r="Q37" s="136"/>
       <c r="R37" s="78"/>
     </row>
-    <row r="38" spans="1:18" ht="33.75">
+    <row r="38" spans="1:18" ht="33">
       <c r="A38" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A38" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E38),
@@ -27786,7 +27743,7 @@
       <c r="Q38" s="136"/>
       <c r="R38" s="78"/>
     </row>
-    <row r="39" spans="1:18" ht="33.75">
+    <row r="39" spans="1:18" ht="33">
       <c r="A39" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A39" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E39),
@@ -27821,7 +27778,7 @@
       <c r="Q39" s="136"/>
       <c r="R39" s="78"/>
     </row>
-    <row r="40" spans="1:18" ht="33.75">
+    <row r="40" spans="1:18" ht="33">
       <c r="A40" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A40" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E40),
@@ -27860,7 +27817,7 @@
       <c r="Q40" s="136"/>
       <c r="R40" s="78"/>
     </row>
-    <row r="41" spans="1:18" ht="22.5">
+    <row r="41" spans="1:18" ht="22">
       <c r="A41" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A41" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E41),
@@ -27895,7 +27852,7 @@
       <c r="Q41" s="136"/>
       <c r="R41" s="78"/>
     </row>
-    <row r="42" spans="1:18" ht="22.5">
+    <row r="42" spans="1:18" ht="22">
       <c r="A42" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A42" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E42),
@@ -27938,7 +27895,7 @@
       <c r="Q42" s="136"/>
       <c r="R42" s="78"/>
     </row>
-    <row r="43" spans="1:18" ht="22.5">
+    <row r="43" spans="1:18" ht="22">
       <c r="A43" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A43" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E43),
@@ -27973,7 +27930,7 @@
       <c r="Q43" s="136"/>
       <c r="R43" s="78"/>
     </row>
-    <row r="44" spans="1:18" ht="33.75">
+    <row r="44" spans="1:18" ht="33">
       <c r="A44" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A44" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E44),
@@ -28008,7 +27965,7 @@
       <c r="Q44" s="136"/>
       <c r="R44" s="78"/>
     </row>
-    <row r="45" spans="1:18" ht="22.5">
+    <row r="45" spans="1:18" ht="22">
       <c r="A45" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A45" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E45),
@@ -28045,7 +28002,7 @@
       <c r="Q45" s="136"/>
       <c r="R45" s="78"/>
     </row>
-    <row r="46" spans="1:18" ht="22.5">
+    <row r="46" spans="1:18" ht="22">
       <c r="A46" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A46" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E46),
@@ -28080,7 +28037,7 @@
       <c r="Q46" s="136"/>
       <c r="R46" s="78"/>
     </row>
-    <row r="47" spans="1:18" ht="33.75">
+    <row r="47" spans="1:18" ht="33">
       <c r="A47" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A47" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E47),
@@ -28115,7 +28072,7 @@
       <c r="Q47" s="136"/>
       <c r="R47" s="78"/>
     </row>
-    <row r="48" spans="1:18" ht="22.5">
+    <row r="48" spans="1:18" ht="22">
       <c r="A48" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A48" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E48),
@@ -28152,7 +28109,7 @@
       <c r="Q48" s="136"/>
       <c r="R48" s="78"/>
     </row>
-    <row r="49" spans="1:18" ht="22.5">
+    <row r="49" spans="1:18" ht="22">
       <c r="A49" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A49" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E49),
@@ -28187,7 +28144,7 @@
       <c r="Q49" s="136"/>
       <c r="R49" s="78"/>
     </row>
-    <row r="50" spans="1:18" ht="22.5">
+    <row r="50" spans="1:18" ht="22">
       <c r="A50" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A50" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E50),
@@ -28224,7 +28181,7 @@
       <c r="Q50" s="136"/>
       <c r="R50" s="78"/>
     </row>
-    <row r="51" spans="1:18" ht="22.5">
+    <row r="51" spans="1:18" ht="22">
       <c r="A51" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A51" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E51),
@@ -28259,7 +28216,7 @@
       <c r="Q51" s="136"/>
       <c r="R51" s="78"/>
     </row>
-    <row r="52" spans="1:18" ht="22.5">
+    <row r="52" spans="1:18" ht="22">
       <c r="A52" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A52" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E52),
@@ -28294,7 +28251,7 @@
       <c r="Q52" s="136"/>
       <c r="R52" s="78"/>
     </row>
-    <row r="53" spans="1:18" ht="22.5">
+    <row r="53" spans="1:18" ht="22">
       <c r="A53" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A53" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E53),
@@ -28329,7 +28286,7 @@
       <c r="Q53" s="136"/>
       <c r="R53" s="78"/>
     </row>
-    <row r="54" spans="1:18" ht="22.5">
+    <row r="54" spans="1:18" ht="22">
       <c r="A54" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A54" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E54),
@@ -28364,7 +28321,7 @@
       <c r="Q54" s="136"/>
       <c r="R54" s="78"/>
     </row>
-    <row r="55" spans="1:18" ht="22.5">
+    <row r="55" spans="1:18" ht="22">
       <c r="A55" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A55" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E55),
@@ -28399,7 +28356,7 @@
       <c r="Q55" s="136"/>
       <c r="R55" s="78"/>
     </row>
-    <row r="56" spans="1:18" ht="45">
+    <row r="56" spans="1:18" ht="44">
       <c r="A56" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A56" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E56),
@@ -28436,7 +28393,7 @@
       <c r="Q56" s="136"/>
       <c r="R56" s="78"/>
     </row>
-    <row r="57" spans="1:18" ht="33.75">
+    <row r="57" spans="1:18" ht="33">
       <c r="A57" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A57" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E57),
@@ -28473,7 +28430,7 @@
       <c r="Q57" s="136"/>
       <c r="R57" s="78"/>
     </row>
-    <row r="58" spans="1:18" ht="22.5">
+    <row r="58" spans="1:18" ht="22">
       <c r="A58" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A58" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E58),
@@ -28510,7 +28467,7 @@
       <c r="Q58" s="136"/>
       <c r="R58" s="78"/>
     </row>
-    <row r="59" spans="1:18" ht="22.5">
+    <row r="59" spans="1:18" ht="22">
       <c r="A59" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A59" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E59),
@@ -28549,7 +28506,7 @@
       <c r="Q59" s="136"/>
       <c r="R59" s="78"/>
     </row>
-    <row r="60" spans="1:18" ht="22.5">
+    <row r="60" spans="1:18" ht="22">
       <c r="A60" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A60" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E60),
@@ -28584,7 +28541,7 @@
       <c r="Q60" s="136"/>
       <c r="R60" s="78"/>
     </row>
-    <row r="61" spans="1:18" ht="22.5">
+    <row r="61" spans="1:18" ht="22">
       <c r="A61" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A61" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E61),
@@ -28619,7 +28576,7 @@
       <c r="Q61" s="136"/>
       <c r="R61" s="78"/>
     </row>
-    <row r="62" spans="1:18" ht="22.5">
+    <row r="62" spans="1:18" ht="22">
       <c r="A62" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A62" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E62),
@@ -28654,7 +28611,7 @@
       <c r="Q62" s="136"/>
       <c r="R62" s="78"/>
     </row>
-    <row r="63" spans="1:18" ht="22.5">
+    <row r="63" spans="1:18" ht="22">
       <c r="A63" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A63" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E63),
@@ -28689,7 +28646,7 @@
       <c r="Q63" s="136"/>
       <c r="R63" s="78"/>
     </row>
-    <row r="64" spans="1:18" ht="33.75">
+    <row r="64" spans="1:18" ht="33">
       <c r="A64" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A64" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E64),
@@ -28726,7 +28683,7 @@
       <c r="Q64" s="136"/>
       <c r="R64" s="78"/>
     </row>
-    <row r="65" spans="1:18" ht="33.75">
+    <row r="65" spans="1:18" ht="33">
       <c r="A65" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A65" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E65),
@@ -28761,7 +28718,7 @@
       <c r="Q65" s="136"/>
       <c r="R65" s="78"/>
     </row>
-    <row r="66" spans="1:18" ht="45">
+    <row r="66" spans="1:18" ht="44">
       <c r="A66" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A66" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E66),
@@ -28796,7 +28753,7 @@
       <c r="Q66" s="136"/>
       <c r="R66" s="78"/>
     </row>
-    <row r="67" spans="1:18" ht="33.75">
+    <row r="67" spans="1:18" ht="33">
       <c r="A67" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A67" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E67),
@@ -28831,7 +28788,7 @@
       <c r="Q67" s="136"/>
       <c r="R67" s="78"/>
     </row>
-    <row r="68" spans="1:18" ht="33.75">
+    <row r="68" spans="1:18" ht="33">
       <c r="A68" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A68" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E68),
@@ -28866,7 +28823,7 @@
       <c r="Q68" s="136"/>
       <c r="R68" s="78"/>
     </row>
-    <row r="69" spans="1:18" ht="22.5">
+    <row r="69" spans="1:18" ht="22">
       <c r="A69" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A69" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E69),
@@ -28901,7 +28858,7 @@
       <c r="Q69" s="136"/>
       <c r="R69" s="78"/>
     </row>
-    <row r="70" spans="1:18" ht="22.5">
+    <row r="70" spans="1:18" ht="22">
       <c r="A70" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A70" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E70),
@@ -28936,7 +28893,7 @@
       <c r="Q70" s="136"/>
       <c r="R70" s="78"/>
     </row>
-    <row r="71" spans="1:18" ht="33.75">
+    <row r="71" spans="1:18" ht="33">
       <c r="A71" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A71" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E71),
@@ -28971,7 +28928,7 @@
       <c r="Q71" s="136"/>
       <c r="R71" s="78"/>
     </row>
-    <row r="72" spans="1:18" ht="22.5">
+    <row r="72" spans="1:18" ht="22">
       <c r="A72" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A72" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E72),
@@ -29045,7 +29002,7 @@
       <c r="Q73" s="136"/>
       <c r="R73" s="78"/>
     </row>
-    <row r="74" spans="1:18" ht="22.5">
+    <row r="74" spans="1:18" ht="22">
       <c r="A74" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A74" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E74),
@@ -29115,7 +29072,7 @@
       <c r="Q75" s="136"/>
       <c r="R75" s="78"/>
     </row>
-    <row r="76" spans="1:18" ht="22.5">
+    <row r="76" spans="1:18" ht="22">
       <c r="A76" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A76" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E76),
@@ -29150,7 +29107,7 @@
       <c r="Q76" s="136"/>
       <c r="R76" s="78"/>
     </row>
-    <row r="77" spans="1:18" ht="33.75">
+    <row r="77" spans="1:18" ht="33">
       <c r="A77" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A77" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E77),
@@ -29185,7 +29142,7 @@
       <c r="Q77" s="136"/>
       <c r="R77" s="78"/>
     </row>
-    <row r="78" spans="1:18" ht="22.5">
+    <row r="78" spans="1:18" ht="22">
       <c r="A78" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A78" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E78),
@@ -29226,7 +29183,7 @@
       <c r="Q78" s="136"/>
       <c r="R78" s="78"/>
     </row>
-    <row r="79" spans="1:18" ht="33.75">
+    <row r="79" spans="1:18" ht="33">
       <c r="A79" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A79" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E79),
@@ -29298,7 +29255,7 @@
       <c r="Q80" s="136"/>
       <c r="R80" s="78"/>
     </row>
-    <row r="81" spans="1:18" ht="33.75">
+    <row r="81" spans="1:18" ht="33">
       <c r="A81" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A81" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E81),
@@ -29335,7 +29292,7 @@
       <c r="Q81" s="136"/>
       <c r="R81" s="78"/>
     </row>
-    <row r="82" spans="1:18" ht="33.75">
+    <row r="82" spans="1:18" ht="33">
       <c r="A82" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A82" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E82),
@@ -29370,7 +29327,7 @@
       <c r="Q82" s="136"/>
       <c r="R82" s="78"/>
     </row>
-    <row r="83" spans="1:18" ht="22.5">
+    <row r="83" spans="1:18" ht="22">
       <c r="A83" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A83" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E83),
@@ -29407,7 +29364,7 @@
       <c r="Q83" s="136"/>
       <c r="R83" s="78"/>
     </row>
-    <row r="84" spans="1:18" ht="22.5">
+    <row r="84" spans="1:18" ht="22">
       <c r="A84" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A84" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E84),
@@ -29444,7 +29401,7 @@
       <c r="Q84" s="136"/>
       <c r="R84" s="78"/>
     </row>
-    <row r="85" spans="1:18" ht="22.5">
+    <row r="85" spans="1:18" ht="22">
       <c r="A85" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A85" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E85),
@@ -29522,7 +29479,7 @@
       <c r="Q86" s="136"/>
       <c r="R86" s="78"/>
     </row>
-    <row r="87" spans="1:18" ht="33.75">
+    <row r="87" spans="1:18" ht="33">
       <c r="A87" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A87" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E87),
@@ -29559,7 +29516,7 @@
       <c r="Q87" s="136"/>
       <c r="R87" s="78"/>
     </row>
-    <row r="88" spans="1:18" ht="22.5">
+    <row r="88" spans="1:18" ht="22">
       <c r="A88" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A88" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E88),
@@ -29600,7 +29557,7 @@
       <c r="Q88" s="136"/>
       <c r="R88" s="78"/>
     </row>
-    <row r="89" spans="1:18" ht="33.75">
+    <row r="89" spans="1:18" ht="33">
       <c r="A89" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A89" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E89),
@@ -29672,7 +29629,7 @@
       <c r="Q90" s="136"/>
       <c r="R90" s="78"/>
     </row>
-    <row r="91" spans="1:18" ht="33.75">
+    <row r="91" spans="1:18" ht="33">
       <c r="A91" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A91" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E91),
@@ -29709,7 +29666,7 @@
       <c r="Q91" s="136"/>
       <c r="R91" s="78"/>
     </row>
-    <row r="92" spans="1:18" ht="33.75">
+    <row r="92" spans="1:18" ht="33">
       <c r="A92" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A92" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E92),
@@ -29744,7 +29701,7 @@
       <c r="Q92" s="136"/>
       <c r="R92" s="78"/>
     </row>
-    <row r="93" spans="1:18" ht="33.75">
+    <row r="93" spans="1:18" ht="33">
       <c r="A93" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A93" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E93),
@@ -29781,7 +29738,7 @@
       <c r="Q93" s="136"/>
       <c r="R93" s="78"/>
     </row>
-    <row r="94" spans="1:18" ht="22.5">
+    <row r="94" spans="1:18" ht="22">
       <c r="A94" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A94" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E94),
@@ -29822,7 +29779,7 @@
       <c r="Q94" s="136"/>
       <c r="R94" s="78"/>
     </row>
-    <row r="95" spans="1:18" ht="33.75">
+    <row r="95" spans="1:18" ht="33">
       <c r="A95" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A95" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E95),
@@ -29892,7 +29849,7 @@
       <c r="Q96" s="136"/>
       <c r="R96" s="78"/>
     </row>
-    <row r="97" spans="1:18" ht="33.75">
+    <row r="97" spans="1:18" ht="33">
       <c r="A97" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A97" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E97),
@@ -29927,7 +29884,7 @@
       <c r="Q97" s="136"/>
       <c r="R97" s="78"/>
     </row>
-    <row r="98" spans="1:18" ht="33.75">
+    <row r="98" spans="1:18" ht="33">
       <c r="A98" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A98" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E98),
@@ -29962,7 +29919,7 @@
       <c r="Q98" s="136"/>
       <c r="R98" s="78"/>
     </row>
-    <row r="99" spans="1:18" ht="22.5">
+    <row r="99" spans="1:18" ht="22">
       <c r="A99" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A99" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E99),
@@ -29999,7 +29956,7 @@
       <c r="Q99" s="136"/>
       <c r="R99" s="78"/>
     </row>
-    <row r="100" spans="1:18" ht="33.75">
+    <row r="100" spans="1:18" ht="33">
       <c r="A100" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A100" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E100),
@@ -30069,7 +30026,7 @@
       <c r="Q101" s="136"/>
       <c r="R101" s="78"/>
     </row>
-    <row r="102" spans="1:18" ht="33.75">
+    <row r="102" spans="1:18" ht="33">
       <c r="A102" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A102" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E102),
@@ -30104,7 +30061,7 @@
       <c r="Q102" s="136"/>
       <c r="R102" s="78"/>
     </row>
-    <row r="103" spans="1:18" ht="33.75">
+    <row r="103" spans="1:18" ht="33">
       <c r="A103" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A103" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E103),
@@ -30139,7 +30096,7 @@
       <c r="Q103" s="136"/>
       <c r="R103" s="78"/>
     </row>
-    <row r="104" spans="1:18" ht="33.75">
+    <row r="104" spans="1:18" ht="33">
       <c r="A104" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A104" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E104),
@@ -30176,7 +30133,7 @@
       <c r="Q104" s="136"/>
       <c r="R104" s="78"/>
     </row>
-    <row r="105" spans="1:18" ht="33.75">
+    <row r="105" spans="1:18" ht="33">
       <c r="A105" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A105" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E105),
@@ -30219,7 +30176,7 @@
       <c r="Q105" s="136"/>
       <c r="R105" s="78"/>
     </row>
-    <row r="106" spans="1:18" ht="22.5">
+    <row r="106" spans="1:18" ht="22">
       <c r="A106" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A106" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E106),
@@ -30260,7 +30217,7 @@
       <c r="Q106" s="136"/>
       <c r="R106" s="78"/>
     </row>
-    <row r="107" spans="1:18" ht="22.5">
+    <row r="107" spans="1:18" ht="22">
       <c r="A107" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A107" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E107),
@@ -30295,7 +30252,7 @@
       <c r="Q107" s="136"/>
       <c r="R107" s="78"/>
     </row>
-    <row r="108" spans="1:18" ht="22.5">
+    <row r="108" spans="1:18" ht="22">
       <c r="A108" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A108" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E108),
@@ -30336,7 +30293,7 @@
       <c r="Q108" s="136"/>
       <c r="R108" s="78"/>
     </row>
-    <row r="109" spans="1:18" ht="22.5">
+    <row r="109" spans="1:18" ht="22">
       <c r="A109" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A109" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E109),
@@ -30377,7 +30334,7 @@
       <c r="Q109" s="136"/>
       <c r="R109" s="78"/>
     </row>
-    <row r="110" spans="1:18" ht="22.5">
+    <row r="110" spans="1:18" ht="22">
       <c r="A110" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A110" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E110),
@@ -30412,7 +30369,7 @@
       <c r="Q110" s="136"/>
       <c r="R110" s="78"/>
     </row>
-    <row r="111" spans="1:18" ht="33.75">
+    <row r="111" spans="1:18" ht="33">
       <c r="A111" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A111" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E111),
@@ -30455,7 +30412,7 @@
       <c r="Q111" s="136"/>
       <c r="R111" s="78"/>
     </row>
-    <row r="112" spans="1:18" ht="22.5">
+    <row r="112" spans="1:18" ht="22">
       <c r="A112" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A112" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E112),
@@ -30492,7 +30449,7 @@
       <c r="Q112" s="136"/>
       <c r="R112" s="78"/>
     </row>
-    <row r="113" spans="1:18" ht="33.75">
+    <row r="113" spans="1:18" ht="33">
       <c r="A113" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A113" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E113),
@@ -30527,7 +30484,7 @@
       <c r="Q113" s="136"/>
       <c r="R113" s="78"/>
     </row>
-    <row r="114" spans="1:18" ht="33.75">
+    <row r="114" spans="1:18" ht="33">
       <c r="A114" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A114" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E114),
@@ -30562,7 +30519,7 @@
       <c r="Q114" s="136"/>
       <c r="R114" s="78"/>
     </row>
-    <row r="115" spans="1:18" ht="56.25">
+    <row r="115" spans="1:18" ht="55">
       <c r="A115" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A115" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E115),
@@ -30592,10 +30549,10 @@
         <v>557</v>
       </c>
       <c r="J115" s="110" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="K115" s="110" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="L115" s="111" t="s">
         <v>53</v>
@@ -30609,7 +30566,7 @@
       <c r="Q115" s="112"/>
       <c r="R115" s="110"/>
     </row>
-    <row r="116" spans="1:18" ht="22.5">
+    <row r="116" spans="1:18" ht="22">
       <c r="A116" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A116" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E116),
@@ -30644,7 +30601,7 @@
       <c r="Q116" s="136"/>
       <c r="R116" s="78"/>
     </row>
-    <row r="117" spans="1:18" ht="22.5">
+    <row r="117" spans="1:18" ht="22">
       <c r="A117" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A117" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E117),
@@ -30679,7 +30636,7 @@
       <c r="Q117" s="136"/>
       <c r="R117" s="78"/>
     </row>
-    <row r="118" spans="1:18" ht="22.5">
+    <row r="118" spans="1:18" ht="22">
       <c r="A118" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A118" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E118),
@@ -30714,7 +30671,7 @@
       <c r="Q118" s="136"/>
       <c r="R118" s="78"/>
     </row>
-    <row r="119" spans="1:18" ht="33.75">
+    <row r="119" spans="1:18" ht="33">
       <c r="A119" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A119" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E119),
@@ -30749,7 +30706,7 @@
       <c r="Q119" s="136"/>
       <c r="R119" s="78"/>
     </row>
-    <row r="120" spans="1:18" ht="67.5">
+    <row r="120" spans="1:18" ht="66">
       <c r="A120" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A120" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E120),
@@ -30779,7 +30736,7 @@
         <v>557</v>
       </c>
       <c r="J120" s="110" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="K120" s="110" t="s">
         <v>32</v>
@@ -30796,7 +30753,7 @@
       <c r="Q120" s="112"/>
       <c r="R120" s="110"/>
     </row>
-    <row r="121" spans="1:18" ht="56.25">
+    <row r="121" spans="1:18" ht="55">
       <c r="A121" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A121" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E121),
@@ -30824,7 +30781,7 @@
         <v>557</v>
       </c>
       <c r="J121" s="110" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="K121" s="110" t="s">
         <v>31</v>
@@ -30841,7 +30798,7 @@
       <c r="Q121" s="112"/>
       <c r="R121" s="110"/>
     </row>
-    <row r="122" spans="1:18" ht="45">
+    <row r="122" spans="1:18" ht="44">
       <c r="A122" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A122" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E122),
@@ -30869,7 +30826,7 @@
         <v>557</v>
       </c>
       <c r="J122" s="110" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="K122" s="110" t="s">
         <v>33</v>
@@ -30886,7 +30843,7 @@
       <c r="Q122" s="112"/>
       <c r="R122" s="110"/>
     </row>
-    <row r="123" spans="1:18" ht="56.25">
+    <row r="123" spans="1:18" ht="55">
       <c r="A123" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A123" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E123),
@@ -30914,7 +30871,7 @@
         <v>557</v>
       </c>
       <c r="J123" s="110" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="K123" s="110" t="s">
         <v>31</v>
@@ -30931,7 +30888,7 @@
       <c r="Q123" s="112"/>
       <c r="R123" s="110"/>
     </row>
-    <row r="124" spans="1:18" ht="67.5">
+    <row r="124" spans="1:18" ht="66">
       <c r="A124" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A124" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E124),
@@ -30959,7 +30916,7 @@
         <v>557</v>
       </c>
       <c r="J124" s="110" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="K124" s="110" t="s">
         <v>32</v>
@@ -30976,7 +30933,7 @@
       <c r="Q124" s="112"/>
       <c r="R124" s="110"/>
     </row>
-    <row r="125" spans="1:18" ht="33.75">
+    <row r="125" spans="1:18" ht="33">
       <c r="A125" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A125" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E125),
@@ -31013,7 +30970,7 @@
       <c r="Q125" s="136"/>
       <c r="R125" s="78"/>
     </row>
-    <row r="126" spans="1:18" ht="33.75">
+    <row r="126" spans="1:18" ht="33">
       <c r="A126" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A126" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E126),
@@ -31052,7 +31009,7 @@
       <c r="Q126" s="136"/>
       <c r="R126" s="78"/>
     </row>
-    <row r="127" spans="1:18" ht="78.75">
+    <row r="127" spans="1:18" ht="77">
       <c r="A127" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A127" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E127),
@@ -31086,7 +31043,7 @@
         <v>557</v>
       </c>
       <c r="J127" s="110" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K127" s="110" t="s">
         <v>44</v>
@@ -31103,7 +31060,7 @@
       <c r="Q127" s="112"/>
       <c r="R127" s="110"/>
     </row>
-    <row r="128" spans="1:18" ht="78.75">
+    <row r="128" spans="1:18" ht="77">
       <c r="A128" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A128" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E128),
@@ -31129,7 +31086,7 @@
         <v>557</v>
       </c>
       <c r="J128" s="110" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="K128" s="110" t="s">
         <v>44</v>
@@ -31146,7 +31103,7 @@
       <c r="Q128" s="112"/>
       <c r="R128" s="110"/>
     </row>
-    <row r="129" spans="1:18" ht="101.25">
+    <row r="129" spans="1:18" ht="99">
       <c r="A129" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A129" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E129),
@@ -31172,7 +31129,7 @@
         <v>557</v>
       </c>
       <c r="J129" s="110" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K129" s="110" t="s">
         <v>45</v>
@@ -31189,7 +31146,7 @@
       <c r="Q129" s="112"/>
       <c r="R129" s="110"/>
     </row>
-    <row r="130" spans="1:18" ht="101.25">
+    <row r="130" spans="1:18" ht="99">
       <c r="A130" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A130" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E130),
@@ -31215,7 +31172,7 @@
         <v>557</v>
       </c>
       <c r="J130" s="110" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="K130" s="110" t="s">
         <v>45</v>
@@ -31232,7 +31189,7 @@
       <c r="Q130" s="112"/>
       <c r="R130" s="110"/>
     </row>
-    <row r="131" spans="1:18" ht="101.25">
+    <row r="131" spans="1:18" ht="99">
       <c r="A131" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A131" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E131),
@@ -31258,7 +31215,7 @@
         <v>557</v>
       </c>
       <c r="J131" s="110" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="K131" s="110" t="s">
         <v>46</v>
@@ -31275,7 +31232,7 @@
       <c r="Q131" s="112"/>
       <c r="R131" s="110"/>
     </row>
-    <row r="132" spans="1:18" ht="101.25">
+    <row r="132" spans="1:18" ht="99">
       <c r="A132" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A132" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E132),
@@ -31301,7 +31258,7 @@
         <v>557</v>
       </c>
       <c r="J132" s="110" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="K132" s="110" t="s">
         <v>47</v>
@@ -31318,7 +31275,7 @@
       <c r="Q132" s="112"/>
       <c r="R132" s="110"/>
     </row>
-    <row r="133" spans="1:18" ht="101.25">
+    <row r="133" spans="1:18" ht="99">
       <c r="A133" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A133" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E133),
@@ -31344,7 +31301,7 @@
         <v>557</v>
       </c>
       <c r="J133" s="110" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="K133" s="110" t="s">
         <v>48</v>
@@ -31361,7 +31318,7 @@
       <c r="Q133" s="112"/>
       <c r="R133" s="110"/>
     </row>
-    <row r="134" spans="1:18" ht="101.25">
+    <row r="134" spans="1:18" ht="99">
       <c r="A134" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A134" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E134),
@@ -31387,7 +31344,7 @@
         <v>557</v>
       </c>
       <c r="J134" s="110" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="K134" s="110" t="s">
         <v>48</v>
@@ -31404,7 +31361,7 @@
       <c r="Q134" s="112"/>
       <c r="R134" s="110"/>
     </row>
-    <row r="135" spans="1:18" ht="33.75">
+    <row r="135" spans="1:18" ht="33">
       <c r="A135" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A135" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E135),
@@ -31441,7 +31398,7 @@
       <c r="Q135" s="136"/>
       <c r="R135" s="78"/>
     </row>
-    <row r="136" spans="1:18" ht="22.5">
+    <row r="136" spans="1:18" ht="22">
       <c r="A136" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A136" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E136),
@@ -31476,7 +31433,7 @@
       <c r="Q136" s="136"/>
       <c r="R136" s="78"/>
     </row>
-    <row r="137" spans="1:18" ht="45">
+    <row r="137" spans="1:18" ht="44">
       <c r="A137" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A137" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E137),
@@ -31511,7 +31468,7 @@
       <c r="Q137" s="136"/>
       <c r="R137" s="78"/>
     </row>
-    <row r="138" spans="1:18" ht="22.5">
+    <row r="138" spans="1:18" ht="22">
       <c r="A138" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A138" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E138),
@@ -31554,7 +31511,7 @@
       <c r="Q138" s="136"/>
       <c r="R138" s="78"/>
     </row>
-    <row r="139" spans="1:18" ht="22.5">
+    <row r="139" spans="1:18" ht="22">
       <c r="A139" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A139" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E139),
@@ -31591,7 +31548,7 @@
       <c r="Q139" s="136"/>
       <c r="R139" s="78"/>
     </row>
-    <row r="140" spans="1:18" ht="33.75">
+    <row r="140" spans="1:18" ht="33">
       <c r="A140" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A140" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E140),
@@ -31626,7 +31583,7 @@
       <c r="Q140" s="136"/>
       <c r="R140" s="78"/>
     </row>
-    <row r="141" spans="1:18" ht="22.5">
+    <row r="141" spans="1:18" ht="22">
       <c r="A141" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A141" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E141),
@@ -31661,7 +31618,7 @@
       <c r="Q141" s="136"/>
       <c r="R141" s="78"/>
     </row>
-    <row r="142" spans="1:18" ht="22.5">
+    <row r="142" spans="1:18" ht="22">
       <c r="A142" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A142" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E142),
@@ -31698,7 +31655,7 @@
       <c r="Q142" s="136"/>
       <c r="R142" s="78"/>
     </row>
-    <row r="143" spans="1:18" ht="33.75">
+    <row r="143" spans="1:18" ht="33">
       <c r="A143" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A143" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E143),
@@ -31733,7 +31690,7 @@
       <c r="Q143" s="136"/>
       <c r="R143" s="78"/>
     </row>
-    <row r="144" spans="1:18" ht="33.75">
+    <row r="144" spans="1:18" ht="33">
       <c r="A144" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A144" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E144),
@@ -31772,7 +31729,7 @@
       <c r="Q144" s="136"/>
       <c r="R144" s="78"/>
     </row>
-    <row r="145" spans="1:18" ht="33.75">
+    <row r="145" spans="1:18" ht="33">
       <c r="A145" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A145" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E145),
@@ -31813,7 +31770,7 @@
       <c r="Q145" s="136"/>
       <c r="R145" s="78"/>
     </row>
-    <row r="146" spans="1:18" ht="33.75">
+    <row r="146" spans="1:18" ht="33">
       <c r="A146" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A146" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E146),
@@ -31850,7 +31807,7 @@
       <c r="Q146" s="136"/>
       <c r="R146" s="78"/>
     </row>
-    <row r="147" spans="1:18" ht="33.75">
+    <row r="147" spans="1:18" ht="33">
       <c r="A147" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A147" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E147),
@@ -31887,7 +31844,7 @@
       <c r="Q147" s="136"/>
       <c r="R147" s="78"/>
     </row>
-    <row r="148" spans="1:18" ht="33.75">
+    <row r="148" spans="1:18" ht="33">
       <c r="A148" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A148" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E148),
@@ -31924,7 +31881,7 @@
       <c r="Q148" s="136"/>
       <c r="R148" s="78"/>
     </row>
-    <row r="149" spans="1:18" ht="33.75">
+    <row r="149" spans="1:18" ht="33">
       <c r="A149" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A149" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E149),
@@ -31961,7 +31918,7 @@
       <c r="Q149" s="136"/>
       <c r="R149" s="78"/>
     </row>
-    <row r="150" spans="1:18" ht="22.5">
+    <row r="150" spans="1:18" ht="22">
       <c r="A150" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A150" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E150),
@@ -31998,7 +31955,7 @@
       <c r="Q150" s="136"/>
       <c r="R150" s="78"/>
     </row>
-    <row r="151" spans="1:18" ht="22.5">
+    <row r="151" spans="1:18" ht="22">
       <c r="A151" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A151" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E151),
@@ -32033,7 +31990,7 @@
       <c r="Q151" s="136"/>
       <c r="R151" s="78"/>
     </row>
-    <row r="152" spans="1:18" ht="22.5">
+    <row r="152" spans="1:18" ht="22">
       <c r="A152" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A152" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E152),
@@ -32068,7 +32025,7 @@
       <c r="Q152" s="136"/>
       <c r="R152" s="78"/>
     </row>
-    <row r="153" spans="1:18" ht="22.5">
+    <row r="153" spans="1:18" ht="22">
       <c r="A153" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A153" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E153),
@@ -32103,7 +32060,7 @@
       <c r="Q153" s="136"/>
       <c r="R153" s="78"/>
     </row>
-    <row r="154" spans="1:18" ht="22.5">
+    <row r="154" spans="1:18" ht="22">
       <c r="A154" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A154" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E154),
@@ -32138,7 +32095,7 @@
       <c r="Q154" s="136"/>
       <c r="R154" s="78"/>
     </row>
-    <row r="155" spans="1:18" ht="22.5">
+    <row r="155" spans="1:18" ht="22">
       <c r="A155" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A155" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E155),
@@ -32173,7 +32130,7 @@
       <c r="Q155" s="136"/>
       <c r="R155" s="78"/>
     </row>
-    <row r="156" spans="1:18" ht="22.5">
+    <row r="156" spans="1:18" ht="22">
       <c r="A156" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A156" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E156),
@@ -32212,7 +32169,7 @@
       <c r="Q156" s="136"/>
       <c r="R156" s="78"/>
     </row>
-    <row r="157" spans="1:18" ht="22.5">
+    <row r="157" spans="1:18" ht="22">
       <c r="A157" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A157" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E157),
@@ -32247,7 +32204,7 @@
       <c r="Q157" s="136"/>
       <c r="R157" s="78"/>
     </row>
-    <row r="158" spans="1:18" ht="33.75">
+    <row r="158" spans="1:18" ht="33">
       <c r="A158" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A158" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E158),
@@ -32284,7 +32241,7 @@
       <c r="Q158" s="136"/>
       <c r="R158" s="78"/>
     </row>
-    <row r="159" spans="1:18" ht="33.75">
+    <row r="159" spans="1:18" ht="33">
       <c r="A159" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A159" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E159),
@@ -32319,7 +32276,7 @@
       <c r="Q159" s="136"/>
       <c r="R159" s="78"/>
     </row>
-    <row r="160" spans="1:18" ht="45">
+    <row r="160" spans="1:18" ht="44">
       <c r="A160" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A160" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E160),
@@ -32354,7 +32311,7 @@
       <c r="Q160" s="136"/>
       <c r="R160" s="78"/>
     </row>
-    <row r="161" spans="1:18" ht="33.75">
+    <row r="161" spans="1:18" ht="33">
       <c r="A161" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A161" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E161),
@@ -32389,7 +32346,7 @@
       <c r="Q161" s="136"/>
       <c r="R161" s="78"/>
     </row>
-    <row r="162" spans="1:18" ht="33.75">
+    <row r="162" spans="1:18" ht="33">
       <c r="A162" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A162" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E162),
@@ -32424,7 +32381,7 @@
       <c r="Q162" s="136"/>
       <c r="R162" s="78"/>
     </row>
-    <row r="163" spans="1:18" ht="22.5">
+    <row r="163" spans="1:18" ht="22">
       <c r="A163" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A163" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E163),
@@ -32459,7 +32416,7 @@
       <c r="Q163" s="136"/>
       <c r="R163" s="78"/>
     </row>
-    <row r="164" spans="1:18" ht="22.5">
+    <row r="164" spans="1:18" ht="22">
       <c r="A164" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A164" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E164),
@@ -32494,7 +32451,7 @@
       <c r="Q164" s="136"/>
       <c r="R164" s="78"/>
     </row>
-    <row r="165" spans="1:18" ht="33.75">
+    <row r="165" spans="1:18" ht="33">
       <c r="A165" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A165" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E165),
@@ -32529,7 +32486,7 @@
       <c r="Q165" s="136"/>
       <c r="R165" s="78"/>
     </row>
-    <row r="166" spans="1:18" ht="33.75">
+    <row r="166" spans="1:18" ht="33">
       <c r="A166" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A166" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E166),
@@ -32564,7 +32521,7 @@
       <c r="Q166" s="136"/>
       <c r="R166" s="78"/>
     </row>
-    <row r="167" spans="1:18" ht="45">
+    <row r="167" spans="1:18" ht="44">
       <c r="A167" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A167" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E167),
@@ -32599,7 +32556,7 @@
       <c r="Q167" s="136"/>
       <c r="R167" s="78"/>
     </row>
-    <row r="168" spans="1:18" ht="33.75">
+    <row r="168" spans="1:18" ht="33">
       <c r="A168" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A168" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E168),
@@ -32634,7 +32591,7 @@
       <c r="Q168" s="136"/>
       <c r="R168" s="78"/>
     </row>
-    <row r="169" spans="1:18" ht="22.5">
+    <row r="169" spans="1:18" ht="22">
       <c r="A169" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A169" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E169),
@@ -32671,7 +32628,7 @@
       <c r="Q169" s="136"/>
       <c r="R169" s="78"/>
     </row>
-    <row r="170" spans="1:18" ht="22.5">
+    <row r="170" spans="1:18" ht="22">
       <c r="A170" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A170" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E170),
@@ -32706,7 +32663,7 @@
       <c r="Q170" s="136"/>
       <c r="R170" s="78"/>
     </row>
-    <row r="171" spans="1:18" ht="33.75">
+    <row r="171" spans="1:18" ht="33">
       <c r="A171" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A171" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E171),
@@ -32741,7 +32698,7 @@
       <c r="Q171" s="136"/>
       <c r="R171" s="78"/>
     </row>
-    <row r="172" spans="1:18" ht="22.5">
+    <row r="172" spans="1:18" ht="22">
       <c r="A172" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A172" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E172),
@@ -32776,7 +32733,7 @@
       <c r="Q172" s="136"/>
       <c r="R172" s="78"/>
     </row>
-    <row r="173" spans="1:18" ht="22.5">
+    <row r="173" spans="1:18" ht="22">
       <c r="A173" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A173" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E173),
@@ -32811,7 +32768,7 @@
       <c r="Q173" s="136"/>
       <c r="R173" s="78"/>
     </row>
-    <row r="174" spans="1:18" ht="33.75">
+    <row r="174" spans="1:18" ht="33">
       <c r="A174" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A174" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E174),
@@ -32846,7 +32803,7 @@
       <c r="Q174" s="136"/>
       <c r="R174" s="78"/>
     </row>
-    <row r="175" spans="1:18" ht="22.5">
+    <row r="175" spans="1:18" ht="22">
       <c r="A175" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A175" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E175),
@@ -32881,7 +32838,7 @@
       <c r="Q175" s="136"/>
       <c r="R175" s="78"/>
     </row>
-    <row r="176" spans="1:18" ht="22.5">
+    <row r="176" spans="1:18" ht="22">
       <c r="A176" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A176" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E176),
@@ -32918,7 +32875,7 @@
       <c r="Q176" s="136"/>
       <c r="R176" s="78"/>
     </row>
-    <row r="177" spans="1:18" ht="33.75">
+    <row r="177" spans="1:18" ht="33">
       <c r="A177" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A177" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E177),
@@ -32953,7 +32910,7 @@
       <c r="Q177" s="136"/>
       <c r="R177" s="78"/>
     </row>
-    <row r="178" spans="1:18" ht="33.75">
+    <row r="178" spans="1:18" ht="33">
       <c r="A178" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A178" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E178),
@@ -32988,7 +32945,7 @@
       <c r="Q178" s="136"/>
       <c r="R178" s="78"/>
     </row>
-    <row r="179" spans="1:18" ht="45">
+    <row r="179" spans="1:18" ht="44">
       <c r="A179" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A179" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E179),
@@ -33023,7 +32980,7 @@
       <c r="Q179" s="136"/>
       <c r="R179" s="78"/>
     </row>
-    <row r="180" spans="1:18" ht="45">
+    <row r="180" spans="1:18" ht="44">
       <c r="A180" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A180" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E180),
@@ -33058,7 +33015,7 @@
       <c r="Q180" s="136"/>
       <c r="R180" s="78"/>
     </row>
-    <row r="181" spans="1:18" ht="33.75">
+    <row r="181" spans="1:18" ht="33">
       <c r="A181" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A181" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E181),
@@ -33093,7 +33050,7 @@
       <c r="Q181" s="136"/>
       <c r="R181" s="78"/>
     </row>
-    <row r="182" spans="1:18" ht="45">
+    <row r="182" spans="1:18" ht="44">
       <c r="A182" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A182" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E182),
@@ -33128,7 +33085,7 @@
       <c r="Q182" s="136"/>
       <c r="R182" s="78"/>
     </row>
-    <row r="183" spans="1:18" ht="45">
+    <row r="183" spans="1:18" ht="44">
       <c r="A183" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A183" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E183),
@@ -33163,7 +33120,7 @@
       <c r="Q183" s="136"/>
       <c r="R183" s="78"/>
     </row>
-    <row r="184" spans="1:18" ht="22.5">
+    <row r="184" spans="1:18" ht="22">
       <c r="A184" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A184" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E184),
@@ -33198,7 +33155,7 @@
       <c r="Q184" s="136"/>
       <c r="R184" s="78"/>
     </row>
-    <row r="185" spans="1:18" ht="33.75">
+    <row r="185" spans="1:18" ht="33">
       <c r="A185" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A185" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E185),
@@ -33235,7 +33192,7 @@
       <c r="Q185" s="136"/>
       <c r="R185" s="78"/>
     </row>
-    <row r="186" spans="1:18" ht="22.5">
+    <row r="186" spans="1:18" ht="22">
       <c r="A186" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A186" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E186),
@@ -33272,7 +33229,7 @@
       <c r="Q186" s="136"/>
       <c r="R186" s="78"/>
     </row>
-    <row r="187" spans="1:18" ht="22.5">
+    <row r="187" spans="1:18" ht="22">
       <c r="A187" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A187" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E187),
@@ -33315,7 +33272,7 @@
       <c r="Q187" s="136"/>
       <c r="R187" s="78"/>
     </row>
-    <row r="188" spans="1:18" ht="22.5">
+    <row r="188" spans="1:18" ht="22">
       <c r="A188" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A188" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E188),
@@ -33393,7 +33350,7 @@
       <c r="Q189" s="136"/>
       <c r="R189" s="78"/>
     </row>
-    <row r="190" spans="1:18" ht="22.5">
+    <row r="190" spans="1:18" ht="22">
       <c r="A190" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A190" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E190),
@@ -33436,7 +33393,7 @@
       <c r="Q190" s="136"/>
       <c r="R190" s="78"/>
     </row>
-    <row r="191" spans="1:18" ht="22.5">
+    <row r="191" spans="1:18" ht="22">
       <c r="A191" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A191" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E191),
@@ -33473,7 +33430,7 @@
       <c r="Q191" s="136"/>
       <c r="R191" s="78"/>
     </row>
-    <row r="192" spans="1:18" ht="22.5">
+    <row r="192" spans="1:18" ht="22">
       <c r="A192" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A192" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E192),
@@ -33508,7 +33465,7 @@
       <c r="Q192" s="136"/>
       <c r="R192" s="78"/>
     </row>
-    <row r="193" spans="1:18" ht="33.75">
+    <row r="193" spans="1:18" ht="33">
       <c r="A193" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A193" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E193),
@@ -33545,7 +33502,7 @@
       <c r="Q193" s="136"/>
       <c r="R193" s="78"/>
     </row>
-    <row r="194" spans="1:18" ht="33.75">
+    <row r="194" spans="1:18" ht="33">
       <c r="A194" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A194" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E194),
@@ -33580,7 +33537,7 @@
       <c r="Q194" s="136"/>
       <c r="R194" s="78"/>
     </row>
-    <row r="195" spans="1:18" ht="33.75">
+    <row r="195" spans="1:18" ht="33">
       <c r="A195" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A195" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E195),
@@ -33619,7 +33576,7 @@
       <c r="Q195" s="136"/>
       <c r="R195" s="78"/>
     </row>
-    <row r="196" spans="1:18" ht="22.5">
+    <row r="196" spans="1:18" ht="22">
       <c r="A196" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A196" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E196),
@@ -33660,7 +33617,7 @@
       <c r="Q196" s="136"/>
       <c r="R196" s="78"/>
     </row>
-    <row r="197" spans="1:18" ht="22.5">
+    <row r="197" spans="1:18" ht="22">
       <c r="A197" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A197" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E197),
@@ -33695,7 +33652,7 @@
       <c r="Q197" s="136"/>
       <c r="R197" s="78"/>
     </row>
-    <row r="198" spans="1:18" ht="22.5">
+    <row r="198" spans="1:18" ht="22">
       <c r="A198" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A198" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E198),
@@ -33730,7 +33687,7 @@
       <c r="Q198" s="136"/>
       <c r="R198" s="78"/>
     </row>
-    <row r="199" spans="1:18" ht="22.5">
+    <row r="199" spans="1:18" ht="22">
       <c r="A199" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A199" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E199),
@@ -33765,7 +33722,7 @@
       <c r="Q199" s="136"/>
       <c r="R199" s="78"/>
     </row>
-    <row r="200" spans="1:18" ht="22.5">
+    <row r="200" spans="1:18" ht="22">
       <c r="A200" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A200" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E200),
@@ -33800,7 +33757,7 @@
       <c r="Q200" s="136"/>
       <c r="R200" s="78"/>
     </row>
-    <row r="201" spans="1:18" ht="22.5">
+    <row r="201" spans="1:18" ht="22">
       <c r="A201" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A201" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E201),
@@ -33835,7 +33792,7 @@
       <c r="Q201" s="136"/>
       <c r="R201" s="78"/>
     </row>
-    <row r="202" spans="1:18" ht="22.5">
+    <row r="202" spans="1:18" ht="22">
       <c r="A202" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A202" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E202),
@@ -33870,7 +33827,7 @@
       <c r="Q202" s="136"/>
       <c r="R202" s="78"/>
     </row>
-    <row r="203" spans="1:18" ht="22.5">
+    <row r="203" spans="1:18" ht="22">
       <c r="A203" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A203" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E203),
@@ -33907,7 +33864,7 @@
       <c r="Q203" s="136"/>
       <c r="R203" s="78"/>
     </row>
-    <row r="204" spans="1:18" ht="22.5">
+    <row r="204" spans="1:18" ht="22">
       <c r="A204" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A204" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E204),
@@ -33946,7 +33903,7 @@
       <c r="Q204" s="136"/>
       <c r="R204" s="78"/>
     </row>
-    <row r="205" spans="1:18" ht="22.5">
+    <row r="205" spans="1:18" ht="22">
       <c r="A205" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A205" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E205),
@@ -33981,7 +33938,7 @@
       <c r="Q205" s="136"/>
       <c r="R205" s="78"/>
     </row>
-    <row r="206" spans="1:18" ht="22.5">
+    <row r="206" spans="1:18" ht="22">
       <c r="A206" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A206" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E206),
@@ -34016,7 +33973,7 @@
       <c r="Q206" s="136"/>
       <c r="R206" s="78"/>
     </row>
-    <row r="207" spans="1:18" ht="22.5">
+    <row r="207" spans="1:18" ht="22">
       <c r="A207" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A207" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E207),
@@ -34051,7 +34008,7 @@
       <c r="Q207" s="136"/>
       <c r="R207" s="78"/>
     </row>
-    <row r="208" spans="1:18" ht="33.75">
+    <row r="208" spans="1:18" ht="33">
       <c r="A208" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A208" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E208),
@@ -34086,7 +34043,7 @@
       <c r="Q208" s="136"/>
       <c r="R208" s="78"/>
     </row>
-    <row r="209" spans="1:18" ht="45">
+    <row r="209" spans="1:18" ht="44">
       <c r="A209" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A209" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E209),
@@ -34121,7 +34078,7 @@
       <c r="Q209" s="136"/>
       <c r="R209" s="78"/>
     </row>
-    <row r="210" spans="1:18" ht="45">
+    <row r="210" spans="1:18" ht="44">
       <c r="A210" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A210" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E210),
@@ -34156,7 +34113,7 @@
       <c r="Q210" s="136"/>
       <c r="R210" s="78"/>
     </row>
-    <row r="211" spans="1:18" ht="45">
+    <row r="211" spans="1:18" ht="44">
       <c r="A211" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A211" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E211),
@@ -34191,7 +34148,7 @@
       <c r="Q211" s="136"/>
       <c r="R211" s="78"/>
     </row>
-    <row r="212" spans="1:18" ht="33.75">
+    <row r="212" spans="1:18" ht="33">
       <c r="A212" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A212" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E212),
@@ -34226,7 +34183,7 @@
       <c r="Q212" s="136"/>
       <c r="R212" s="78"/>
     </row>
-    <row r="213" spans="1:18" ht="22.5">
+    <row r="213" spans="1:18" ht="22">
       <c r="A213" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A213" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E213),
@@ -34261,7 +34218,7 @@
       <c r="Q213" s="136"/>
       <c r="R213" s="78"/>
     </row>
-    <row r="214" spans="1:18" ht="22.5">
+    <row r="214" spans="1:18" ht="22">
       <c r="A214" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A214" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E214),
@@ -34296,7 +34253,7 @@
       <c r="Q214" s="136"/>
       <c r="R214" s="78"/>
     </row>
-    <row r="215" spans="1:18" ht="33.75">
+    <row r="215" spans="1:18" ht="33">
       <c r="A215" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A215" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E215),
@@ -34331,7 +34288,7 @@
       <c r="Q215" s="136"/>
       <c r="R215" s="78"/>
     </row>
-    <row r="216" spans="1:18" ht="22.5">
+    <row r="216" spans="1:18" ht="22">
       <c r="A216" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A216" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E216),
@@ -34366,7 +34323,7 @@
       <c r="Q216" s="136"/>
       <c r="R216" s="78"/>
     </row>
-    <row r="217" spans="1:18" ht="22.5">
+    <row r="217" spans="1:18" ht="22">
       <c r="A217" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A217" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E217),
@@ -34405,7 +34362,7 @@
       <c r="Q217" s="136"/>
       <c r="R217" s="78"/>
     </row>
-    <row r="218" spans="1:18" ht="22.5">
+    <row r="218" spans="1:18" ht="22">
       <c r="A218" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A218" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E218),
@@ -34440,7 +34397,7 @@
       <c r="Q218" s="136"/>
       <c r="R218" s="78"/>
     </row>
-    <row r="219" spans="1:18" ht="22.5">
+    <row r="219" spans="1:18" ht="22">
       <c r="A219" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A219" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E219),
@@ -34475,7 +34432,7 @@
       <c r="Q219" s="136"/>
       <c r="R219" s="78"/>
     </row>
-    <row r="220" spans="1:18" ht="22.5">
+    <row r="220" spans="1:18" ht="22">
       <c r="A220" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A220" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E220),
@@ -34510,7 +34467,7 @@
       <c r="Q220" s="136"/>
       <c r="R220" s="78"/>
     </row>
-    <row r="221" spans="1:18" ht="22.5">
+    <row r="221" spans="1:18" ht="22">
       <c r="A221" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A221" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E221),
@@ -34545,7 +34502,7 @@
       <c r="Q221" s="136"/>
       <c r="R221" s="78"/>
     </row>
-    <row r="222" spans="1:18" ht="45">
+    <row r="222" spans="1:18" ht="44">
       <c r="A222" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A222" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E222),
@@ -34580,7 +34537,7 @@
       <c r="Q222" s="136"/>
       <c r="R222" s="78"/>
     </row>
-    <row r="223" spans="1:18" ht="33.75">
+    <row r="223" spans="1:18" ht="33">
       <c r="A223" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A223" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E223),
@@ -34615,7 +34572,7 @@
       <c r="Q223" s="136"/>
       <c r="R223" s="78"/>
     </row>
-    <row r="224" spans="1:18" ht="45">
+    <row r="224" spans="1:18" ht="44">
       <c r="A224" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A224" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E224),
@@ -34650,7 +34607,7 @@
       <c r="Q224" s="136"/>
       <c r="R224" s="78"/>
     </row>
-    <row r="225" spans="1:18" ht="45">
+    <row r="225" spans="1:18" ht="44">
       <c r="A225" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A225" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E225),
@@ -34685,7 +34642,7 @@
       <c r="Q225" s="136"/>
       <c r="R225" s="78"/>
     </row>
-    <row r="226" spans="1:18" ht="45">
+    <row r="226" spans="1:18" ht="44">
       <c r="A226" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A226" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E226),
@@ -34720,7 +34677,7 @@
       <c r="Q226" s="136"/>
       <c r="R226" s="78"/>
     </row>
-    <row r="227" spans="1:18" ht="33.75">
+    <row r="227" spans="1:18" ht="33">
       <c r="A227" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A227" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E227),
@@ -34755,7 +34712,7 @@
       <c r="Q227" s="136"/>
       <c r="R227" s="78"/>
     </row>
-    <row r="228" spans="1:18" ht="22.5">
+    <row r="228" spans="1:18" ht="22">
       <c r="A228" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A228" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E228),
@@ -34790,7 +34747,7 @@
       <c r="Q228" s="136"/>
       <c r="R228" s="78"/>
     </row>
-    <row r="229" spans="1:18" ht="22.5">
+    <row r="229" spans="1:18" ht="22">
       <c r="A229" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A229" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E229),
@@ -34825,7 +34782,7 @@
       <c r="Q229" s="136"/>
       <c r="R229" s="78"/>
     </row>
-    <row r="230" spans="1:18" ht="33.75">
+    <row r="230" spans="1:18" ht="33">
       <c r="A230" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A230" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E230),
@@ -34860,7 +34817,7 @@
       <c r="Q230" s="136"/>
       <c r="R230" s="78"/>
     </row>
-    <row r="231" spans="1:18" ht="22.5">
+    <row r="231" spans="1:18" ht="22">
       <c r="A231" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A231" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E231),
@@ -34895,7 +34852,7 @@
       <c r="Q231" s="136"/>
       <c r="R231" s="78"/>
     </row>
-    <row r="232" spans="1:18" ht="45">
+    <row r="232" spans="1:18" ht="44">
       <c r="A232" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A232" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E232),
@@ -34932,7 +34889,7 @@
       <c r="Q232" s="136"/>
       <c r="R232" s="78"/>
     </row>
-    <row r="233" spans="1:18" ht="45">
+    <row r="233" spans="1:18" ht="44">
       <c r="A233" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A233" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E233),
@@ -34967,7 +34924,7 @@
       <c r="Q233" s="136"/>
       <c r="R233" s="78"/>
     </row>
-    <row r="234" spans="1:18" ht="45">
+    <row r="234" spans="1:18" ht="44">
       <c r="A234" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A234" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E234),
@@ -35002,7 +34959,7 @@
       <c r="Q234" s="136"/>
       <c r="R234" s="78"/>
     </row>
-    <row r="235" spans="1:18" ht="45">
+    <row r="235" spans="1:18" ht="44">
       <c r="A235" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A235" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E235),
@@ -35039,7 +34996,7 @@
       <c r="Q235" s="136"/>
       <c r="R235" s="78"/>
     </row>
-    <row r="236" spans="1:18" ht="22.5">
+    <row r="236" spans="1:18" ht="22">
       <c r="A236" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A236" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E236),
@@ -35076,7 +35033,7 @@
       <c r="Q236" s="136"/>
       <c r="R236" s="78"/>
     </row>
-    <row r="237" spans="1:18" ht="22.5">
+    <row r="237" spans="1:18" ht="22">
       <c r="A237" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A237" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E237),
@@ -35119,7 +35076,7 @@
       <c r="Q237" s="136"/>
       <c r="R237" s="78"/>
     </row>
-    <row r="238" spans="1:18" ht="22.5">
+    <row r="238" spans="1:18" ht="22">
       <c r="A238" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A238" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E238),
@@ -35156,7 +35113,7 @@
       <c r="Q238" s="136"/>
       <c r="R238" s="78"/>
     </row>
-    <row r="239" spans="1:18" ht="22.5">
+    <row r="239" spans="1:18" ht="22">
       <c r="A239" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A239" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E239),
@@ -35191,7 +35148,7 @@
       <c r="Q239" s="136"/>
       <c r="R239" s="78"/>
     </row>
-    <row r="240" spans="1:18" ht="22.5">
+    <row r="240" spans="1:18" ht="22">
       <c r="A240" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A240" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E240),
@@ -35226,7 +35183,7 @@
       <c r="Q240" s="136"/>
       <c r="R240" s="78"/>
     </row>
-    <row r="241" spans="1:18" ht="22.5">
+    <row r="241" spans="1:18" ht="22">
       <c r="A241" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A241" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E241),
@@ -35261,7 +35218,7 @@
       <c r="Q241" s="136"/>
       <c r="R241" s="78"/>
     </row>
-    <row r="242" spans="1:18" ht="33.75">
+    <row r="242" spans="1:18" ht="33">
       <c r="A242" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A242" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E242),
@@ -35296,7 +35253,7 @@
       <c r="Q242" s="136"/>
       <c r="R242" s="78"/>
     </row>
-    <row r="243" spans="1:18" ht="33.75">
+    <row r="243" spans="1:18" ht="33">
       <c r="A243" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A243" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E243),
@@ -35333,7 +35290,7 @@
       <c r="Q243" s="136"/>
       <c r="R243" s="78"/>
     </row>
-    <row r="244" spans="1:18" ht="33.75">
+    <row r="244" spans="1:18" ht="33">
       <c r="A244" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A244" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E244),
@@ -35368,7 +35325,7 @@
       <c r="Q244" s="136"/>
       <c r="R244" s="78"/>
     </row>
-    <row r="245" spans="1:18" ht="45">
+    <row r="245" spans="1:18" ht="44">
       <c r="A245" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A245" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E245),
@@ -35403,7 +35360,7 @@
       <c r="Q245" s="136"/>
       <c r="R245" s="78"/>
     </row>
-    <row r="246" spans="1:18" ht="45">
+    <row r="246" spans="1:18" ht="44">
       <c r="A246" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A246" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E246),
@@ -35438,7 +35395,7 @@
       <c r="Q246" s="136"/>
       <c r="R246" s="78"/>
     </row>
-    <row r="247" spans="1:18" ht="33.75">
+    <row r="247" spans="1:18" ht="33">
       <c r="A247" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A247" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E247),
@@ -35473,7 +35430,7 @@
       <c r="Q247" s="136"/>
       <c r="R247" s="78"/>
     </row>
-    <row r="248" spans="1:18" ht="33.75">
+    <row r="248" spans="1:18" ht="33">
       <c r="A248" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A248" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E248),
@@ -35510,7 +35467,7 @@
       <c r="Q248" s="136"/>
       <c r="R248" s="78"/>
     </row>
-    <row r="249" spans="1:18" ht="45">
+    <row r="249" spans="1:18" ht="44">
       <c r="A249" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A249" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E249),
@@ -35551,7 +35508,7 @@
       <c r="Q249" s="136"/>
       <c r="R249" s="78"/>
     </row>
-    <row r="250" spans="1:18" ht="33.75">
+    <row r="250" spans="1:18" ht="33">
       <c r="A250" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A250" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E250),
@@ -35594,7 +35551,7 @@
       <c r="Q250" s="136"/>
       <c r="R250" s="78"/>
     </row>
-    <row r="251" spans="1:18" ht="33.75">
+    <row r="251" spans="1:18" ht="33">
       <c r="A251" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A251" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E251),
@@ -35629,7 +35586,7 @@
       <c r="Q251" s="136"/>
       <c r="R251" s="78"/>
     </row>
-    <row r="252" spans="1:18" ht="33.75">
+    <row r="252" spans="1:18" ht="33">
       <c r="A252" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A252" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E252),
@@ -35668,7 +35625,7 @@
       <c r="Q252" s="136"/>
       <c r="R252" s="78"/>
     </row>
-    <row r="253" spans="1:18" ht="33.75">
+    <row r="253" spans="1:18" ht="33">
       <c r="A253" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A253" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E253),
@@ -35703,7 +35660,7 @@
       <c r="Q253" s="136"/>
       <c r="R253" s="78"/>
     </row>
-    <row r="254" spans="1:18" ht="33.75">
+    <row r="254" spans="1:18" ht="33">
       <c r="A254" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A254" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E254),
@@ -35744,7 +35701,7 @@
       <c r="Q254" s="136"/>
       <c r="R254" s="78"/>
     </row>
-    <row r="255" spans="1:18" ht="33.75">
+    <row r="255" spans="1:18" ht="33">
       <c r="A255" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A255" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E255),
@@ -35781,7 +35738,7 @@
       <c r="Q255" s="136"/>
       <c r="R255" s="78"/>
     </row>
-    <row r="256" spans="1:18" ht="33.75">
+    <row r="256" spans="1:18" ht="33">
       <c r="A256" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A256" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E256),
@@ -35818,7 +35775,7 @@
       <c r="Q256" s="136"/>
       <c r="R256" s="78"/>
     </row>
-    <row r="257" spans="1:18" ht="33.75">
+    <row r="257" spans="1:18" ht="33">
       <c r="A257" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A257" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E257),
@@ -35855,7 +35812,7 @@
       <c r="Q257" s="136"/>
       <c r="R257" s="78"/>
     </row>
-    <row r="258" spans="1:18" ht="22.5">
+    <row r="258" spans="1:18" ht="22">
       <c r="A258" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A258" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E258),
@@ -35894,7 +35851,7 @@
       <c r="Q258" s="136"/>
       <c r="R258" s="78"/>
     </row>
-    <row r="259" spans="1:18" ht="22.5">
+    <row r="259" spans="1:18" ht="22">
       <c r="A259" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A259" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E259),
@@ -35929,7 +35886,7 @@
       <c r="Q259" s="136"/>
       <c r="R259" s="78"/>
     </row>
-    <row r="260" spans="1:18" ht="33.75">
+    <row r="260" spans="1:18" ht="33">
       <c r="A260" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A260" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E260),
@@ -35966,7 +35923,7 @@
       <c r="Q260" s="136"/>
       <c r="R260" s="78"/>
     </row>
-    <row r="261" spans="1:18" ht="33.75">
+    <row r="261" spans="1:18" ht="33">
       <c r="A261" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A261" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E261),
@@ -36001,7 +35958,7 @@
       <c r="Q261" s="136"/>
       <c r="R261" s="78"/>
     </row>
-    <row r="262" spans="1:18" ht="45">
+    <row r="262" spans="1:18" ht="44">
       <c r="A262" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A262" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E262),
@@ -36036,7 +35993,7 @@
       <c r="Q262" s="136"/>
       <c r="R262" s="78"/>
     </row>
-    <row r="263" spans="1:18" ht="33.75">
+    <row r="263" spans="1:18" ht="33">
       <c r="A263" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A263" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E263),
@@ -36071,7 +36028,7 @@
       <c r="Q263" s="136"/>
       <c r="R263" s="78"/>
     </row>
-    <row r="264" spans="1:18" ht="33.75">
+    <row r="264" spans="1:18" ht="33">
       <c r="A264" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A264" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E264),
@@ -36106,7 +36063,7 @@
       <c r="Q264" s="136"/>
       <c r="R264" s="78"/>
     </row>
-    <row r="265" spans="1:18" ht="22.5">
+    <row r="265" spans="1:18" ht="22">
       <c r="A265" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A265" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E265),
@@ -36141,7 +36098,7 @@
       <c r="Q265" s="136"/>
       <c r="R265" s="78"/>
     </row>
-    <row r="266" spans="1:18" ht="22.5">
+    <row r="266" spans="1:18" ht="22">
       <c r="A266" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A266" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E266),
@@ -36176,7 +36133,7 @@
       <c r="Q266" s="136"/>
       <c r="R266" s="78"/>
     </row>
-    <row r="267" spans="1:18" ht="33.75">
+    <row r="267" spans="1:18" ht="33">
       <c r="A267" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A267" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E267),
@@ -36211,7 +36168,7 @@
       <c r="Q267" s="136"/>
       <c r="R267" s="78"/>
     </row>
-    <row r="268" spans="1:18" ht="33.75">
+    <row r="268" spans="1:18" ht="33">
       <c r="A268" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A268" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E268),
@@ -36246,7 +36203,7 @@
       <c r="Q268" s="136"/>
       <c r="R268" s="78"/>
     </row>
-    <row r="269" spans="1:18" ht="45">
+    <row r="269" spans="1:18" ht="44">
       <c r="A269" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A269" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E269),
@@ -36281,7 +36238,7 @@
       <c r="Q269" s="136"/>
       <c r="R269" s="78"/>
     </row>
-    <row r="270" spans="1:18" ht="33.75">
+    <row r="270" spans="1:18" ht="33">
       <c r="A270" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A270" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E270),
@@ -36316,7 +36273,7 @@
       <c r="Q270" s="136"/>
       <c r="R270" s="78"/>
     </row>
-    <row r="271" spans="1:18" ht="22.5">
+    <row r="271" spans="1:18" ht="22">
       <c r="A271" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A271" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E271),
@@ -36353,7 +36310,7 @@
       <c r="Q271" s="136"/>
       <c r="R271" s="78"/>
     </row>
-    <row r="272" spans="1:18" ht="22.5">
+    <row r="272" spans="1:18" ht="22">
       <c r="A272" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A272" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E272),
@@ -36388,7 +36345,7 @@
       <c r="Q272" s="136"/>
       <c r="R272" s="78"/>
     </row>
-    <row r="273" spans="1:18" ht="33.75">
+    <row r="273" spans="1:18" ht="33">
       <c r="A273" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A273" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E273),
@@ -36423,7 +36380,7 @@
       <c r="Q273" s="136"/>
       <c r="R273" s="78"/>
     </row>
-    <row r="274" spans="1:18" ht="22.5">
+    <row r="274" spans="1:18" ht="22">
       <c r="A274" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A274" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E274),
@@ -36458,7 +36415,7 @@
       <c r="Q274" s="136"/>
       <c r="R274" s="78"/>
     </row>
-    <row r="275" spans="1:18" ht="22.5">
+    <row r="275" spans="1:18" ht="22">
       <c r="A275" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A275" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E275),
@@ -36493,7 +36450,7 @@
       <c r="Q275" s="136"/>
       <c r="R275" s="78"/>
     </row>
-    <row r="276" spans="1:18" ht="33.75">
+    <row r="276" spans="1:18" ht="33">
       <c r="A276" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A276" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E276),
@@ -36528,7 +36485,7 @@
       <c r="Q276" s="136"/>
       <c r="R276" s="78"/>
     </row>
-    <row r="277" spans="1:18" ht="22.5">
+    <row r="277" spans="1:18" ht="22">
       <c r="A277" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A277" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E277),
@@ -36565,7 +36522,7 @@
       <c r="Q277" s="136"/>
       <c r="R277" s="78"/>
     </row>
-    <row r="278" spans="1:18" ht="33.75">
+    <row r="278" spans="1:18" ht="33">
       <c r="A278" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A278" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E278),
@@ -36600,7 +36557,7 @@
       <c r="Q278" s="136"/>
       <c r="R278" s="78"/>
     </row>
-    <row r="279" spans="1:18" ht="45">
+    <row r="279" spans="1:18" ht="44">
       <c r="A279" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A279" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E279),
@@ -36635,7 +36592,7 @@
       <c r="Q279" s="136"/>
       <c r="R279" s="78"/>
     </row>
-    <row r="280" spans="1:18" ht="45">
+    <row r="280" spans="1:18" ht="44">
       <c r="A280" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A280" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E280),
@@ -36670,7 +36627,7 @@
       <c r="Q280" s="136"/>
       <c r="R280" s="78"/>
     </row>
-    <row r="281" spans="1:18" ht="33.75">
+    <row r="281" spans="1:18" ht="33">
       <c r="A281" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A281" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E281),
@@ -36705,7 +36662,7 @@
       <c r="Q281" s="136"/>
       <c r="R281" s="78"/>
     </row>
-    <row r="282" spans="1:18" ht="45">
+    <row r="282" spans="1:18" ht="44">
       <c r="A282" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A282" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E282),
@@ -36740,7 +36697,7 @@
       <c r="Q282" s="136"/>
       <c r="R282" s="78"/>
     </row>
-    <row r="283" spans="1:18" ht="45">
+    <row r="283" spans="1:18" ht="44">
       <c r="A283" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A283" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E283),
@@ -36775,7 +36732,7 @@
       <c r="Q283" s="136"/>
       <c r="R283" s="78"/>
     </row>
-    <row r="284" spans="1:18" ht="22.5">
+    <row r="284" spans="1:18" ht="22">
       <c r="A284" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A284" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E284),
@@ -36810,7 +36767,7 @@
       <c r="Q284" s="136"/>
       <c r="R284" s="78"/>
     </row>
-    <row r="285" spans="1:18" ht="22.5">
+    <row r="285" spans="1:18" ht="22">
       <c r="A285" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A285" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E285),
@@ -36847,7 +36804,7 @@
       <c r="Q285" s="136"/>
       <c r="R285" s="78"/>
     </row>
-    <row r="286" spans="1:18" ht="22.5">
+    <row r="286" spans="1:18" ht="22">
       <c r="A286" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A286" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E286),
@@ -36890,7 +36847,7 @@
       <c r="Q286" s="136"/>
       <c r="R286" s="78"/>
     </row>
-    <row r="287" spans="1:18" ht="22.5">
+    <row r="287" spans="1:18" ht="22">
       <c r="A287" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A287" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E287),
@@ -36925,7 +36882,7 @@
       <c r="Q287" s="136"/>
       <c r="R287" s="78"/>
     </row>
-    <row r="288" spans="1:18" ht="22.5">
+    <row r="288" spans="1:18" ht="22">
       <c r="A288" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A288" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E288),
@@ -36960,7 +36917,7 @@
       <c r="Q288" s="136"/>
       <c r="R288" s="78"/>
     </row>
-    <row r="289" spans="1:18" ht="22.5">
+    <row r="289" spans="1:18" ht="22">
       <c r="A289" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A289" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E289),
@@ -36995,7 +36952,7 @@
       <c r="Q289" s="136"/>
       <c r="R289" s="78"/>
     </row>
-    <row r="290" spans="1:18" ht="22.5">
+    <row r="290" spans="1:18" ht="22">
       <c r="A290" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A290" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E290),
@@ -37036,7 +36993,7 @@
       <c r="Q290" s="136"/>
       <c r="R290" s="78"/>
     </row>
-    <row r="291" spans="1:18" ht="22.5">
+    <row r="291" spans="1:18" ht="22">
       <c r="A291" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A291" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E291),
@@ -37073,7 +37030,7 @@
       <c r="Q291" s="136"/>
       <c r="R291" s="78"/>
     </row>
-    <row r="292" spans="1:18" ht="22.5">
+    <row r="292" spans="1:18" ht="22">
       <c r="A292" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A292" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E292),
@@ -37110,7 +37067,7 @@
       <c r="Q292" s="136"/>
       <c r="R292" s="78"/>
     </row>
-    <row r="293" spans="1:18" ht="22.5">
+    <row r="293" spans="1:18" ht="22">
       <c r="A293" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A293" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E293),
@@ -37147,7 +37104,7 @@
       <c r="Q293" s="136"/>
       <c r="R293" s="78"/>
     </row>
-    <row r="294" spans="1:18" ht="22.5">
+    <row r="294" spans="1:18" ht="22">
       <c r="A294" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A294" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E294),
@@ -37186,7 +37143,7 @@
       <c r="Q294" s="136"/>
       <c r="R294" s="78"/>
     </row>
-    <row r="295" spans="1:18" ht="22.5">
+    <row r="295" spans="1:18" ht="22">
       <c r="A295" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A295" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E295),
@@ -37221,7 +37178,7 @@
       <c r="Q295" s="136"/>
       <c r="R295" s="78"/>
     </row>
-    <row r="296" spans="1:18" ht="33.75">
+    <row r="296" spans="1:18" ht="33">
       <c r="A296" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A296" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E296),
@@ -37256,7 +37213,7 @@
       <c r="Q296" s="136"/>
       <c r="R296" s="78"/>
     </row>
-    <row r="297" spans="1:18" ht="33.75">
+    <row r="297" spans="1:18" ht="33">
       <c r="A297" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A297" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E297),
@@ -37291,7 +37248,7 @@
       <c r="Q297" s="136"/>
       <c r="R297" s="78"/>
     </row>
-    <row r="298" spans="1:18" ht="45">
+    <row r="298" spans="1:18" ht="44">
       <c r="A298" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A298" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E298),
@@ -37326,7 +37283,7 @@
       <c r="Q298" s="136"/>
       <c r="R298" s="78"/>
     </row>
-    <row r="299" spans="1:18" ht="33.75">
+    <row r="299" spans="1:18" ht="33">
       <c r="A299" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A299" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E299),
@@ -37361,7 +37318,7 @@
       <c r="Q299" s="136"/>
       <c r="R299" s="78"/>
     </row>
-    <row r="300" spans="1:18" ht="33.75">
+    <row r="300" spans="1:18" ht="33">
       <c r="A300" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A300" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E300),
@@ -37396,7 +37353,7 @@
       <c r="Q300" s="136"/>
       <c r="R300" s="78"/>
     </row>
-    <row r="301" spans="1:18" ht="22.5">
+    <row r="301" spans="1:18" ht="22">
       <c r="A301" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A301" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E301),
@@ -37431,7 +37388,7 @@
       <c r="Q301" s="136"/>
       <c r="R301" s="78"/>
     </row>
-    <row r="302" spans="1:18" ht="22.5">
+    <row r="302" spans="1:18" ht="22">
       <c r="A302" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A302" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E302),
@@ -37466,7 +37423,7 @@
       <c r="Q302" s="136"/>
       <c r="R302" s="78"/>
     </row>
-    <row r="303" spans="1:18" ht="45">
+    <row r="303" spans="1:18" ht="44">
       <c r="A303" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A303" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E303),
@@ -37499,10 +37456,10 @@
         <v>541</v>
       </c>
       <c r="I303" s="48" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="J303" s="48" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="K303" s="48" t="s">
         <v>542</v>
@@ -37519,7 +37476,7 @@
       <c r="Q303" s="48"/>
       <c r="R303" s="48"/>
     </row>
-    <row r="304" spans="1:18" ht="45">
+    <row r="304" spans="1:18" ht="44">
       <c r="A304" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A304" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E304),
@@ -37544,10 +37501,10 @@
         <v>541</v>
       </c>
       <c r="I304" s="48" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="J304" s="48" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K304" s="48" t="s">
         <v>542</v>
@@ -37564,7 +37521,7 @@
       <c r="Q304" s="48"/>
       <c r="R304" s="48"/>
     </row>
-    <row r="305" spans="1:18" ht="45">
+    <row r="305" spans="1:18" ht="44">
       <c r="A305" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A305" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E305),
@@ -37589,10 +37546,10 @@
         <v>541</v>
       </c>
       <c r="I305" s="48" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="J305" s="48" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="K305" s="48" t="s">
         <v>542</v>
@@ -37609,7 +37566,7 @@
       <c r="Q305" s="48"/>
       <c r="R305" s="48"/>
     </row>
-    <row r="306" spans="1:18" ht="78.75">
+    <row r="306" spans="1:18" ht="77">
       <c r="A306" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A306" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E306),
@@ -37634,10 +37591,10 @@
         <v>541</v>
       </c>
       <c r="I306" s="48" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="J306" s="48" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="K306" s="50" t="s">
         <v>543</v>
@@ -37654,7 +37611,7 @@
       <c r="Q306" s="48"/>
       <c r="R306" s="48"/>
     </row>
-    <row r="307" spans="1:18" ht="112.5">
+    <row r="307" spans="1:18" ht="110">
       <c r="A307" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A307" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E307),
@@ -37684,13 +37641,13 @@
         <v>21</v>
       </c>
       <c r="J307" s="48" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="K307" s="48" t="s">
         <v>35</v>
       </c>
       <c r="L307" s="48" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="M307" s="48"/>
       <c r="N307" s="48"/>
@@ -37699,7 +37656,7 @@
       <c r="Q307" s="48"/>
       <c r="R307" s="48"/>
     </row>
-    <row r="308" spans="1:18" ht="33.75">
+    <row r="308" spans="1:18" ht="33">
       <c r="A308" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A308" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E308),
@@ -37736,7 +37693,7 @@
       <c r="Q308" s="80"/>
       <c r="R308" s="80"/>
     </row>
-    <row r="309" spans="1:18" ht="33.75">
+    <row r="309" spans="1:18" ht="33">
       <c r="A309" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A309" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E309),
@@ -37773,7 +37730,7 @@
       <c r="Q309" s="80"/>
       <c r="R309" s="80"/>
     </row>
-    <row r="310" spans="1:18" ht="33.75">
+    <row r="310" spans="1:18" ht="33">
       <c r="A310" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A310" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E310),
@@ -37810,7 +37767,7 @@
       <c r="Q310" s="80"/>
       <c r="R310" s="80"/>
     </row>
-    <row r="311" spans="1:18" ht="56.25">
+    <row r="311" spans="1:18" ht="55">
       <c r="A311" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A311" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E311),
@@ -37839,10 +37796,10 @@
         <v>574</v>
       </c>
       <c r="I311" s="48" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J311" s="48" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="K311" s="48" t="s">
         <v>576</v>
@@ -37859,7 +37816,7 @@
       <c r="Q311" s="48"/>
       <c r="R311" s="48"/>
     </row>
-    <row r="312" spans="1:18" ht="78.75">
+    <row r="312" spans="1:18" ht="77">
       <c r="A312" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A312" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E312),
@@ -37884,10 +37841,10 @@
         <v>19</v>
       </c>
       <c r="I312" s="48" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J312" s="48" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="K312" s="48" t="s">
         <v>37</v>
@@ -37904,7 +37861,7 @@
       <c r="Q312" s="48"/>
       <c r="R312" s="48"/>
     </row>
-    <row r="313" spans="1:18" ht="78.75">
+    <row r="313" spans="1:18" ht="77">
       <c r="A313" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A313" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E313),
@@ -37927,10 +37884,10 @@
         <v>19</v>
       </c>
       <c r="I313" s="48" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J313" s="48" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="K313" s="48" t="s">
         <v>38</v>
@@ -37947,7 +37904,7 @@
       <c r="Q313" s="48"/>
       <c r="R313" s="48"/>
     </row>
-    <row r="314" spans="1:18" ht="78.75">
+    <row r="314" spans="1:18" ht="77">
       <c r="A314" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A314" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E314),
@@ -37970,10 +37927,10 @@
         <v>19</v>
       </c>
       <c r="I314" s="48" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J314" s="48" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="K314" s="48" t="s">
         <v>39</v>
@@ -37990,7 +37947,7 @@
       <c r="Q314" s="48"/>
       <c r="R314" s="48"/>
     </row>
-    <row r="315" spans="1:18" ht="78.75">
+    <row r="315" spans="1:18" ht="77">
       <c r="A315" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A315" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E315),
@@ -38013,10 +37970,10 @@
         <v>19</v>
       </c>
       <c r="I315" s="48" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J315" s="48" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="K315" s="48" t="s">
         <v>40</v>
@@ -38068,7 +38025,7 @@
       <c r="Q316" s="80"/>
       <c r="R316" s="80"/>
     </row>
-    <row r="317" spans="1:18" ht="33.75">
+    <row r="317" spans="1:18" ht="33">
       <c r="A317" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A317" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E317),
@@ -38100,7 +38057,7 @@
         <v>557</v>
       </c>
       <c r="J317" s="48" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="K317" s="48" t="s">
         <v>577</v>
@@ -38117,7 +38074,7 @@
       <c r="Q317" s="48"/>
       <c r="R317" s="48"/>
     </row>
-    <row r="318" spans="1:18" ht="33.75">
+    <row r="318" spans="1:18" ht="33">
       <c r="A318" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A318" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E318),
@@ -38152,7 +38109,7 @@
       <c r="Q318" s="80"/>
       <c r="R318" s="80"/>
     </row>
-    <row r="319" spans="1:18" ht="45">
+    <row r="319" spans="1:18" ht="44">
       <c r="A319" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A319" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E319),
@@ -38180,7 +38137,7 @@
         <v>557</v>
       </c>
       <c r="J319" s="48" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="K319" s="48" t="s">
         <v>578</v>
@@ -38197,7 +38154,7 @@
       <c r="Q319" s="48"/>
       <c r="R319" s="48"/>
     </row>
-    <row r="320" spans="1:18" ht="78.75">
+    <row r="320" spans="1:18" ht="77">
       <c r="A320" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A320" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E320),
@@ -38226,10 +38183,10 @@
         <v>19</v>
       </c>
       <c r="I320" s="48" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J320" s="48" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="K320" s="48" t="s">
         <v>50</v>
@@ -38246,7 +38203,7 @@
       <c r="Q320" s="48"/>
       <c r="R320" s="48"/>
     </row>
-    <row r="321" spans="1:18" ht="33.75">
+    <row r="321" spans="1:18" ht="33">
       <c r="A321" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A321" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E321),
@@ -38281,7 +38238,7 @@
       <c r="Q321" s="80"/>
       <c r="R321" s="80"/>
     </row>
-    <row r="322" spans="1:18" ht="45">
+    <row r="322" spans="1:18" ht="44">
       <c r="A322" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A322" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E322),
@@ -38316,7 +38273,7 @@
       <c r="Q322" s="80"/>
       <c r="R322" s="80"/>
     </row>
-    <row r="323" spans="1:18" ht="33.75">
+    <row r="323" spans="1:18" ht="33">
       <c r="A323" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A323" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E323),
@@ -38351,7 +38308,7 @@
       <c r="Q323" s="80"/>
       <c r="R323" s="80"/>
     </row>
-    <row r="324" spans="1:18" ht="45">
+    <row r="324" spans="1:18" ht="44">
       <c r="A324" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A324" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E324),
@@ -38386,7 +38343,7 @@
       <c r="Q324" s="80"/>
       <c r="R324" s="80"/>
     </row>
-    <row r="325" spans="1:18" ht="33.75">
+    <row r="325" spans="1:18" ht="33">
       <c r="A325" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A325" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E325),
@@ -38421,7 +38378,7 @@
       <c r="Q325" s="80"/>
       <c r="R325" s="80"/>
     </row>
-    <row r="326" spans="1:18" ht="45">
+    <row r="326" spans="1:18" ht="44">
       <c r="A326" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A326" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E326),
@@ -38456,7 +38413,7 @@
       <c r="Q326" s="80"/>
       <c r="R326" s="80"/>
     </row>
-    <row r="327" spans="1:18" ht="22.5">
+    <row r="327" spans="1:18" ht="22">
       <c r="A327" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A327" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E327),
@@ -38491,7 +38448,7 @@
       <c r="Q327" s="80"/>
       <c r="R327" s="80"/>
     </row>
-    <row r="328" spans="1:18" ht="78.75">
+    <row r="328" spans="1:18" ht="77">
       <c r="A328" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A328" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E328),
@@ -38527,7 +38484,7 @@
         <v>545</v>
       </c>
       <c r="J328" s="48" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="K328" s="50" t="s">
         <v>546</v>
@@ -38544,7 +38501,7 @@
       <c r="Q328" s="48"/>
       <c r="R328" s="48"/>
     </row>
-    <row r="329" spans="1:18" ht="33.75">
+    <row r="329" spans="1:18" ht="33">
       <c r="A329" s="50" t="str" cm="1">
         <f t="array" aca="1" ref="A329" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E329),
@@ -38628,17 +38585,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P553"/>
-  <sheetFormatPr defaultRowHeight="11.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="8.625" style="28" customWidth="1"/>
-    <col min="2" max="3" width="10.625" style="28" customWidth="1"/>
-    <col min="4" max="4" width="15.625" style="29" customWidth="1"/>
+    <col min="1" max="1" width="8.58203125" style="28" customWidth="1"/>
+    <col min="2" max="3" width="10.58203125" style="28" customWidth="1"/>
+    <col min="4" max="4" width="15.58203125" style="29" customWidth="1"/>
     <col min="5" max="5" width="15.5" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.875" style="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.125" style="103" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="9" width="30.625" style="28" customWidth="1"/>
-    <col min="10" max="10" width="20.625" style="28" customWidth="1"/>
-    <col min="11" max="14" width="8.625" style="28" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.08203125" style="103" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="9" width="30.58203125" style="28" customWidth="1"/>
+    <col min="10" max="10" width="20.58203125" style="28" customWidth="1"/>
+    <col min="11" max="14" width="8.58203125" style="28" customWidth="1"/>
     <col min="15" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
@@ -38679,7 +38636,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="12" thickBot="1">
+    <row r="8" spans="1:16" ht="11.5" thickBot="1">
       <c r="A8" s="30"/>
       <c r="B8" s="30"/>
       <c r="C8" s="30"/>
@@ -38748,7 +38705,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:16" s="35" customFormat="1" ht="45">
+    <row r="11" spans="1:16" s="35" customFormat="1" ht="44">
       <c r="A11" s="38" t="s">
         <v>29</v>
       </c>
@@ -38769,13 +38726,13 @@
       </c>
       <c r="G11" s="106"/>
       <c r="H11" s="36" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="I11" s="36" t="s">
         <v>57</v>
       </c>
       <c r="J11" s="40" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="K11" s="41">
         <v>1</v>
@@ -38786,9 +38743,9 @@
       <c r="O11" s="41"/>
       <c r="P11" s="41"/>
     </row>
-    <row r="12" spans="1:16" s="35" customFormat="1" ht="45">
+    <row r="12" spans="1:16" s="35" customFormat="1" ht="44">
       <c r="A12" s="38" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B12" s="42"/>
       <c r="C12" s="42"/>
@@ -38797,13 +38754,13 @@
       <c r="F12" s="43"/>
       <c r="G12" s="107"/>
       <c r="H12" s="36" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I12" s="36" t="s">
         <v>58</v>
       </c>
       <c r="J12" s="40" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="K12" s="41">
         <v>2</v>
@@ -38814,7 +38771,7 @@
       <c r="O12" s="41"/>
       <c r="P12" s="41"/>
     </row>
-    <row r="13" spans="1:16" s="35" customFormat="1" ht="90">
+    <row r="13" spans="1:16" s="35" customFormat="1" ht="88">
       <c r="A13" s="38" t="s">
         <v>30</v>
       </c>
@@ -38831,7 +38788,7 @@
       </c>
       <c r="G13" s="106"/>
       <c r="H13" s="36" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="I13" s="36" t="s">
         <v>60</v>
@@ -38848,9 +38805,9 @@
       <c r="O13" s="41"/>
       <c r="P13" s="41"/>
     </row>
-    <row r="14" spans="1:16" s="35" customFormat="1" ht="90">
+    <row r="14" spans="1:16" s="35" customFormat="1" ht="88">
       <c r="A14" s="38" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B14" s="42"/>
       <c r="C14" s="42"/>
@@ -38859,7 +38816,7 @@
       <c r="F14" s="42"/>
       <c r="G14" s="107"/>
       <c r="H14" s="36" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="I14" s="36" t="s">
         <v>61</v>
@@ -38876,9 +38833,9 @@
       <c r="O14" s="41"/>
       <c r="P14" s="41"/>
     </row>
-    <row r="15" spans="1:16" s="35" customFormat="1" ht="67.5">
+    <row r="15" spans="1:16" s="35" customFormat="1" ht="66">
       <c r="A15" s="38" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B15" s="43"/>
       <c r="C15" s="43"/>
@@ -38887,7 +38844,7 @@
       <c r="F15" s="43"/>
       <c r="G15" s="108"/>
       <c r="H15" s="36" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="I15" s="36" t="s">
         <v>62</v>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(バッチ)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(バッチ)_サンプル.xlsx
@@ -3,28 +3,28 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E23CA8B-A29B-4064-9D31-5AFCB8A02CE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E9AD7A2-9D0E-408C-9206-DDC02299BCCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="619" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
-    <sheet name="【バッチ処理ID】_クラス単体テスト" sheetId="25" r:id="rId3"/>
-    <sheet name="【バッチ処理ID】_リクエスト単体テスト" sheetId="26" r:id="rId4"/>
-    <sheet name="取引単体テスト" sheetId="17" r:id="rId5"/>
+    <sheet name="XxxAction_クラス単体" sheetId="25" r:id="rId3"/>
+    <sheet name="RBxxxxxxxx_リクエスト単体" sheetId="26" r:id="rId4"/>
+    <sheet name="取引単体" sheetId="17" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【バッチ処理ID】_クラス単体テスト!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【バッチ処理ID】_リクエスト単体テスト!$A$10:$R$329</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">【バッチ処理ID】_クラス単体テスト!$A$1:$R$304</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">【バッチ処理ID】_リクエスト単体テスト!$A$1:$R$329</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体テスト!$A$1:$P$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RBxxxxxxxx_リクエスト単体!$A$10:$R$329</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">XxxAction_クラス単体!$A$10:$R$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">RBxxxxxxxx_リクエスト単体!$A$1:$R$329</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">XxxAction_クラス単体!$A$1:$R$304</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$P$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">【バッチ処理ID】_クラス単体テスト!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">【バッチ処理ID】_リクエスト単体テスト!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体テスト!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">RBxxxxxxxx_リクエスト単体!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">XxxAction_クラス単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1897" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1897" uniqueCount="649">
   <si>
     <t>正常取引</t>
     <rPh sb="0" eb="2">
@@ -8959,6 +8959,13 @@
   <si>
     <t>単体テスト仕様書(バッチ)
 サンプル取引/BXXXXXXX</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>バッチ処理ID：RBxxxxxxxx</t>
+    <rPh sb="3" eb="5">
+      <t>ショリ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -9905,72 +9912,6 @@
     <xf numFmtId="31" fontId="13" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="6" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -10077,6 +10018,72 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -14248,57 +14255,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="193" t="s">
+      <c r="A1" s="171" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="194"/>
-      <c r="C1" s="194"/>
-      <c r="D1" s="195"/>
-      <c r="E1" s="196" t="s">
+      <c r="B1" s="172"/>
+      <c r="C1" s="172"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="174" t="s">
         <v>85</v>
       </c>
-      <c r="F1" s="197"/>
-      <c r="G1" s="197"/>
-      <c r="H1" s="197"/>
-      <c r="I1" s="197"/>
-      <c r="J1" s="197"/>
-      <c r="K1" s="197"/>
-      <c r="L1" s="197"/>
-      <c r="M1" s="197"/>
-      <c r="N1" s="198"/>
-      <c r="O1" s="202" t="s">
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
+      <c r="H1" s="175"/>
+      <c r="I1" s="175"/>
+      <c r="J1" s="175"/>
+      <c r="K1" s="175"/>
+      <c r="L1" s="175"/>
+      <c r="M1" s="175"/>
+      <c r="N1" s="176"/>
+      <c r="O1" s="180" t="s">
         <v>66</v>
       </c>
-      <c r="P1" s="203"/>
-      <c r="Q1" s="203"/>
-      <c r="R1" s="204"/>
-      <c r="S1" s="211" t="s">
+      <c r="P1" s="181"/>
+      <c r="Q1" s="181"/>
+      <c r="R1" s="182"/>
+      <c r="S1" s="189" t="s">
         <v>647</v>
       </c>
-      <c r="T1" s="212"/>
-      <c r="U1" s="212"/>
-      <c r="V1" s="212"/>
-      <c r="W1" s="212"/>
-      <c r="X1" s="212"/>
-      <c r="Y1" s="212"/>
-      <c r="Z1" s="213"/>
-      <c r="AA1" s="193" t="s">
+      <c r="T1" s="190"/>
+      <c r="U1" s="190"/>
+      <c r="V1" s="190"/>
+      <c r="W1" s="190"/>
+      <c r="X1" s="190"/>
+      <c r="Y1" s="190"/>
+      <c r="Z1" s="191"/>
+      <c r="AA1" s="171" t="s">
         <v>67</v>
       </c>
-      <c r="AB1" s="195"/>
-      <c r="AC1" s="220" t="str">
+      <c r="AB1" s="173"/>
+      <c r="AC1" s="198" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="221"/>
-      <c r="AE1" s="221"/>
-      <c r="AF1" s="222"/>
-      <c r="AG1" s="187">
+      <c r="AD1" s="199"/>
+      <c r="AE1" s="199"/>
+      <c r="AF1" s="200"/>
+      <c r="AG1" s="165">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="188"/>
-      <c r="AI1" s="189"/>
+      <c r="AH1" s="166"/>
+      <c r="AI1" s="167"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -14306,53 +14313,53 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="193" t="s">
+      <c r="A2" s="171" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="194"/>
-      <c r="C2" s="194"/>
-      <c r="D2" s="195"/>
-      <c r="E2" s="196" t="s">
+      <c r="B2" s="172"/>
+      <c r="C2" s="172"/>
+      <c r="D2" s="173"/>
+      <c r="E2" s="174" t="s">
         <v>86</v>
       </c>
-      <c r="F2" s="197"/>
-      <c r="G2" s="197"/>
-      <c r="H2" s="197"/>
-      <c r="I2" s="197"/>
-      <c r="J2" s="197"/>
-      <c r="K2" s="197"/>
-      <c r="L2" s="197"/>
-      <c r="M2" s="197"/>
-      <c r="N2" s="198"/>
-      <c r="O2" s="205"/>
-      <c r="P2" s="206"/>
-      <c r="Q2" s="206"/>
-      <c r="R2" s="207"/>
-      <c r="S2" s="214"/>
-      <c r="T2" s="215"/>
-      <c r="U2" s="215"/>
-      <c r="V2" s="215"/>
-      <c r="W2" s="215"/>
-      <c r="X2" s="215"/>
-      <c r="Y2" s="215"/>
-      <c r="Z2" s="216"/>
-      <c r="AA2" s="193" t="s">
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
+      <c r="H2" s="175"/>
+      <c r="I2" s="175"/>
+      <c r="J2" s="175"/>
+      <c r="K2" s="175"/>
+      <c r="L2" s="175"/>
+      <c r="M2" s="175"/>
+      <c r="N2" s="176"/>
+      <c r="O2" s="183"/>
+      <c r="P2" s="184"/>
+      <c r="Q2" s="184"/>
+      <c r="R2" s="185"/>
+      <c r="S2" s="192"/>
+      <c r="T2" s="193"/>
+      <c r="U2" s="193"/>
+      <c r="V2" s="193"/>
+      <c r="W2" s="193"/>
+      <c r="X2" s="193"/>
+      <c r="Y2" s="193"/>
+      <c r="Z2" s="194"/>
+      <c r="AA2" s="171" t="s">
         <v>69</v>
       </c>
-      <c r="AB2" s="195"/>
-      <c r="AC2" s="199" t="str">
+      <c r="AB2" s="173"/>
+      <c r="AC2" s="177" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="200"/>
-      <c r="AE2" s="200"/>
-      <c r="AF2" s="201"/>
-      <c r="AG2" s="187">
+      <c r="AD2" s="178"/>
+      <c r="AE2" s="178"/>
+      <c r="AF2" s="179"/>
+      <c r="AG2" s="165">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44852</v>
       </c>
-      <c r="AH2" s="188"/>
-      <c r="AI2" s="189"/>
+      <c r="AH2" s="166"/>
+      <c r="AI2" s="167"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -14360,45 +14367,45 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="193" t="s">
+      <c r="A3" s="171" t="s">
         <v>70</v>
       </c>
-      <c r="B3" s="194"/>
-      <c r="C3" s="194"/>
-      <c r="D3" s="195"/>
-      <c r="E3" s="196" t="s">
+      <c r="B3" s="172"/>
+      <c r="C3" s="172"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="174" t="s">
         <v>87</v>
       </c>
-      <c r="F3" s="197"/>
-      <c r="G3" s="197"/>
-      <c r="H3" s="197"/>
-      <c r="I3" s="197"/>
-      <c r="J3" s="197"/>
-      <c r="K3" s="197"/>
-      <c r="L3" s="197"/>
-      <c r="M3" s="197"/>
-      <c r="N3" s="198"/>
-      <c r="O3" s="208"/>
-      <c r="P3" s="209"/>
-      <c r="Q3" s="209"/>
-      <c r="R3" s="210"/>
-      <c r="S3" s="217"/>
-      <c r="T3" s="218"/>
-      <c r="U3" s="218"/>
-      <c r="V3" s="218"/>
-      <c r="W3" s="218"/>
-      <c r="X3" s="218"/>
-      <c r="Y3" s="218"/>
-      <c r="Z3" s="219"/>
-      <c r="AA3" s="193"/>
-      <c r="AB3" s="195"/>
-      <c r="AC3" s="220"/>
-      <c r="AD3" s="221"/>
-      <c r="AE3" s="221"/>
-      <c r="AF3" s="222"/>
-      <c r="AG3" s="187"/>
-      <c r="AH3" s="188"/>
-      <c r="AI3" s="189"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
+      <c r="H3" s="175"/>
+      <c r="I3" s="175"/>
+      <c r="J3" s="175"/>
+      <c r="K3" s="175"/>
+      <c r="L3" s="175"/>
+      <c r="M3" s="175"/>
+      <c r="N3" s="176"/>
+      <c r="O3" s="186"/>
+      <c r="P3" s="187"/>
+      <c r="Q3" s="187"/>
+      <c r="R3" s="188"/>
+      <c r="S3" s="195"/>
+      <c r="T3" s="196"/>
+      <c r="U3" s="196"/>
+      <c r="V3" s="196"/>
+      <c r="W3" s="196"/>
+      <c r="X3" s="196"/>
+      <c r="Y3" s="196"/>
+      <c r="Z3" s="197"/>
+      <c r="AA3" s="171"/>
+      <c r="AB3" s="173"/>
+      <c r="AC3" s="198"/>
+      <c r="AD3" s="199"/>
+      <c r="AE3" s="199"/>
+      <c r="AF3" s="200"/>
+      <c r="AG3" s="165"/>
+      <c r="AH3" s="166"/>
+      <c r="AI3" s="167"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -14435,97 +14442,97 @@
       <c r="A7" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="190" t="s">
+      <c r="B7" s="168" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="191"/>
-      <c r="D7" s="190" t="s">
+      <c r="C7" s="169"/>
+      <c r="D7" s="168" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="192"/>
-      <c r="F7" s="191"/>
-      <c r="G7" s="190" t="s">
+      <c r="E7" s="170"/>
+      <c r="F7" s="169"/>
+      <c r="G7" s="168" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="192"/>
-      <c r="I7" s="191"/>
-      <c r="J7" s="190" t="s">
+      <c r="H7" s="170"/>
+      <c r="I7" s="169"/>
+      <c r="J7" s="168" t="s">
         <v>75</v>
       </c>
-      <c r="K7" s="192"/>
-      <c r="L7" s="192"/>
-      <c r="M7" s="192"/>
-      <c r="N7" s="192"/>
-      <c r="O7" s="192"/>
-      <c r="P7" s="191"/>
-      <c r="Q7" s="190" t="s">
+      <c r="K7" s="170"/>
+      <c r="L7" s="170"/>
+      <c r="M7" s="170"/>
+      <c r="N7" s="170"/>
+      <c r="O7" s="170"/>
+      <c r="P7" s="169"/>
+      <c r="Q7" s="168" t="s">
         <v>76</v>
       </c>
-      <c r="R7" s="192"/>
-      <c r="S7" s="192"/>
-      <c r="T7" s="192"/>
-      <c r="U7" s="192"/>
-      <c r="V7" s="192"/>
-      <c r="W7" s="192"/>
-      <c r="X7" s="192"/>
-      <c r="Y7" s="192"/>
-      <c r="Z7" s="192"/>
-      <c r="AA7" s="192"/>
-      <c r="AB7" s="192"/>
-      <c r="AC7" s="192"/>
-      <c r="AD7" s="192"/>
-      <c r="AE7" s="191"/>
-      <c r="AF7" s="190" t="s">
+      <c r="R7" s="170"/>
+      <c r="S7" s="170"/>
+      <c r="T7" s="170"/>
+      <c r="U7" s="170"/>
+      <c r="V7" s="170"/>
+      <c r="W7" s="170"/>
+      <c r="X7" s="170"/>
+      <c r="Y7" s="170"/>
+      <c r="Z7" s="170"/>
+      <c r="AA7" s="170"/>
+      <c r="AB7" s="170"/>
+      <c r="AC7" s="170"/>
+      <c r="AD7" s="170"/>
+      <c r="AE7" s="169"/>
+      <c r="AF7" s="168" t="s">
         <v>77</v>
       </c>
-      <c r="AG7" s="192"/>
-      <c r="AH7" s="192"/>
-      <c r="AI7" s="191"/>
+      <c r="AG7" s="170"/>
+      <c r="AH7" s="170"/>
+      <c r="AI7" s="169"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="24">
         <v>1</v>
       </c>
-      <c r="B8" s="178" t="s">
+      <c r="B8" s="213" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="179"/>
-      <c r="D8" s="180">
+      <c r="C8" s="214"/>
+      <c r="D8" s="215">
         <v>43336</v>
       </c>
-      <c r="E8" s="181"/>
-      <c r="F8" s="182"/>
-      <c r="G8" s="178" t="s">
+      <c r="E8" s="216"/>
+      <c r="F8" s="217"/>
+      <c r="G8" s="213" t="s">
         <v>79</v>
       </c>
-      <c r="H8" s="183"/>
-      <c r="I8" s="179"/>
-      <c r="J8" s="184" t="s">
+      <c r="H8" s="218"/>
+      <c r="I8" s="214"/>
+      <c r="J8" s="219" t="s">
         <v>80</v>
       </c>
-      <c r="K8" s="185"/>
-      <c r="L8" s="185"/>
-      <c r="M8" s="185"/>
-      <c r="N8" s="185"/>
-      <c r="O8" s="185"/>
-      <c r="P8" s="186"/>
-      <c r="Q8" s="184" t="s">
+      <c r="K8" s="220"/>
+      <c r="L8" s="220"/>
+      <c r="M8" s="220"/>
+      <c r="N8" s="220"/>
+      <c r="O8" s="220"/>
+      <c r="P8" s="221"/>
+      <c r="Q8" s="219" t="s">
         <v>81</v>
       </c>
-      <c r="R8" s="185"/>
-      <c r="S8" s="185"/>
-      <c r="T8" s="185"/>
-      <c r="U8" s="185"/>
-      <c r="V8" s="185"/>
-      <c r="W8" s="185"/>
-      <c r="X8" s="185"/>
-      <c r="Y8" s="185"/>
-      <c r="Z8" s="185"/>
-      <c r="AA8" s="185"/>
-      <c r="AB8" s="185"/>
-      <c r="AC8" s="185"/>
-      <c r="AD8" s="185"/>
-      <c r="AE8" s="186"/>
+      <c r="R8" s="220"/>
+      <c r="S8" s="220"/>
+      <c r="T8" s="220"/>
+      <c r="U8" s="220"/>
+      <c r="V8" s="220"/>
+      <c r="W8" s="220"/>
+      <c r="X8" s="220"/>
+      <c r="Y8" s="220"/>
+      <c r="Z8" s="220"/>
+      <c r="AA8" s="220"/>
+      <c r="AB8" s="220"/>
+      <c r="AC8" s="220"/>
+      <c r="AD8" s="220"/>
+      <c r="AE8" s="221"/>
       <c r="AF8" s="25" t="s">
         <v>82</v>
       </c>
@@ -14537,946 +14544,1101 @@
       <c r="A9" s="24">
         <v>2</v>
       </c>
-      <c r="B9" s="165" t="s">
+      <c r="B9" s="201" t="s">
         <v>549</v>
       </c>
-      <c r="C9" s="166"/>
-      <c r="D9" s="167">
+      <c r="C9" s="202"/>
+      <c r="D9" s="203">
         <v>44852</v>
       </c>
-      <c r="E9" s="168"/>
-      <c r="F9" s="169"/>
-      <c r="G9" s="167" t="s">
+      <c r="E9" s="204"/>
+      <c r="F9" s="205"/>
+      <c r="G9" s="203" t="s">
         <v>550</v>
       </c>
-      <c r="H9" s="170"/>
-      <c r="I9" s="166"/>
-      <c r="J9" s="174" t="s">
+      <c r="H9" s="206"/>
+      <c r="I9" s="202"/>
+      <c r="J9" s="207" t="s">
         <v>552</v>
       </c>
-      <c r="K9" s="172"/>
-      <c r="L9" s="172"/>
-      <c r="M9" s="172"/>
-      <c r="N9" s="172"/>
-      <c r="O9" s="172"/>
-      <c r="P9" s="173"/>
-      <c r="Q9" s="174" t="s">
+      <c r="K9" s="208"/>
+      <c r="L9" s="208"/>
+      <c r="M9" s="208"/>
+      <c r="N9" s="208"/>
+      <c r="O9" s="208"/>
+      <c r="P9" s="209"/>
+      <c r="Q9" s="207" t="s">
         <v>551</v>
       </c>
-      <c r="R9" s="175"/>
-      <c r="S9" s="175"/>
-      <c r="T9" s="175"/>
-      <c r="U9" s="175"/>
-      <c r="V9" s="175"/>
-      <c r="W9" s="175"/>
-      <c r="X9" s="175"/>
-      <c r="Y9" s="175"/>
-      <c r="Z9" s="175"/>
-      <c r="AA9" s="175"/>
-      <c r="AB9" s="175"/>
-      <c r="AC9" s="175"/>
-      <c r="AD9" s="175"/>
-      <c r="AE9" s="176"/>
-      <c r="AF9" s="171" t="s">
+      <c r="R9" s="210"/>
+      <c r="S9" s="210"/>
+      <c r="T9" s="210"/>
+      <c r="U9" s="210"/>
+      <c r="V9" s="210"/>
+      <c r="W9" s="210"/>
+      <c r="X9" s="210"/>
+      <c r="Y9" s="210"/>
+      <c r="Z9" s="210"/>
+      <c r="AA9" s="210"/>
+      <c r="AB9" s="210"/>
+      <c r="AC9" s="210"/>
+      <c r="AD9" s="210"/>
+      <c r="AE9" s="211"/>
+      <c r="AF9" s="212" t="s">
         <v>82</v>
       </c>
-      <c r="AG9" s="172"/>
-      <c r="AH9" s="172"/>
-      <c r="AI9" s="173"/>
+      <c r="AG9" s="208"/>
+      <c r="AH9" s="208"/>
+      <c r="AI9" s="209"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="21"/>
-      <c r="B10" s="165"/>
-      <c r="C10" s="166"/>
-      <c r="D10" s="167"/>
-      <c r="E10" s="168"/>
-      <c r="F10" s="169"/>
-      <c r="G10" s="165"/>
-      <c r="H10" s="170"/>
-      <c r="I10" s="166"/>
-      <c r="J10" s="171"/>
-      <c r="K10" s="172"/>
-      <c r="L10" s="172"/>
-      <c r="M10" s="172"/>
-      <c r="N10" s="172"/>
-      <c r="O10" s="172"/>
-      <c r="P10" s="173"/>
-      <c r="Q10" s="174"/>
-      <c r="R10" s="175"/>
-      <c r="S10" s="175"/>
-      <c r="T10" s="175"/>
-      <c r="U10" s="175"/>
-      <c r="V10" s="175"/>
-      <c r="W10" s="175"/>
-      <c r="X10" s="175"/>
-      <c r="Y10" s="175"/>
-      <c r="Z10" s="175"/>
-      <c r="AA10" s="175"/>
-      <c r="AB10" s="175"/>
-      <c r="AC10" s="175"/>
-      <c r="AD10" s="175"/>
-      <c r="AE10" s="176"/>
-      <c r="AF10" s="171"/>
-      <c r="AG10" s="172"/>
-      <c r="AH10" s="172"/>
-      <c r="AI10" s="173"/>
+      <c r="B10" s="201"/>
+      <c r="C10" s="202"/>
+      <c r="D10" s="203"/>
+      <c r="E10" s="204"/>
+      <c r="F10" s="205"/>
+      <c r="G10" s="201"/>
+      <c r="H10" s="206"/>
+      <c r="I10" s="202"/>
+      <c r="J10" s="212"/>
+      <c r="K10" s="208"/>
+      <c r="L10" s="208"/>
+      <c r="M10" s="208"/>
+      <c r="N10" s="208"/>
+      <c r="O10" s="208"/>
+      <c r="P10" s="209"/>
+      <c r="Q10" s="207"/>
+      <c r="R10" s="210"/>
+      <c r="S10" s="210"/>
+      <c r="T10" s="210"/>
+      <c r="U10" s="210"/>
+      <c r="V10" s="210"/>
+      <c r="W10" s="210"/>
+      <c r="X10" s="210"/>
+      <c r="Y10" s="210"/>
+      <c r="Z10" s="210"/>
+      <c r="AA10" s="210"/>
+      <c r="AB10" s="210"/>
+      <c r="AC10" s="210"/>
+      <c r="AD10" s="210"/>
+      <c r="AE10" s="211"/>
+      <c r="AF10" s="212"/>
+      <c r="AG10" s="208"/>
+      <c r="AH10" s="208"/>
+      <c r="AI10" s="209"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="21"/>
-      <c r="B11" s="165"/>
-      <c r="C11" s="166"/>
-      <c r="D11" s="167"/>
-      <c r="E11" s="168"/>
-      <c r="F11" s="169"/>
-      <c r="G11" s="165"/>
-      <c r="H11" s="170"/>
-      <c r="I11" s="166"/>
-      <c r="J11" s="171"/>
-      <c r="K11" s="172"/>
-      <c r="L11" s="172"/>
-      <c r="M11" s="172"/>
-      <c r="N11" s="172"/>
-      <c r="O11" s="172"/>
-      <c r="P11" s="173"/>
-      <c r="Q11" s="174"/>
-      <c r="R11" s="175"/>
-      <c r="S11" s="175"/>
-      <c r="T11" s="175"/>
-      <c r="U11" s="175"/>
-      <c r="V11" s="175"/>
-      <c r="W11" s="175"/>
-      <c r="X11" s="175"/>
-      <c r="Y11" s="175"/>
-      <c r="Z11" s="175"/>
-      <c r="AA11" s="175"/>
-      <c r="AB11" s="175"/>
-      <c r="AC11" s="175"/>
-      <c r="AD11" s="175"/>
-      <c r="AE11" s="176"/>
-      <c r="AF11" s="171"/>
-      <c r="AG11" s="172"/>
-      <c r="AH11" s="172"/>
-      <c r="AI11" s="173"/>
+      <c r="B11" s="201"/>
+      <c r="C11" s="202"/>
+      <c r="D11" s="203"/>
+      <c r="E11" s="204"/>
+      <c r="F11" s="205"/>
+      <c r="G11" s="201"/>
+      <c r="H11" s="206"/>
+      <c r="I11" s="202"/>
+      <c r="J11" s="212"/>
+      <c r="K11" s="208"/>
+      <c r="L11" s="208"/>
+      <c r="M11" s="208"/>
+      <c r="N11" s="208"/>
+      <c r="O11" s="208"/>
+      <c r="P11" s="209"/>
+      <c r="Q11" s="207"/>
+      <c r="R11" s="210"/>
+      <c r="S11" s="210"/>
+      <c r="T11" s="210"/>
+      <c r="U11" s="210"/>
+      <c r="V11" s="210"/>
+      <c r="W11" s="210"/>
+      <c r="X11" s="210"/>
+      <c r="Y11" s="210"/>
+      <c r="Z11" s="210"/>
+      <c r="AA11" s="210"/>
+      <c r="AB11" s="210"/>
+      <c r="AC11" s="210"/>
+      <c r="AD11" s="210"/>
+      <c r="AE11" s="211"/>
+      <c r="AF11" s="212"/>
+      <c r="AG11" s="208"/>
+      <c r="AH11" s="208"/>
+      <c r="AI11" s="209"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="21"/>
-      <c r="B12" s="165"/>
-      <c r="C12" s="166"/>
-      <c r="D12" s="167"/>
-      <c r="E12" s="168"/>
-      <c r="F12" s="169"/>
-      <c r="G12" s="165"/>
-      <c r="H12" s="170"/>
-      <c r="I12" s="166"/>
-      <c r="J12" s="171"/>
-      <c r="K12" s="172"/>
-      <c r="L12" s="172"/>
-      <c r="M12" s="172"/>
-      <c r="N12" s="172"/>
-      <c r="O12" s="172"/>
-      <c r="P12" s="173"/>
-      <c r="Q12" s="174"/>
-      <c r="R12" s="175"/>
-      <c r="S12" s="175"/>
-      <c r="T12" s="175"/>
-      <c r="U12" s="175"/>
-      <c r="V12" s="175"/>
-      <c r="W12" s="175"/>
-      <c r="X12" s="175"/>
-      <c r="Y12" s="175"/>
-      <c r="Z12" s="175"/>
-      <c r="AA12" s="175"/>
-      <c r="AB12" s="175"/>
-      <c r="AC12" s="175"/>
-      <c r="AD12" s="175"/>
-      <c r="AE12" s="176"/>
-      <c r="AF12" s="171"/>
-      <c r="AG12" s="172"/>
-      <c r="AH12" s="172"/>
-      <c r="AI12" s="173"/>
+      <c r="B12" s="201"/>
+      <c r="C12" s="202"/>
+      <c r="D12" s="203"/>
+      <c r="E12" s="204"/>
+      <c r="F12" s="205"/>
+      <c r="G12" s="201"/>
+      <c r="H12" s="206"/>
+      <c r="I12" s="202"/>
+      <c r="J12" s="212"/>
+      <c r="K12" s="208"/>
+      <c r="L12" s="208"/>
+      <c r="M12" s="208"/>
+      <c r="N12" s="208"/>
+      <c r="O12" s="208"/>
+      <c r="P12" s="209"/>
+      <c r="Q12" s="207"/>
+      <c r="R12" s="210"/>
+      <c r="S12" s="210"/>
+      <c r="T12" s="210"/>
+      <c r="U12" s="210"/>
+      <c r="V12" s="210"/>
+      <c r="W12" s="210"/>
+      <c r="X12" s="210"/>
+      <c r="Y12" s="210"/>
+      <c r="Z12" s="210"/>
+      <c r="AA12" s="210"/>
+      <c r="AB12" s="210"/>
+      <c r="AC12" s="210"/>
+      <c r="AD12" s="210"/>
+      <c r="AE12" s="211"/>
+      <c r="AF12" s="212"/>
+      <c r="AG12" s="208"/>
+      <c r="AH12" s="208"/>
+      <c r="AI12" s="209"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="21"/>
-      <c r="B13" s="165"/>
-      <c r="C13" s="166"/>
-      <c r="D13" s="167"/>
-      <c r="E13" s="168"/>
-      <c r="F13" s="169"/>
-      <c r="G13" s="165"/>
-      <c r="H13" s="170"/>
-      <c r="I13" s="166"/>
-      <c r="J13" s="171"/>
-      <c r="K13" s="172"/>
-      <c r="L13" s="172"/>
-      <c r="M13" s="172"/>
-      <c r="N13" s="172"/>
-      <c r="O13" s="172"/>
-      <c r="P13" s="173"/>
-      <c r="Q13" s="174"/>
-      <c r="R13" s="175"/>
-      <c r="S13" s="175"/>
-      <c r="T13" s="175"/>
-      <c r="U13" s="175"/>
-      <c r="V13" s="175"/>
-      <c r="W13" s="175"/>
-      <c r="X13" s="175"/>
-      <c r="Y13" s="175"/>
-      <c r="Z13" s="175"/>
-      <c r="AA13" s="175"/>
-      <c r="AB13" s="175"/>
-      <c r="AC13" s="175"/>
-      <c r="AD13" s="175"/>
-      <c r="AE13" s="176"/>
-      <c r="AF13" s="171"/>
-      <c r="AG13" s="172"/>
-      <c r="AH13" s="172"/>
-      <c r="AI13" s="173"/>
+      <c r="B13" s="201"/>
+      <c r="C13" s="202"/>
+      <c r="D13" s="203"/>
+      <c r="E13" s="204"/>
+      <c r="F13" s="205"/>
+      <c r="G13" s="201"/>
+      <c r="H13" s="206"/>
+      <c r="I13" s="202"/>
+      <c r="J13" s="212"/>
+      <c r="K13" s="208"/>
+      <c r="L13" s="208"/>
+      <c r="M13" s="208"/>
+      <c r="N13" s="208"/>
+      <c r="O13" s="208"/>
+      <c r="P13" s="209"/>
+      <c r="Q13" s="207"/>
+      <c r="R13" s="210"/>
+      <c r="S13" s="210"/>
+      <c r="T13" s="210"/>
+      <c r="U13" s="210"/>
+      <c r="V13" s="210"/>
+      <c r="W13" s="210"/>
+      <c r="X13" s="210"/>
+      <c r="Y13" s="210"/>
+      <c r="Z13" s="210"/>
+      <c r="AA13" s="210"/>
+      <c r="AB13" s="210"/>
+      <c r="AC13" s="210"/>
+      <c r="AD13" s="210"/>
+      <c r="AE13" s="211"/>
+      <c r="AF13" s="212"/>
+      <c r="AG13" s="208"/>
+      <c r="AH13" s="208"/>
+      <c r="AI13" s="209"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="165"/>
-      <c r="C14" s="166"/>
-      <c r="D14" s="167"/>
-      <c r="E14" s="168"/>
-      <c r="F14" s="169"/>
-      <c r="G14" s="165"/>
-      <c r="H14" s="170"/>
-      <c r="I14" s="166"/>
-      <c r="J14" s="171"/>
-      <c r="K14" s="172"/>
-      <c r="L14" s="172"/>
-      <c r="M14" s="172"/>
-      <c r="N14" s="172"/>
-      <c r="O14" s="172"/>
-      <c r="P14" s="173"/>
-      <c r="Q14" s="174"/>
-      <c r="R14" s="175"/>
-      <c r="S14" s="175"/>
-      <c r="T14" s="175"/>
-      <c r="U14" s="175"/>
-      <c r="V14" s="175"/>
-      <c r="W14" s="175"/>
-      <c r="X14" s="175"/>
-      <c r="Y14" s="175"/>
-      <c r="Z14" s="175"/>
-      <c r="AA14" s="175"/>
-      <c r="AB14" s="175"/>
-      <c r="AC14" s="175"/>
-      <c r="AD14" s="175"/>
-      <c r="AE14" s="176"/>
-      <c r="AF14" s="171"/>
-      <c r="AG14" s="172"/>
-      <c r="AH14" s="172"/>
-      <c r="AI14" s="173"/>
+      <c r="B14" s="201"/>
+      <c r="C14" s="202"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="204"/>
+      <c r="F14" s="205"/>
+      <c r="G14" s="201"/>
+      <c r="H14" s="206"/>
+      <c r="I14" s="202"/>
+      <c r="J14" s="212"/>
+      <c r="K14" s="208"/>
+      <c r="L14" s="208"/>
+      <c r="M14" s="208"/>
+      <c r="N14" s="208"/>
+      <c r="O14" s="208"/>
+      <c r="P14" s="209"/>
+      <c r="Q14" s="207"/>
+      <c r="R14" s="210"/>
+      <c r="S14" s="210"/>
+      <c r="T14" s="210"/>
+      <c r="U14" s="210"/>
+      <c r="V14" s="210"/>
+      <c r="W14" s="210"/>
+      <c r="X14" s="210"/>
+      <c r="Y14" s="210"/>
+      <c r="Z14" s="210"/>
+      <c r="AA14" s="210"/>
+      <c r="AB14" s="210"/>
+      <c r="AC14" s="210"/>
+      <c r="AD14" s="210"/>
+      <c r="AE14" s="211"/>
+      <c r="AF14" s="212"/>
+      <c r="AG14" s="208"/>
+      <c r="AH14" s="208"/>
+      <c r="AI14" s="209"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="21"/>
-      <c r="B15" s="165"/>
-      <c r="C15" s="166"/>
-      <c r="D15" s="167"/>
-      <c r="E15" s="168"/>
-      <c r="F15" s="169"/>
-      <c r="G15" s="165"/>
-      <c r="H15" s="170"/>
-      <c r="I15" s="166"/>
-      <c r="J15" s="171"/>
-      <c r="K15" s="172"/>
-      <c r="L15" s="172"/>
-      <c r="M15" s="172"/>
-      <c r="N15" s="172"/>
-      <c r="O15" s="172"/>
-      <c r="P15" s="173"/>
-      <c r="Q15" s="174"/>
-      <c r="R15" s="175"/>
-      <c r="S15" s="175"/>
-      <c r="T15" s="175"/>
-      <c r="U15" s="175"/>
-      <c r="V15" s="175"/>
-      <c r="W15" s="175"/>
-      <c r="X15" s="175"/>
-      <c r="Y15" s="175"/>
-      <c r="Z15" s="175"/>
-      <c r="AA15" s="175"/>
-      <c r="AB15" s="175"/>
-      <c r="AC15" s="175"/>
-      <c r="AD15" s="175"/>
-      <c r="AE15" s="176"/>
-      <c r="AF15" s="171"/>
-      <c r="AG15" s="172"/>
-      <c r="AH15" s="172"/>
-      <c r="AI15" s="173"/>
+      <c r="B15" s="201"/>
+      <c r="C15" s="202"/>
+      <c r="D15" s="203"/>
+      <c r="E15" s="204"/>
+      <c r="F15" s="205"/>
+      <c r="G15" s="201"/>
+      <c r="H15" s="206"/>
+      <c r="I15" s="202"/>
+      <c r="J15" s="212"/>
+      <c r="K15" s="208"/>
+      <c r="L15" s="208"/>
+      <c r="M15" s="208"/>
+      <c r="N15" s="208"/>
+      <c r="O15" s="208"/>
+      <c r="P15" s="209"/>
+      <c r="Q15" s="207"/>
+      <c r="R15" s="210"/>
+      <c r="S15" s="210"/>
+      <c r="T15" s="210"/>
+      <c r="U15" s="210"/>
+      <c r="V15" s="210"/>
+      <c r="W15" s="210"/>
+      <c r="X15" s="210"/>
+      <c r="Y15" s="210"/>
+      <c r="Z15" s="210"/>
+      <c r="AA15" s="210"/>
+      <c r="AB15" s="210"/>
+      <c r="AC15" s="210"/>
+      <c r="AD15" s="210"/>
+      <c r="AE15" s="211"/>
+      <c r="AF15" s="212"/>
+      <c r="AG15" s="208"/>
+      <c r="AH15" s="208"/>
+      <c r="AI15" s="209"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="21"/>
-      <c r="B16" s="165"/>
-      <c r="C16" s="166"/>
-      <c r="D16" s="167"/>
-      <c r="E16" s="168"/>
-      <c r="F16" s="169"/>
-      <c r="G16" s="165"/>
-      <c r="H16" s="170"/>
-      <c r="I16" s="166"/>
-      <c r="J16" s="171"/>
-      <c r="K16" s="172"/>
-      <c r="L16" s="172"/>
-      <c r="M16" s="172"/>
-      <c r="N16" s="172"/>
-      <c r="O16" s="172"/>
-      <c r="P16" s="173"/>
-      <c r="Q16" s="174"/>
-      <c r="R16" s="175"/>
-      <c r="S16" s="175"/>
-      <c r="T16" s="175"/>
-      <c r="U16" s="175"/>
-      <c r="V16" s="175"/>
-      <c r="W16" s="175"/>
-      <c r="X16" s="175"/>
-      <c r="Y16" s="175"/>
-      <c r="Z16" s="175"/>
-      <c r="AA16" s="175"/>
-      <c r="AB16" s="175"/>
-      <c r="AC16" s="175"/>
-      <c r="AD16" s="175"/>
-      <c r="AE16" s="176"/>
-      <c r="AF16" s="171"/>
-      <c r="AG16" s="172"/>
-      <c r="AH16" s="172"/>
-      <c r="AI16" s="173"/>
+      <c r="B16" s="201"/>
+      <c r="C16" s="202"/>
+      <c r="D16" s="203"/>
+      <c r="E16" s="204"/>
+      <c r="F16" s="205"/>
+      <c r="G16" s="201"/>
+      <c r="H16" s="206"/>
+      <c r="I16" s="202"/>
+      <c r="J16" s="212"/>
+      <c r="K16" s="208"/>
+      <c r="L16" s="208"/>
+      <c r="M16" s="208"/>
+      <c r="N16" s="208"/>
+      <c r="O16" s="208"/>
+      <c r="P16" s="209"/>
+      <c r="Q16" s="207"/>
+      <c r="R16" s="210"/>
+      <c r="S16" s="210"/>
+      <c r="T16" s="210"/>
+      <c r="U16" s="210"/>
+      <c r="V16" s="210"/>
+      <c r="W16" s="210"/>
+      <c r="X16" s="210"/>
+      <c r="Y16" s="210"/>
+      <c r="Z16" s="210"/>
+      <c r="AA16" s="210"/>
+      <c r="AB16" s="210"/>
+      <c r="AC16" s="210"/>
+      <c r="AD16" s="210"/>
+      <c r="AE16" s="211"/>
+      <c r="AF16" s="212"/>
+      <c r="AG16" s="208"/>
+      <c r="AH16" s="208"/>
+      <c r="AI16" s="209"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="21"/>
-      <c r="B17" s="165"/>
-      <c r="C17" s="166"/>
-      <c r="D17" s="167"/>
-      <c r="E17" s="168"/>
-      <c r="F17" s="169"/>
-      <c r="G17" s="165"/>
-      <c r="H17" s="170"/>
-      <c r="I17" s="166"/>
-      <c r="J17" s="171"/>
-      <c r="K17" s="172"/>
-      <c r="L17" s="172"/>
-      <c r="M17" s="172"/>
-      <c r="N17" s="172"/>
-      <c r="O17" s="172"/>
-      <c r="P17" s="173"/>
-      <c r="Q17" s="174"/>
-      <c r="R17" s="175"/>
-      <c r="S17" s="175"/>
-      <c r="T17" s="175"/>
-      <c r="U17" s="175"/>
-      <c r="V17" s="175"/>
-      <c r="W17" s="175"/>
-      <c r="X17" s="175"/>
-      <c r="Y17" s="175"/>
-      <c r="Z17" s="175"/>
-      <c r="AA17" s="175"/>
-      <c r="AB17" s="175"/>
-      <c r="AC17" s="175"/>
-      <c r="AD17" s="175"/>
-      <c r="AE17" s="176"/>
-      <c r="AF17" s="171"/>
-      <c r="AG17" s="172"/>
-      <c r="AH17" s="172"/>
-      <c r="AI17" s="173"/>
+      <c r="B17" s="201"/>
+      <c r="C17" s="202"/>
+      <c r="D17" s="203"/>
+      <c r="E17" s="204"/>
+      <c r="F17" s="205"/>
+      <c r="G17" s="201"/>
+      <c r="H17" s="206"/>
+      <c r="I17" s="202"/>
+      <c r="J17" s="212"/>
+      <c r="K17" s="208"/>
+      <c r="L17" s="208"/>
+      <c r="M17" s="208"/>
+      <c r="N17" s="208"/>
+      <c r="O17" s="208"/>
+      <c r="P17" s="209"/>
+      <c r="Q17" s="207"/>
+      <c r="R17" s="210"/>
+      <c r="S17" s="210"/>
+      <c r="T17" s="210"/>
+      <c r="U17" s="210"/>
+      <c r="V17" s="210"/>
+      <c r="W17" s="210"/>
+      <c r="X17" s="210"/>
+      <c r="Y17" s="210"/>
+      <c r="Z17" s="210"/>
+      <c r="AA17" s="210"/>
+      <c r="AB17" s="210"/>
+      <c r="AC17" s="210"/>
+      <c r="AD17" s="210"/>
+      <c r="AE17" s="211"/>
+      <c r="AF17" s="212"/>
+      <c r="AG17" s="208"/>
+      <c r="AH17" s="208"/>
+      <c r="AI17" s="209"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="21"/>
-      <c r="B18" s="165"/>
-      <c r="C18" s="166"/>
-      <c r="D18" s="167"/>
-      <c r="E18" s="168"/>
-      <c r="F18" s="169"/>
-      <c r="G18" s="165"/>
-      <c r="H18" s="170"/>
-      <c r="I18" s="166"/>
-      <c r="J18" s="171"/>
-      <c r="K18" s="172"/>
-      <c r="L18" s="172"/>
-      <c r="M18" s="172"/>
-      <c r="N18" s="172"/>
-      <c r="O18" s="172"/>
-      <c r="P18" s="173"/>
-      <c r="Q18" s="174"/>
-      <c r="R18" s="175"/>
-      <c r="S18" s="175"/>
-      <c r="T18" s="175"/>
-      <c r="U18" s="175"/>
-      <c r="V18" s="175"/>
-      <c r="W18" s="175"/>
-      <c r="X18" s="175"/>
-      <c r="Y18" s="175"/>
-      <c r="Z18" s="175"/>
-      <c r="AA18" s="175"/>
-      <c r="AB18" s="175"/>
-      <c r="AC18" s="175"/>
-      <c r="AD18" s="175"/>
-      <c r="AE18" s="176"/>
-      <c r="AF18" s="171"/>
-      <c r="AG18" s="172"/>
-      <c r="AH18" s="172"/>
-      <c r="AI18" s="173"/>
+      <c r="B18" s="201"/>
+      <c r="C18" s="202"/>
+      <c r="D18" s="203"/>
+      <c r="E18" s="204"/>
+      <c r="F18" s="205"/>
+      <c r="G18" s="201"/>
+      <c r="H18" s="206"/>
+      <c r="I18" s="202"/>
+      <c r="J18" s="212"/>
+      <c r="K18" s="208"/>
+      <c r="L18" s="208"/>
+      <c r="M18" s="208"/>
+      <c r="N18" s="208"/>
+      <c r="O18" s="208"/>
+      <c r="P18" s="209"/>
+      <c r="Q18" s="207"/>
+      <c r="R18" s="210"/>
+      <c r="S18" s="210"/>
+      <c r="T18" s="210"/>
+      <c r="U18" s="210"/>
+      <c r="V18" s="210"/>
+      <c r="W18" s="210"/>
+      <c r="X18" s="210"/>
+      <c r="Y18" s="210"/>
+      <c r="Z18" s="210"/>
+      <c r="AA18" s="210"/>
+      <c r="AB18" s="210"/>
+      <c r="AC18" s="210"/>
+      <c r="AD18" s="210"/>
+      <c r="AE18" s="211"/>
+      <c r="AF18" s="212"/>
+      <c r="AG18" s="208"/>
+      <c r="AH18" s="208"/>
+      <c r="AI18" s="209"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="21"/>
-      <c r="B19" s="165"/>
-      <c r="C19" s="166"/>
-      <c r="D19" s="167"/>
-      <c r="E19" s="168"/>
-      <c r="F19" s="169"/>
-      <c r="G19" s="165"/>
-      <c r="H19" s="170"/>
-      <c r="I19" s="166"/>
-      <c r="J19" s="171"/>
-      <c r="K19" s="172"/>
-      <c r="L19" s="172"/>
-      <c r="M19" s="172"/>
-      <c r="N19" s="172"/>
-      <c r="O19" s="172"/>
-      <c r="P19" s="173"/>
-      <c r="Q19" s="174"/>
-      <c r="R19" s="175"/>
-      <c r="S19" s="175"/>
-      <c r="T19" s="175"/>
-      <c r="U19" s="175"/>
-      <c r="V19" s="175"/>
-      <c r="W19" s="175"/>
-      <c r="X19" s="175"/>
-      <c r="Y19" s="175"/>
-      <c r="Z19" s="175"/>
-      <c r="AA19" s="175"/>
-      <c r="AB19" s="175"/>
-      <c r="AC19" s="175"/>
-      <c r="AD19" s="175"/>
-      <c r="AE19" s="176"/>
-      <c r="AF19" s="171"/>
-      <c r="AG19" s="172"/>
-      <c r="AH19" s="172"/>
-      <c r="AI19" s="173"/>
+      <c r="B19" s="201"/>
+      <c r="C19" s="202"/>
+      <c r="D19" s="203"/>
+      <c r="E19" s="204"/>
+      <c r="F19" s="205"/>
+      <c r="G19" s="201"/>
+      <c r="H19" s="206"/>
+      <c r="I19" s="202"/>
+      <c r="J19" s="212"/>
+      <c r="K19" s="208"/>
+      <c r="L19" s="208"/>
+      <c r="M19" s="208"/>
+      <c r="N19" s="208"/>
+      <c r="O19" s="208"/>
+      <c r="P19" s="209"/>
+      <c r="Q19" s="207"/>
+      <c r="R19" s="210"/>
+      <c r="S19" s="210"/>
+      <c r="T19" s="210"/>
+      <c r="U19" s="210"/>
+      <c r="V19" s="210"/>
+      <c r="W19" s="210"/>
+      <c r="X19" s="210"/>
+      <c r="Y19" s="210"/>
+      <c r="Z19" s="210"/>
+      <c r="AA19" s="210"/>
+      <c r="AB19" s="210"/>
+      <c r="AC19" s="210"/>
+      <c r="AD19" s="210"/>
+      <c r="AE19" s="211"/>
+      <c r="AF19" s="212"/>
+      <c r="AG19" s="208"/>
+      <c r="AH19" s="208"/>
+      <c r="AI19" s="209"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="21"/>
-      <c r="B20" s="165"/>
-      <c r="C20" s="166"/>
-      <c r="D20" s="167"/>
-      <c r="E20" s="168"/>
-      <c r="F20" s="169"/>
-      <c r="G20" s="165"/>
-      <c r="H20" s="170"/>
-      <c r="I20" s="166"/>
-      <c r="J20" s="171"/>
-      <c r="K20" s="172"/>
-      <c r="L20" s="172"/>
-      <c r="M20" s="172"/>
-      <c r="N20" s="172"/>
-      <c r="O20" s="172"/>
-      <c r="P20" s="173"/>
-      <c r="Q20" s="174"/>
-      <c r="R20" s="175"/>
-      <c r="S20" s="175"/>
-      <c r="T20" s="175"/>
-      <c r="U20" s="175"/>
-      <c r="V20" s="175"/>
-      <c r="W20" s="175"/>
-      <c r="X20" s="175"/>
-      <c r="Y20" s="175"/>
-      <c r="Z20" s="175"/>
-      <c r="AA20" s="175"/>
-      <c r="AB20" s="175"/>
-      <c r="AC20" s="175"/>
-      <c r="AD20" s="175"/>
-      <c r="AE20" s="176"/>
-      <c r="AF20" s="171"/>
-      <c r="AG20" s="172"/>
-      <c r="AH20" s="172"/>
-      <c r="AI20" s="173"/>
+      <c r="B20" s="201"/>
+      <c r="C20" s="202"/>
+      <c r="D20" s="203"/>
+      <c r="E20" s="204"/>
+      <c r="F20" s="205"/>
+      <c r="G20" s="201"/>
+      <c r="H20" s="206"/>
+      <c r="I20" s="202"/>
+      <c r="J20" s="212"/>
+      <c r="K20" s="208"/>
+      <c r="L20" s="208"/>
+      <c r="M20" s="208"/>
+      <c r="N20" s="208"/>
+      <c r="O20" s="208"/>
+      <c r="P20" s="209"/>
+      <c r="Q20" s="207"/>
+      <c r="R20" s="210"/>
+      <c r="S20" s="210"/>
+      <c r="T20" s="210"/>
+      <c r="U20" s="210"/>
+      <c r="V20" s="210"/>
+      <c r="W20" s="210"/>
+      <c r="X20" s="210"/>
+      <c r="Y20" s="210"/>
+      <c r="Z20" s="210"/>
+      <c r="AA20" s="210"/>
+      <c r="AB20" s="210"/>
+      <c r="AC20" s="210"/>
+      <c r="AD20" s="210"/>
+      <c r="AE20" s="211"/>
+      <c r="AF20" s="212"/>
+      <c r="AG20" s="208"/>
+      <c r="AH20" s="208"/>
+      <c r="AI20" s="209"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="21"/>
-      <c r="B21" s="165"/>
-      <c r="C21" s="166"/>
-      <c r="D21" s="167"/>
-      <c r="E21" s="168"/>
-      <c r="F21" s="169"/>
-      <c r="G21" s="165"/>
-      <c r="H21" s="170"/>
-      <c r="I21" s="166"/>
-      <c r="J21" s="171"/>
-      <c r="K21" s="172"/>
-      <c r="L21" s="172"/>
-      <c r="M21" s="172"/>
-      <c r="N21" s="172"/>
-      <c r="O21" s="172"/>
-      <c r="P21" s="173"/>
-      <c r="Q21" s="174"/>
-      <c r="R21" s="175"/>
-      <c r="S21" s="175"/>
-      <c r="T21" s="175"/>
-      <c r="U21" s="175"/>
-      <c r="V21" s="175"/>
-      <c r="W21" s="175"/>
-      <c r="X21" s="175"/>
-      <c r="Y21" s="175"/>
-      <c r="Z21" s="175"/>
-      <c r="AA21" s="175"/>
-      <c r="AB21" s="175"/>
-      <c r="AC21" s="175"/>
-      <c r="AD21" s="175"/>
-      <c r="AE21" s="176"/>
-      <c r="AF21" s="171"/>
-      <c r="AG21" s="172"/>
-      <c r="AH21" s="172"/>
-      <c r="AI21" s="173"/>
+      <c r="B21" s="201"/>
+      <c r="C21" s="202"/>
+      <c r="D21" s="203"/>
+      <c r="E21" s="204"/>
+      <c r="F21" s="205"/>
+      <c r="G21" s="201"/>
+      <c r="H21" s="206"/>
+      <c r="I21" s="202"/>
+      <c r="J21" s="212"/>
+      <c r="K21" s="208"/>
+      <c r="L21" s="208"/>
+      <c r="M21" s="208"/>
+      <c r="N21" s="208"/>
+      <c r="O21" s="208"/>
+      <c r="P21" s="209"/>
+      <c r="Q21" s="207"/>
+      <c r="R21" s="210"/>
+      <c r="S21" s="210"/>
+      <c r="T21" s="210"/>
+      <c r="U21" s="210"/>
+      <c r="V21" s="210"/>
+      <c r="W21" s="210"/>
+      <c r="X21" s="210"/>
+      <c r="Y21" s="210"/>
+      <c r="Z21" s="210"/>
+      <c r="AA21" s="210"/>
+      <c r="AB21" s="210"/>
+      <c r="AC21" s="210"/>
+      <c r="AD21" s="210"/>
+      <c r="AE21" s="211"/>
+      <c r="AF21" s="212"/>
+      <c r="AG21" s="208"/>
+      <c r="AH21" s="208"/>
+      <c r="AI21" s="209"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="21"/>
-      <c r="B22" s="165"/>
-      <c r="C22" s="166"/>
-      <c r="D22" s="167"/>
-      <c r="E22" s="168"/>
-      <c r="F22" s="169"/>
-      <c r="G22" s="165"/>
-      <c r="H22" s="170"/>
-      <c r="I22" s="166"/>
-      <c r="J22" s="171"/>
-      <c r="K22" s="172"/>
-      <c r="L22" s="172"/>
-      <c r="M22" s="172"/>
-      <c r="N22" s="172"/>
-      <c r="O22" s="172"/>
-      <c r="P22" s="173"/>
-      <c r="Q22" s="174"/>
-      <c r="R22" s="175"/>
-      <c r="S22" s="175"/>
-      <c r="T22" s="175"/>
-      <c r="U22" s="175"/>
-      <c r="V22" s="175"/>
-      <c r="W22" s="175"/>
-      <c r="X22" s="175"/>
-      <c r="Y22" s="175"/>
-      <c r="Z22" s="175"/>
-      <c r="AA22" s="175"/>
-      <c r="AB22" s="175"/>
-      <c r="AC22" s="175"/>
-      <c r="AD22" s="175"/>
-      <c r="AE22" s="176"/>
-      <c r="AF22" s="171"/>
-      <c r="AG22" s="172"/>
-      <c r="AH22" s="172"/>
-      <c r="AI22" s="173"/>
+      <c r="B22" s="201"/>
+      <c r="C22" s="202"/>
+      <c r="D22" s="203"/>
+      <c r="E22" s="204"/>
+      <c r="F22" s="205"/>
+      <c r="G22" s="201"/>
+      <c r="H22" s="206"/>
+      <c r="I22" s="202"/>
+      <c r="J22" s="212"/>
+      <c r="K22" s="208"/>
+      <c r="L22" s="208"/>
+      <c r="M22" s="208"/>
+      <c r="N22" s="208"/>
+      <c r="O22" s="208"/>
+      <c r="P22" s="209"/>
+      <c r="Q22" s="207"/>
+      <c r="R22" s="210"/>
+      <c r="S22" s="210"/>
+      <c r="T22" s="210"/>
+      <c r="U22" s="210"/>
+      <c r="V22" s="210"/>
+      <c r="W22" s="210"/>
+      <c r="X22" s="210"/>
+      <c r="Y22" s="210"/>
+      <c r="Z22" s="210"/>
+      <c r="AA22" s="210"/>
+      <c r="AB22" s="210"/>
+      <c r="AC22" s="210"/>
+      <c r="AD22" s="210"/>
+      <c r="AE22" s="211"/>
+      <c r="AF22" s="212"/>
+      <c r="AG22" s="208"/>
+      <c r="AH22" s="208"/>
+      <c r="AI22" s="209"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="21"/>
-      <c r="B23" s="165"/>
-      <c r="C23" s="166"/>
-      <c r="D23" s="167"/>
-      <c r="E23" s="168"/>
-      <c r="F23" s="169"/>
-      <c r="G23" s="165"/>
-      <c r="H23" s="170"/>
-      <c r="I23" s="166"/>
-      <c r="J23" s="171"/>
-      <c r="K23" s="172"/>
-      <c r="L23" s="172"/>
-      <c r="M23" s="172"/>
-      <c r="N23" s="172"/>
-      <c r="O23" s="172"/>
-      <c r="P23" s="173"/>
-      <c r="Q23" s="174"/>
-      <c r="R23" s="175"/>
-      <c r="S23" s="175"/>
-      <c r="T23" s="175"/>
-      <c r="U23" s="175"/>
-      <c r="V23" s="175"/>
-      <c r="W23" s="175"/>
-      <c r="X23" s="175"/>
-      <c r="Y23" s="175"/>
-      <c r="Z23" s="175"/>
-      <c r="AA23" s="175"/>
-      <c r="AB23" s="175"/>
-      <c r="AC23" s="175"/>
-      <c r="AD23" s="175"/>
-      <c r="AE23" s="176"/>
-      <c r="AF23" s="171"/>
-      <c r="AG23" s="172"/>
-      <c r="AH23" s="172"/>
-      <c r="AI23" s="173"/>
+      <c r="B23" s="201"/>
+      <c r="C23" s="202"/>
+      <c r="D23" s="203"/>
+      <c r="E23" s="204"/>
+      <c r="F23" s="205"/>
+      <c r="G23" s="201"/>
+      <c r="H23" s="206"/>
+      <c r="I23" s="202"/>
+      <c r="J23" s="212"/>
+      <c r="K23" s="208"/>
+      <c r="L23" s="208"/>
+      <c r="M23" s="208"/>
+      <c r="N23" s="208"/>
+      <c r="O23" s="208"/>
+      <c r="P23" s="209"/>
+      <c r="Q23" s="207"/>
+      <c r="R23" s="210"/>
+      <c r="S23" s="210"/>
+      <c r="T23" s="210"/>
+      <c r="U23" s="210"/>
+      <c r="V23" s="210"/>
+      <c r="W23" s="210"/>
+      <c r="X23" s="210"/>
+      <c r="Y23" s="210"/>
+      <c r="Z23" s="210"/>
+      <c r="AA23" s="210"/>
+      <c r="AB23" s="210"/>
+      <c r="AC23" s="210"/>
+      <c r="AD23" s="210"/>
+      <c r="AE23" s="211"/>
+      <c r="AF23" s="212"/>
+      <c r="AG23" s="208"/>
+      <c r="AH23" s="208"/>
+      <c r="AI23" s="209"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="21"/>
-      <c r="B24" s="165"/>
-      <c r="C24" s="166"/>
-      <c r="D24" s="167"/>
-      <c r="E24" s="168"/>
-      <c r="F24" s="169"/>
-      <c r="G24" s="165"/>
-      <c r="H24" s="170"/>
-      <c r="I24" s="166"/>
-      <c r="J24" s="171"/>
-      <c r="K24" s="172"/>
-      <c r="L24" s="172"/>
-      <c r="M24" s="172"/>
-      <c r="N24" s="172"/>
-      <c r="O24" s="172"/>
-      <c r="P24" s="173"/>
-      <c r="Q24" s="174"/>
-      <c r="R24" s="175"/>
-      <c r="S24" s="175"/>
-      <c r="T24" s="175"/>
-      <c r="U24" s="175"/>
-      <c r="V24" s="175"/>
-      <c r="W24" s="175"/>
-      <c r="X24" s="175"/>
-      <c r="Y24" s="175"/>
-      <c r="Z24" s="175"/>
-      <c r="AA24" s="175"/>
-      <c r="AB24" s="175"/>
-      <c r="AC24" s="175"/>
-      <c r="AD24" s="175"/>
-      <c r="AE24" s="176"/>
-      <c r="AF24" s="171"/>
-      <c r="AG24" s="172"/>
-      <c r="AH24" s="172"/>
-      <c r="AI24" s="173"/>
+      <c r="B24" s="201"/>
+      <c r="C24" s="202"/>
+      <c r="D24" s="203"/>
+      <c r="E24" s="204"/>
+      <c r="F24" s="205"/>
+      <c r="G24" s="201"/>
+      <c r="H24" s="206"/>
+      <c r="I24" s="202"/>
+      <c r="J24" s="212"/>
+      <c r="K24" s="208"/>
+      <c r="L24" s="208"/>
+      <c r="M24" s="208"/>
+      <c r="N24" s="208"/>
+      <c r="O24" s="208"/>
+      <c r="P24" s="209"/>
+      <c r="Q24" s="207"/>
+      <c r="R24" s="210"/>
+      <c r="S24" s="210"/>
+      <c r="T24" s="210"/>
+      <c r="U24" s="210"/>
+      <c r="V24" s="210"/>
+      <c r="W24" s="210"/>
+      <c r="X24" s="210"/>
+      <c r="Y24" s="210"/>
+      <c r="Z24" s="210"/>
+      <c r="AA24" s="210"/>
+      <c r="AB24" s="210"/>
+      <c r="AC24" s="210"/>
+      <c r="AD24" s="210"/>
+      <c r="AE24" s="211"/>
+      <c r="AF24" s="212"/>
+      <c r="AG24" s="208"/>
+      <c r="AH24" s="208"/>
+      <c r="AI24" s="209"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="21"/>
-      <c r="B25" s="165"/>
-      <c r="C25" s="166"/>
-      <c r="D25" s="167"/>
-      <c r="E25" s="168"/>
-      <c r="F25" s="169"/>
-      <c r="G25" s="165"/>
-      <c r="H25" s="170"/>
-      <c r="I25" s="166"/>
-      <c r="J25" s="171"/>
-      <c r="K25" s="172"/>
-      <c r="L25" s="172"/>
-      <c r="M25" s="172"/>
-      <c r="N25" s="172"/>
-      <c r="O25" s="172"/>
-      <c r="P25" s="173"/>
-      <c r="Q25" s="174"/>
-      <c r="R25" s="175"/>
-      <c r="S25" s="175"/>
-      <c r="T25" s="175"/>
-      <c r="U25" s="175"/>
-      <c r="V25" s="175"/>
-      <c r="W25" s="175"/>
-      <c r="X25" s="175"/>
-      <c r="Y25" s="175"/>
-      <c r="Z25" s="175"/>
-      <c r="AA25" s="175"/>
-      <c r="AB25" s="175"/>
-      <c r="AC25" s="175"/>
-      <c r="AD25" s="175"/>
-      <c r="AE25" s="176"/>
-      <c r="AF25" s="171"/>
-      <c r="AG25" s="172"/>
-      <c r="AH25" s="172"/>
-      <c r="AI25" s="173"/>
+      <c r="B25" s="201"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="203"/>
+      <c r="E25" s="204"/>
+      <c r="F25" s="205"/>
+      <c r="G25" s="201"/>
+      <c r="H25" s="206"/>
+      <c r="I25" s="202"/>
+      <c r="J25" s="212"/>
+      <c r="K25" s="208"/>
+      <c r="L25" s="208"/>
+      <c r="M25" s="208"/>
+      <c r="N25" s="208"/>
+      <c r="O25" s="208"/>
+      <c r="P25" s="209"/>
+      <c r="Q25" s="207"/>
+      <c r="R25" s="210"/>
+      <c r="S25" s="210"/>
+      <c r="T25" s="210"/>
+      <c r="U25" s="210"/>
+      <c r="V25" s="210"/>
+      <c r="W25" s="210"/>
+      <c r="X25" s="210"/>
+      <c r="Y25" s="210"/>
+      <c r="Z25" s="210"/>
+      <c r="AA25" s="210"/>
+      <c r="AB25" s="210"/>
+      <c r="AC25" s="210"/>
+      <c r="AD25" s="210"/>
+      <c r="AE25" s="211"/>
+      <c r="AF25" s="212"/>
+      <c r="AG25" s="208"/>
+      <c r="AH25" s="208"/>
+      <c r="AI25" s="209"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="21"/>
-      <c r="B26" s="165"/>
-      <c r="C26" s="166"/>
-      <c r="D26" s="167"/>
-      <c r="E26" s="168"/>
-      <c r="F26" s="169"/>
-      <c r="G26" s="165"/>
-      <c r="H26" s="170"/>
-      <c r="I26" s="166"/>
-      <c r="J26" s="171"/>
-      <c r="K26" s="172"/>
-      <c r="L26" s="172"/>
-      <c r="M26" s="172"/>
-      <c r="N26" s="172"/>
-      <c r="O26" s="172"/>
-      <c r="P26" s="173"/>
-      <c r="Q26" s="174"/>
-      <c r="R26" s="175"/>
-      <c r="S26" s="175"/>
-      <c r="T26" s="175"/>
-      <c r="U26" s="175"/>
-      <c r="V26" s="175"/>
-      <c r="W26" s="175"/>
-      <c r="X26" s="175"/>
-      <c r="Y26" s="175"/>
-      <c r="Z26" s="175"/>
-      <c r="AA26" s="175"/>
-      <c r="AB26" s="175"/>
-      <c r="AC26" s="175"/>
-      <c r="AD26" s="175"/>
-      <c r="AE26" s="176"/>
-      <c r="AF26" s="171"/>
-      <c r="AG26" s="172"/>
-      <c r="AH26" s="172"/>
-      <c r="AI26" s="173"/>
+      <c r="B26" s="201"/>
+      <c r="C26" s="202"/>
+      <c r="D26" s="203"/>
+      <c r="E26" s="204"/>
+      <c r="F26" s="205"/>
+      <c r="G26" s="201"/>
+      <c r="H26" s="206"/>
+      <c r="I26" s="202"/>
+      <c r="J26" s="212"/>
+      <c r="K26" s="208"/>
+      <c r="L26" s="208"/>
+      <c r="M26" s="208"/>
+      <c r="N26" s="208"/>
+      <c r="O26" s="208"/>
+      <c r="P26" s="209"/>
+      <c r="Q26" s="207"/>
+      <c r="R26" s="210"/>
+      <c r="S26" s="210"/>
+      <c r="T26" s="210"/>
+      <c r="U26" s="210"/>
+      <c r="V26" s="210"/>
+      <c r="W26" s="210"/>
+      <c r="X26" s="210"/>
+      <c r="Y26" s="210"/>
+      <c r="Z26" s="210"/>
+      <c r="AA26" s="210"/>
+      <c r="AB26" s="210"/>
+      <c r="AC26" s="210"/>
+      <c r="AD26" s="210"/>
+      <c r="AE26" s="211"/>
+      <c r="AF26" s="212"/>
+      <c r="AG26" s="208"/>
+      <c r="AH26" s="208"/>
+      <c r="AI26" s="209"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="21"/>
-      <c r="B27" s="165"/>
-      <c r="C27" s="166"/>
-      <c r="D27" s="167"/>
-      <c r="E27" s="168"/>
-      <c r="F27" s="169"/>
-      <c r="G27" s="165"/>
-      <c r="H27" s="170"/>
-      <c r="I27" s="166"/>
-      <c r="J27" s="171"/>
-      <c r="K27" s="172"/>
-      <c r="L27" s="172"/>
-      <c r="M27" s="172"/>
-      <c r="N27" s="172"/>
-      <c r="O27" s="172"/>
-      <c r="P27" s="173"/>
-      <c r="Q27" s="174"/>
-      <c r="R27" s="175"/>
-      <c r="S27" s="175"/>
-      <c r="T27" s="175"/>
-      <c r="U27" s="175"/>
-      <c r="V27" s="175"/>
-      <c r="W27" s="175"/>
-      <c r="X27" s="175"/>
-      <c r="Y27" s="175"/>
-      <c r="Z27" s="175"/>
-      <c r="AA27" s="175"/>
-      <c r="AB27" s="175"/>
-      <c r="AC27" s="175"/>
-      <c r="AD27" s="175"/>
-      <c r="AE27" s="176"/>
-      <c r="AF27" s="171"/>
-      <c r="AG27" s="172"/>
-      <c r="AH27" s="172"/>
-      <c r="AI27" s="173"/>
+      <c r="B27" s="201"/>
+      <c r="C27" s="202"/>
+      <c r="D27" s="203"/>
+      <c r="E27" s="204"/>
+      <c r="F27" s="205"/>
+      <c r="G27" s="201"/>
+      <c r="H27" s="206"/>
+      <c r="I27" s="202"/>
+      <c r="J27" s="212"/>
+      <c r="K27" s="208"/>
+      <c r="L27" s="208"/>
+      <c r="M27" s="208"/>
+      <c r="N27" s="208"/>
+      <c r="O27" s="208"/>
+      <c r="P27" s="209"/>
+      <c r="Q27" s="207"/>
+      <c r="R27" s="210"/>
+      <c r="S27" s="210"/>
+      <c r="T27" s="210"/>
+      <c r="U27" s="210"/>
+      <c r="V27" s="210"/>
+      <c r="W27" s="210"/>
+      <c r="X27" s="210"/>
+      <c r="Y27" s="210"/>
+      <c r="Z27" s="210"/>
+      <c r="AA27" s="210"/>
+      <c r="AB27" s="210"/>
+      <c r="AC27" s="210"/>
+      <c r="AD27" s="210"/>
+      <c r="AE27" s="211"/>
+      <c r="AF27" s="212"/>
+      <c r="AG27" s="208"/>
+      <c r="AH27" s="208"/>
+      <c r="AI27" s="209"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="21"/>
-      <c r="B28" s="165"/>
-      <c r="C28" s="166"/>
-      <c r="D28" s="167"/>
-      <c r="E28" s="168"/>
-      <c r="F28" s="169"/>
-      <c r="G28" s="165"/>
-      <c r="H28" s="170"/>
-      <c r="I28" s="166"/>
-      <c r="J28" s="171"/>
-      <c r="K28" s="172"/>
-      <c r="L28" s="172"/>
-      <c r="M28" s="172"/>
-      <c r="N28" s="172"/>
-      <c r="O28" s="172"/>
-      <c r="P28" s="173"/>
-      <c r="Q28" s="174"/>
-      <c r="R28" s="175"/>
-      <c r="S28" s="175"/>
-      <c r="T28" s="175"/>
-      <c r="U28" s="175"/>
-      <c r="V28" s="175"/>
-      <c r="W28" s="175"/>
-      <c r="X28" s="175"/>
-      <c r="Y28" s="175"/>
-      <c r="Z28" s="175"/>
-      <c r="AA28" s="175"/>
-      <c r="AB28" s="175"/>
-      <c r="AC28" s="175"/>
-      <c r="AD28" s="175"/>
-      <c r="AE28" s="176"/>
-      <c r="AF28" s="171"/>
-      <c r="AG28" s="172"/>
-      <c r="AH28" s="172"/>
-      <c r="AI28" s="173"/>
+      <c r="B28" s="201"/>
+      <c r="C28" s="202"/>
+      <c r="D28" s="203"/>
+      <c r="E28" s="204"/>
+      <c r="F28" s="205"/>
+      <c r="G28" s="201"/>
+      <c r="H28" s="206"/>
+      <c r="I28" s="202"/>
+      <c r="J28" s="212"/>
+      <c r="K28" s="208"/>
+      <c r="L28" s="208"/>
+      <c r="M28" s="208"/>
+      <c r="N28" s="208"/>
+      <c r="O28" s="208"/>
+      <c r="P28" s="209"/>
+      <c r="Q28" s="207"/>
+      <c r="R28" s="210"/>
+      <c r="S28" s="210"/>
+      <c r="T28" s="210"/>
+      <c r="U28" s="210"/>
+      <c r="V28" s="210"/>
+      <c r="W28" s="210"/>
+      <c r="X28" s="210"/>
+      <c r="Y28" s="210"/>
+      <c r="Z28" s="210"/>
+      <c r="AA28" s="210"/>
+      <c r="AB28" s="210"/>
+      <c r="AC28" s="210"/>
+      <c r="AD28" s="210"/>
+      <c r="AE28" s="211"/>
+      <c r="AF28" s="212"/>
+      <c r="AG28" s="208"/>
+      <c r="AH28" s="208"/>
+      <c r="AI28" s="209"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="21"/>
-      <c r="B29" s="165"/>
-      <c r="C29" s="166"/>
-      <c r="D29" s="167"/>
-      <c r="E29" s="168"/>
-      <c r="F29" s="169"/>
-      <c r="G29" s="165"/>
-      <c r="H29" s="170"/>
-      <c r="I29" s="166"/>
-      <c r="J29" s="171"/>
-      <c r="K29" s="172"/>
-      <c r="L29" s="172"/>
-      <c r="M29" s="172"/>
-      <c r="N29" s="172"/>
-      <c r="O29" s="172"/>
-      <c r="P29" s="173"/>
-      <c r="Q29" s="174"/>
-      <c r="R29" s="175"/>
-      <c r="S29" s="175"/>
-      <c r="T29" s="175"/>
-      <c r="U29" s="175"/>
-      <c r="V29" s="175"/>
-      <c r="W29" s="175"/>
-      <c r="X29" s="175"/>
-      <c r="Y29" s="175"/>
-      <c r="Z29" s="175"/>
-      <c r="AA29" s="175"/>
-      <c r="AB29" s="175"/>
-      <c r="AC29" s="175"/>
-      <c r="AD29" s="175"/>
-      <c r="AE29" s="176"/>
-      <c r="AF29" s="171"/>
-      <c r="AG29" s="172"/>
-      <c r="AH29" s="172"/>
-      <c r="AI29" s="173"/>
+      <c r="B29" s="201"/>
+      <c r="C29" s="202"/>
+      <c r="D29" s="203"/>
+      <c r="E29" s="204"/>
+      <c r="F29" s="205"/>
+      <c r="G29" s="201"/>
+      <c r="H29" s="206"/>
+      <c r="I29" s="202"/>
+      <c r="J29" s="212"/>
+      <c r="K29" s="208"/>
+      <c r="L29" s="208"/>
+      <c r="M29" s="208"/>
+      <c r="N29" s="208"/>
+      <c r="O29" s="208"/>
+      <c r="P29" s="209"/>
+      <c r="Q29" s="207"/>
+      <c r="R29" s="210"/>
+      <c r="S29" s="210"/>
+      <c r="T29" s="210"/>
+      <c r="U29" s="210"/>
+      <c r="V29" s="210"/>
+      <c r="W29" s="210"/>
+      <c r="X29" s="210"/>
+      <c r="Y29" s="210"/>
+      <c r="Z29" s="210"/>
+      <c r="AA29" s="210"/>
+      <c r="AB29" s="210"/>
+      <c r="AC29" s="210"/>
+      <c r="AD29" s="210"/>
+      <c r="AE29" s="211"/>
+      <c r="AF29" s="212"/>
+      <c r="AG29" s="208"/>
+      <c r="AH29" s="208"/>
+      <c r="AI29" s="209"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="21"/>
-      <c r="B30" s="165"/>
-      <c r="C30" s="166"/>
-      <c r="D30" s="167"/>
-      <c r="E30" s="168"/>
-      <c r="F30" s="169"/>
-      <c r="G30" s="165"/>
-      <c r="H30" s="170"/>
-      <c r="I30" s="166"/>
-      <c r="J30" s="171"/>
-      <c r="K30" s="172"/>
-      <c r="L30" s="172"/>
-      <c r="M30" s="172"/>
-      <c r="N30" s="172"/>
-      <c r="O30" s="172"/>
-      <c r="P30" s="173"/>
-      <c r="Q30" s="174"/>
-      <c r="R30" s="175"/>
-      <c r="S30" s="175"/>
-      <c r="T30" s="175"/>
-      <c r="U30" s="175"/>
-      <c r="V30" s="175"/>
-      <c r="W30" s="175"/>
-      <c r="X30" s="175"/>
-      <c r="Y30" s="175"/>
-      <c r="Z30" s="175"/>
-      <c r="AA30" s="175"/>
-      <c r="AB30" s="175"/>
-      <c r="AC30" s="175"/>
-      <c r="AD30" s="175"/>
-      <c r="AE30" s="176"/>
-      <c r="AF30" s="171"/>
-      <c r="AG30" s="172"/>
-      <c r="AH30" s="172"/>
-      <c r="AI30" s="173"/>
+      <c r="B30" s="201"/>
+      <c r="C30" s="202"/>
+      <c r="D30" s="203"/>
+      <c r="E30" s="204"/>
+      <c r="F30" s="205"/>
+      <c r="G30" s="201"/>
+      <c r="H30" s="206"/>
+      <c r="I30" s="202"/>
+      <c r="J30" s="212"/>
+      <c r="K30" s="208"/>
+      <c r="L30" s="208"/>
+      <c r="M30" s="208"/>
+      <c r="N30" s="208"/>
+      <c r="O30" s="208"/>
+      <c r="P30" s="209"/>
+      <c r="Q30" s="207"/>
+      <c r="R30" s="210"/>
+      <c r="S30" s="210"/>
+      <c r="T30" s="210"/>
+      <c r="U30" s="210"/>
+      <c r="V30" s="210"/>
+      <c r="W30" s="210"/>
+      <c r="X30" s="210"/>
+      <c r="Y30" s="210"/>
+      <c r="Z30" s="210"/>
+      <c r="AA30" s="210"/>
+      <c r="AB30" s="210"/>
+      <c r="AC30" s="210"/>
+      <c r="AD30" s="210"/>
+      <c r="AE30" s="211"/>
+      <c r="AF30" s="212"/>
+      <c r="AG30" s="208"/>
+      <c r="AH30" s="208"/>
+      <c r="AI30" s="209"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="165"/>
-      <c r="C31" s="166"/>
-      <c r="D31" s="167"/>
-      <c r="E31" s="168"/>
-      <c r="F31" s="169"/>
-      <c r="G31" s="165"/>
-      <c r="H31" s="170"/>
-      <c r="I31" s="166"/>
-      <c r="J31" s="171"/>
-      <c r="K31" s="172"/>
-      <c r="L31" s="172"/>
-      <c r="M31" s="172"/>
-      <c r="N31" s="172"/>
-      <c r="O31" s="172"/>
-      <c r="P31" s="173"/>
-      <c r="Q31" s="174"/>
-      <c r="R31" s="175"/>
-      <c r="S31" s="175"/>
-      <c r="T31" s="175"/>
-      <c r="U31" s="175"/>
-      <c r="V31" s="175"/>
-      <c r="W31" s="175"/>
-      <c r="X31" s="175"/>
-      <c r="Y31" s="175"/>
-      <c r="Z31" s="175"/>
-      <c r="AA31" s="175"/>
-      <c r="AB31" s="175"/>
-      <c r="AC31" s="175"/>
-      <c r="AD31" s="175"/>
-      <c r="AE31" s="176"/>
-      <c r="AF31" s="171"/>
-      <c r="AG31" s="172"/>
-      <c r="AH31" s="172"/>
-      <c r="AI31" s="173"/>
+      <c r="B31" s="201"/>
+      <c r="C31" s="202"/>
+      <c r="D31" s="203"/>
+      <c r="E31" s="204"/>
+      <c r="F31" s="205"/>
+      <c r="G31" s="201"/>
+      <c r="H31" s="206"/>
+      <c r="I31" s="202"/>
+      <c r="J31" s="212"/>
+      <c r="K31" s="208"/>
+      <c r="L31" s="208"/>
+      <c r="M31" s="208"/>
+      <c r="N31" s="208"/>
+      <c r="O31" s="208"/>
+      <c r="P31" s="209"/>
+      <c r="Q31" s="207"/>
+      <c r="R31" s="210"/>
+      <c r="S31" s="210"/>
+      <c r="T31" s="210"/>
+      <c r="U31" s="210"/>
+      <c r="V31" s="210"/>
+      <c r="W31" s="210"/>
+      <c r="X31" s="210"/>
+      <c r="Y31" s="210"/>
+      <c r="Z31" s="210"/>
+      <c r="AA31" s="210"/>
+      <c r="AB31" s="210"/>
+      <c r="AC31" s="210"/>
+      <c r="AD31" s="210"/>
+      <c r="AE31" s="211"/>
+      <c r="AF31" s="212"/>
+      <c r="AG31" s="208"/>
+      <c r="AH31" s="208"/>
+      <c r="AI31" s="209"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="21"/>
-      <c r="B32" s="165"/>
-      <c r="C32" s="166"/>
-      <c r="D32" s="167"/>
-      <c r="E32" s="168"/>
-      <c r="F32" s="169"/>
-      <c r="G32" s="165"/>
-      <c r="H32" s="170"/>
-      <c r="I32" s="166"/>
-      <c r="J32" s="171"/>
-      <c r="K32" s="177"/>
-      <c r="L32" s="172"/>
-      <c r="M32" s="172"/>
-      <c r="N32" s="172"/>
-      <c r="O32" s="172"/>
-      <c r="P32" s="173"/>
-      <c r="Q32" s="174"/>
-      <c r="R32" s="175"/>
-      <c r="S32" s="175"/>
-      <c r="T32" s="175"/>
-      <c r="U32" s="175"/>
-      <c r="V32" s="175"/>
-      <c r="W32" s="175"/>
-      <c r="X32" s="175"/>
-      <c r="Y32" s="175"/>
-      <c r="Z32" s="175"/>
-      <c r="AA32" s="175"/>
-      <c r="AB32" s="175"/>
-      <c r="AC32" s="175"/>
-      <c r="AD32" s="175"/>
-      <c r="AE32" s="176"/>
-      <c r="AF32" s="171"/>
-      <c r="AG32" s="172"/>
-      <c r="AH32" s="172"/>
-      <c r="AI32" s="173"/>
+      <c r="B32" s="201"/>
+      <c r="C32" s="202"/>
+      <c r="D32" s="203"/>
+      <c r="E32" s="204"/>
+      <c r="F32" s="205"/>
+      <c r="G32" s="201"/>
+      <c r="H32" s="206"/>
+      <c r="I32" s="202"/>
+      <c r="J32" s="212"/>
+      <c r="K32" s="222"/>
+      <c r="L32" s="208"/>
+      <c r="M32" s="208"/>
+      <c r="N32" s="208"/>
+      <c r="O32" s="208"/>
+      <c r="P32" s="209"/>
+      <c r="Q32" s="207"/>
+      <c r="R32" s="210"/>
+      <c r="S32" s="210"/>
+      <c r="T32" s="210"/>
+      <c r="U32" s="210"/>
+      <c r="V32" s="210"/>
+      <c r="W32" s="210"/>
+      <c r="X32" s="210"/>
+      <c r="Y32" s="210"/>
+      <c r="Z32" s="210"/>
+      <c r="AA32" s="210"/>
+      <c r="AB32" s="210"/>
+      <c r="AC32" s="210"/>
+      <c r="AD32" s="210"/>
+      <c r="AE32" s="211"/>
+      <c r="AF32" s="212"/>
+      <c r="AG32" s="208"/>
+      <c r="AH32" s="208"/>
+      <c r="AI32" s="209"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="21"/>
-      <c r="B33" s="165"/>
-      <c r="C33" s="166"/>
-      <c r="D33" s="167"/>
-      <c r="E33" s="168"/>
-      <c r="F33" s="169"/>
-      <c r="G33" s="165"/>
-      <c r="H33" s="170"/>
-      <c r="I33" s="166"/>
-      <c r="J33" s="171"/>
-      <c r="K33" s="172"/>
-      <c r="L33" s="172"/>
-      <c r="M33" s="172"/>
-      <c r="N33" s="172"/>
-      <c r="O33" s="172"/>
-      <c r="P33" s="173"/>
-      <c r="Q33" s="174"/>
-      <c r="R33" s="175"/>
-      <c r="S33" s="175"/>
-      <c r="T33" s="175"/>
-      <c r="U33" s="175"/>
-      <c r="V33" s="175"/>
-      <c r="W33" s="175"/>
-      <c r="X33" s="175"/>
-      <c r="Y33" s="175"/>
-      <c r="Z33" s="175"/>
-      <c r="AA33" s="175"/>
-      <c r="AB33" s="175"/>
-      <c r="AC33" s="175"/>
-      <c r="AD33" s="175"/>
-      <c r="AE33" s="176"/>
-      <c r="AF33" s="171"/>
-      <c r="AG33" s="172"/>
-      <c r="AH33" s="172"/>
-      <c r="AI33" s="173"/>
+      <c r="B33" s="201"/>
+      <c r="C33" s="202"/>
+      <c r="D33" s="203"/>
+      <c r="E33" s="204"/>
+      <c r="F33" s="205"/>
+      <c r="G33" s="201"/>
+      <c r="H33" s="206"/>
+      <c r="I33" s="202"/>
+      <c r="J33" s="212"/>
+      <c r="K33" s="208"/>
+      <c r="L33" s="208"/>
+      <c r="M33" s="208"/>
+      <c r="N33" s="208"/>
+      <c r="O33" s="208"/>
+      <c r="P33" s="209"/>
+      <c r="Q33" s="207"/>
+      <c r="R33" s="210"/>
+      <c r="S33" s="210"/>
+      <c r="T33" s="210"/>
+      <c r="U33" s="210"/>
+      <c r="V33" s="210"/>
+      <c r="W33" s="210"/>
+      <c r="X33" s="210"/>
+      <c r="Y33" s="210"/>
+      <c r="Z33" s="210"/>
+      <c r="AA33" s="210"/>
+      <c r="AB33" s="210"/>
+      <c r="AC33" s="210"/>
+      <c r="AD33" s="210"/>
+      <c r="AE33" s="211"/>
+      <c r="AF33" s="212"/>
+      <c r="AG33" s="208"/>
+      <c r="AH33" s="208"/>
+      <c r="AI33" s="209"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -15500,161 +15662,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -26637,7 +26644,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="28" t="s">
-        <v>580</v>
+        <v>648</v>
       </c>
       <c r="O7" s="28" t="s">
         <v>23</v>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(バッチ)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(バッチ)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D61BEC-12DB-4BC3-87B4-E6036CB9EB48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B77CD9C-CE51-43EB-AC17-55DC8C47BF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="619" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8942,9 +8942,9 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>バッチ処理ID：RBxxxxxxxx</t>
-    <rPh sb="3" eb="5">
-      <t>ショリ</t>
+    <t>テストターゲット名：RBxxxxxxxx</t>
+    <rPh sb="8" eb="9">
+      <t>メイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -9889,72 +9889,6 @@
     <xf numFmtId="31" fontId="13" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="6" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -10061,6 +9995,72 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -14232,57 +14232,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="170" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="194"/>
-      <c r="E1" s="195" t="s">
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="173" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="196"/>
-      <c r="G1" s="196"/>
-      <c r="H1" s="196"/>
-      <c r="I1" s="196"/>
-      <c r="J1" s="196"/>
-      <c r="K1" s="196"/>
-      <c r="L1" s="196"/>
-      <c r="M1" s="196"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="201" t="s">
+      <c r="F1" s="174"/>
+      <c r="G1" s="174"/>
+      <c r="H1" s="174"/>
+      <c r="I1" s="174"/>
+      <c r="J1" s="174"/>
+      <c r="K1" s="174"/>
+      <c r="L1" s="174"/>
+      <c r="M1" s="174"/>
+      <c r="N1" s="175"/>
+      <c r="O1" s="179" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="202"/>
-      <c r="Q1" s="202"/>
-      <c r="R1" s="203"/>
-      <c r="S1" s="210" t="s">
+      <c r="P1" s="180"/>
+      <c r="Q1" s="180"/>
+      <c r="R1" s="181"/>
+      <c r="S1" s="188" t="s">
         <v>642</v>
       </c>
-      <c r="T1" s="211"/>
-      <c r="U1" s="211"/>
-      <c r="V1" s="211"/>
-      <c r="W1" s="211"/>
-      <c r="X1" s="211"/>
-      <c r="Y1" s="211"/>
-      <c r="Z1" s="212"/>
-      <c r="AA1" s="192" t="s">
+      <c r="T1" s="189"/>
+      <c r="U1" s="189"/>
+      <c r="V1" s="189"/>
+      <c r="W1" s="189"/>
+      <c r="X1" s="189"/>
+      <c r="Y1" s="189"/>
+      <c r="Z1" s="190"/>
+      <c r="AA1" s="170" t="s">
         <v>65</v>
       </c>
-      <c r="AB1" s="194"/>
-      <c r="AC1" s="219" t="str">
+      <c r="AB1" s="172"/>
+      <c r="AC1" s="197" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="220"/>
-      <c r="AE1" s="220"/>
-      <c r="AF1" s="221"/>
-      <c r="AG1" s="186">
+      <c r="AD1" s="198"/>
+      <c r="AE1" s="198"/>
+      <c r="AF1" s="199"/>
+      <c r="AG1" s="164">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="187"/>
-      <c r="AI1" s="188"/>
+      <c r="AH1" s="165"/>
+      <c r="AI1" s="166"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -14290,53 +14290,53 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="192" t="s">
+      <c r="A2" s="170" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="193"/>
-      <c r="C2" s="193"/>
-      <c r="D2" s="194"/>
-      <c r="E2" s="195" t="s">
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="173" t="s">
         <v>84</v>
       </c>
-      <c r="F2" s="196"/>
-      <c r="G2" s="196"/>
-      <c r="H2" s="196"/>
-      <c r="I2" s="196"/>
-      <c r="J2" s="196"/>
-      <c r="K2" s="196"/>
-      <c r="L2" s="196"/>
-      <c r="M2" s="196"/>
-      <c r="N2" s="197"/>
-      <c r="O2" s="204"/>
-      <c r="P2" s="205"/>
-      <c r="Q2" s="205"/>
-      <c r="R2" s="206"/>
-      <c r="S2" s="213"/>
-      <c r="T2" s="214"/>
-      <c r="U2" s="214"/>
-      <c r="V2" s="214"/>
-      <c r="W2" s="214"/>
-      <c r="X2" s="214"/>
-      <c r="Y2" s="214"/>
-      <c r="Z2" s="215"/>
-      <c r="AA2" s="192" t="s">
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
+      <c r="L2" s="174"/>
+      <c r="M2" s="174"/>
+      <c r="N2" s="175"/>
+      <c r="O2" s="182"/>
+      <c r="P2" s="183"/>
+      <c r="Q2" s="183"/>
+      <c r="R2" s="184"/>
+      <c r="S2" s="191"/>
+      <c r="T2" s="192"/>
+      <c r="U2" s="192"/>
+      <c r="V2" s="192"/>
+      <c r="W2" s="192"/>
+      <c r="X2" s="192"/>
+      <c r="Y2" s="192"/>
+      <c r="Z2" s="193"/>
+      <c r="AA2" s="170" t="s">
         <v>67</v>
       </c>
-      <c r="AB2" s="194"/>
-      <c r="AC2" s="198" t="str">
+      <c r="AB2" s="172"/>
+      <c r="AC2" s="176" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="199"/>
-      <c r="AE2" s="199"/>
-      <c r="AF2" s="200"/>
-      <c r="AG2" s="186">
+      <c r="AD2" s="177"/>
+      <c r="AE2" s="177"/>
+      <c r="AF2" s="178"/>
+      <c r="AG2" s="164">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44852</v>
       </c>
-      <c r="AH2" s="187"/>
-      <c r="AI2" s="188"/>
+      <c r="AH2" s="165"/>
+      <c r="AI2" s="166"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -14344,45 +14344,45 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="192" t="s">
+      <c r="A3" s="170" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="193"/>
-      <c r="C3" s="193"/>
-      <c r="D3" s="194"/>
-      <c r="E3" s="195" t="s">
+      <c r="B3" s="171"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="173" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="196"/>
-      <c r="G3" s="196"/>
-      <c r="H3" s="196"/>
-      <c r="I3" s="196"/>
-      <c r="J3" s="196"/>
-      <c r="K3" s="196"/>
-      <c r="L3" s="196"/>
-      <c r="M3" s="196"/>
-      <c r="N3" s="197"/>
-      <c r="O3" s="207"/>
-      <c r="P3" s="208"/>
-      <c r="Q3" s="208"/>
-      <c r="R3" s="209"/>
-      <c r="S3" s="216"/>
-      <c r="T3" s="217"/>
-      <c r="U3" s="217"/>
-      <c r="V3" s="217"/>
-      <c r="W3" s="217"/>
-      <c r="X3" s="217"/>
-      <c r="Y3" s="217"/>
-      <c r="Z3" s="218"/>
-      <c r="AA3" s="192"/>
-      <c r="AB3" s="194"/>
-      <c r="AC3" s="219"/>
-      <c r="AD3" s="220"/>
-      <c r="AE3" s="220"/>
-      <c r="AF3" s="221"/>
-      <c r="AG3" s="186"/>
-      <c r="AH3" s="187"/>
-      <c r="AI3" s="188"/>
+      <c r="F3" s="174"/>
+      <c r="G3" s="174"/>
+      <c r="H3" s="174"/>
+      <c r="I3" s="174"/>
+      <c r="J3" s="174"/>
+      <c r="K3" s="174"/>
+      <c r="L3" s="174"/>
+      <c r="M3" s="174"/>
+      <c r="N3" s="175"/>
+      <c r="O3" s="185"/>
+      <c r="P3" s="186"/>
+      <c r="Q3" s="186"/>
+      <c r="R3" s="187"/>
+      <c r="S3" s="194"/>
+      <c r="T3" s="195"/>
+      <c r="U3" s="195"/>
+      <c r="V3" s="195"/>
+      <c r="W3" s="195"/>
+      <c r="X3" s="195"/>
+      <c r="Y3" s="195"/>
+      <c r="Z3" s="196"/>
+      <c r="AA3" s="170"/>
+      <c r="AB3" s="172"/>
+      <c r="AC3" s="197"/>
+      <c r="AD3" s="198"/>
+      <c r="AE3" s="198"/>
+      <c r="AF3" s="199"/>
+      <c r="AG3" s="164"/>
+      <c r="AH3" s="165"/>
+      <c r="AI3" s="166"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -14419,97 +14419,97 @@
       <c r="A7" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="189" t="s">
+      <c r="B7" s="167" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="190"/>
-      <c r="D7" s="189" t="s">
+      <c r="C7" s="168"/>
+      <c r="D7" s="167" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="191"/>
-      <c r="F7" s="190"/>
-      <c r="G7" s="189" t="s">
+      <c r="E7" s="169"/>
+      <c r="F7" s="168"/>
+      <c r="G7" s="167" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="191"/>
-      <c r="I7" s="190"/>
-      <c r="J7" s="189" t="s">
+      <c r="H7" s="169"/>
+      <c r="I7" s="168"/>
+      <c r="J7" s="167" t="s">
         <v>73</v>
       </c>
-      <c r="K7" s="191"/>
-      <c r="L7" s="191"/>
-      <c r="M7" s="191"/>
-      <c r="N7" s="191"/>
-      <c r="O7" s="191"/>
-      <c r="P7" s="190"/>
-      <c r="Q7" s="189" t="s">
+      <c r="K7" s="169"/>
+      <c r="L7" s="169"/>
+      <c r="M7" s="169"/>
+      <c r="N7" s="169"/>
+      <c r="O7" s="169"/>
+      <c r="P7" s="168"/>
+      <c r="Q7" s="167" t="s">
         <v>74</v>
       </c>
-      <c r="R7" s="191"/>
-      <c r="S7" s="191"/>
-      <c r="T7" s="191"/>
-      <c r="U7" s="191"/>
-      <c r="V7" s="191"/>
-      <c r="W7" s="191"/>
-      <c r="X7" s="191"/>
-      <c r="Y7" s="191"/>
-      <c r="Z7" s="191"/>
-      <c r="AA7" s="191"/>
-      <c r="AB7" s="191"/>
-      <c r="AC7" s="191"/>
-      <c r="AD7" s="191"/>
-      <c r="AE7" s="190"/>
-      <c r="AF7" s="189" t="s">
+      <c r="R7" s="169"/>
+      <c r="S7" s="169"/>
+      <c r="T7" s="169"/>
+      <c r="U7" s="169"/>
+      <c r="V7" s="169"/>
+      <c r="W7" s="169"/>
+      <c r="X7" s="169"/>
+      <c r="Y7" s="169"/>
+      <c r="Z7" s="169"/>
+      <c r="AA7" s="169"/>
+      <c r="AB7" s="169"/>
+      <c r="AC7" s="169"/>
+      <c r="AD7" s="169"/>
+      <c r="AE7" s="168"/>
+      <c r="AF7" s="167" t="s">
         <v>75</v>
       </c>
-      <c r="AG7" s="191"/>
-      <c r="AH7" s="191"/>
-      <c r="AI7" s="190"/>
+      <c r="AG7" s="169"/>
+      <c r="AH7" s="169"/>
+      <c r="AI7" s="168"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="24">
         <v>1</v>
       </c>
-      <c r="B8" s="177" t="s">
+      <c r="B8" s="212" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="178"/>
-      <c r="D8" s="179">
+      <c r="C8" s="213"/>
+      <c r="D8" s="214">
         <v>43336</v>
       </c>
-      <c r="E8" s="180"/>
-      <c r="F8" s="181"/>
-      <c r="G8" s="177" t="s">
+      <c r="E8" s="215"/>
+      <c r="F8" s="216"/>
+      <c r="G8" s="212" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="182"/>
-      <c r="I8" s="178"/>
-      <c r="J8" s="183" t="s">
+      <c r="H8" s="217"/>
+      <c r="I8" s="213"/>
+      <c r="J8" s="218" t="s">
         <v>78</v>
       </c>
-      <c r="K8" s="184"/>
-      <c r="L8" s="184"/>
-      <c r="M8" s="184"/>
-      <c r="N8" s="184"/>
-      <c r="O8" s="184"/>
-      <c r="P8" s="185"/>
-      <c r="Q8" s="183" t="s">
+      <c r="K8" s="219"/>
+      <c r="L8" s="219"/>
+      <c r="M8" s="219"/>
+      <c r="N8" s="219"/>
+      <c r="O8" s="219"/>
+      <c r="P8" s="220"/>
+      <c r="Q8" s="218" t="s">
         <v>79</v>
       </c>
-      <c r="R8" s="184"/>
-      <c r="S8" s="184"/>
-      <c r="T8" s="184"/>
-      <c r="U8" s="184"/>
-      <c r="V8" s="184"/>
-      <c r="W8" s="184"/>
-      <c r="X8" s="184"/>
-      <c r="Y8" s="184"/>
-      <c r="Z8" s="184"/>
-      <c r="AA8" s="184"/>
-      <c r="AB8" s="184"/>
-      <c r="AC8" s="184"/>
-      <c r="AD8" s="184"/>
-      <c r="AE8" s="185"/>
+      <c r="R8" s="219"/>
+      <c r="S8" s="219"/>
+      <c r="T8" s="219"/>
+      <c r="U8" s="219"/>
+      <c r="V8" s="219"/>
+      <c r="W8" s="219"/>
+      <c r="X8" s="219"/>
+      <c r="Y8" s="219"/>
+      <c r="Z8" s="219"/>
+      <c r="AA8" s="219"/>
+      <c r="AB8" s="219"/>
+      <c r="AC8" s="219"/>
+      <c r="AD8" s="219"/>
+      <c r="AE8" s="220"/>
       <c r="AF8" s="25" t="s">
         <v>80</v>
       </c>
@@ -14521,946 +14521,1101 @@
       <c r="A9" s="24">
         <v>2</v>
       </c>
-      <c r="B9" s="164" t="s">
+      <c r="B9" s="200" t="s">
         <v>547</v>
       </c>
-      <c r="C9" s="165"/>
-      <c r="D9" s="166">
+      <c r="C9" s="201"/>
+      <c r="D9" s="202">
         <v>44852</v>
       </c>
-      <c r="E9" s="167"/>
-      <c r="F9" s="168"/>
-      <c r="G9" s="166" t="s">
+      <c r="E9" s="203"/>
+      <c r="F9" s="204"/>
+      <c r="G9" s="202" t="s">
         <v>548</v>
       </c>
-      <c r="H9" s="169"/>
-      <c r="I9" s="165"/>
-      <c r="J9" s="173" t="s">
+      <c r="H9" s="205"/>
+      <c r="I9" s="201"/>
+      <c r="J9" s="206" t="s">
         <v>550</v>
       </c>
-      <c r="K9" s="171"/>
-      <c r="L9" s="171"/>
-      <c r="M9" s="171"/>
-      <c r="N9" s="171"/>
-      <c r="O9" s="171"/>
-      <c r="P9" s="172"/>
-      <c r="Q9" s="173" t="s">
+      <c r="K9" s="207"/>
+      <c r="L9" s="207"/>
+      <c r="M9" s="207"/>
+      <c r="N9" s="207"/>
+      <c r="O9" s="207"/>
+      <c r="P9" s="208"/>
+      <c r="Q9" s="206" t="s">
         <v>549</v>
       </c>
-      <c r="R9" s="174"/>
-      <c r="S9" s="174"/>
-      <c r="T9" s="174"/>
-      <c r="U9" s="174"/>
-      <c r="V9" s="174"/>
-      <c r="W9" s="174"/>
-      <c r="X9" s="174"/>
-      <c r="Y9" s="174"/>
-      <c r="Z9" s="174"/>
-      <c r="AA9" s="174"/>
-      <c r="AB9" s="174"/>
-      <c r="AC9" s="174"/>
-      <c r="AD9" s="174"/>
-      <c r="AE9" s="175"/>
-      <c r="AF9" s="170" t="s">
+      <c r="R9" s="209"/>
+      <c r="S9" s="209"/>
+      <c r="T9" s="209"/>
+      <c r="U9" s="209"/>
+      <c r="V9" s="209"/>
+      <c r="W9" s="209"/>
+      <c r="X9" s="209"/>
+      <c r="Y9" s="209"/>
+      <c r="Z9" s="209"/>
+      <c r="AA9" s="209"/>
+      <c r="AB9" s="209"/>
+      <c r="AC9" s="209"/>
+      <c r="AD9" s="209"/>
+      <c r="AE9" s="210"/>
+      <c r="AF9" s="211" t="s">
         <v>80</v>
       </c>
-      <c r="AG9" s="171"/>
-      <c r="AH9" s="171"/>
-      <c r="AI9" s="172"/>
+      <c r="AG9" s="207"/>
+      <c r="AH9" s="207"/>
+      <c r="AI9" s="208"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="21"/>
-      <c r="B10" s="164"/>
-      <c r="C10" s="165"/>
-      <c r="D10" s="166"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="168"/>
-      <c r="G10" s="164"/>
-      <c r="H10" s="169"/>
-      <c r="I10" s="165"/>
-      <c r="J10" s="170"/>
-      <c r="K10" s="171"/>
-      <c r="L10" s="171"/>
-      <c r="M10" s="171"/>
-      <c r="N10" s="171"/>
-      <c r="O10" s="171"/>
-      <c r="P10" s="172"/>
-      <c r="Q10" s="173"/>
-      <c r="R10" s="174"/>
-      <c r="S10" s="174"/>
-      <c r="T10" s="174"/>
-      <c r="U10" s="174"/>
-      <c r="V10" s="174"/>
-      <c r="W10" s="174"/>
-      <c r="X10" s="174"/>
-      <c r="Y10" s="174"/>
-      <c r="Z10" s="174"/>
-      <c r="AA10" s="174"/>
-      <c r="AB10" s="174"/>
-      <c r="AC10" s="174"/>
-      <c r="AD10" s="174"/>
-      <c r="AE10" s="175"/>
-      <c r="AF10" s="170"/>
-      <c r="AG10" s="171"/>
-      <c r="AH10" s="171"/>
-      <c r="AI10" s="172"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="201"/>
+      <c r="D10" s="202"/>
+      <c r="E10" s="203"/>
+      <c r="F10" s="204"/>
+      <c r="G10" s="200"/>
+      <c r="H10" s="205"/>
+      <c r="I10" s="201"/>
+      <c r="J10" s="211"/>
+      <c r="K10" s="207"/>
+      <c r="L10" s="207"/>
+      <c r="M10" s="207"/>
+      <c r="N10" s="207"/>
+      <c r="O10" s="207"/>
+      <c r="P10" s="208"/>
+      <c r="Q10" s="206"/>
+      <c r="R10" s="209"/>
+      <c r="S10" s="209"/>
+      <c r="T10" s="209"/>
+      <c r="U10" s="209"/>
+      <c r="V10" s="209"/>
+      <c r="W10" s="209"/>
+      <c r="X10" s="209"/>
+      <c r="Y10" s="209"/>
+      <c r="Z10" s="209"/>
+      <c r="AA10" s="209"/>
+      <c r="AB10" s="209"/>
+      <c r="AC10" s="209"/>
+      <c r="AD10" s="209"/>
+      <c r="AE10" s="210"/>
+      <c r="AF10" s="211"/>
+      <c r="AG10" s="207"/>
+      <c r="AH10" s="207"/>
+      <c r="AI10" s="208"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="21"/>
-      <c r="B11" s="164"/>
-      <c r="C11" s="165"/>
-      <c r="D11" s="166"/>
-      <c r="E11" s="167"/>
-      <c r="F11" s="168"/>
-      <c r="G11" s="164"/>
-      <c r="H11" s="169"/>
-      <c r="I11" s="165"/>
-      <c r="J11" s="170"/>
-      <c r="K11" s="171"/>
-      <c r="L11" s="171"/>
-      <c r="M11" s="171"/>
-      <c r="N11" s="171"/>
-      <c r="O11" s="171"/>
-      <c r="P11" s="172"/>
-      <c r="Q11" s="173"/>
-      <c r="R11" s="174"/>
-      <c r="S11" s="174"/>
-      <c r="T11" s="174"/>
-      <c r="U11" s="174"/>
-      <c r="V11" s="174"/>
-      <c r="W11" s="174"/>
-      <c r="X11" s="174"/>
-      <c r="Y11" s="174"/>
-      <c r="Z11" s="174"/>
-      <c r="AA11" s="174"/>
-      <c r="AB11" s="174"/>
-      <c r="AC11" s="174"/>
-      <c r="AD11" s="174"/>
-      <c r="AE11" s="175"/>
-      <c r="AF11" s="170"/>
-      <c r="AG11" s="171"/>
-      <c r="AH11" s="171"/>
-      <c r="AI11" s="172"/>
+      <c r="B11" s="200"/>
+      <c r="C11" s="201"/>
+      <c r="D11" s="202"/>
+      <c r="E11" s="203"/>
+      <c r="F11" s="204"/>
+      <c r="G11" s="200"/>
+      <c r="H11" s="205"/>
+      <c r="I11" s="201"/>
+      <c r="J11" s="211"/>
+      <c r="K11" s="207"/>
+      <c r="L11" s="207"/>
+      <c r="M11" s="207"/>
+      <c r="N11" s="207"/>
+      <c r="O11" s="207"/>
+      <c r="P11" s="208"/>
+      <c r="Q11" s="206"/>
+      <c r="R11" s="209"/>
+      <c r="S11" s="209"/>
+      <c r="T11" s="209"/>
+      <c r="U11" s="209"/>
+      <c r="V11" s="209"/>
+      <c r="W11" s="209"/>
+      <c r="X11" s="209"/>
+      <c r="Y11" s="209"/>
+      <c r="Z11" s="209"/>
+      <c r="AA11" s="209"/>
+      <c r="AB11" s="209"/>
+      <c r="AC11" s="209"/>
+      <c r="AD11" s="209"/>
+      <c r="AE11" s="210"/>
+      <c r="AF11" s="211"/>
+      <c r="AG11" s="207"/>
+      <c r="AH11" s="207"/>
+      <c r="AI11" s="208"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="21"/>
-      <c r="B12" s="164"/>
-      <c r="C12" s="165"/>
-      <c r="D12" s="166"/>
-      <c r="E12" s="167"/>
-      <c r="F12" s="168"/>
-      <c r="G12" s="164"/>
-      <c r="H12" s="169"/>
-      <c r="I12" s="165"/>
-      <c r="J12" s="170"/>
-      <c r="K12" s="171"/>
-      <c r="L12" s="171"/>
-      <c r="M12" s="171"/>
-      <c r="N12" s="171"/>
-      <c r="O12" s="171"/>
-      <c r="P12" s="172"/>
-      <c r="Q12" s="173"/>
-      <c r="R12" s="174"/>
-      <c r="S12" s="174"/>
-      <c r="T12" s="174"/>
-      <c r="U12" s="174"/>
-      <c r="V12" s="174"/>
-      <c r="W12" s="174"/>
-      <c r="X12" s="174"/>
-      <c r="Y12" s="174"/>
-      <c r="Z12" s="174"/>
-      <c r="AA12" s="174"/>
-      <c r="AB12" s="174"/>
-      <c r="AC12" s="174"/>
-      <c r="AD12" s="174"/>
-      <c r="AE12" s="175"/>
-      <c r="AF12" s="170"/>
-      <c r="AG12" s="171"/>
-      <c r="AH12" s="171"/>
-      <c r="AI12" s="172"/>
+      <c r="B12" s="200"/>
+      <c r="C12" s="201"/>
+      <c r="D12" s="202"/>
+      <c r="E12" s="203"/>
+      <c r="F12" s="204"/>
+      <c r="G12" s="200"/>
+      <c r="H12" s="205"/>
+      <c r="I12" s="201"/>
+      <c r="J12" s="211"/>
+      <c r="K12" s="207"/>
+      <c r="L12" s="207"/>
+      <c r="M12" s="207"/>
+      <c r="N12" s="207"/>
+      <c r="O12" s="207"/>
+      <c r="P12" s="208"/>
+      <c r="Q12" s="206"/>
+      <c r="R12" s="209"/>
+      <c r="S12" s="209"/>
+      <c r="T12" s="209"/>
+      <c r="U12" s="209"/>
+      <c r="V12" s="209"/>
+      <c r="W12" s="209"/>
+      <c r="X12" s="209"/>
+      <c r="Y12" s="209"/>
+      <c r="Z12" s="209"/>
+      <c r="AA12" s="209"/>
+      <c r="AB12" s="209"/>
+      <c r="AC12" s="209"/>
+      <c r="AD12" s="209"/>
+      <c r="AE12" s="210"/>
+      <c r="AF12" s="211"/>
+      <c r="AG12" s="207"/>
+      <c r="AH12" s="207"/>
+      <c r="AI12" s="208"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="21"/>
-      <c r="B13" s="164"/>
-      <c r="C13" s="165"/>
-      <c r="D13" s="166"/>
-      <c r="E13" s="167"/>
-      <c r="F13" s="168"/>
-      <c r="G13" s="164"/>
-      <c r="H13" s="169"/>
-      <c r="I13" s="165"/>
-      <c r="J13" s="170"/>
-      <c r="K13" s="171"/>
-      <c r="L13" s="171"/>
-      <c r="M13" s="171"/>
-      <c r="N13" s="171"/>
-      <c r="O13" s="171"/>
-      <c r="P13" s="172"/>
-      <c r="Q13" s="173"/>
-      <c r="R13" s="174"/>
-      <c r="S13" s="174"/>
-      <c r="T13" s="174"/>
-      <c r="U13" s="174"/>
-      <c r="V13" s="174"/>
-      <c r="W13" s="174"/>
-      <c r="X13" s="174"/>
-      <c r="Y13" s="174"/>
-      <c r="Z13" s="174"/>
-      <c r="AA13" s="174"/>
-      <c r="AB13" s="174"/>
-      <c r="AC13" s="174"/>
-      <c r="AD13" s="174"/>
-      <c r="AE13" s="175"/>
-      <c r="AF13" s="170"/>
-      <c r="AG13" s="171"/>
-      <c r="AH13" s="171"/>
-      <c r="AI13" s="172"/>
+      <c r="B13" s="200"/>
+      <c r="C13" s="201"/>
+      <c r="D13" s="202"/>
+      <c r="E13" s="203"/>
+      <c r="F13" s="204"/>
+      <c r="G13" s="200"/>
+      <c r="H13" s="205"/>
+      <c r="I13" s="201"/>
+      <c r="J13" s="211"/>
+      <c r="K13" s="207"/>
+      <c r="L13" s="207"/>
+      <c r="M13" s="207"/>
+      <c r="N13" s="207"/>
+      <c r="O13" s="207"/>
+      <c r="P13" s="208"/>
+      <c r="Q13" s="206"/>
+      <c r="R13" s="209"/>
+      <c r="S13" s="209"/>
+      <c r="T13" s="209"/>
+      <c r="U13" s="209"/>
+      <c r="V13" s="209"/>
+      <c r="W13" s="209"/>
+      <c r="X13" s="209"/>
+      <c r="Y13" s="209"/>
+      <c r="Z13" s="209"/>
+      <c r="AA13" s="209"/>
+      <c r="AB13" s="209"/>
+      <c r="AC13" s="209"/>
+      <c r="AD13" s="209"/>
+      <c r="AE13" s="210"/>
+      <c r="AF13" s="211"/>
+      <c r="AG13" s="207"/>
+      <c r="AH13" s="207"/>
+      <c r="AI13" s="208"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="164"/>
-      <c r="C14" s="165"/>
-      <c r="D14" s="166"/>
-      <c r="E14" s="167"/>
-      <c r="F14" s="168"/>
-      <c r="G14" s="164"/>
-      <c r="H14" s="169"/>
-      <c r="I14" s="165"/>
-      <c r="J14" s="170"/>
-      <c r="K14" s="171"/>
-      <c r="L14" s="171"/>
-      <c r="M14" s="171"/>
-      <c r="N14" s="171"/>
-      <c r="O14" s="171"/>
-      <c r="P14" s="172"/>
-      <c r="Q14" s="173"/>
-      <c r="R14" s="174"/>
-      <c r="S14" s="174"/>
-      <c r="T14" s="174"/>
-      <c r="U14" s="174"/>
-      <c r="V14" s="174"/>
-      <c r="W14" s="174"/>
-      <c r="X14" s="174"/>
-      <c r="Y14" s="174"/>
-      <c r="Z14" s="174"/>
-      <c r="AA14" s="174"/>
-      <c r="AB14" s="174"/>
-      <c r="AC14" s="174"/>
-      <c r="AD14" s="174"/>
-      <c r="AE14" s="175"/>
-      <c r="AF14" s="170"/>
-      <c r="AG14" s="171"/>
-      <c r="AH14" s="171"/>
-      <c r="AI14" s="172"/>
+      <c r="B14" s="200"/>
+      <c r="C14" s="201"/>
+      <c r="D14" s="202"/>
+      <c r="E14" s="203"/>
+      <c r="F14" s="204"/>
+      <c r="G14" s="200"/>
+      <c r="H14" s="205"/>
+      <c r="I14" s="201"/>
+      <c r="J14" s="211"/>
+      <c r="K14" s="207"/>
+      <c r="L14" s="207"/>
+      <c r="M14" s="207"/>
+      <c r="N14" s="207"/>
+      <c r="O14" s="207"/>
+      <c r="P14" s="208"/>
+      <c r="Q14" s="206"/>
+      <c r="R14" s="209"/>
+      <c r="S14" s="209"/>
+      <c r="T14" s="209"/>
+      <c r="U14" s="209"/>
+      <c r="V14" s="209"/>
+      <c r="W14" s="209"/>
+      <c r="X14" s="209"/>
+      <c r="Y14" s="209"/>
+      <c r="Z14" s="209"/>
+      <c r="AA14" s="209"/>
+      <c r="AB14" s="209"/>
+      <c r="AC14" s="209"/>
+      <c r="AD14" s="209"/>
+      <c r="AE14" s="210"/>
+      <c r="AF14" s="211"/>
+      <c r="AG14" s="207"/>
+      <c r="AH14" s="207"/>
+      <c r="AI14" s="208"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="21"/>
-      <c r="B15" s="164"/>
-      <c r="C15" s="165"/>
-      <c r="D15" s="166"/>
-      <c r="E15" s="167"/>
-      <c r="F15" s="168"/>
-      <c r="G15" s="164"/>
-      <c r="H15" s="169"/>
-      <c r="I15" s="165"/>
-      <c r="J15" s="170"/>
-      <c r="K15" s="171"/>
-      <c r="L15" s="171"/>
-      <c r="M15" s="171"/>
-      <c r="N15" s="171"/>
-      <c r="O15" s="171"/>
-      <c r="P15" s="172"/>
-      <c r="Q15" s="173"/>
-      <c r="R15" s="174"/>
-      <c r="S15" s="174"/>
-      <c r="T15" s="174"/>
-      <c r="U15" s="174"/>
-      <c r="V15" s="174"/>
-      <c r="W15" s="174"/>
-      <c r="X15" s="174"/>
-      <c r="Y15" s="174"/>
-      <c r="Z15" s="174"/>
-      <c r="AA15" s="174"/>
-      <c r="AB15" s="174"/>
-      <c r="AC15" s="174"/>
-      <c r="AD15" s="174"/>
-      <c r="AE15" s="175"/>
-      <c r="AF15" s="170"/>
-      <c r="AG15" s="171"/>
-      <c r="AH15" s="171"/>
-      <c r="AI15" s="172"/>
+      <c r="B15" s="200"/>
+      <c r="C15" s="201"/>
+      <c r="D15" s="202"/>
+      <c r="E15" s="203"/>
+      <c r="F15" s="204"/>
+      <c r="G15" s="200"/>
+      <c r="H15" s="205"/>
+      <c r="I15" s="201"/>
+      <c r="J15" s="211"/>
+      <c r="K15" s="207"/>
+      <c r="L15" s="207"/>
+      <c r="M15" s="207"/>
+      <c r="N15" s="207"/>
+      <c r="O15" s="207"/>
+      <c r="P15" s="208"/>
+      <c r="Q15" s="206"/>
+      <c r="R15" s="209"/>
+      <c r="S15" s="209"/>
+      <c r="T15" s="209"/>
+      <c r="U15" s="209"/>
+      <c r="V15" s="209"/>
+      <c r="W15" s="209"/>
+      <c r="X15" s="209"/>
+      <c r="Y15" s="209"/>
+      <c r="Z15" s="209"/>
+      <c r="AA15" s="209"/>
+      <c r="AB15" s="209"/>
+      <c r="AC15" s="209"/>
+      <c r="AD15" s="209"/>
+      <c r="AE15" s="210"/>
+      <c r="AF15" s="211"/>
+      <c r="AG15" s="207"/>
+      <c r="AH15" s="207"/>
+      <c r="AI15" s="208"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="21"/>
-      <c r="B16" s="164"/>
-      <c r="C16" s="165"/>
-      <c r="D16" s="166"/>
-      <c r="E16" s="167"/>
-      <c r="F16" s="168"/>
-      <c r="G16" s="164"/>
-      <c r="H16" s="169"/>
-      <c r="I16" s="165"/>
-      <c r="J16" s="170"/>
-      <c r="K16" s="171"/>
-      <c r="L16" s="171"/>
-      <c r="M16" s="171"/>
-      <c r="N16" s="171"/>
-      <c r="O16" s="171"/>
-      <c r="P16" s="172"/>
-      <c r="Q16" s="173"/>
-      <c r="R16" s="174"/>
-      <c r="S16" s="174"/>
-      <c r="T16" s="174"/>
-      <c r="U16" s="174"/>
-      <c r="V16" s="174"/>
-      <c r="W16" s="174"/>
-      <c r="X16" s="174"/>
-      <c r="Y16" s="174"/>
-      <c r="Z16" s="174"/>
-      <c r="AA16" s="174"/>
-      <c r="AB16" s="174"/>
-      <c r="AC16" s="174"/>
-      <c r="AD16" s="174"/>
-      <c r="AE16" s="175"/>
-      <c r="AF16" s="170"/>
-      <c r="AG16" s="171"/>
-      <c r="AH16" s="171"/>
-      <c r="AI16" s="172"/>
+      <c r="B16" s="200"/>
+      <c r="C16" s="201"/>
+      <c r="D16" s="202"/>
+      <c r="E16" s="203"/>
+      <c r="F16" s="204"/>
+      <c r="G16" s="200"/>
+      <c r="H16" s="205"/>
+      <c r="I16" s="201"/>
+      <c r="J16" s="211"/>
+      <c r="K16" s="207"/>
+      <c r="L16" s="207"/>
+      <c r="M16" s="207"/>
+      <c r="N16" s="207"/>
+      <c r="O16" s="207"/>
+      <c r="P16" s="208"/>
+      <c r="Q16" s="206"/>
+      <c r="R16" s="209"/>
+      <c r="S16" s="209"/>
+      <c r="T16" s="209"/>
+      <c r="U16" s="209"/>
+      <c r="V16" s="209"/>
+      <c r="W16" s="209"/>
+      <c r="X16" s="209"/>
+      <c r="Y16" s="209"/>
+      <c r="Z16" s="209"/>
+      <c r="AA16" s="209"/>
+      <c r="AB16" s="209"/>
+      <c r="AC16" s="209"/>
+      <c r="AD16" s="209"/>
+      <c r="AE16" s="210"/>
+      <c r="AF16" s="211"/>
+      <c r="AG16" s="207"/>
+      <c r="AH16" s="207"/>
+      <c r="AI16" s="208"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="21"/>
-      <c r="B17" s="164"/>
-      <c r="C17" s="165"/>
-      <c r="D17" s="166"/>
-      <c r="E17" s="167"/>
-      <c r="F17" s="168"/>
-      <c r="G17" s="164"/>
-      <c r="H17" s="169"/>
-      <c r="I17" s="165"/>
-      <c r="J17" s="170"/>
-      <c r="K17" s="171"/>
-      <c r="L17" s="171"/>
-      <c r="M17" s="171"/>
-      <c r="N17" s="171"/>
-      <c r="O17" s="171"/>
-      <c r="P17" s="172"/>
-      <c r="Q17" s="173"/>
-      <c r="R17" s="174"/>
-      <c r="S17" s="174"/>
-      <c r="T17" s="174"/>
-      <c r="U17" s="174"/>
-      <c r="V17" s="174"/>
-      <c r="W17" s="174"/>
-      <c r="X17" s="174"/>
-      <c r="Y17" s="174"/>
-      <c r="Z17" s="174"/>
-      <c r="AA17" s="174"/>
-      <c r="AB17" s="174"/>
-      <c r="AC17" s="174"/>
-      <c r="AD17" s="174"/>
-      <c r="AE17" s="175"/>
-      <c r="AF17" s="170"/>
-      <c r="AG17" s="171"/>
-      <c r="AH17" s="171"/>
-      <c r="AI17" s="172"/>
+      <c r="B17" s="200"/>
+      <c r="C17" s="201"/>
+      <c r="D17" s="202"/>
+      <c r="E17" s="203"/>
+      <c r="F17" s="204"/>
+      <c r="G17" s="200"/>
+      <c r="H17" s="205"/>
+      <c r="I17" s="201"/>
+      <c r="J17" s="211"/>
+      <c r="K17" s="207"/>
+      <c r="L17" s="207"/>
+      <c r="M17" s="207"/>
+      <c r="N17" s="207"/>
+      <c r="O17" s="207"/>
+      <c r="P17" s="208"/>
+      <c r="Q17" s="206"/>
+      <c r="R17" s="209"/>
+      <c r="S17" s="209"/>
+      <c r="T17" s="209"/>
+      <c r="U17" s="209"/>
+      <c r="V17" s="209"/>
+      <c r="W17" s="209"/>
+      <c r="X17" s="209"/>
+      <c r="Y17" s="209"/>
+      <c r="Z17" s="209"/>
+      <c r="AA17" s="209"/>
+      <c r="AB17" s="209"/>
+      <c r="AC17" s="209"/>
+      <c r="AD17" s="209"/>
+      <c r="AE17" s="210"/>
+      <c r="AF17" s="211"/>
+      <c r="AG17" s="207"/>
+      <c r="AH17" s="207"/>
+      <c r="AI17" s="208"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="21"/>
-      <c r="B18" s="164"/>
-      <c r="C18" s="165"/>
-      <c r="D18" s="166"/>
-      <c r="E18" s="167"/>
-      <c r="F18" s="168"/>
-      <c r="G18" s="164"/>
-      <c r="H18" s="169"/>
-      <c r="I18" s="165"/>
-      <c r="J18" s="170"/>
-      <c r="K18" s="171"/>
-      <c r="L18" s="171"/>
-      <c r="M18" s="171"/>
-      <c r="N18" s="171"/>
-      <c r="O18" s="171"/>
-      <c r="P18" s="172"/>
-      <c r="Q18" s="173"/>
-      <c r="R18" s="174"/>
-      <c r="S18" s="174"/>
-      <c r="T18" s="174"/>
-      <c r="U18" s="174"/>
-      <c r="V18" s="174"/>
-      <c r="W18" s="174"/>
-      <c r="X18" s="174"/>
-      <c r="Y18" s="174"/>
-      <c r="Z18" s="174"/>
-      <c r="AA18" s="174"/>
-      <c r="AB18" s="174"/>
-      <c r="AC18" s="174"/>
-      <c r="AD18" s="174"/>
-      <c r="AE18" s="175"/>
-      <c r="AF18" s="170"/>
-      <c r="AG18" s="171"/>
-      <c r="AH18" s="171"/>
-      <c r="AI18" s="172"/>
+      <c r="B18" s="200"/>
+      <c r="C18" s="201"/>
+      <c r="D18" s="202"/>
+      <c r="E18" s="203"/>
+      <c r="F18" s="204"/>
+      <c r="G18" s="200"/>
+      <c r="H18" s="205"/>
+      <c r="I18" s="201"/>
+      <c r="J18" s="211"/>
+      <c r="K18" s="207"/>
+      <c r="L18" s="207"/>
+      <c r="M18" s="207"/>
+      <c r="N18" s="207"/>
+      <c r="O18" s="207"/>
+      <c r="P18" s="208"/>
+      <c r="Q18" s="206"/>
+      <c r="R18" s="209"/>
+      <c r="S18" s="209"/>
+      <c r="T18" s="209"/>
+      <c r="U18" s="209"/>
+      <c r="V18" s="209"/>
+      <c r="W18" s="209"/>
+      <c r="X18" s="209"/>
+      <c r="Y18" s="209"/>
+      <c r="Z18" s="209"/>
+      <c r="AA18" s="209"/>
+      <c r="AB18" s="209"/>
+      <c r="AC18" s="209"/>
+      <c r="AD18" s="209"/>
+      <c r="AE18" s="210"/>
+      <c r="AF18" s="211"/>
+      <c r="AG18" s="207"/>
+      <c r="AH18" s="207"/>
+      <c r="AI18" s="208"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="21"/>
-      <c r="B19" s="164"/>
-      <c r="C19" s="165"/>
-      <c r="D19" s="166"/>
-      <c r="E19" s="167"/>
-      <c r="F19" s="168"/>
-      <c r="G19" s="164"/>
-      <c r="H19" s="169"/>
-      <c r="I19" s="165"/>
-      <c r="J19" s="170"/>
-      <c r="K19" s="171"/>
-      <c r="L19" s="171"/>
-      <c r="M19" s="171"/>
-      <c r="N19" s="171"/>
-      <c r="O19" s="171"/>
-      <c r="P19" s="172"/>
-      <c r="Q19" s="173"/>
-      <c r="R19" s="174"/>
-      <c r="S19" s="174"/>
-      <c r="T19" s="174"/>
-      <c r="U19" s="174"/>
-      <c r="V19" s="174"/>
-      <c r="W19" s="174"/>
-      <c r="X19" s="174"/>
-      <c r="Y19" s="174"/>
-      <c r="Z19" s="174"/>
-      <c r="AA19" s="174"/>
-      <c r="AB19" s="174"/>
-      <c r="AC19" s="174"/>
-      <c r="AD19" s="174"/>
-      <c r="AE19" s="175"/>
-      <c r="AF19" s="170"/>
-      <c r="AG19" s="171"/>
-      <c r="AH19" s="171"/>
-      <c r="AI19" s="172"/>
+      <c r="B19" s="200"/>
+      <c r="C19" s="201"/>
+      <c r="D19" s="202"/>
+      <c r="E19" s="203"/>
+      <c r="F19" s="204"/>
+      <c r="G19" s="200"/>
+      <c r="H19" s="205"/>
+      <c r="I19" s="201"/>
+      <c r="J19" s="211"/>
+      <c r="K19" s="207"/>
+      <c r="L19" s="207"/>
+      <c r="M19" s="207"/>
+      <c r="N19" s="207"/>
+      <c r="O19" s="207"/>
+      <c r="P19" s="208"/>
+      <c r="Q19" s="206"/>
+      <c r="R19" s="209"/>
+      <c r="S19" s="209"/>
+      <c r="T19" s="209"/>
+      <c r="U19" s="209"/>
+      <c r="V19" s="209"/>
+      <c r="W19" s="209"/>
+      <c r="X19" s="209"/>
+      <c r="Y19" s="209"/>
+      <c r="Z19" s="209"/>
+      <c r="AA19" s="209"/>
+      <c r="AB19" s="209"/>
+      <c r="AC19" s="209"/>
+      <c r="AD19" s="209"/>
+      <c r="AE19" s="210"/>
+      <c r="AF19" s="211"/>
+      <c r="AG19" s="207"/>
+      <c r="AH19" s="207"/>
+      <c r="AI19" s="208"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="21"/>
-      <c r="B20" s="164"/>
-      <c r="C20" s="165"/>
-      <c r="D20" s="166"/>
-      <c r="E20" s="167"/>
-      <c r="F20" s="168"/>
-      <c r="G20" s="164"/>
-      <c r="H20" s="169"/>
-      <c r="I20" s="165"/>
-      <c r="J20" s="170"/>
-      <c r="K20" s="171"/>
-      <c r="L20" s="171"/>
-      <c r="M20" s="171"/>
-      <c r="N20" s="171"/>
-      <c r="O20" s="171"/>
-      <c r="P20" s="172"/>
-      <c r="Q20" s="173"/>
-      <c r="R20" s="174"/>
-      <c r="S20" s="174"/>
-      <c r="T20" s="174"/>
-      <c r="U20" s="174"/>
-      <c r="V20" s="174"/>
-      <c r="W20" s="174"/>
-      <c r="X20" s="174"/>
-      <c r="Y20" s="174"/>
-      <c r="Z20" s="174"/>
-      <c r="AA20" s="174"/>
-      <c r="AB20" s="174"/>
-      <c r="AC20" s="174"/>
-      <c r="AD20" s="174"/>
-      <c r="AE20" s="175"/>
-      <c r="AF20" s="170"/>
-      <c r="AG20" s="171"/>
-      <c r="AH20" s="171"/>
-      <c r="AI20" s="172"/>
+      <c r="B20" s="200"/>
+      <c r="C20" s="201"/>
+      <c r="D20" s="202"/>
+      <c r="E20" s="203"/>
+      <c r="F20" s="204"/>
+      <c r="G20" s="200"/>
+      <c r="H20" s="205"/>
+      <c r="I20" s="201"/>
+      <c r="J20" s="211"/>
+      <c r="K20" s="207"/>
+      <c r="L20" s="207"/>
+      <c r="M20" s="207"/>
+      <c r="N20" s="207"/>
+      <c r="O20" s="207"/>
+      <c r="P20" s="208"/>
+      <c r="Q20" s="206"/>
+      <c r="R20" s="209"/>
+      <c r="S20" s="209"/>
+      <c r="T20" s="209"/>
+      <c r="U20" s="209"/>
+      <c r="V20" s="209"/>
+      <c r="W20" s="209"/>
+      <c r="X20" s="209"/>
+      <c r="Y20" s="209"/>
+      <c r="Z20" s="209"/>
+      <c r="AA20" s="209"/>
+      <c r="AB20" s="209"/>
+      <c r="AC20" s="209"/>
+      <c r="AD20" s="209"/>
+      <c r="AE20" s="210"/>
+      <c r="AF20" s="211"/>
+      <c r="AG20" s="207"/>
+      <c r="AH20" s="207"/>
+      <c r="AI20" s="208"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="21"/>
-      <c r="B21" s="164"/>
-      <c r="C21" s="165"/>
-      <c r="D21" s="166"/>
-      <c r="E21" s="167"/>
-      <c r="F21" s="168"/>
-      <c r="G21" s="164"/>
-      <c r="H21" s="169"/>
-      <c r="I21" s="165"/>
-      <c r="J21" s="170"/>
-      <c r="K21" s="171"/>
-      <c r="L21" s="171"/>
-      <c r="M21" s="171"/>
-      <c r="N21" s="171"/>
-      <c r="O21" s="171"/>
-      <c r="P21" s="172"/>
-      <c r="Q21" s="173"/>
-      <c r="R21" s="174"/>
-      <c r="S21" s="174"/>
-      <c r="T21" s="174"/>
-      <c r="U21" s="174"/>
-      <c r="V21" s="174"/>
-      <c r="W21" s="174"/>
-      <c r="X21" s="174"/>
-      <c r="Y21" s="174"/>
-      <c r="Z21" s="174"/>
-      <c r="AA21" s="174"/>
-      <c r="AB21" s="174"/>
-      <c r="AC21" s="174"/>
-      <c r="AD21" s="174"/>
-      <c r="AE21" s="175"/>
-      <c r="AF21" s="170"/>
-      <c r="AG21" s="171"/>
-      <c r="AH21" s="171"/>
-      <c r="AI21" s="172"/>
+      <c r="B21" s="200"/>
+      <c r="C21" s="201"/>
+      <c r="D21" s="202"/>
+      <c r="E21" s="203"/>
+      <c r="F21" s="204"/>
+      <c r="G21" s="200"/>
+      <c r="H21" s="205"/>
+      <c r="I21" s="201"/>
+      <c r="J21" s="211"/>
+      <c r="K21" s="207"/>
+      <c r="L21" s="207"/>
+      <c r="M21" s="207"/>
+      <c r="N21" s="207"/>
+      <c r="O21" s="207"/>
+      <c r="P21" s="208"/>
+      <c r="Q21" s="206"/>
+      <c r="R21" s="209"/>
+      <c r="S21" s="209"/>
+      <c r="T21" s="209"/>
+      <c r="U21" s="209"/>
+      <c r="V21" s="209"/>
+      <c r="W21" s="209"/>
+      <c r="X21" s="209"/>
+      <c r="Y21" s="209"/>
+      <c r="Z21" s="209"/>
+      <c r="AA21" s="209"/>
+      <c r="AB21" s="209"/>
+      <c r="AC21" s="209"/>
+      <c r="AD21" s="209"/>
+      <c r="AE21" s="210"/>
+      <c r="AF21" s="211"/>
+      <c r="AG21" s="207"/>
+      <c r="AH21" s="207"/>
+      <c r="AI21" s="208"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="21"/>
-      <c r="B22" s="164"/>
-      <c r="C22" s="165"/>
-      <c r="D22" s="166"/>
-      <c r="E22" s="167"/>
-      <c r="F22" s="168"/>
-      <c r="G22" s="164"/>
-      <c r="H22" s="169"/>
-      <c r="I22" s="165"/>
-      <c r="J22" s="170"/>
-      <c r="K22" s="171"/>
-      <c r="L22" s="171"/>
-      <c r="M22" s="171"/>
-      <c r="N22" s="171"/>
-      <c r="O22" s="171"/>
-      <c r="P22" s="172"/>
-      <c r="Q22" s="173"/>
-      <c r="R22" s="174"/>
-      <c r="S22" s="174"/>
-      <c r="T22" s="174"/>
-      <c r="U22" s="174"/>
-      <c r="V22" s="174"/>
-      <c r="W22" s="174"/>
-      <c r="X22" s="174"/>
-      <c r="Y22" s="174"/>
-      <c r="Z22" s="174"/>
-      <c r="AA22" s="174"/>
-      <c r="AB22" s="174"/>
-      <c r="AC22" s="174"/>
-      <c r="AD22" s="174"/>
-      <c r="AE22" s="175"/>
-      <c r="AF22" s="170"/>
-      <c r="AG22" s="171"/>
-      <c r="AH22" s="171"/>
-      <c r="AI22" s="172"/>
+      <c r="B22" s="200"/>
+      <c r="C22" s="201"/>
+      <c r="D22" s="202"/>
+      <c r="E22" s="203"/>
+      <c r="F22" s="204"/>
+      <c r="G22" s="200"/>
+      <c r="H22" s="205"/>
+      <c r="I22" s="201"/>
+      <c r="J22" s="211"/>
+      <c r="K22" s="207"/>
+      <c r="L22" s="207"/>
+      <c r="M22" s="207"/>
+      <c r="N22" s="207"/>
+      <c r="O22" s="207"/>
+      <c r="P22" s="208"/>
+      <c r="Q22" s="206"/>
+      <c r="R22" s="209"/>
+      <c r="S22" s="209"/>
+      <c r="T22" s="209"/>
+      <c r="U22" s="209"/>
+      <c r="V22" s="209"/>
+      <c r="W22" s="209"/>
+      <c r="X22" s="209"/>
+      <c r="Y22" s="209"/>
+      <c r="Z22" s="209"/>
+      <c r="AA22" s="209"/>
+      <c r="AB22" s="209"/>
+      <c r="AC22" s="209"/>
+      <c r="AD22" s="209"/>
+      <c r="AE22" s="210"/>
+      <c r="AF22" s="211"/>
+      <c r="AG22" s="207"/>
+      <c r="AH22" s="207"/>
+      <c r="AI22" s="208"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="21"/>
-      <c r="B23" s="164"/>
-      <c r="C23" s="165"/>
-      <c r="D23" s="166"/>
-      <c r="E23" s="167"/>
-      <c r="F23" s="168"/>
-      <c r="G23" s="164"/>
-      <c r="H23" s="169"/>
-      <c r="I23" s="165"/>
-      <c r="J23" s="170"/>
-      <c r="K23" s="171"/>
-      <c r="L23" s="171"/>
-      <c r="M23" s="171"/>
-      <c r="N23" s="171"/>
-      <c r="O23" s="171"/>
-      <c r="P23" s="172"/>
-      <c r="Q23" s="173"/>
-      <c r="R23" s="174"/>
-      <c r="S23" s="174"/>
-      <c r="T23" s="174"/>
-      <c r="U23" s="174"/>
-      <c r="V23" s="174"/>
-      <c r="W23" s="174"/>
-      <c r="X23" s="174"/>
-      <c r="Y23" s="174"/>
-      <c r="Z23" s="174"/>
-      <c r="AA23" s="174"/>
-      <c r="AB23" s="174"/>
-      <c r="AC23" s="174"/>
-      <c r="AD23" s="174"/>
-      <c r="AE23" s="175"/>
-      <c r="AF23" s="170"/>
-      <c r="AG23" s="171"/>
-      <c r="AH23" s="171"/>
-      <c r="AI23" s="172"/>
+      <c r="B23" s="200"/>
+      <c r="C23" s="201"/>
+      <c r="D23" s="202"/>
+      <c r="E23" s="203"/>
+      <c r="F23" s="204"/>
+      <c r="G23" s="200"/>
+      <c r="H23" s="205"/>
+      <c r="I23" s="201"/>
+      <c r="J23" s="211"/>
+      <c r="K23" s="207"/>
+      <c r="L23" s="207"/>
+      <c r="M23" s="207"/>
+      <c r="N23" s="207"/>
+      <c r="O23" s="207"/>
+      <c r="P23" s="208"/>
+      <c r="Q23" s="206"/>
+      <c r="R23" s="209"/>
+      <c r="S23" s="209"/>
+      <c r="T23" s="209"/>
+      <c r="U23" s="209"/>
+      <c r="V23" s="209"/>
+      <c r="W23" s="209"/>
+      <c r="X23" s="209"/>
+      <c r="Y23" s="209"/>
+      <c r="Z23" s="209"/>
+      <c r="AA23" s="209"/>
+      <c r="AB23" s="209"/>
+      <c r="AC23" s="209"/>
+      <c r="AD23" s="209"/>
+      <c r="AE23" s="210"/>
+      <c r="AF23" s="211"/>
+      <c r="AG23" s="207"/>
+      <c r="AH23" s="207"/>
+      <c r="AI23" s="208"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="21"/>
-      <c r="B24" s="164"/>
-      <c r="C24" s="165"/>
-      <c r="D24" s="166"/>
-      <c r="E24" s="167"/>
-      <c r="F24" s="168"/>
-      <c r="G24" s="164"/>
-      <c r="H24" s="169"/>
-      <c r="I24" s="165"/>
-      <c r="J24" s="170"/>
-      <c r="K24" s="171"/>
-      <c r="L24" s="171"/>
-      <c r="M24" s="171"/>
-      <c r="N24" s="171"/>
-      <c r="O24" s="171"/>
-      <c r="P24" s="172"/>
-      <c r="Q24" s="173"/>
-      <c r="R24" s="174"/>
-      <c r="S24" s="174"/>
-      <c r="T24" s="174"/>
-      <c r="U24" s="174"/>
-      <c r="V24" s="174"/>
-      <c r="W24" s="174"/>
-      <c r="X24" s="174"/>
-      <c r="Y24" s="174"/>
-      <c r="Z24" s="174"/>
-      <c r="AA24" s="174"/>
-      <c r="AB24" s="174"/>
-      <c r="AC24" s="174"/>
-      <c r="AD24" s="174"/>
-      <c r="AE24" s="175"/>
-      <c r="AF24" s="170"/>
-      <c r="AG24" s="171"/>
-      <c r="AH24" s="171"/>
-      <c r="AI24" s="172"/>
+      <c r="B24" s="200"/>
+      <c r="C24" s="201"/>
+      <c r="D24" s="202"/>
+      <c r="E24" s="203"/>
+      <c r="F24" s="204"/>
+      <c r="G24" s="200"/>
+      <c r="H24" s="205"/>
+      <c r="I24" s="201"/>
+      <c r="J24" s="211"/>
+      <c r="K24" s="207"/>
+      <c r="L24" s="207"/>
+      <c r="M24" s="207"/>
+      <c r="N24" s="207"/>
+      <c r="O24" s="207"/>
+      <c r="P24" s="208"/>
+      <c r="Q24" s="206"/>
+      <c r="R24" s="209"/>
+      <c r="S24" s="209"/>
+      <c r="T24" s="209"/>
+      <c r="U24" s="209"/>
+      <c r="V24" s="209"/>
+      <c r="W24" s="209"/>
+      <c r="X24" s="209"/>
+      <c r="Y24" s="209"/>
+      <c r="Z24" s="209"/>
+      <c r="AA24" s="209"/>
+      <c r="AB24" s="209"/>
+      <c r="AC24" s="209"/>
+      <c r="AD24" s="209"/>
+      <c r="AE24" s="210"/>
+      <c r="AF24" s="211"/>
+      <c r="AG24" s="207"/>
+      <c r="AH24" s="207"/>
+      <c r="AI24" s="208"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="21"/>
-      <c r="B25" s="164"/>
-      <c r="C25" s="165"/>
-      <c r="D25" s="166"/>
-      <c r="E25" s="167"/>
-      <c r="F25" s="168"/>
-      <c r="G25" s="164"/>
-      <c r="H25" s="169"/>
-      <c r="I25" s="165"/>
-      <c r="J25" s="170"/>
-      <c r="K25" s="171"/>
-      <c r="L25" s="171"/>
-      <c r="M25" s="171"/>
-      <c r="N25" s="171"/>
-      <c r="O25" s="171"/>
-      <c r="P25" s="172"/>
-      <c r="Q25" s="173"/>
-      <c r="R25" s="174"/>
-      <c r="S25" s="174"/>
-      <c r="T25" s="174"/>
-      <c r="U25" s="174"/>
-      <c r="V25" s="174"/>
-      <c r="W25" s="174"/>
-      <c r="X25" s="174"/>
-      <c r="Y25" s="174"/>
-      <c r="Z25" s="174"/>
-      <c r="AA25" s="174"/>
-      <c r="AB25" s="174"/>
-      <c r="AC25" s="174"/>
-      <c r="AD25" s="174"/>
-      <c r="AE25" s="175"/>
-      <c r="AF25" s="170"/>
-      <c r="AG25" s="171"/>
-      <c r="AH25" s="171"/>
-      <c r="AI25" s="172"/>
+      <c r="B25" s="200"/>
+      <c r="C25" s="201"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="203"/>
+      <c r="F25" s="204"/>
+      <c r="G25" s="200"/>
+      <c r="H25" s="205"/>
+      <c r="I25" s="201"/>
+      <c r="J25" s="211"/>
+      <c r="K25" s="207"/>
+      <c r="L25" s="207"/>
+      <c r="M25" s="207"/>
+      <c r="N25" s="207"/>
+      <c r="O25" s="207"/>
+      <c r="P25" s="208"/>
+      <c r="Q25" s="206"/>
+      <c r="R25" s="209"/>
+      <c r="S25" s="209"/>
+      <c r="T25" s="209"/>
+      <c r="U25" s="209"/>
+      <c r="V25" s="209"/>
+      <c r="W25" s="209"/>
+      <c r="X25" s="209"/>
+      <c r="Y25" s="209"/>
+      <c r="Z25" s="209"/>
+      <c r="AA25" s="209"/>
+      <c r="AB25" s="209"/>
+      <c r="AC25" s="209"/>
+      <c r="AD25" s="209"/>
+      <c r="AE25" s="210"/>
+      <c r="AF25" s="211"/>
+      <c r="AG25" s="207"/>
+      <c r="AH25" s="207"/>
+      <c r="AI25" s="208"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="21"/>
-      <c r="B26" s="164"/>
-      <c r="C26" s="165"/>
-      <c r="D26" s="166"/>
-      <c r="E26" s="167"/>
-      <c r="F26" s="168"/>
-      <c r="G26" s="164"/>
-      <c r="H26" s="169"/>
-      <c r="I26" s="165"/>
-      <c r="J26" s="170"/>
-      <c r="K26" s="171"/>
-      <c r="L26" s="171"/>
-      <c r="M26" s="171"/>
-      <c r="N26" s="171"/>
-      <c r="O26" s="171"/>
-      <c r="P26" s="172"/>
-      <c r="Q26" s="173"/>
-      <c r="R26" s="174"/>
-      <c r="S26" s="174"/>
-      <c r="T26" s="174"/>
-      <c r="U26" s="174"/>
-      <c r="V26" s="174"/>
-      <c r="W26" s="174"/>
-      <c r="X26" s="174"/>
-      <c r="Y26" s="174"/>
-      <c r="Z26" s="174"/>
-      <c r="AA26" s="174"/>
-      <c r="AB26" s="174"/>
-      <c r="AC26" s="174"/>
-      <c r="AD26" s="174"/>
-      <c r="AE26" s="175"/>
-      <c r="AF26" s="170"/>
-      <c r="AG26" s="171"/>
-      <c r="AH26" s="171"/>
-      <c r="AI26" s="172"/>
+      <c r="B26" s="200"/>
+      <c r="C26" s="201"/>
+      <c r="D26" s="202"/>
+      <c r="E26" s="203"/>
+      <c r="F26" s="204"/>
+      <c r="G26" s="200"/>
+      <c r="H26" s="205"/>
+      <c r="I26" s="201"/>
+      <c r="J26" s="211"/>
+      <c r="K26" s="207"/>
+      <c r="L26" s="207"/>
+      <c r="M26" s="207"/>
+      <c r="N26" s="207"/>
+      <c r="O26" s="207"/>
+      <c r="P26" s="208"/>
+      <c r="Q26" s="206"/>
+      <c r="R26" s="209"/>
+      <c r="S26" s="209"/>
+      <c r="T26" s="209"/>
+      <c r="U26" s="209"/>
+      <c r="V26" s="209"/>
+      <c r="W26" s="209"/>
+      <c r="X26" s="209"/>
+      <c r="Y26" s="209"/>
+      <c r="Z26" s="209"/>
+      <c r="AA26" s="209"/>
+      <c r="AB26" s="209"/>
+      <c r="AC26" s="209"/>
+      <c r="AD26" s="209"/>
+      <c r="AE26" s="210"/>
+      <c r="AF26" s="211"/>
+      <c r="AG26" s="207"/>
+      <c r="AH26" s="207"/>
+      <c r="AI26" s="208"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="21"/>
-      <c r="B27" s="164"/>
-      <c r="C27" s="165"/>
-      <c r="D27" s="166"/>
-      <c r="E27" s="167"/>
-      <c r="F27" s="168"/>
-      <c r="G27" s="164"/>
-      <c r="H27" s="169"/>
-      <c r="I27" s="165"/>
-      <c r="J27" s="170"/>
-      <c r="K27" s="171"/>
-      <c r="L27" s="171"/>
-      <c r="M27" s="171"/>
-      <c r="N27" s="171"/>
-      <c r="O27" s="171"/>
-      <c r="P27" s="172"/>
-      <c r="Q27" s="173"/>
-      <c r="R27" s="174"/>
-      <c r="S27" s="174"/>
-      <c r="T27" s="174"/>
-      <c r="U27" s="174"/>
-      <c r="V27" s="174"/>
-      <c r="W27" s="174"/>
-      <c r="X27" s="174"/>
-      <c r="Y27" s="174"/>
-      <c r="Z27" s="174"/>
-      <c r="AA27" s="174"/>
-      <c r="AB27" s="174"/>
-      <c r="AC27" s="174"/>
-      <c r="AD27" s="174"/>
-      <c r="AE27" s="175"/>
-      <c r="AF27" s="170"/>
-      <c r="AG27" s="171"/>
-      <c r="AH27" s="171"/>
-      <c r="AI27" s="172"/>
+      <c r="B27" s="200"/>
+      <c r="C27" s="201"/>
+      <c r="D27" s="202"/>
+      <c r="E27" s="203"/>
+      <c r="F27" s="204"/>
+      <c r="G27" s="200"/>
+      <c r="H27" s="205"/>
+      <c r="I27" s="201"/>
+      <c r="J27" s="211"/>
+      <c r="K27" s="207"/>
+      <c r="L27" s="207"/>
+      <c r="M27" s="207"/>
+      <c r="N27" s="207"/>
+      <c r="O27" s="207"/>
+      <c r="P27" s="208"/>
+      <c r="Q27" s="206"/>
+      <c r="R27" s="209"/>
+      <c r="S27" s="209"/>
+      <c r="T27" s="209"/>
+      <c r="U27" s="209"/>
+      <c r="V27" s="209"/>
+      <c r="W27" s="209"/>
+      <c r="X27" s="209"/>
+      <c r="Y27" s="209"/>
+      <c r="Z27" s="209"/>
+      <c r="AA27" s="209"/>
+      <c r="AB27" s="209"/>
+      <c r="AC27" s="209"/>
+      <c r="AD27" s="209"/>
+      <c r="AE27" s="210"/>
+      <c r="AF27" s="211"/>
+      <c r="AG27" s="207"/>
+      <c r="AH27" s="207"/>
+      <c r="AI27" s="208"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="21"/>
-      <c r="B28" s="164"/>
-      <c r="C28" s="165"/>
-      <c r="D28" s="166"/>
-      <c r="E28" s="167"/>
-      <c r="F28" s="168"/>
-      <c r="G28" s="164"/>
-      <c r="H28" s="169"/>
-      <c r="I28" s="165"/>
-      <c r="J28" s="170"/>
-      <c r="K28" s="171"/>
-      <c r="L28" s="171"/>
-      <c r="M28" s="171"/>
-      <c r="N28" s="171"/>
-      <c r="O28" s="171"/>
-      <c r="P28" s="172"/>
-      <c r="Q28" s="173"/>
-      <c r="R28" s="174"/>
-      <c r="S28" s="174"/>
-      <c r="T28" s="174"/>
-      <c r="U28" s="174"/>
-      <c r="V28" s="174"/>
-      <c r="W28" s="174"/>
-      <c r="X28" s="174"/>
-      <c r="Y28" s="174"/>
-      <c r="Z28" s="174"/>
-      <c r="AA28" s="174"/>
-      <c r="AB28" s="174"/>
-      <c r="AC28" s="174"/>
-      <c r="AD28" s="174"/>
-      <c r="AE28" s="175"/>
-      <c r="AF28" s="170"/>
-      <c r="AG28" s="171"/>
-      <c r="AH28" s="171"/>
-      <c r="AI28" s="172"/>
+      <c r="B28" s="200"/>
+      <c r="C28" s="201"/>
+      <c r="D28" s="202"/>
+      <c r="E28" s="203"/>
+      <c r="F28" s="204"/>
+      <c r="G28" s="200"/>
+      <c r="H28" s="205"/>
+      <c r="I28" s="201"/>
+      <c r="J28" s="211"/>
+      <c r="K28" s="207"/>
+      <c r="L28" s="207"/>
+      <c r="M28" s="207"/>
+      <c r="N28" s="207"/>
+      <c r="O28" s="207"/>
+      <c r="P28" s="208"/>
+      <c r="Q28" s="206"/>
+      <c r="R28" s="209"/>
+      <c r="S28" s="209"/>
+      <c r="T28" s="209"/>
+      <c r="U28" s="209"/>
+      <c r="V28" s="209"/>
+      <c r="W28" s="209"/>
+      <c r="X28" s="209"/>
+      <c r="Y28" s="209"/>
+      <c r="Z28" s="209"/>
+      <c r="AA28" s="209"/>
+      <c r="AB28" s="209"/>
+      <c r="AC28" s="209"/>
+      <c r="AD28" s="209"/>
+      <c r="AE28" s="210"/>
+      <c r="AF28" s="211"/>
+      <c r="AG28" s="207"/>
+      <c r="AH28" s="207"/>
+      <c r="AI28" s="208"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="21"/>
-      <c r="B29" s="164"/>
-      <c r="C29" s="165"/>
-      <c r="D29" s="166"/>
-      <c r="E29" s="167"/>
-      <c r="F29" s="168"/>
-      <c r="G29" s="164"/>
-      <c r="H29" s="169"/>
-      <c r="I29" s="165"/>
-      <c r="J29" s="170"/>
-      <c r="K29" s="171"/>
-      <c r="L29" s="171"/>
-      <c r="M29" s="171"/>
-      <c r="N29" s="171"/>
-      <c r="O29" s="171"/>
-      <c r="P29" s="172"/>
-      <c r="Q29" s="173"/>
-      <c r="R29" s="174"/>
-      <c r="S29" s="174"/>
-      <c r="T29" s="174"/>
-      <c r="U29" s="174"/>
-      <c r="V29" s="174"/>
-      <c r="W29" s="174"/>
-      <c r="X29" s="174"/>
-      <c r="Y29" s="174"/>
-      <c r="Z29" s="174"/>
-      <c r="AA29" s="174"/>
-      <c r="AB29" s="174"/>
-      <c r="AC29" s="174"/>
-      <c r="AD29" s="174"/>
-      <c r="AE29" s="175"/>
-      <c r="AF29" s="170"/>
-      <c r="AG29" s="171"/>
-      <c r="AH29" s="171"/>
-      <c r="AI29" s="172"/>
+      <c r="B29" s="200"/>
+      <c r="C29" s="201"/>
+      <c r="D29" s="202"/>
+      <c r="E29" s="203"/>
+      <c r="F29" s="204"/>
+      <c r="G29" s="200"/>
+      <c r="H29" s="205"/>
+      <c r="I29" s="201"/>
+      <c r="J29" s="211"/>
+      <c r="K29" s="207"/>
+      <c r="L29" s="207"/>
+      <c r="M29" s="207"/>
+      <c r="N29" s="207"/>
+      <c r="O29" s="207"/>
+      <c r="P29" s="208"/>
+      <c r="Q29" s="206"/>
+      <c r="R29" s="209"/>
+      <c r="S29" s="209"/>
+      <c r="T29" s="209"/>
+      <c r="U29" s="209"/>
+      <c r="V29" s="209"/>
+      <c r="W29" s="209"/>
+      <c r="X29" s="209"/>
+      <c r="Y29" s="209"/>
+      <c r="Z29" s="209"/>
+      <c r="AA29" s="209"/>
+      <c r="AB29" s="209"/>
+      <c r="AC29" s="209"/>
+      <c r="AD29" s="209"/>
+      <c r="AE29" s="210"/>
+      <c r="AF29" s="211"/>
+      <c r="AG29" s="207"/>
+      <c r="AH29" s="207"/>
+      <c r="AI29" s="208"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="21"/>
-      <c r="B30" s="164"/>
-      <c r="C30" s="165"/>
-      <c r="D30" s="166"/>
-      <c r="E30" s="167"/>
-      <c r="F30" s="168"/>
-      <c r="G30" s="164"/>
-      <c r="H30" s="169"/>
-      <c r="I30" s="165"/>
-      <c r="J30" s="170"/>
-      <c r="K30" s="171"/>
-      <c r="L30" s="171"/>
-      <c r="M30" s="171"/>
-      <c r="N30" s="171"/>
-      <c r="O30" s="171"/>
-      <c r="P30" s="172"/>
-      <c r="Q30" s="173"/>
-      <c r="R30" s="174"/>
-      <c r="S30" s="174"/>
-      <c r="T30" s="174"/>
-      <c r="U30" s="174"/>
-      <c r="V30" s="174"/>
-      <c r="W30" s="174"/>
-      <c r="X30" s="174"/>
-      <c r="Y30" s="174"/>
-      <c r="Z30" s="174"/>
-      <c r="AA30" s="174"/>
-      <c r="AB30" s="174"/>
-      <c r="AC30" s="174"/>
-      <c r="AD30" s="174"/>
-      <c r="AE30" s="175"/>
-      <c r="AF30" s="170"/>
-      <c r="AG30" s="171"/>
-      <c r="AH30" s="171"/>
-      <c r="AI30" s="172"/>
+      <c r="B30" s="200"/>
+      <c r="C30" s="201"/>
+      <c r="D30" s="202"/>
+      <c r="E30" s="203"/>
+      <c r="F30" s="204"/>
+      <c r="G30" s="200"/>
+      <c r="H30" s="205"/>
+      <c r="I30" s="201"/>
+      <c r="J30" s="211"/>
+      <c r="K30" s="207"/>
+      <c r="L30" s="207"/>
+      <c r="M30" s="207"/>
+      <c r="N30" s="207"/>
+      <c r="O30" s="207"/>
+      <c r="P30" s="208"/>
+      <c r="Q30" s="206"/>
+      <c r="R30" s="209"/>
+      <c r="S30" s="209"/>
+      <c r="T30" s="209"/>
+      <c r="U30" s="209"/>
+      <c r="V30" s="209"/>
+      <c r="W30" s="209"/>
+      <c r="X30" s="209"/>
+      <c r="Y30" s="209"/>
+      <c r="Z30" s="209"/>
+      <c r="AA30" s="209"/>
+      <c r="AB30" s="209"/>
+      <c r="AC30" s="209"/>
+      <c r="AD30" s="209"/>
+      <c r="AE30" s="210"/>
+      <c r="AF30" s="211"/>
+      <c r="AG30" s="207"/>
+      <c r="AH30" s="207"/>
+      <c r="AI30" s="208"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="164"/>
-      <c r="C31" s="165"/>
-      <c r="D31" s="166"/>
-      <c r="E31" s="167"/>
-      <c r="F31" s="168"/>
-      <c r="G31" s="164"/>
-      <c r="H31" s="169"/>
-      <c r="I31" s="165"/>
-      <c r="J31" s="170"/>
-      <c r="K31" s="171"/>
-      <c r="L31" s="171"/>
-      <c r="M31" s="171"/>
-      <c r="N31" s="171"/>
-      <c r="O31" s="171"/>
-      <c r="P31" s="172"/>
-      <c r="Q31" s="173"/>
-      <c r="R31" s="174"/>
-      <c r="S31" s="174"/>
-      <c r="T31" s="174"/>
-      <c r="U31" s="174"/>
-      <c r="V31" s="174"/>
-      <c r="W31" s="174"/>
-      <c r="X31" s="174"/>
-      <c r="Y31" s="174"/>
-      <c r="Z31" s="174"/>
-      <c r="AA31" s="174"/>
-      <c r="AB31" s="174"/>
-      <c r="AC31" s="174"/>
-      <c r="AD31" s="174"/>
-      <c r="AE31" s="175"/>
-      <c r="AF31" s="170"/>
-      <c r="AG31" s="171"/>
-      <c r="AH31" s="171"/>
-      <c r="AI31" s="172"/>
+      <c r="B31" s="200"/>
+      <c r="C31" s="201"/>
+      <c r="D31" s="202"/>
+      <c r="E31" s="203"/>
+      <c r="F31" s="204"/>
+      <c r="G31" s="200"/>
+      <c r="H31" s="205"/>
+      <c r="I31" s="201"/>
+      <c r="J31" s="211"/>
+      <c r="K31" s="207"/>
+      <c r="L31" s="207"/>
+      <c r="M31" s="207"/>
+      <c r="N31" s="207"/>
+      <c r="O31" s="207"/>
+      <c r="P31" s="208"/>
+      <c r="Q31" s="206"/>
+      <c r="R31" s="209"/>
+      <c r="S31" s="209"/>
+      <c r="T31" s="209"/>
+      <c r="U31" s="209"/>
+      <c r="V31" s="209"/>
+      <c r="W31" s="209"/>
+      <c r="X31" s="209"/>
+      <c r="Y31" s="209"/>
+      <c r="Z31" s="209"/>
+      <c r="AA31" s="209"/>
+      <c r="AB31" s="209"/>
+      <c r="AC31" s="209"/>
+      <c r="AD31" s="209"/>
+      <c r="AE31" s="210"/>
+      <c r="AF31" s="211"/>
+      <c r="AG31" s="207"/>
+      <c r="AH31" s="207"/>
+      <c r="AI31" s="208"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="21"/>
-      <c r="B32" s="164"/>
-      <c r="C32" s="165"/>
-      <c r="D32" s="166"/>
-      <c r="E32" s="167"/>
-      <c r="F32" s="168"/>
-      <c r="G32" s="164"/>
-      <c r="H32" s="169"/>
-      <c r="I32" s="165"/>
-      <c r="J32" s="170"/>
-      <c r="K32" s="176"/>
-      <c r="L32" s="171"/>
-      <c r="M32" s="171"/>
-      <c r="N32" s="171"/>
-      <c r="O32" s="171"/>
-      <c r="P32" s="172"/>
-      <c r="Q32" s="173"/>
-      <c r="R32" s="174"/>
-      <c r="S32" s="174"/>
-      <c r="T32" s="174"/>
-      <c r="U32" s="174"/>
-      <c r="V32" s="174"/>
-      <c r="W32" s="174"/>
-      <c r="X32" s="174"/>
-      <c r="Y32" s="174"/>
-      <c r="Z32" s="174"/>
-      <c r="AA32" s="174"/>
-      <c r="AB32" s="174"/>
-      <c r="AC32" s="174"/>
-      <c r="AD32" s="174"/>
-      <c r="AE32" s="175"/>
-      <c r="AF32" s="170"/>
-      <c r="AG32" s="171"/>
-      <c r="AH32" s="171"/>
-      <c r="AI32" s="172"/>
+      <c r="B32" s="200"/>
+      <c r="C32" s="201"/>
+      <c r="D32" s="202"/>
+      <c r="E32" s="203"/>
+      <c r="F32" s="204"/>
+      <c r="G32" s="200"/>
+      <c r="H32" s="205"/>
+      <c r="I32" s="201"/>
+      <c r="J32" s="211"/>
+      <c r="K32" s="221"/>
+      <c r="L32" s="207"/>
+      <c r="M32" s="207"/>
+      <c r="N32" s="207"/>
+      <c r="O32" s="207"/>
+      <c r="P32" s="208"/>
+      <c r="Q32" s="206"/>
+      <c r="R32" s="209"/>
+      <c r="S32" s="209"/>
+      <c r="T32" s="209"/>
+      <c r="U32" s="209"/>
+      <c r="V32" s="209"/>
+      <c r="W32" s="209"/>
+      <c r="X32" s="209"/>
+      <c r="Y32" s="209"/>
+      <c r="Z32" s="209"/>
+      <c r="AA32" s="209"/>
+      <c r="AB32" s="209"/>
+      <c r="AC32" s="209"/>
+      <c r="AD32" s="209"/>
+      <c r="AE32" s="210"/>
+      <c r="AF32" s="211"/>
+      <c r="AG32" s="207"/>
+      <c r="AH32" s="207"/>
+      <c r="AI32" s="208"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="21"/>
-      <c r="B33" s="164"/>
-      <c r="C33" s="165"/>
-      <c r="D33" s="166"/>
-      <c r="E33" s="167"/>
-      <c r="F33" s="168"/>
-      <c r="G33" s="164"/>
-      <c r="H33" s="169"/>
-      <c r="I33" s="165"/>
-      <c r="J33" s="170"/>
-      <c r="K33" s="171"/>
-      <c r="L33" s="171"/>
-      <c r="M33" s="171"/>
-      <c r="N33" s="171"/>
-      <c r="O33" s="171"/>
-      <c r="P33" s="172"/>
-      <c r="Q33" s="173"/>
-      <c r="R33" s="174"/>
-      <c r="S33" s="174"/>
-      <c r="T33" s="174"/>
-      <c r="U33" s="174"/>
-      <c r="V33" s="174"/>
-      <c r="W33" s="174"/>
-      <c r="X33" s="174"/>
-      <c r="Y33" s="174"/>
-      <c r="Z33" s="174"/>
-      <c r="AA33" s="174"/>
-      <c r="AB33" s="174"/>
-      <c r="AC33" s="174"/>
-      <c r="AD33" s="174"/>
-      <c r="AE33" s="175"/>
-      <c r="AF33" s="170"/>
-      <c r="AG33" s="171"/>
-      <c r="AH33" s="171"/>
-      <c r="AI33" s="172"/>
+      <c r="B33" s="200"/>
+      <c r="C33" s="201"/>
+      <c r="D33" s="202"/>
+      <c r="E33" s="203"/>
+      <c r="F33" s="204"/>
+      <c r="G33" s="200"/>
+      <c r="H33" s="205"/>
+      <c r="I33" s="201"/>
+      <c r="J33" s="211"/>
+      <c r="K33" s="207"/>
+      <c r="L33" s="207"/>
+      <c r="M33" s="207"/>
+      <c r="N33" s="207"/>
+      <c r="O33" s="207"/>
+      <c r="P33" s="208"/>
+      <c r="Q33" s="206"/>
+      <c r="R33" s="209"/>
+      <c r="S33" s="209"/>
+      <c r="T33" s="209"/>
+      <c r="U33" s="209"/>
+      <c r="V33" s="209"/>
+      <c r="W33" s="209"/>
+      <c r="X33" s="209"/>
+      <c r="Y33" s="209"/>
+      <c r="Z33" s="209"/>
+      <c r="AA33" s="209"/>
+      <c r="AB33" s="209"/>
+      <c r="AC33" s="209"/>
+      <c r="AD33" s="209"/>
+      <c r="AE33" s="210"/>
+      <c r="AF33" s="211"/>
+      <c r="AG33" s="207"/>
+      <c r="AH33" s="207"/>
+      <c r="AI33" s="208"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -15484,161 +15639,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(バッチ)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(バッチ)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B77CD9C-CE51-43EB-AC17-55DC8C47BF12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4DF45E-3DAA-4252-A493-57EE5DCF4117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="619" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="643">
   <si>
     <t>正常取引</t>
     <rPh sb="0" eb="2">
@@ -6547,34 +6547,6 @@
       <t>ニュウリョク</t>
     </rPh>
     <rPh sb="19" eb="21">
-      <t>バアイ</t>
-    </rPh>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>数値項目に有効範囲の下限値＋1が入力された場合、エラーとなること。</t>
-    <rPh sb="0" eb="2">
-      <t>スウチ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ユウコウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ハンイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>カゲン</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>チ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="21" eb="23">
       <t>バアイ</t>
     </rPh>
     <phoneticPr fontId="20"/>
@@ -9889,6 +9861,72 @@
     <xf numFmtId="31" fontId="13" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="6" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -9995,72 +10033,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -13664,7 +13636,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="J23" s="7" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="24" spans="6:11" ht="13.5" customHeight="1">
@@ -14232,57 +14204,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="192" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="173" t="s">
+      <c r="B1" s="193"/>
+      <c r="C1" s="193"/>
+      <c r="D1" s="194"/>
+      <c r="E1" s="195" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="174"/>
-      <c r="G1" s="174"/>
-      <c r="H1" s="174"/>
-      <c r="I1" s="174"/>
-      <c r="J1" s="174"/>
-      <c r="K1" s="174"/>
-      <c r="L1" s="174"/>
-      <c r="M1" s="174"/>
-      <c r="N1" s="175"/>
-      <c r="O1" s="179" t="s">
+      <c r="F1" s="196"/>
+      <c r="G1" s="196"/>
+      <c r="H1" s="196"/>
+      <c r="I1" s="196"/>
+      <c r="J1" s="196"/>
+      <c r="K1" s="196"/>
+      <c r="L1" s="196"/>
+      <c r="M1" s="196"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="201" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="180"/>
-      <c r="Q1" s="180"/>
-      <c r="R1" s="181"/>
-      <c r="S1" s="188" t="s">
-        <v>642</v>
-      </c>
-      <c r="T1" s="189"/>
-      <c r="U1" s="189"/>
-      <c r="V1" s="189"/>
-      <c r="W1" s="189"/>
-      <c r="X1" s="189"/>
-      <c r="Y1" s="189"/>
-      <c r="Z1" s="190"/>
-      <c r="AA1" s="170" t="s">
+      <c r="P1" s="202"/>
+      <c r="Q1" s="202"/>
+      <c r="R1" s="203"/>
+      <c r="S1" s="210" t="s">
+        <v>641</v>
+      </c>
+      <c r="T1" s="211"/>
+      <c r="U1" s="211"/>
+      <c r="V1" s="211"/>
+      <c r="W1" s="211"/>
+      <c r="X1" s="211"/>
+      <c r="Y1" s="211"/>
+      <c r="Z1" s="212"/>
+      <c r="AA1" s="192" t="s">
         <v>65</v>
       </c>
-      <c r="AB1" s="172"/>
-      <c r="AC1" s="197" t="str">
+      <c r="AB1" s="194"/>
+      <c r="AC1" s="219" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="198"/>
-      <c r="AE1" s="198"/>
-      <c r="AF1" s="199"/>
-      <c r="AG1" s="164">
+      <c r="AD1" s="220"/>
+      <c r="AE1" s="220"/>
+      <c r="AF1" s="221"/>
+      <c r="AG1" s="186">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="165"/>
-      <c r="AI1" s="166"/>
+      <c r="AH1" s="187"/>
+      <c r="AI1" s="188"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -14290,53 +14262,53 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="170" t="s">
+      <c r="A2" s="192" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="171"/>
-      <c r="C2" s="171"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="173" t="s">
+      <c r="B2" s="193"/>
+      <c r="C2" s="193"/>
+      <c r="D2" s="194"/>
+      <c r="E2" s="195" t="s">
         <v>84</v>
       </c>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
-      <c r="L2" s="174"/>
-      <c r="M2" s="174"/>
-      <c r="N2" s="175"/>
-      <c r="O2" s="182"/>
-      <c r="P2" s="183"/>
-      <c r="Q2" s="183"/>
-      <c r="R2" s="184"/>
-      <c r="S2" s="191"/>
-      <c r="T2" s="192"/>
-      <c r="U2" s="192"/>
-      <c r="V2" s="192"/>
-      <c r="W2" s="192"/>
-      <c r="X2" s="192"/>
-      <c r="Y2" s="192"/>
-      <c r="Z2" s="193"/>
-      <c r="AA2" s="170" t="s">
+      <c r="F2" s="196"/>
+      <c r="G2" s="196"/>
+      <c r="H2" s="196"/>
+      <c r="I2" s="196"/>
+      <c r="J2" s="196"/>
+      <c r="K2" s="196"/>
+      <c r="L2" s="196"/>
+      <c r="M2" s="196"/>
+      <c r="N2" s="197"/>
+      <c r="O2" s="204"/>
+      <c r="P2" s="205"/>
+      <c r="Q2" s="205"/>
+      <c r="R2" s="206"/>
+      <c r="S2" s="213"/>
+      <c r="T2" s="214"/>
+      <c r="U2" s="214"/>
+      <c r="V2" s="214"/>
+      <c r="W2" s="214"/>
+      <c r="X2" s="214"/>
+      <c r="Y2" s="214"/>
+      <c r="Z2" s="215"/>
+      <c r="AA2" s="192" t="s">
         <v>67</v>
       </c>
-      <c r="AB2" s="172"/>
-      <c r="AC2" s="176" t="str">
+      <c r="AB2" s="194"/>
+      <c r="AC2" s="198" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="177"/>
-      <c r="AE2" s="177"/>
-      <c r="AF2" s="178"/>
-      <c r="AG2" s="164">
+      <c r="AD2" s="199"/>
+      <c r="AE2" s="199"/>
+      <c r="AF2" s="200"/>
+      <c r="AG2" s="186">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44852</v>
       </c>
-      <c r="AH2" s="165"/>
-      <c r="AI2" s="166"/>
+      <c r="AH2" s="187"/>
+      <c r="AI2" s="188"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -14344,45 +14316,45 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="170" t="s">
+      <c r="A3" s="192" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="171"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="173" t="s">
+      <c r="B3" s="193"/>
+      <c r="C3" s="193"/>
+      <c r="D3" s="194"/>
+      <c r="E3" s="195" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="174"/>
-      <c r="G3" s="174"/>
-      <c r="H3" s="174"/>
-      <c r="I3" s="174"/>
-      <c r="J3" s="174"/>
-      <c r="K3" s="174"/>
-      <c r="L3" s="174"/>
-      <c r="M3" s="174"/>
-      <c r="N3" s="175"/>
-      <c r="O3" s="185"/>
-      <c r="P3" s="186"/>
-      <c r="Q3" s="186"/>
-      <c r="R3" s="187"/>
-      <c r="S3" s="194"/>
-      <c r="T3" s="195"/>
-      <c r="U3" s="195"/>
-      <c r="V3" s="195"/>
-      <c r="W3" s="195"/>
-      <c r="X3" s="195"/>
-      <c r="Y3" s="195"/>
-      <c r="Z3" s="196"/>
-      <c r="AA3" s="170"/>
-      <c r="AB3" s="172"/>
-      <c r="AC3" s="197"/>
-      <c r="AD3" s="198"/>
-      <c r="AE3" s="198"/>
-      <c r="AF3" s="199"/>
-      <c r="AG3" s="164"/>
-      <c r="AH3" s="165"/>
-      <c r="AI3" s="166"/>
+      <c r="F3" s="196"/>
+      <c r="G3" s="196"/>
+      <c r="H3" s="196"/>
+      <c r="I3" s="196"/>
+      <c r="J3" s="196"/>
+      <c r="K3" s="196"/>
+      <c r="L3" s="196"/>
+      <c r="M3" s="196"/>
+      <c r="N3" s="197"/>
+      <c r="O3" s="207"/>
+      <c r="P3" s="208"/>
+      <c r="Q3" s="208"/>
+      <c r="R3" s="209"/>
+      <c r="S3" s="216"/>
+      <c r="T3" s="217"/>
+      <c r="U3" s="217"/>
+      <c r="V3" s="217"/>
+      <c r="W3" s="217"/>
+      <c r="X3" s="217"/>
+      <c r="Y3" s="217"/>
+      <c r="Z3" s="218"/>
+      <c r="AA3" s="192"/>
+      <c r="AB3" s="194"/>
+      <c r="AC3" s="219"/>
+      <c r="AD3" s="220"/>
+      <c r="AE3" s="220"/>
+      <c r="AF3" s="221"/>
+      <c r="AG3" s="186"/>
+      <c r="AH3" s="187"/>
+      <c r="AI3" s="188"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -14419,97 +14391,97 @@
       <c r="A7" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="167" t="s">
+      <c r="B7" s="189" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="168"/>
-      <c r="D7" s="167" t="s">
+      <c r="C7" s="190"/>
+      <c r="D7" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="169"/>
-      <c r="F7" s="168"/>
-      <c r="G7" s="167" t="s">
+      <c r="E7" s="191"/>
+      <c r="F7" s="190"/>
+      <c r="G7" s="189" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="169"/>
-      <c r="I7" s="168"/>
-      <c r="J7" s="167" t="s">
+      <c r="H7" s="191"/>
+      <c r="I7" s="190"/>
+      <c r="J7" s="189" t="s">
         <v>73</v>
       </c>
-      <c r="K7" s="169"/>
-      <c r="L7" s="169"/>
-      <c r="M7" s="169"/>
-      <c r="N7" s="169"/>
-      <c r="O7" s="169"/>
-      <c r="P7" s="168"/>
-      <c r="Q7" s="167" t="s">
+      <c r="K7" s="191"/>
+      <c r="L7" s="191"/>
+      <c r="M7" s="191"/>
+      <c r="N7" s="191"/>
+      <c r="O7" s="191"/>
+      <c r="P7" s="190"/>
+      <c r="Q7" s="189" t="s">
         <v>74</v>
       </c>
-      <c r="R7" s="169"/>
-      <c r="S7" s="169"/>
-      <c r="T7" s="169"/>
-      <c r="U7" s="169"/>
-      <c r="V7" s="169"/>
-      <c r="W7" s="169"/>
-      <c r="X7" s="169"/>
-      <c r="Y7" s="169"/>
-      <c r="Z7" s="169"/>
-      <c r="AA7" s="169"/>
-      <c r="AB7" s="169"/>
-      <c r="AC7" s="169"/>
-      <c r="AD7" s="169"/>
-      <c r="AE7" s="168"/>
-      <c r="AF7" s="167" t="s">
+      <c r="R7" s="191"/>
+      <c r="S7" s="191"/>
+      <c r="T7" s="191"/>
+      <c r="U7" s="191"/>
+      <c r="V7" s="191"/>
+      <c r="W7" s="191"/>
+      <c r="X7" s="191"/>
+      <c r="Y7" s="191"/>
+      <c r="Z7" s="191"/>
+      <c r="AA7" s="191"/>
+      <c r="AB7" s="191"/>
+      <c r="AC7" s="191"/>
+      <c r="AD7" s="191"/>
+      <c r="AE7" s="190"/>
+      <c r="AF7" s="189" t="s">
         <v>75</v>
       </c>
-      <c r="AG7" s="169"/>
-      <c r="AH7" s="169"/>
-      <c r="AI7" s="168"/>
+      <c r="AG7" s="191"/>
+      <c r="AH7" s="191"/>
+      <c r="AI7" s="190"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="24">
         <v>1</v>
       </c>
-      <c r="B8" s="212" t="s">
+      <c r="B8" s="177" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="213"/>
-      <c r="D8" s="214">
+      <c r="C8" s="178"/>
+      <c r="D8" s="179">
         <v>43336</v>
       </c>
-      <c r="E8" s="215"/>
-      <c r="F8" s="216"/>
-      <c r="G8" s="212" t="s">
+      <c r="E8" s="180"/>
+      <c r="F8" s="181"/>
+      <c r="G8" s="177" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="217"/>
-      <c r="I8" s="213"/>
-      <c r="J8" s="218" t="s">
+      <c r="H8" s="182"/>
+      <c r="I8" s="178"/>
+      <c r="J8" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="K8" s="219"/>
-      <c r="L8" s="219"/>
-      <c r="M8" s="219"/>
-      <c r="N8" s="219"/>
-      <c r="O8" s="219"/>
-      <c r="P8" s="220"/>
-      <c r="Q8" s="218" t="s">
+      <c r="K8" s="184"/>
+      <c r="L8" s="184"/>
+      <c r="M8" s="184"/>
+      <c r="N8" s="184"/>
+      <c r="O8" s="184"/>
+      <c r="P8" s="185"/>
+      <c r="Q8" s="183" t="s">
         <v>79</v>
       </c>
-      <c r="R8" s="219"/>
-      <c r="S8" s="219"/>
-      <c r="T8" s="219"/>
-      <c r="U8" s="219"/>
-      <c r="V8" s="219"/>
-      <c r="W8" s="219"/>
-      <c r="X8" s="219"/>
-      <c r="Y8" s="219"/>
-      <c r="Z8" s="219"/>
-      <c r="AA8" s="219"/>
-      <c r="AB8" s="219"/>
-      <c r="AC8" s="219"/>
-      <c r="AD8" s="219"/>
-      <c r="AE8" s="220"/>
+      <c r="R8" s="184"/>
+      <c r="S8" s="184"/>
+      <c r="T8" s="184"/>
+      <c r="U8" s="184"/>
+      <c r="V8" s="184"/>
+      <c r="W8" s="184"/>
+      <c r="X8" s="184"/>
+      <c r="Y8" s="184"/>
+      <c r="Z8" s="184"/>
+      <c r="AA8" s="184"/>
+      <c r="AB8" s="184"/>
+      <c r="AC8" s="184"/>
+      <c r="AD8" s="184"/>
+      <c r="AE8" s="185"/>
       <c r="AF8" s="25" t="s">
         <v>80</v>
       </c>
@@ -14521,1101 +14493,946 @@
       <c r="A9" s="24">
         <v>2</v>
       </c>
-      <c r="B9" s="200" t="s">
+      <c r="B9" s="164" t="s">
+        <v>546</v>
+      </c>
+      <c r="C9" s="165"/>
+      <c r="D9" s="166">
+        <v>44852</v>
+      </c>
+      <c r="E9" s="167"/>
+      <c r="F9" s="168"/>
+      <c r="G9" s="166" t="s">
         <v>547</v>
       </c>
-      <c r="C9" s="201"/>
-      <c r="D9" s="202">
-        <v>44852</v>
-      </c>
-      <c r="E9" s="203"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="202" t="s">
+      <c r="H9" s="169"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="173" t="s">
+        <v>549</v>
+      </c>
+      <c r="K9" s="171"/>
+      <c r="L9" s="171"/>
+      <c r="M9" s="171"/>
+      <c r="N9" s="171"/>
+      <c r="O9" s="171"/>
+      <c r="P9" s="172"/>
+      <c r="Q9" s="173" t="s">
         <v>548</v>
       </c>
-      <c r="H9" s="205"/>
-      <c r="I9" s="201"/>
-      <c r="J9" s="206" t="s">
-        <v>550</v>
-      </c>
-      <c r="K9" s="207"/>
-      <c r="L9" s="207"/>
-      <c r="M9" s="207"/>
-      <c r="N9" s="207"/>
-      <c r="O9" s="207"/>
-      <c r="P9" s="208"/>
-      <c r="Q9" s="206" t="s">
-        <v>549</v>
-      </c>
-      <c r="R9" s="209"/>
-      <c r="S9" s="209"/>
-      <c r="T9" s="209"/>
-      <c r="U9" s="209"/>
-      <c r="V9" s="209"/>
-      <c r="W9" s="209"/>
-      <c r="X9" s="209"/>
-      <c r="Y9" s="209"/>
-      <c r="Z9" s="209"/>
-      <c r="AA9" s="209"/>
-      <c r="AB9" s="209"/>
-      <c r="AC9" s="209"/>
-      <c r="AD9" s="209"/>
-      <c r="AE9" s="210"/>
-      <c r="AF9" s="211" t="s">
+      <c r="R9" s="174"/>
+      <c r="S9" s="174"/>
+      <c r="T9" s="174"/>
+      <c r="U9" s="174"/>
+      <c r="V9" s="174"/>
+      <c r="W9" s="174"/>
+      <c r="X9" s="174"/>
+      <c r="Y9" s="174"/>
+      <c r="Z9" s="174"/>
+      <c r="AA9" s="174"/>
+      <c r="AB9" s="174"/>
+      <c r="AC9" s="174"/>
+      <c r="AD9" s="174"/>
+      <c r="AE9" s="175"/>
+      <c r="AF9" s="170" t="s">
         <v>80</v>
       </c>
-      <c r="AG9" s="207"/>
-      <c r="AH9" s="207"/>
-      <c r="AI9" s="208"/>
+      <c r="AG9" s="171"/>
+      <c r="AH9" s="171"/>
+      <c r="AI9" s="172"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="21"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="201"/>
-      <c r="D10" s="202"/>
-      <c r="E10" s="203"/>
-      <c r="F10" s="204"/>
-      <c r="G10" s="200"/>
-      <c r="H10" s="205"/>
-      <c r="I10" s="201"/>
-      <c r="J10" s="211"/>
-      <c r="K10" s="207"/>
-      <c r="L10" s="207"/>
-      <c r="M10" s="207"/>
-      <c r="N10" s="207"/>
-      <c r="O10" s="207"/>
-      <c r="P10" s="208"/>
-      <c r="Q10" s="206"/>
-      <c r="R10" s="209"/>
-      <c r="S10" s="209"/>
-      <c r="T10" s="209"/>
-      <c r="U10" s="209"/>
-      <c r="V10" s="209"/>
-      <c r="W10" s="209"/>
-      <c r="X10" s="209"/>
-      <c r="Y10" s="209"/>
-      <c r="Z10" s="209"/>
-      <c r="AA10" s="209"/>
-      <c r="AB10" s="209"/>
-      <c r="AC10" s="209"/>
-      <c r="AD10" s="209"/>
-      <c r="AE10" s="210"/>
-      <c r="AF10" s="211"/>
-      <c r="AG10" s="207"/>
-      <c r="AH10" s="207"/>
-      <c r="AI10" s="208"/>
+      <c r="B10" s="164"/>
+      <c r="C10" s="165"/>
+      <c r="D10" s="166"/>
+      <c r="E10" s="167"/>
+      <c r="F10" s="168"/>
+      <c r="G10" s="164"/>
+      <c r="H10" s="169"/>
+      <c r="I10" s="165"/>
+      <c r="J10" s="170"/>
+      <c r="K10" s="171"/>
+      <c r="L10" s="171"/>
+      <c r="M10" s="171"/>
+      <c r="N10" s="171"/>
+      <c r="O10" s="171"/>
+      <c r="P10" s="172"/>
+      <c r="Q10" s="173"/>
+      <c r="R10" s="174"/>
+      <c r="S10" s="174"/>
+      <c r="T10" s="174"/>
+      <c r="U10" s="174"/>
+      <c r="V10" s="174"/>
+      <c r="W10" s="174"/>
+      <c r="X10" s="174"/>
+      <c r="Y10" s="174"/>
+      <c r="Z10" s="174"/>
+      <c r="AA10" s="174"/>
+      <c r="AB10" s="174"/>
+      <c r="AC10" s="174"/>
+      <c r="AD10" s="174"/>
+      <c r="AE10" s="175"/>
+      <c r="AF10" s="170"/>
+      <c r="AG10" s="171"/>
+      <c r="AH10" s="171"/>
+      <c r="AI10" s="172"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="21"/>
-      <c r="B11" s="200"/>
-      <c r="C11" s="201"/>
-      <c r="D11" s="202"/>
-      <c r="E11" s="203"/>
-      <c r="F11" s="204"/>
-      <c r="G11" s="200"/>
-      <c r="H11" s="205"/>
-      <c r="I11" s="201"/>
-      <c r="J11" s="211"/>
-      <c r="K11" s="207"/>
-      <c r="L11" s="207"/>
-      <c r="M11" s="207"/>
-      <c r="N11" s="207"/>
-      <c r="O11" s="207"/>
-      <c r="P11" s="208"/>
-      <c r="Q11" s="206"/>
-      <c r="R11" s="209"/>
-      <c r="S11" s="209"/>
-      <c r="T11" s="209"/>
-      <c r="U11" s="209"/>
-      <c r="V11" s="209"/>
-      <c r="W11" s="209"/>
-      <c r="X11" s="209"/>
-      <c r="Y11" s="209"/>
-      <c r="Z11" s="209"/>
-      <c r="AA11" s="209"/>
-      <c r="AB11" s="209"/>
-      <c r="AC11" s="209"/>
-      <c r="AD11" s="209"/>
-      <c r="AE11" s="210"/>
-      <c r="AF11" s="211"/>
-      <c r="AG11" s="207"/>
-      <c r="AH11" s="207"/>
-      <c r="AI11" s="208"/>
+      <c r="B11" s="164"/>
+      <c r="C11" s="165"/>
+      <c r="D11" s="166"/>
+      <c r="E11" s="167"/>
+      <c r="F11" s="168"/>
+      <c r="G11" s="164"/>
+      <c r="H11" s="169"/>
+      <c r="I11" s="165"/>
+      <c r="J11" s="170"/>
+      <c r="K11" s="171"/>
+      <c r="L11" s="171"/>
+      <c r="M11" s="171"/>
+      <c r="N11" s="171"/>
+      <c r="O11" s="171"/>
+      <c r="P11" s="172"/>
+      <c r="Q11" s="173"/>
+      <c r="R11" s="174"/>
+      <c r="S11" s="174"/>
+      <c r="T11" s="174"/>
+      <c r="U11" s="174"/>
+      <c r="V11" s="174"/>
+      <c r="W11" s="174"/>
+      <c r="X11" s="174"/>
+      <c r="Y11" s="174"/>
+      <c r="Z11" s="174"/>
+      <c r="AA11" s="174"/>
+      <c r="AB11" s="174"/>
+      <c r="AC11" s="174"/>
+      <c r="AD11" s="174"/>
+      <c r="AE11" s="175"/>
+      <c r="AF11" s="170"/>
+      <c r="AG11" s="171"/>
+      <c r="AH11" s="171"/>
+      <c r="AI11" s="172"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="21"/>
-      <c r="B12" s="200"/>
-      <c r="C12" s="201"/>
-      <c r="D12" s="202"/>
-      <c r="E12" s="203"/>
-      <c r="F12" s="204"/>
-      <c r="G12" s="200"/>
-      <c r="H12" s="205"/>
-      <c r="I12" s="201"/>
-      <c r="J12" s="211"/>
-      <c r="K12" s="207"/>
-      <c r="L12" s="207"/>
-      <c r="M12" s="207"/>
-      <c r="N12" s="207"/>
-      <c r="O12" s="207"/>
-      <c r="P12" s="208"/>
-      <c r="Q12" s="206"/>
-      <c r="R12" s="209"/>
-      <c r="S12" s="209"/>
-      <c r="T12" s="209"/>
-      <c r="U12" s="209"/>
-      <c r="V12" s="209"/>
-      <c r="W12" s="209"/>
-      <c r="X12" s="209"/>
-      <c r="Y12" s="209"/>
-      <c r="Z12" s="209"/>
-      <c r="AA12" s="209"/>
-      <c r="AB12" s="209"/>
-      <c r="AC12" s="209"/>
-      <c r="AD12" s="209"/>
-      <c r="AE12" s="210"/>
-      <c r="AF12" s="211"/>
-      <c r="AG12" s="207"/>
-      <c r="AH12" s="207"/>
-      <c r="AI12" s="208"/>
+      <c r="B12" s="164"/>
+      <c r="C12" s="165"/>
+      <c r="D12" s="166"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="168"/>
+      <c r="G12" s="164"/>
+      <c r="H12" s="169"/>
+      <c r="I12" s="165"/>
+      <c r="J12" s="170"/>
+      <c r="K12" s="171"/>
+      <c r="L12" s="171"/>
+      <c r="M12" s="171"/>
+      <c r="N12" s="171"/>
+      <c r="O12" s="171"/>
+      <c r="P12" s="172"/>
+      <c r="Q12" s="173"/>
+      <c r="R12" s="174"/>
+      <c r="S12" s="174"/>
+      <c r="T12" s="174"/>
+      <c r="U12" s="174"/>
+      <c r="V12" s="174"/>
+      <c r="W12" s="174"/>
+      <c r="X12" s="174"/>
+      <c r="Y12" s="174"/>
+      <c r="Z12" s="174"/>
+      <c r="AA12" s="174"/>
+      <c r="AB12" s="174"/>
+      <c r="AC12" s="174"/>
+      <c r="AD12" s="174"/>
+      <c r="AE12" s="175"/>
+      <c r="AF12" s="170"/>
+      <c r="AG12" s="171"/>
+      <c r="AH12" s="171"/>
+      <c r="AI12" s="172"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="21"/>
-      <c r="B13" s="200"/>
-      <c r="C13" s="201"/>
-      <c r="D13" s="202"/>
-      <c r="E13" s="203"/>
-      <c r="F13" s="204"/>
-      <c r="G13" s="200"/>
-      <c r="H13" s="205"/>
-      <c r="I13" s="201"/>
-      <c r="J13" s="211"/>
-      <c r="K13" s="207"/>
-      <c r="L13" s="207"/>
-      <c r="M13" s="207"/>
-      <c r="N13" s="207"/>
-      <c r="O13" s="207"/>
-      <c r="P13" s="208"/>
-      <c r="Q13" s="206"/>
-      <c r="R13" s="209"/>
-      <c r="S13" s="209"/>
-      <c r="T13" s="209"/>
-      <c r="U13" s="209"/>
-      <c r="V13" s="209"/>
-      <c r="W13" s="209"/>
-      <c r="X13" s="209"/>
-      <c r="Y13" s="209"/>
-      <c r="Z13" s="209"/>
-      <c r="AA13" s="209"/>
-      <c r="AB13" s="209"/>
-      <c r="AC13" s="209"/>
-      <c r="AD13" s="209"/>
-      <c r="AE13" s="210"/>
-      <c r="AF13" s="211"/>
-      <c r="AG13" s="207"/>
-      <c r="AH13" s="207"/>
-      <c r="AI13" s="208"/>
+      <c r="B13" s="164"/>
+      <c r="C13" s="165"/>
+      <c r="D13" s="166"/>
+      <c r="E13" s="167"/>
+      <c r="F13" s="168"/>
+      <c r="G13" s="164"/>
+      <c r="H13" s="169"/>
+      <c r="I13" s="165"/>
+      <c r="J13" s="170"/>
+      <c r="K13" s="171"/>
+      <c r="L13" s="171"/>
+      <c r="M13" s="171"/>
+      <c r="N13" s="171"/>
+      <c r="O13" s="171"/>
+      <c r="P13" s="172"/>
+      <c r="Q13" s="173"/>
+      <c r="R13" s="174"/>
+      <c r="S13" s="174"/>
+      <c r="T13" s="174"/>
+      <c r="U13" s="174"/>
+      <c r="V13" s="174"/>
+      <c r="W13" s="174"/>
+      <c r="X13" s="174"/>
+      <c r="Y13" s="174"/>
+      <c r="Z13" s="174"/>
+      <c r="AA13" s="174"/>
+      <c r="AB13" s="174"/>
+      <c r="AC13" s="174"/>
+      <c r="AD13" s="174"/>
+      <c r="AE13" s="175"/>
+      <c r="AF13" s="170"/>
+      <c r="AG13" s="171"/>
+      <c r="AH13" s="171"/>
+      <c r="AI13" s="172"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="200"/>
-      <c r="C14" s="201"/>
-      <c r="D14" s="202"/>
-      <c r="E14" s="203"/>
-      <c r="F14" s="204"/>
-      <c r="G14" s="200"/>
-      <c r="H14" s="205"/>
-      <c r="I14" s="201"/>
-      <c r="J14" s="211"/>
-      <c r="K14" s="207"/>
-      <c r="L14" s="207"/>
-      <c r="M14" s="207"/>
-      <c r="N14" s="207"/>
-      <c r="O14" s="207"/>
-      <c r="P14" s="208"/>
-      <c r="Q14" s="206"/>
-      <c r="R14" s="209"/>
-      <c r="S14" s="209"/>
-      <c r="T14" s="209"/>
-      <c r="U14" s="209"/>
-      <c r="V14" s="209"/>
-      <c r="W14" s="209"/>
-      <c r="X14" s="209"/>
-      <c r="Y14" s="209"/>
-      <c r="Z14" s="209"/>
-      <c r="AA14" s="209"/>
-      <c r="AB14" s="209"/>
-      <c r="AC14" s="209"/>
-      <c r="AD14" s="209"/>
-      <c r="AE14" s="210"/>
-      <c r="AF14" s="211"/>
-      <c r="AG14" s="207"/>
-      <c r="AH14" s="207"/>
-      <c r="AI14" s="208"/>
+      <c r="B14" s="164"/>
+      <c r="C14" s="165"/>
+      <c r="D14" s="166"/>
+      <c r="E14" s="167"/>
+      <c r="F14" s="168"/>
+      <c r="G14" s="164"/>
+      <c r="H14" s="169"/>
+      <c r="I14" s="165"/>
+      <c r="J14" s="170"/>
+      <c r="K14" s="171"/>
+      <c r="L14" s="171"/>
+      <c r="M14" s="171"/>
+      <c r="N14" s="171"/>
+      <c r="O14" s="171"/>
+      <c r="P14" s="172"/>
+      <c r="Q14" s="173"/>
+      <c r="R14" s="174"/>
+      <c r="S14" s="174"/>
+      <c r="T14" s="174"/>
+      <c r="U14" s="174"/>
+      <c r="V14" s="174"/>
+      <c r="W14" s="174"/>
+      <c r="X14" s="174"/>
+      <c r="Y14" s="174"/>
+      <c r="Z14" s="174"/>
+      <c r="AA14" s="174"/>
+      <c r="AB14" s="174"/>
+      <c r="AC14" s="174"/>
+      <c r="AD14" s="174"/>
+      <c r="AE14" s="175"/>
+      <c r="AF14" s="170"/>
+      <c r="AG14" s="171"/>
+      <c r="AH14" s="171"/>
+      <c r="AI14" s="172"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="21"/>
-      <c r="B15" s="200"/>
-      <c r="C15" s="201"/>
-      <c r="D15" s="202"/>
-      <c r="E15" s="203"/>
-      <c r="F15" s="204"/>
-      <c r="G15" s="200"/>
-      <c r="H15" s="205"/>
-      <c r="I15" s="201"/>
-      <c r="J15" s="211"/>
-      <c r="K15" s="207"/>
-      <c r="L15" s="207"/>
-      <c r="M15" s="207"/>
-      <c r="N15" s="207"/>
-      <c r="O15" s="207"/>
-      <c r="P15" s="208"/>
-      <c r="Q15" s="206"/>
-      <c r="R15" s="209"/>
-      <c r="S15" s="209"/>
-      <c r="T15" s="209"/>
-      <c r="U15" s="209"/>
-      <c r="V15" s="209"/>
-      <c r="W15" s="209"/>
-      <c r="X15" s="209"/>
-      <c r="Y15" s="209"/>
-      <c r="Z15" s="209"/>
-      <c r="AA15" s="209"/>
-      <c r="AB15" s="209"/>
-      <c r="AC15" s="209"/>
-      <c r="AD15" s="209"/>
-      <c r="AE15" s="210"/>
-      <c r="AF15" s="211"/>
-      <c r="AG15" s="207"/>
-      <c r="AH15" s="207"/>
-      <c r="AI15" s="208"/>
+      <c r="B15" s="164"/>
+      <c r="C15" s="165"/>
+      <c r="D15" s="166"/>
+      <c r="E15" s="167"/>
+      <c r="F15" s="168"/>
+      <c r="G15" s="164"/>
+      <c r="H15" s="169"/>
+      <c r="I15" s="165"/>
+      <c r="J15" s="170"/>
+      <c r="K15" s="171"/>
+      <c r="L15" s="171"/>
+      <c r="M15" s="171"/>
+      <c r="N15" s="171"/>
+      <c r="O15" s="171"/>
+      <c r="P15" s="172"/>
+      <c r="Q15" s="173"/>
+      <c r="R15" s="174"/>
+      <c r="S15" s="174"/>
+      <c r="T15" s="174"/>
+      <c r="U15" s="174"/>
+      <c r="V15" s="174"/>
+      <c r="W15" s="174"/>
+      <c r="X15" s="174"/>
+      <c r="Y15" s="174"/>
+      <c r="Z15" s="174"/>
+      <c r="AA15" s="174"/>
+      <c r="AB15" s="174"/>
+      <c r="AC15" s="174"/>
+      <c r="AD15" s="174"/>
+      <c r="AE15" s="175"/>
+      <c r="AF15" s="170"/>
+      <c r="AG15" s="171"/>
+      <c r="AH15" s="171"/>
+      <c r="AI15" s="172"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="21"/>
-      <c r="B16" s="200"/>
-      <c r="C16" s="201"/>
-      <c r="D16" s="202"/>
-      <c r="E16" s="203"/>
-      <c r="F16" s="204"/>
-      <c r="G16" s="200"/>
-      <c r="H16" s="205"/>
-      <c r="I16" s="201"/>
-      <c r="J16" s="211"/>
-      <c r="K16" s="207"/>
-      <c r="L16" s="207"/>
-      <c r="M16" s="207"/>
-      <c r="N16" s="207"/>
-      <c r="O16" s="207"/>
-      <c r="P16" s="208"/>
-      <c r="Q16" s="206"/>
-      <c r="R16" s="209"/>
-      <c r="S16" s="209"/>
-      <c r="T16" s="209"/>
-      <c r="U16" s="209"/>
-      <c r="V16" s="209"/>
-      <c r="W16" s="209"/>
-      <c r="X16" s="209"/>
-      <c r="Y16" s="209"/>
-      <c r="Z16" s="209"/>
-      <c r="AA16" s="209"/>
-      <c r="AB16" s="209"/>
-      <c r="AC16" s="209"/>
-      <c r="AD16" s="209"/>
-      <c r="AE16" s="210"/>
-      <c r="AF16" s="211"/>
-      <c r="AG16" s="207"/>
-      <c r="AH16" s="207"/>
-      <c r="AI16" s="208"/>
+      <c r="B16" s="164"/>
+      <c r="C16" s="165"/>
+      <c r="D16" s="166"/>
+      <c r="E16" s="167"/>
+      <c r="F16" s="168"/>
+      <c r="G16" s="164"/>
+      <c r="H16" s="169"/>
+      <c r="I16" s="165"/>
+      <c r="J16" s="170"/>
+      <c r="K16" s="171"/>
+      <c r="L16" s="171"/>
+      <c r="M16" s="171"/>
+      <c r="N16" s="171"/>
+      <c r="O16" s="171"/>
+      <c r="P16" s="172"/>
+      <c r="Q16" s="173"/>
+      <c r="R16" s="174"/>
+      <c r="S16" s="174"/>
+      <c r="T16" s="174"/>
+      <c r="U16" s="174"/>
+      <c r="V16" s="174"/>
+      <c r="W16" s="174"/>
+      <c r="X16" s="174"/>
+      <c r="Y16" s="174"/>
+      <c r="Z16" s="174"/>
+      <c r="AA16" s="174"/>
+      <c r="AB16" s="174"/>
+      <c r="AC16" s="174"/>
+      <c r="AD16" s="174"/>
+      <c r="AE16" s="175"/>
+      <c r="AF16" s="170"/>
+      <c r="AG16" s="171"/>
+      <c r="AH16" s="171"/>
+      <c r="AI16" s="172"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="21"/>
-      <c r="B17" s="200"/>
-      <c r="C17" s="201"/>
-      <c r="D17" s="202"/>
-      <c r="E17" s="203"/>
-      <c r="F17" s="204"/>
-      <c r="G17" s="200"/>
-      <c r="H17" s="205"/>
-      <c r="I17" s="201"/>
-      <c r="J17" s="211"/>
-      <c r="K17" s="207"/>
-      <c r="L17" s="207"/>
-      <c r="M17" s="207"/>
-      <c r="N17" s="207"/>
-      <c r="O17" s="207"/>
-      <c r="P17" s="208"/>
-      <c r="Q17" s="206"/>
-      <c r="R17" s="209"/>
-      <c r="S17" s="209"/>
-      <c r="T17" s="209"/>
-      <c r="U17" s="209"/>
-      <c r="V17" s="209"/>
-      <c r="W17" s="209"/>
-      <c r="X17" s="209"/>
-      <c r="Y17" s="209"/>
-      <c r="Z17" s="209"/>
-      <c r="AA17" s="209"/>
-      <c r="AB17" s="209"/>
-      <c r="AC17" s="209"/>
-      <c r="AD17" s="209"/>
-      <c r="AE17" s="210"/>
-      <c r="AF17" s="211"/>
-      <c r="AG17" s="207"/>
-      <c r="AH17" s="207"/>
-      <c r="AI17" s="208"/>
+      <c r="B17" s="164"/>
+      <c r="C17" s="165"/>
+      <c r="D17" s="166"/>
+      <c r="E17" s="167"/>
+      <c r="F17" s="168"/>
+      <c r="G17" s="164"/>
+      <c r="H17" s="169"/>
+      <c r="I17" s="165"/>
+      <c r="J17" s="170"/>
+      <c r="K17" s="171"/>
+      <c r="L17" s="171"/>
+      <c r="M17" s="171"/>
+      <c r="N17" s="171"/>
+      <c r="O17" s="171"/>
+      <c r="P17" s="172"/>
+      <c r="Q17" s="173"/>
+      <c r="R17" s="174"/>
+      <c r="S17" s="174"/>
+      <c r="T17" s="174"/>
+      <c r="U17" s="174"/>
+      <c r="V17" s="174"/>
+      <c r="W17" s="174"/>
+      <c r="X17" s="174"/>
+      <c r="Y17" s="174"/>
+      <c r="Z17" s="174"/>
+      <c r="AA17" s="174"/>
+      <c r="AB17" s="174"/>
+      <c r="AC17" s="174"/>
+      <c r="AD17" s="174"/>
+      <c r="AE17" s="175"/>
+      <c r="AF17" s="170"/>
+      <c r="AG17" s="171"/>
+      <c r="AH17" s="171"/>
+      <c r="AI17" s="172"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="21"/>
-      <c r="B18" s="200"/>
-      <c r="C18" s="201"/>
-      <c r="D18" s="202"/>
-      <c r="E18" s="203"/>
-      <c r="F18" s="204"/>
-      <c r="G18" s="200"/>
-      <c r="H18" s="205"/>
-      <c r="I18" s="201"/>
-      <c r="J18" s="211"/>
-      <c r="K18" s="207"/>
-      <c r="L18" s="207"/>
-      <c r="M18" s="207"/>
-      <c r="N18" s="207"/>
-      <c r="O18" s="207"/>
-      <c r="P18" s="208"/>
-      <c r="Q18" s="206"/>
-      <c r="R18" s="209"/>
-      <c r="S18" s="209"/>
-      <c r="T18" s="209"/>
-      <c r="U18" s="209"/>
-      <c r="V18" s="209"/>
-      <c r="W18" s="209"/>
-      <c r="X18" s="209"/>
-      <c r="Y18" s="209"/>
-      <c r="Z18" s="209"/>
-      <c r="AA18" s="209"/>
-      <c r="AB18" s="209"/>
-      <c r="AC18" s="209"/>
-      <c r="AD18" s="209"/>
-      <c r="AE18" s="210"/>
-      <c r="AF18" s="211"/>
-      <c r="AG18" s="207"/>
-      <c r="AH18" s="207"/>
-      <c r="AI18" s="208"/>
+      <c r="B18" s="164"/>
+      <c r="C18" s="165"/>
+      <c r="D18" s="166"/>
+      <c r="E18" s="167"/>
+      <c r="F18" s="168"/>
+      <c r="G18" s="164"/>
+      <c r="H18" s="169"/>
+      <c r="I18" s="165"/>
+      <c r="J18" s="170"/>
+      <c r="K18" s="171"/>
+      <c r="L18" s="171"/>
+      <c r="M18" s="171"/>
+      <c r="N18" s="171"/>
+      <c r="O18" s="171"/>
+      <c r="P18" s="172"/>
+      <c r="Q18" s="173"/>
+      <c r="R18" s="174"/>
+      <c r="S18" s="174"/>
+      <c r="T18" s="174"/>
+      <c r="U18" s="174"/>
+      <c r="V18" s="174"/>
+      <c r="W18" s="174"/>
+      <c r="X18" s="174"/>
+      <c r="Y18" s="174"/>
+      <c r="Z18" s="174"/>
+      <c r="AA18" s="174"/>
+      <c r="AB18" s="174"/>
+      <c r="AC18" s="174"/>
+      <c r="AD18" s="174"/>
+      <c r="AE18" s="175"/>
+      <c r="AF18" s="170"/>
+      <c r="AG18" s="171"/>
+      <c r="AH18" s="171"/>
+      <c r="AI18" s="172"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="21"/>
-      <c r="B19" s="200"/>
-      <c r="C19" s="201"/>
-      <c r="D19" s="202"/>
-      <c r="E19" s="203"/>
-      <c r="F19" s="204"/>
-      <c r="G19" s="200"/>
-      <c r="H19" s="205"/>
-      <c r="I19" s="201"/>
-      <c r="J19" s="211"/>
-      <c r="K19" s="207"/>
-      <c r="L19" s="207"/>
-      <c r="M19" s="207"/>
-      <c r="N19" s="207"/>
-      <c r="O19" s="207"/>
-      <c r="P19" s="208"/>
-      <c r="Q19" s="206"/>
-      <c r="R19" s="209"/>
-      <c r="S19" s="209"/>
-      <c r="T19" s="209"/>
-      <c r="U19" s="209"/>
-      <c r="V19" s="209"/>
-      <c r="W19" s="209"/>
-      <c r="X19" s="209"/>
-      <c r="Y19" s="209"/>
-      <c r="Z19" s="209"/>
-      <c r="AA19" s="209"/>
-      <c r="AB19" s="209"/>
-      <c r="AC19" s="209"/>
-      <c r="AD19" s="209"/>
-      <c r="AE19" s="210"/>
-      <c r="AF19" s="211"/>
-      <c r="AG19" s="207"/>
-      <c r="AH19" s="207"/>
-      <c r="AI19" s="208"/>
+      <c r="B19" s="164"/>
+      <c r="C19" s="165"/>
+      <c r="D19" s="166"/>
+      <c r="E19" s="167"/>
+      <c r="F19" s="168"/>
+      <c r="G19" s="164"/>
+      <c r="H19" s="169"/>
+      <c r="I19" s="165"/>
+      <c r="J19" s="170"/>
+      <c r="K19" s="171"/>
+      <c r="L19" s="171"/>
+      <c r="M19" s="171"/>
+      <c r="N19" s="171"/>
+      <c r="O19" s="171"/>
+      <c r="P19" s="172"/>
+      <c r="Q19" s="173"/>
+      <c r="R19" s="174"/>
+      <c r="S19" s="174"/>
+      <c r="T19" s="174"/>
+      <c r="U19" s="174"/>
+      <c r="V19" s="174"/>
+      <c r="W19" s="174"/>
+      <c r="X19" s="174"/>
+      <c r="Y19" s="174"/>
+      <c r="Z19" s="174"/>
+      <c r="AA19" s="174"/>
+      <c r="AB19" s="174"/>
+      <c r="AC19" s="174"/>
+      <c r="AD19" s="174"/>
+      <c r="AE19" s="175"/>
+      <c r="AF19" s="170"/>
+      <c r="AG19" s="171"/>
+      <c r="AH19" s="171"/>
+      <c r="AI19" s="172"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="21"/>
-      <c r="B20" s="200"/>
-      <c r="C20" s="201"/>
-      <c r="D20" s="202"/>
-      <c r="E20" s="203"/>
-      <c r="F20" s="204"/>
-      <c r="G20" s="200"/>
-      <c r="H20" s="205"/>
-      <c r="I20" s="201"/>
-      <c r="J20" s="211"/>
-      <c r="K20" s="207"/>
-      <c r="L20" s="207"/>
-      <c r="M20" s="207"/>
-      <c r="N20" s="207"/>
-      <c r="O20" s="207"/>
-      <c r="P20" s="208"/>
-      <c r="Q20" s="206"/>
-      <c r="R20" s="209"/>
-      <c r="S20" s="209"/>
-      <c r="T20" s="209"/>
-      <c r="U20" s="209"/>
-      <c r="V20" s="209"/>
-      <c r="W20" s="209"/>
-      <c r="X20" s="209"/>
-      <c r="Y20" s="209"/>
-      <c r="Z20" s="209"/>
-      <c r="AA20" s="209"/>
-      <c r="AB20" s="209"/>
-      <c r="AC20" s="209"/>
-      <c r="AD20" s="209"/>
-      <c r="AE20" s="210"/>
-      <c r="AF20" s="211"/>
-      <c r="AG20" s="207"/>
-      <c r="AH20" s="207"/>
-      <c r="AI20" s="208"/>
+      <c r="B20" s="164"/>
+      <c r="C20" s="165"/>
+      <c r="D20" s="166"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="168"/>
+      <c r="G20" s="164"/>
+      <c r="H20" s="169"/>
+      <c r="I20" s="165"/>
+      <c r="J20" s="170"/>
+      <c r="K20" s="171"/>
+      <c r="L20" s="171"/>
+      <c r="M20" s="171"/>
+      <c r="N20" s="171"/>
+      <c r="O20" s="171"/>
+      <c r="P20" s="172"/>
+      <c r="Q20" s="173"/>
+      <c r="R20" s="174"/>
+      <c r="S20" s="174"/>
+      <c r="T20" s="174"/>
+      <c r="U20" s="174"/>
+      <c r="V20" s="174"/>
+      <c r="W20" s="174"/>
+      <c r="X20" s="174"/>
+      <c r="Y20" s="174"/>
+      <c r="Z20" s="174"/>
+      <c r="AA20" s="174"/>
+      <c r="AB20" s="174"/>
+      <c r="AC20" s="174"/>
+      <c r="AD20" s="174"/>
+      <c r="AE20" s="175"/>
+      <c r="AF20" s="170"/>
+      <c r="AG20" s="171"/>
+      <c r="AH20" s="171"/>
+      <c r="AI20" s="172"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="21"/>
-      <c r="B21" s="200"/>
-      <c r="C21" s="201"/>
-      <c r="D21" s="202"/>
-      <c r="E21" s="203"/>
-      <c r="F21" s="204"/>
-      <c r="G21" s="200"/>
-      <c r="H21" s="205"/>
-      <c r="I21" s="201"/>
-      <c r="J21" s="211"/>
-      <c r="K21" s="207"/>
-      <c r="L21" s="207"/>
-      <c r="M21" s="207"/>
-      <c r="N21" s="207"/>
-      <c r="O21" s="207"/>
-      <c r="P21" s="208"/>
-      <c r="Q21" s="206"/>
-      <c r="R21" s="209"/>
-      <c r="S21" s="209"/>
-      <c r="T21" s="209"/>
-      <c r="U21" s="209"/>
-      <c r="V21" s="209"/>
-      <c r="W21" s="209"/>
-      <c r="X21" s="209"/>
-      <c r="Y21" s="209"/>
-      <c r="Z21" s="209"/>
-      <c r="AA21" s="209"/>
-      <c r="AB21" s="209"/>
-      <c r="AC21" s="209"/>
-      <c r="AD21" s="209"/>
-      <c r="AE21" s="210"/>
-      <c r="AF21" s="211"/>
-      <c r="AG21" s="207"/>
-      <c r="AH21" s="207"/>
-      <c r="AI21" s="208"/>
+      <c r="B21" s="164"/>
+      <c r="C21" s="165"/>
+      <c r="D21" s="166"/>
+      <c r="E21" s="167"/>
+      <c r="F21" s="168"/>
+      <c r="G21" s="164"/>
+      <c r="H21" s="169"/>
+      <c r="I21" s="165"/>
+      <c r="J21" s="170"/>
+      <c r="K21" s="171"/>
+      <c r="L21" s="171"/>
+      <c r="M21" s="171"/>
+      <c r="N21" s="171"/>
+      <c r="O21" s="171"/>
+      <c r="P21" s="172"/>
+      <c r="Q21" s="173"/>
+      <c r="R21" s="174"/>
+      <c r="S21" s="174"/>
+      <c r="T21" s="174"/>
+      <c r="U21" s="174"/>
+      <c r="V21" s="174"/>
+      <c r="W21" s="174"/>
+      <c r="X21" s="174"/>
+      <c r="Y21" s="174"/>
+      <c r="Z21" s="174"/>
+      <c r="AA21" s="174"/>
+      <c r="AB21" s="174"/>
+      <c r="AC21" s="174"/>
+      <c r="AD21" s="174"/>
+      <c r="AE21" s="175"/>
+      <c r="AF21" s="170"/>
+      <c r="AG21" s="171"/>
+      <c r="AH21" s="171"/>
+      <c r="AI21" s="172"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="21"/>
-      <c r="B22" s="200"/>
-      <c r="C22" s="201"/>
-      <c r="D22" s="202"/>
-      <c r="E22" s="203"/>
-      <c r="F22" s="204"/>
-      <c r="G22" s="200"/>
-      <c r="H22" s="205"/>
-      <c r="I22" s="201"/>
-      <c r="J22" s="211"/>
-      <c r="K22" s="207"/>
-      <c r="L22" s="207"/>
-      <c r="M22" s="207"/>
-      <c r="N22" s="207"/>
-      <c r="O22" s="207"/>
-      <c r="P22" s="208"/>
-      <c r="Q22" s="206"/>
-      <c r="R22" s="209"/>
-      <c r="S22" s="209"/>
-      <c r="T22" s="209"/>
-      <c r="U22" s="209"/>
-      <c r="V22" s="209"/>
-      <c r="W22" s="209"/>
-      <c r="X22" s="209"/>
-      <c r="Y22" s="209"/>
-      <c r="Z22" s="209"/>
-      <c r="AA22" s="209"/>
-      <c r="AB22" s="209"/>
-      <c r="AC22" s="209"/>
-      <c r="AD22" s="209"/>
-      <c r="AE22" s="210"/>
-      <c r="AF22" s="211"/>
-      <c r="AG22" s="207"/>
-      <c r="AH22" s="207"/>
-      <c r="AI22" s="208"/>
+      <c r="B22" s="164"/>
+      <c r="C22" s="165"/>
+      <c r="D22" s="166"/>
+      <c r="E22" s="167"/>
+      <c r="F22" s="168"/>
+      <c r="G22" s="164"/>
+      <c r="H22" s="169"/>
+      <c r="I22" s="165"/>
+      <c r="J22" s="170"/>
+      <c r="K22" s="171"/>
+      <c r="L22" s="171"/>
+      <c r="M22" s="171"/>
+      <c r="N22" s="171"/>
+      <c r="O22" s="171"/>
+      <c r="P22" s="172"/>
+      <c r="Q22" s="173"/>
+      <c r="R22" s="174"/>
+      <c r="S22" s="174"/>
+      <c r="T22" s="174"/>
+      <c r="U22" s="174"/>
+      <c r="V22" s="174"/>
+      <c r="W22" s="174"/>
+      <c r="X22" s="174"/>
+      <c r="Y22" s="174"/>
+      <c r="Z22" s="174"/>
+      <c r="AA22" s="174"/>
+      <c r="AB22" s="174"/>
+      <c r="AC22" s="174"/>
+      <c r="AD22" s="174"/>
+      <c r="AE22" s="175"/>
+      <c r="AF22" s="170"/>
+      <c r="AG22" s="171"/>
+      <c r="AH22" s="171"/>
+      <c r="AI22" s="172"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="21"/>
-      <c r="B23" s="200"/>
-      <c r="C23" s="201"/>
-      <c r="D23" s="202"/>
-      <c r="E23" s="203"/>
-      <c r="F23" s="204"/>
-      <c r="G23" s="200"/>
-      <c r="H23" s="205"/>
-      <c r="I23" s="201"/>
-      <c r="J23" s="211"/>
-      <c r="K23" s="207"/>
-      <c r="L23" s="207"/>
-      <c r="M23" s="207"/>
-      <c r="N23" s="207"/>
-      <c r="O23" s="207"/>
-      <c r="P23" s="208"/>
-      <c r="Q23" s="206"/>
-      <c r="R23" s="209"/>
-      <c r="S23" s="209"/>
-      <c r="T23" s="209"/>
-      <c r="U23" s="209"/>
-      <c r="V23" s="209"/>
-      <c r="W23" s="209"/>
-      <c r="X23" s="209"/>
-      <c r="Y23" s="209"/>
-      <c r="Z23" s="209"/>
-      <c r="AA23" s="209"/>
-      <c r="AB23" s="209"/>
-      <c r="AC23" s="209"/>
-      <c r="AD23" s="209"/>
-      <c r="AE23" s="210"/>
-      <c r="AF23" s="211"/>
-      <c r="AG23" s="207"/>
-      <c r="AH23" s="207"/>
-      <c r="AI23" s="208"/>
+      <c r="B23" s="164"/>
+      <c r="C23" s="165"/>
+      <c r="D23" s="166"/>
+      <c r="E23" s="167"/>
+      <c r="F23" s="168"/>
+      <c r="G23" s="164"/>
+      <c r="H23" s="169"/>
+      <c r="I23" s="165"/>
+      <c r="J23" s="170"/>
+      <c r="K23" s="171"/>
+      <c r="L23" s="171"/>
+      <c r="M23" s="171"/>
+      <c r="N23" s="171"/>
+      <c r="O23" s="171"/>
+      <c r="P23" s="172"/>
+      <c r="Q23" s="173"/>
+      <c r="R23" s="174"/>
+      <c r="S23" s="174"/>
+      <c r="T23" s="174"/>
+      <c r="U23" s="174"/>
+      <c r="V23" s="174"/>
+      <c r="W23" s="174"/>
+      <c r="X23" s="174"/>
+      <c r="Y23" s="174"/>
+      <c r="Z23" s="174"/>
+      <c r="AA23" s="174"/>
+      <c r="AB23" s="174"/>
+      <c r="AC23" s="174"/>
+      <c r="AD23" s="174"/>
+      <c r="AE23" s="175"/>
+      <c r="AF23" s="170"/>
+      <c r="AG23" s="171"/>
+      <c r="AH23" s="171"/>
+      <c r="AI23" s="172"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="21"/>
-      <c r="B24" s="200"/>
-      <c r="C24" s="201"/>
-      <c r="D24" s="202"/>
-      <c r="E24" s="203"/>
-      <c r="F24" s="204"/>
-      <c r="G24" s="200"/>
-      <c r="H24" s="205"/>
-      <c r="I24" s="201"/>
-      <c r="J24" s="211"/>
-      <c r="K24" s="207"/>
-      <c r="L24" s="207"/>
-      <c r="M24" s="207"/>
-      <c r="N24" s="207"/>
-      <c r="O24" s="207"/>
-      <c r="P24" s="208"/>
-      <c r="Q24" s="206"/>
-      <c r="R24" s="209"/>
-      <c r="S24" s="209"/>
-      <c r="T24" s="209"/>
-      <c r="U24" s="209"/>
-      <c r="V24" s="209"/>
-      <c r="W24" s="209"/>
-      <c r="X24" s="209"/>
-      <c r="Y24" s="209"/>
-      <c r="Z24" s="209"/>
-      <c r="AA24" s="209"/>
-      <c r="AB24" s="209"/>
-      <c r="AC24" s="209"/>
-      <c r="AD24" s="209"/>
-      <c r="AE24" s="210"/>
-      <c r="AF24" s="211"/>
-      <c r="AG24" s="207"/>
-      <c r="AH24" s="207"/>
-      <c r="AI24" s="208"/>
+      <c r="B24" s="164"/>
+      <c r="C24" s="165"/>
+      <c r="D24" s="166"/>
+      <c r="E24" s="167"/>
+      <c r="F24" s="168"/>
+      <c r="G24" s="164"/>
+      <c r="H24" s="169"/>
+      <c r="I24" s="165"/>
+      <c r="J24" s="170"/>
+      <c r="K24" s="171"/>
+      <c r="L24" s="171"/>
+      <c r="M24" s="171"/>
+      <c r="N24" s="171"/>
+      <c r="O24" s="171"/>
+      <c r="P24" s="172"/>
+      <c r="Q24" s="173"/>
+      <c r="R24" s="174"/>
+      <c r="S24" s="174"/>
+      <c r="T24" s="174"/>
+      <c r="U24" s="174"/>
+      <c r="V24" s="174"/>
+      <c r="W24" s="174"/>
+      <c r="X24" s="174"/>
+      <c r="Y24" s="174"/>
+      <c r="Z24" s="174"/>
+      <c r="AA24" s="174"/>
+      <c r="AB24" s="174"/>
+      <c r="AC24" s="174"/>
+      <c r="AD24" s="174"/>
+      <c r="AE24" s="175"/>
+      <c r="AF24" s="170"/>
+      <c r="AG24" s="171"/>
+      <c r="AH24" s="171"/>
+      <c r="AI24" s="172"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="21"/>
-      <c r="B25" s="200"/>
-      <c r="C25" s="201"/>
-      <c r="D25" s="202"/>
-      <c r="E25" s="203"/>
-      <c r="F25" s="204"/>
-      <c r="G25" s="200"/>
-      <c r="H25" s="205"/>
-      <c r="I25" s="201"/>
-      <c r="J25" s="211"/>
-      <c r="K25" s="207"/>
-      <c r="L25" s="207"/>
-      <c r="M25" s="207"/>
-      <c r="N25" s="207"/>
-      <c r="O25" s="207"/>
-      <c r="P25" s="208"/>
-      <c r="Q25" s="206"/>
-      <c r="R25" s="209"/>
-      <c r="S25" s="209"/>
-      <c r="T25" s="209"/>
-      <c r="U25" s="209"/>
-      <c r="V25" s="209"/>
-      <c r="W25" s="209"/>
-      <c r="X25" s="209"/>
-      <c r="Y25" s="209"/>
-      <c r="Z25" s="209"/>
-      <c r="AA25" s="209"/>
-      <c r="AB25" s="209"/>
-      <c r="AC25" s="209"/>
-      <c r="AD25" s="209"/>
-      <c r="AE25" s="210"/>
-      <c r="AF25" s="211"/>
-      <c r="AG25" s="207"/>
-      <c r="AH25" s="207"/>
-      <c r="AI25" s="208"/>
+      <c r="B25" s="164"/>
+      <c r="C25" s="165"/>
+      <c r="D25" s="166"/>
+      <c r="E25" s="167"/>
+      <c r="F25" s="168"/>
+      <c r="G25" s="164"/>
+      <c r="H25" s="169"/>
+      <c r="I25" s="165"/>
+      <c r="J25" s="170"/>
+      <c r="K25" s="171"/>
+      <c r="L25" s="171"/>
+      <c r="M25" s="171"/>
+      <c r="N25" s="171"/>
+      <c r="O25" s="171"/>
+      <c r="P25" s="172"/>
+      <c r="Q25" s="173"/>
+      <c r="R25" s="174"/>
+      <c r="S25" s="174"/>
+      <c r="T25" s="174"/>
+      <c r="U25" s="174"/>
+      <c r="V25" s="174"/>
+      <c r="W25" s="174"/>
+      <c r="X25" s="174"/>
+      <c r="Y25" s="174"/>
+      <c r="Z25" s="174"/>
+      <c r="AA25" s="174"/>
+      <c r="AB25" s="174"/>
+      <c r="AC25" s="174"/>
+      <c r="AD25" s="174"/>
+      <c r="AE25" s="175"/>
+      <c r="AF25" s="170"/>
+      <c r="AG25" s="171"/>
+      <c r="AH25" s="171"/>
+      <c r="AI25" s="172"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="21"/>
-      <c r="B26" s="200"/>
-      <c r="C26" s="201"/>
-      <c r="D26" s="202"/>
-      <c r="E26" s="203"/>
-      <c r="F26" s="204"/>
-      <c r="G26" s="200"/>
-      <c r="H26" s="205"/>
-      <c r="I26" s="201"/>
-      <c r="J26" s="211"/>
-      <c r="K26" s="207"/>
-      <c r="L26" s="207"/>
-      <c r="M26" s="207"/>
-      <c r="N26" s="207"/>
-      <c r="O26" s="207"/>
-      <c r="P26" s="208"/>
-      <c r="Q26" s="206"/>
-      <c r="R26" s="209"/>
-      <c r="S26" s="209"/>
-      <c r="T26" s="209"/>
-      <c r="U26" s="209"/>
-      <c r="V26" s="209"/>
-      <c r="W26" s="209"/>
-      <c r="X26" s="209"/>
-      <c r="Y26" s="209"/>
-      <c r="Z26" s="209"/>
-      <c r="AA26" s="209"/>
-      <c r="AB26" s="209"/>
-      <c r="AC26" s="209"/>
-      <c r="AD26" s="209"/>
-      <c r="AE26" s="210"/>
-      <c r="AF26" s="211"/>
-      <c r="AG26" s="207"/>
-      <c r="AH26" s="207"/>
-      <c r="AI26" s="208"/>
+      <c r="B26" s="164"/>
+      <c r="C26" s="165"/>
+      <c r="D26" s="166"/>
+      <c r="E26" s="167"/>
+      <c r="F26" s="168"/>
+      <c r="G26" s="164"/>
+      <c r="H26" s="169"/>
+      <c r="I26" s="165"/>
+      <c r="J26" s="170"/>
+      <c r="K26" s="171"/>
+      <c r="L26" s="171"/>
+      <c r="M26" s="171"/>
+      <c r="N26" s="171"/>
+      <c r="O26" s="171"/>
+      <c r="P26" s="172"/>
+      <c r="Q26" s="173"/>
+      <c r="R26" s="174"/>
+      <c r="S26" s="174"/>
+      <c r="T26" s="174"/>
+      <c r="U26" s="174"/>
+      <c r="V26" s="174"/>
+      <c r="W26" s="174"/>
+      <c r="X26" s="174"/>
+      <c r="Y26" s="174"/>
+      <c r="Z26" s="174"/>
+      <c r="AA26" s="174"/>
+      <c r="AB26" s="174"/>
+      <c r="AC26" s="174"/>
+      <c r="AD26" s="174"/>
+      <c r="AE26" s="175"/>
+      <c r="AF26" s="170"/>
+      <c r="AG26" s="171"/>
+      <c r="AH26" s="171"/>
+      <c r="AI26" s="172"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="21"/>
-      <c r="B27" s="200"/>
-      <c r="C27" s="201"/>
-      <c r="D27" s="202"/>
-      <c r="E27" s="203"/>
-      <c r="F27" s="204"/>
-      <c r="G27" s="200"/>
-      <c r="H27" s="205"/>
-      <c r="I27" s="201"/>
-      <c r="J27" s="211"/>
-      <c r="K27" s="207"/>
-      <c r="L27" s="207"/>
-      <c r="M27" s="207"/>
-      <c r="N27" s="207"/>
-      <c r="O27" s="207"/>
-      <c r="P27" s="208"/>
-      <c r="Q27" s="206"/>
-      <c r="R27" s="209"/>
-      <c r="S27" s="209"/>
-      <c r="T27" s="209"/>
-      <c r="U27" s="209"/>
-      <c r="V27" s="209"/>
-      <c r="W27" s="209"/>
-      <c r="X27" s="209"/>
-      <c r="Y27" s="209"/>
-      <c r="Z27" s="209"/>
-      <c r="AA27" s="209"/>
-      <c r="AB27" s="209"/>
-      <c r="AC27" s="209"/>
-      <c r="AD27" s="209"/>
-      <c r="AE27" s="210"/>
-      <c r="AF27" s="211"/>
-      <c r="AG27" s="207"/>
-      <c r="AH27" s="207"/>
-      <c r="AI27" s="208"/>
+      <c r="B27" s="164"/>
+      <c r="C27" s="165"/>
+      <c r="D27" s="166"/>
+      <c r="E27" s="167"/>
+      <c r="F27" s="168"/>
+      <c r="G27" s="164"/>
+      <c r="H27" s="169"/>
+      <c r="I27" s="165"/>
+      <c r="J27" s="170"/>
+      <c r="K27" s="171"/>
+      <c r="L27" s="171"/>
+      <c r="M27" s="171"/>
+      <c r="N27" s="171"/>
+      <c r="O27" s="171"/>
+      <c r="P27" s="172"/>
+      <c r="Q27" s="173"/>
+      <c r="R27" s="174"/>
+      <c r="S27" s="174"/>
+      <c r="T27" s="174"/>
+      <c r="U27" s="174"/>
+      <c r="V27" s="174"/>
+      <c r="W27" s="174"/>
+      <c r="X27" s="174"/>
+      <c r="Y27" s="174"/>
+      <c r="Z27" s="174"/>
+      <c r="AA27" s="174"/>
+      <c r="AB27" s="174"/>
+      <c r="AC27" s="174"/>
+      <c r="AD27" s="174"/>
+      <c r="AE27" s="175"/>
+      <c r="AF27" s="170"/>
+      <c r="AG27" s="171"/>
+      <c r="AH27" s="171"/>
+      <c r="AI27" s="172"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="21"/>
-      <c r="B28" s="200"/>
-      <c r="C28" s="201"/>
-      <c r="D28" s="202"/>
-      <c r="E28" s="203"/>
-      <c r="F28" s="204"/>
-      <c r="G28" s="200"/>
-      <c r="H28" s="205"/>
-      <c r="I28" s="201"/>
-      <c r="J28" s="211"/>
-      <c r="K28" s="207"/>
-      <c r="L28" s="207"/>
-      <c r="M28" s="207"/>
-      <c r="N28" s="207"/>
-      <c r="O28" s="207"/>
-      <c r="P28" s="208"/>
-      <c r="Q28" s="206"/>
-      <c r="R28" s="209"/>
-      <c r="S28" s="209"/>
-      <c r="T28" s="209"/>
-      <c r="U28" s="209"/>
-      <c r="V28" s="209"/>
-      <c r="W28" s="209"/>
-      <c r="X28" s="209"/>
-      <c r="Y28" s="209"/>
-      <c r="Z28" s="209"/>
-      <c r="AA28" s="209"/>
-      <c r="AB28" s="209"/>
-      <c r="AC28" s="209"/>
-      <c r="AD28" s="209"/>
-      <c r="AE28" s="210"/>
-      <c r="AF28" s="211"/>
-      <c r="AG28" s="207"/>
-      <c r="AH28" s="207"/>
-      <c r="AI28" s="208"/>
+      <c r="B28" s="164"/>
+      <c r="C28" s="165"/>
+      <c r="D28" s="166"/>
+      <c r="E28" s="167"/>
+      <c r="F28" s="168"/>
+      <c r="G28" s="164"/>
+      <c r="H28" s="169"/>
+      <c r="I28" s="165"/>
+      <c r="J28" s="170"/>
+      <c r="K28" s="171"/>
+      <c r="L28" s="171"/>
+      <c r="M28" s="171"/>
+      <c r="N28" s="171"/>
+      <c r="O28" s="171"/>
+      <c r="P28" s="172"/>
+      <c r="Q28" s="173"/>
+      <c r="R28" s="174"/>
+      <c r="S28" s="174"/>
+      <c r="T28" s="174"/>
+      <c r="U28" s="174"/>
+      <c r="V28" s="174"/>
+      <c r="W28" s="174"/>
+      <c r="X28" s="174"/>
+      <c r="Y28" s="174"/>
+      <c r="Z28" s="174"/>
+      <c r="AA28" s="174"/>
+      <c r="AB28" s="174"/>
+      <c r="AC28" s="174"/>
+      <c r="AD28" s="174"/>
+      <c r="AE28" s="175"/>
+      <c r="AF28" s="170"/>
+      <c r="AG28" s="171"/>
+      <c r="AH28" s="171"/>
+      <c r="AI28" s="172"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="21"/>
-      <c r="B29" s="200"/>
-      <c r="C29" s="201"/>
-      <c r="D29" s="202"/>
-      <c r="E29" s="203"/>
-      <c r="F29" s="204"/>
-      <c r="G29" s="200"/>
-      <c r="H29" s="205"/>
-      <c r="I29" s="201"/>
-      <c r="J29" s="211"/>
-      <c r="K29" s="207"/>
-      <c r="L29" s="207"/>
-      <c r="M29" s="207"/>
-      <c r="N29" s="207"/>
-      <c r="O29" s="207"/>
-      <c r="P29" s="208"/>
-      <c r="Q29" s="206"/>
-      <c r="R29" s="209"/>
-      <c r="S29" s="209"/>
-      <c r="T29" s="209"/>
-      <c r="U29" s="209"/>
-      <c r="V29" s="209"/>
-      <c r="W29" s="209"/>
-      <c r="X29" s="209"/>
-      <c r="Y29" s="209"/>
-      <c r="Z29" s="209"/>
-      <c r="AA29" s="209"/>
-      <c r="AB29" s="209"/>
-      <c r="AC29" s="209"/>
-      <c r="AD29" s="209"/>
-      <c r="AE29" s="210"/>
-      <c r="AF29" s="211"/>
-      <c r="AG29" s="207"/>
-      <c r="AH29" s="207"/>
-      <c r="AI29" s="208"/>
+      <c r="B29" s="164"/>
+      <c r="C29" s="165"/>
+      <c r="D29" s="166"/>
+      <c r="E29" s="167"/>
+      <c r="F29" s="168"/>
+      <c r="G29" s="164"/>
+      <c r="H29" s="169"/>
+      <c r="I29" s="165"/>
+      <c r="J29" s="170"/>
+      <c r="K29" s="171"/>
+      <c r="L29" s="171"/>
+      <c r="M29" s="171"/>
+      <c r="N29" s="171"/>
+      <c r="O29" s="171"/>
+      <c r="P29" s="172"/>
+      <c r="Q29" s="173"/>
+      <c r="R29" s="174"/>
+      <c r="S29" s="174"/>
+      <c r="T29" s="174"/>
+      <c r="U29" s="174"/>
+      <c r="V29" s="174"/>
+      <c r="W29" s="174"/>
+      <c r="X29" s="174"/>
+      <c r="Y29" s="174"/>
+      <c r="Z29" s="174"/>
+      <c r="AA29" s="174"/>
+      <c r="AB29" s="174"/>
+      <c r="AC29" s="174"/>
+      <c r="AD29" s="174"/>
+      <c r="AE29" s="175"/>
+      <c r="AF29" s="170"/>
+      <c r="AG29" s="171"/>
+      <c r="AH29" s="171"/>
+      <c r="AI29" s="172"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="21"/>
-      <c r="B30" s="200"/>
-      <c r="C30" s="201"/>
-      <c r="D30" s="202"/>
-      <c r="E30" s="203"/>
-      <c r="F30" s="204"/>
-      <c r="G30" s="200"/>
-      <c r="H30" s="205"/>
-      <c r="I30" s="201"/>
-      <c r="J30" s="211"/>
-      <c r="K30" s="207"/>
-      <c r="L30" s="207"/>
-      <c r="M30" s="207"/>
-      <c r="N30" s="207"/>
-      <c r="O30" s="207"/>
-      <c r="P30" s="208"/>
-      <c r="Q30" s="206"/>
-      <c r="R30" s="209"/>
-      <c r="S30" s="209"/>
-      <c r="T30" s="209"/>
-      <c r="U30" s="209"/>
-      <c r="V30" s="209"/>
-      <c r="W30" s="209"/>
-      <c r="X30" s="209"/>
-      <c r="Y30" s="209"/>
-      <c r="Z30" s="209"/>
-      <c r="AA30" s="209"/>
-      <c r="AB30" s="209"/>
-      <c r="AC30" s="209"/>
-      <c r="AD30" s="209"/>
-      <c r="AE30" s="210"/>
-      <c r="AF30" s="211"/>
-      <c r="AG30" s="207"/>
-      <c r="AH30" s="207"/>
-      <c r="AI30" s="208"/>
+      <c r="B30" s="164"/>
+      <c r="C30" s="165"/>
+      <c r="D30" s="166"/>
+      <c r="E30" s="167"/>
+      <c r="F30" s="168"/>
+      <c r="G30" s="164"/>
+      <c r="H30" s="169"/>
+      <c r="I30" s="165"/>
+      <c r="J30" s="170"/>
+      <c r="K30" s="171"/>
+      <c r="L30" s="171"/>
+      <c r="M30" s="171"/>
+      <c r="N30" s="171"/>
+      <c r="O30" s="171"/>
+      <c r="P30" s="172"/>
+      <c r="Q30" s="173"/>
+      <c r="R30" s="174"/>
+      <c r="S30" s="174"/>
+      <c r="T30" s="174"/>
+      <c r="U30" s="174"/>
+      <c r="V30" s="174"/>
+      <c r="W30" s="174"/>
+      <c r="X30" s="174"/>
+      <c r="Y30" s="174"/>
+      <c r="Z30" s="174"/>
+      <c r="AA30" s="174"/>
+      <c r="AB30" s="174"/>
+      <c r="AC30" s="174"/>
+      <c r="AD30" s="174"/>
+      <c r="AE30" s="175"/>
+      <c r="AF30" s="170"/>
+      <c r="AG30" s="171"/>
+      <c r="AH30" s="171"/>
+      <c r="AI30" s="172"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="200"/>
-      <c r="C31" s="201"/>
-      <c r="D31" s="202"/>
-      <c r="E31" s="203"/>
-      <c r="F31" s="204"/>
-      <c r="G31" s="200"/>
-      <c r="H31" s="205"/>
-      <c r="I31" s="201"/>
-      <c r="J31" s="211"/>
-      <c r="K31" s="207"/>
-      <c r="L31" s="207"/>
-      <c r="M31" s="207"/>
-      <c r="N31" s="207"/>
-      <c r="O31" s="207"/>
-      <c r="P31" s="208"/>
-      <c r="Q31" s="206"/>
-      <c r="R31" s="209"/>
-      <c r="S31" s="209"/>
-      <c r="T31" s="209"/>
-      <c r="U31" s="209"/>
-      <c r="V31" s="209"/>
-      <c r="W31" s="209"/>
-      <c r="X31" s="209"/>
-      <c r="Y31" s="209"/>
-      <c r="Z31" s="209"/>
-      <c r="AA31" s="209"/>
-      <c r="AB31" s="209"/>
-      <c r="AC31" s="209"/>
-      <c r="AD31" s="209"/>
-      <c r="AE31" s="210"/>
-      <c r="AF31" s="211"/>
-      <c r="AG31" s="207"/>
-      <c r="AH31" s="207"/>
-      <c r="AI31" s="208"/>
+      <c r="B31" s="164"/>
+      <c r="C31" s="165"/>
+      <c r="D31" s="166"/>
+      <c r="E31" s="167"/>
+      <c r="F31" s="168"/>
+      <c r="G31" s="164"/>
+      <c r="H31" s="169"/>
+      <c r="I31" s="165"/>
+      <c r="J31" s="170"/>
+      <c r="K31" s="171"/>
+      <c r="L31" s="171"/>
+      <c r="M31" s="171"/>
+      <c r="N31" s="171"/>
+      <c r="O31" s="171"/>
+      <c r="P31" s="172"/>
+      <c r="Q31" s="173"/>
+      <c r="R31" s="174"/>
+      <c r="S31" s="174"/>
+      <c r="T31" s="174"/>
+      <c r="U31" s="174"/>
+      <c r="V31" s="174"/>
+      <c r="W31" s="174"/>
+      <c r="X31" s="174"/>
+      <c r="Y31" s="174"/>
+      <c r="Z31" s="174"/>
+      <c r="AA31" s="174"/>
+      <c r="AB31" s="174"/>
+      <c r="AC31" s="174"/>
+      <c r="AD31" s="174"/>
+      <c r="AE31" s="175"/>
+      <c r="AF31" s="170"/>
+      <c r="AG31" s="171"/>
+      <c r="AH31" s="171"/>
+      <c r="AI31" s="172"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="21"/>
-      <c r="B32" s="200"/>
-      <c r="C32" s="201"/>
-      <c r="D32" s="202"/>
-      <c r="E32" s="203"/>
-      <c r="F32" s="204"/>
-      <c r="G32" s="200"/>
-      <c r="H32" s="205"/>
-      <c r="I32" s="201"/>
-      <c r="J32" s="211"/>
-      <c r="K32" s="221"/>
-      <c r="L32" s="207"/>
-      <c r="M32" s="207"/>
-      <c r="N32" s="207"/>
-      <c r="O32" s="207"/>
-      <c r="P32" s="208"/>
-      <c r="Q32" s="206"/>
-      <c r="R32" s="209"/>
-      <c r="S32" s="209"/>
-      <c r="T32" s="209"/>
-      <c r="U32" s="209"/>
-      <c r="V32" s="209"/>
-      <c r="W32" s="209"/>
-      <c r="X32" s="209"/>
-      <c r="Y32" s="209"/>
-      <c r="Z32" s="209"/>
-      <c r="AA32" s="209"/>
-      <c r="AB32" s="209"/>
-      <c r="AC32" s="209"/>
-      <c r="AD32" s="209"/>
-      <c r="AE32" s="210"/>
-      <c r="AF32" s="211"/>
-      <c r="AG32" s="207"/>
-      <c r="AH32" s="207"/>
-      <c r="AI32" s="208"/>
+      <c r="B32" s="164"/>
+      <c r="C32" s="165"/>
+      <c r="D32" s="166"/>
+      <c r="E32" s="167"/>
+      <c r="F32" s="168"/>
+      <c r="G32" s="164"/>
+      <c r="H32" s="169"/>
+      <c r="I32" s="165"/>
+      <c r="J32" s="170"/>
+      <c r="K32" s="176"/>
+      <c r="L32" s="171"/>
+      <c r="M32" s="171"/>
+      <c r="N32" s="171"/>
+      <c r="O32" s="171"/>
+      <c r="P32" s="172"/>
+      <c r="Q32" s="173"/>
+      <c r="R32" s="174"/>
+      <c r="S32" s="174"/>
+      <c r="T32" s="174"/>
+      <c r="U32" s="174"/>
+      <c r="V32" s="174"/>
+      <c r="W32" s="174"/>
+      <c r="X32" s="174"/>
+      <c r="Y32" s="174"/>
+      <c r="Z32" s="174"/>
+      <c r="AA32" s="174"/>
+      <c r="AB32" s="174"/>
+      <c r="AC32" s="174"/>
+      <c r="AD32" s="174"/>
+      <c r="AE32" s="175"/>
+      <c r="AF32" s="170"/>
+      <c r="AG32" s="171"/>
+      <c r="AH32" s="171"/>
+      <c r="AI32" s="172"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="21"/>
-      <c r="B33" s="200"/>
-      <c r="C33" s="201"/>
-      <c r="D33" s="202"/>
-      <c r="E33" s="203"/>
-      <c r="F33" s="204"/>
-      <c r="G33" s="200"/>
-      <c r="H33" s="205"/>
-      <c r="I33" s="201"/>
-      <c r="J33" s="211"/>
-      <c r="K33" s="207"/>
-      <c r="L33" s="207"/>
-      <c r="M33" s="207"/>
-      <c r="N33" s="207"/>
-      <c r="O33" s="207"/>
-      <c r="P33" s="208"/>
-      <c r="Q33" s="206"/>
-      <c r="R33" s="209"/>
-      <c r="S33" s="209"/>
-      <c r="T33" s="209"/>
-      <c r="U33" s="209"/>
-      <c r="V33" s="209"/>
-      <c r="W33" s="209"/>
-      <c r="X33" s="209"/>
-      <c r="Y33" s="209"/>
-      <c r="Z33" s="209"/>
-      <c r="AA33" s="209"/>
-      <c r="AB33" s="209"/>
-      <c r="AC33" s="209"/>
-      <c r="AD33" s="209"/>
-      <c r="AE33" s="210"/>
-      <c r="AF33" s="211"/>
-      <c r="AG33" s="207"/>
-      <c r="AH33" s="207"/>
-      <c r="AI33" s="208"/>
+      <c r="B33" s="164"/>
+      <c r="C33" s="165"/>
+      <c r="D33" s="166"/>
+      <c r="E33" s="167"/>
+      <c r="F33" s="168"/>
+      <c r="G33" s="164"/>
+      <c r="H33" s="169"/>
+      <c r="I33" s="165"/>
+      <c r="J33" s="170"/>
+      <c r="K33" s="171"/>
+      <c r="L33" s="171"/>
+      <c r="M33" s="171"/>
+      <c r="N33" s="171"/>
+      <c r="O33" s="171"/>
+      <c r="P33" s="172"/>
+      <c r="Q33" s="173"/>
+      <c r="R33" s="174"/>
+      <c r="S33" s="174"/>
+      <c r="T33" s="174"/>
+      <c r="U33" s="174"/>
+      <c r="V33" s="174"/>
+      <c r="W33" s="174"/>
+      <c r="X33" s="174"/>
+      <c r="Y33" s="174"/>
+      <c r="Z33" s="174"/>
+      <c r="AA33" s="174"/>
+      <c r="AB33" s="174"/>
+      <c r="AC33" s="174"/>
+      <c r="AD33" s="174"/>
+      <c r="AE33" s="175"/>
+      <c r="AF33" s="170"/>
+      <c r="AG33" s="171"/>
+      <c r="AH33" s="171"/>
+      <c r="AI33" s="172"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="178">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -15639,6 +15456,161 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -15703,7 +15675,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="28" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="O7" s="28" t="s">
         <v>23</v>
@@ -15768,7 +15740,7 @@
         <v>5</v>
       </c>
       <c r="L10" s="55" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="M10" s="55" t="s">
         <v>16</v>
@@ -15818,7 +15790,7 @@
         <v>102</v>
       </c>
       <c r="G11" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H11" s="75"/>
       <c r="I11" s="75"/>
@@ -15855,7 +15827,7 @@
         <v>104</v>
       </c>
       <c r="G12" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H12" s="60"/>
       <c r="I12" s="60"/>
@@ -15894,7 +15866,7 @@
         <v>106</v>
       </c>
       <c r="G13" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H13" s="60"/>
       <c r="I13" s="60"/>
@@ -15929,7 +15901,7 @@
         <v>107</v>
       </c>
       <c r="G14" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H14" s="60"/>
       <c r="I14" s="60"/>
@@ -15964,7 +15936,7 @@
         <v>108</v>
       </c>
       <c r="G15" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H15" s="60"/>
       <c r="I15" s="67"/>
@@ -15999,7 +15971,7 @@
         <v>109</v>
       </c>
       <c r="G16" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H16" s="60"/>
       <c r="I16" s="67"/>
@@ -16034,7 +16006,7 @@
         <v>110</v>
       </c>
       <c r="G17" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H17" s="60"/>
       <c r="I17" s="67"/>
@@ -16073,7 +16045,7 @@
         <v>113</v>
       </c>
       <c r="G18" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H18" s="60"/>
       <c r="I18" s="60"/>
@@ -16108,7 +16080,7 @@
         <v>114</v>
       </c>
       <c r="G19" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H19" s="60"/>
       <c r="I19" s="60"/>
@@ -16143,7 +16115,7 @@
         <v>115</v>
       </c>
       <c r="G20" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H20" s="60"/>
       <c r="I20" s="67"/>
@@ -16180,7 +16152,7 @@
         <v>117</v>
       </c>
       <c r="G21" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H21" s="60"/>
       <c r="I21" s="60"/>
@@ -16215,7 +16187,7 @@
         <v>118</v>
       </c>
       <c r="G22" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H22" s="60"/>
       <c r="I22" s="60"/>
@@ -16250,7 +16222,7 @@
         <v>119</v>
       </c>
       <c r="G23" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H23" s="60"/>
       <c r="I23" s="60"/>
@@ -16285,7 +16257,7 @@
         <v>120</v>
       </c>
       <c r="G24" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H24" s="60"/>
       <c r="I24" s="60"/>
@@ -16324,7 +16296,7 @@
         <v>122</v>
       </c>
       <c r="G25" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H25" s="60"/>
       <c r="I25" s="60"/>
@@ -16359,7 +16331,7 @@
         <v>123</v>
       </c>
       <c r="G26" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H26" s="60"/>
       <c r="I26" s="60"/>
@@ -16398,7 +16370,7 @@
         <v>126</v>
       </c>
       <c r="G27" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H27" s="60"/>
       <c r="I27" s="60"/>
@@ -16433,7 +16405,7 @@
         <v>127</v>
       </c>
       <c r="G28" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H28" s="60"/>
       <c r="I28" s="60"/>
@@ -16470,7 +16442,7 @@
         <v>129</v>
       </c>
       <c r="G29" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H29" s="60"/>
       <c r="I29" s="60"/>
@@ -16505,7 +16477,7 @@
         <v>130</v>
       </c>
       <c r="G30" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H30" s="60"/>
       <c r="I30" s="60"/>
@@ -16540,7 +16512,7 @@
         <v>131</v>
       </c>
       <c r="G31" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H31" s="60"/>
       <c r="I31" s="60"/>
@@ -16575,7 +16547,7 @@
         <v>132</v>
       </c>
       <c r="G32" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H32" s="60"/>
       <c r="I32" s="60"/>
@@ -16612,7 +16584,7 @@
         <v>134</v>
       </c>
       <c r="G33" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H33" s="60"/>
       <c r="I33" s="67"/>
@@ -16647,7 +16619,7 @@
         <v>135</v>
       </c>
       <c r="G34" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H34" s="60"/>
       <c r="I34" s="67"/>
@@ -16684,7 +16656,7 @@
         <v>137</v>
       </c>
       <c r="G35" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H35" s="67"/>
       <c r="I35" s="67"/>
@@ -16725,7 +16697,7 @@
         <v>139</v>
       </c>
       <c r="G36" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H36" s="66"/>
       <c r="I36" s="66"/>
@@ -16760,7 +16732,7 @@
         <v>140</v>
       </c>
       <c r="G37" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H37" s="66"/>
       <c r="I37" s="66"/>
@@ -16795,7 +16767,7 @@
         <v>141</v>
       </c>
       <c r="G38" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H38" s="66"/>
       <c r="I38" s="75"/>
@@ -16830,7 +16802,7 @@
         <v>142</v>
       </c>
       <c r="G39" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H39" s="66"/>
       <c r="I39" s="75"/>
@@ -16869,7 +16841,7 @@
         <v>144</v>
       </c>
       <c r="G40" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H40" s="66"/>
       <c r="I40" s="66"/>
@@ -16904,7 +16876,7 @@
         <v>145</v>
       </c>
       <c r="G41" s="66" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H41" s="66"/>
       <c r="I41" s="66"/>
@@ -16947,7 +16919,7 @@
         <v>150</v>
       </c>
       <c r="G42" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H42" s="67"/>
       <c r="I42" s="67"/>
@@ -16982,7 +16954,7 @@
         <v>151</v>
       </c>
       <c r="G43" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H43" s="67"/>
       <c r="I43" s="67"/>
@@ -17017,7 +16989,7 @@
         <v>152</v>
       </c>
       <c r="G44" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H44" s="67"/>
       <c r="I44" s="67"/>
@@ -17054,7 +17026,7 @@
         <v>154</v>
       </c>
       <c r="G45" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H45" s="67"/>
       <c r="I45" s="67"/>
@@ -17089,7 +17061,7 @@
         <v>155</v>
       </c>
       <c r="G46" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H46" s="67"/>
       <c r="I46" s="67"/>
@@ -17124,7 +17096,7 @@
         <v>152</v>
       </c>
       <c r="G47" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H47" s="67"/>
       <c r="I47" s="67"/>
@@ -17161,7 +17133,7 @@
         <v>157</v>
       </c>
       <c r="G48" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H48" s="67"/>
       <c r="I48" s="67"/>
@@ -17196,7 +17168,7 @@
         <v>158</v>
       </c>
       <c r="G49" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H49" s="67"/>
       <c r="I49" s="67"/>
@@ -17233,7 +17205,7 @@
         <v>160</v>
       </c>
       <c r="G50" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H50" s="67"/>
       <c r="I50" s="67"/>
@@ -17268,7 +17240,7 @@
         <v>161</v>
       </c>
       <c r="G51" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H51" s="67"/>
       <c r="I51" s="67"/>
@@ -17303,7 +17275,7 @@
         <v>162</v>
       </c>
       <c r="G52" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H52" s="67"/>
       <c r="I52" s="67"/>
@@ -17338,7 +17310,7 @@
         <v>163</v>
       </c>
       <c r="G53" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H53" s="67"/>
       <c r="I53" s="67"/>
@@ -17373,7 +17345,7 @@
         <v>164</v>
       </c>
       <c r="G54" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H54" s="67"/>
       <c r="I54" s="67"/>
@@ -17408,7 +17380,7 @@
         <v>165</v>
       </c>
       <c r="G55" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H55" s="67"/>
       <c r="I55" s="67"/>
@@ -17445,7 +17417,7 @@
         <v>167</v>
       </c>
       <c r="G56" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H56" s="67"/>
       <c r="I56" s="67"/>
@@ -17482,7 +17454,7 @@
         <v>169</v>
       </c>
       <c r="G57" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H57" s="67"/>
       <c r="I57" s="67"/>
@@ -17519,7 +17491,7 @@
         <v>171</v>
       </c>
       <c r="G58" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H58" s="67"/>
       <c r="I58" s="67"/>
@@ -17559,19 +17531,19 @@
       </c>
       <c r="G59" s="113"/>
       <c r="H59" s="113" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I59" s="113" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="J59" s="152" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="K59" s="114" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="L59" s="109" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="M59" s="109" t="s">
         <v>49</v>
@@ -17603,7 +17575,7 @@
         <v>174</v>
       </c>
       <c r="G60" s="66" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -17638,7 +17610,7 @@
         <v>175</v>
       </c>
       <c r="G61" s="66" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H61" s="66"/>
       <c r="I61" s="66"/>
@@ -17673,7 +17645,7 @@
         <v>176</v>
       </c>
       <c r="G62" s="66" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H62" s="66"/>
       <c r="I62" s="66"/>
@@ -17708,7 +17680,7 @@
         <v>177</v>
       </c>
       <c r="G63" s="66" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H63" s="66"/>
       <c r="I63" s="66"/>
@@ -17746,19 +17718,19 @@
       </c>
       <c r="G64" s="113"/>
       <c r="H64" s="113" t="s">
+        <v>552</v>
+      </c>
+      <c r="I64" s="113" t="s">
         <v>553</v>
       </c>
-      <c r="I64" s="113" t="s">
-        <v>554</v>
-      </c>
       <c r="J64" s="37" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="K64" s="114" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L64" s="109" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="M64" s="109" t="s">
         <v>40</v>
@@ -17791,13 +17763,13 @@
       </c>
       <c r="G65" s="115"/>
       <c r="H65" s="113" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I65" s="113" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="J65" s="37" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="K65" s="114" t="s">
         <v>53</v>
@@ -17834,19 +17806,19 @@
       <c r="F66" s="122"/>
       <c r="G66" s="122"/>
       <c r="H66" s="113" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="I66" s="113" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J66" s="37" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="K66" s="114" t="s">
         <v>54</v>
       </c>
       <c r="L66" s="109" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="M66" s="109" t="s">
         <v>41</v>
@@ -17878,7 +17850,7 @@
         <v>181</v>
       </c>
       <c r="G67" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H67" s="66"/>
       <c r="I67" s="66"/>
@@ -17913,7 +17885,7 @@
         <v>182</v>
       </c>
       <c r="G68" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H68" s="66"/>
       <c r="I68" s="66"/>
@@ -17948,7 +17920,7 @@
         <v>183</v>
       </c>
       <c r="G69" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H69" s="66"/>
       <c r="I69" s="66"/>
@@ -17983,7 +17955,7 @@
         <v>184</v>
       </c>
       <c r="G70" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H70" s="66"/>
       <c r="I70" s="66"/>
@@ -18018,7 +17990,7 @@
         <v>185</v>
       </c>
       <c r="G71" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H71" s="66"/>
       <c r="I71" s="66"/>
@@ -18053,7 +18025,7 @@
         <v>186</v>
       </c>
       <c r="G72" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -18091,16 +18063,16 @@
       </c>
       <c r="G73" s="115"/>
       <c r="H73" s="115" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I73" s="115" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="J73" s="37" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="K73" s="114" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="L73" s="109" t="s">
         <v>52</v>
@@ -18136,10 +18108,10 @@
       <c r="H74" s="120"/>
       <c r="I74" s="120"/>
       <c r="J74" s="37" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="K74" s="114" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="L74" s="109" t="s">
         <v>52</v>
@@ -18175,10 +18147,10 @@
       <c r="H75" s="120"/>
       <c r="I75" s="120"/>
       <c r="J75" s="37" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="K75" s="114" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="L75" s="109" t="s">
         <v>52</v>
@@ -18214,10 +18186,10 @@
       <c r="H76" s="120"/>
       <c r="I76" s="120"/>
       <c r="J76" s="37" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="K76" s="114" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L76" s="109" t="s">
         <v>52</v>
@@ -18253,10 +18225,10 @@
       <c r="H77" s="122"/>
       <c r="I77" s="122"/>
       <c r="J77" s="37" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="K77" s="114" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="L77" s="109" t="s">
         <v>52</v>
@@ -18294,16 +18266,16 @@
       </c>
       <c r="G78" s="115"/>
       <c r="H78" s="115" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I78" s="115" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="J78" s="37" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="K78" s="114" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="L78" s="109" t="s">
         <v>52</v>
@@ -18339,10 +18311,10 @@
       <c r="H79" s="120"/>
       <c r="I79" s="120"/>
       <c r="J79" s="37" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="K79" s="114" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="L79" s="109" t="s">
         <v>52</v>
@@ -18378,10 +18350,10 @@
       <c r="H80" s="120"/>
       <c r="I80" s="120"/>
       <c r="J80" s="37" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="K80" s="114" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="L80" s="109" t="s">
         <v>52</v>
@@ -18417,10 +18389,10 @@
       <c r="H81" s="120"/>
       <c r="I81" s="120"/>
       <c r="J81" s="37" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K81" s="114" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L81" s="109" t="s">
         <v>52</v>
@@ -18456,10 +18428,10 @@
       <c r="H82" s="122"/>
       <c r="I82" s="122"/>
       <c r="J82" s="37" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K82" s="114" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="L82" s="109" t="s">
         <v>52</v>
@@ -18494,7 +18466,7 @@
         <v>191</v>
       </c>
       <c r="G83" s="66" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H83" s="66"/>
       <c r="I83" s="66"/>
@@ -18529,7 +18501,7 @@
         <v>192</v>
       </c>
       <c r="G84" s="66" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H84" s="66"/>
       <c r="I84" s="66"/>
@@ -18564,7 +18536,7 @@
         <v>193</v>
       </c>
       <c r="G85" s="66" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H85" s="66"/>
       <c r="I85" s="66"/>
@@ -18599,7 +18571,7 @@
         <v>194</v>
       </c>
       <c r="G86" s="66" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H86" s="66"/>
       <c r="I86" s="66"/>
@@ -18640,7 +18612,7 @@
         <v>198</v>
       </c>
       <c r="G87" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H87" s="67"/>
       <c r="I87" s="67"/>
@@ -18675,7 +18647,7 @@
         <v>199</v>
       </c>
       <c r="G88" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H88" s="67"/>
       <c r="I88" s="67"/>
@@ -18712,7 +18684,7 @@
         <v>201</v>
       </c>
       <c r="G89" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H89" s="67"/>
       <c r="I89" s="67"/>
@@ -18749,7 +18721,7 @@
         <v>203</v>
       </c>
       <c r="G90" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H90" s="67"/>
       <c r="I90" s="67"/>
@@ -18784,7 +18756,7 @@
         <v>204</v>
       </c>
       <c r="G91" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H91" s="67"/>
       <c r="I91" s="67"/>
@@ -18821,7 +18793,7 @@
         <v>206</v>
       </c>
       <c r="G92" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H92" s="67"/>
       <c r="I92" s="67"/>
@@ -18858,7 +18830,7 @@
         <v>208</v>
       </c>
       <c r="G93" s="66" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H93" s="67"/>
       <c r="I93" s="67"/>
@@ -18900,19 +18872,19 @@
       </c>
       <c r="G94" s="113"/>
       <c r="H94" s="113" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="I94" s="113" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="J94" s="37" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="K94" s="110" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L94" s="109" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="M94" s="109" t="s">
         <v>49</v>
@@ -18947,19 +18919,19 @@
       </c>
       <c r="G95" s="113"/>
       <c r="H95" s="113" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="I95" s="113" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="J95" s="37" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="K95" s="110" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L95" s="109" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="M95" s="109" t="s">
         <v>49</v>
@@ -18993,7 +18965,7 @@
         <v>213</v>
       </c>
       <c r="G96" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H96" s="66"/>
       <c r="I96" s="66"/>
@@ -19034,7 +19006,7 @@
         <v>215</v>
       </c>
       <c r="G97" s="66" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H97" s="67"/>
       <c r="I97" s="67"/>
@@ -19069,7 +19041,7 @@
         <v>216</v>
       </c>
       <c r="G98" s="66" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H98" s="67"/>
       <c r="I98" s="67"/>
@@ -19106,7 +19078,7 @@
         <v>217</v>
       </c>
       <c r="G99" s="66" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H99" s="67"/>
       <c r="I99" s="67"/>
@@ -19143,7 +19115,7 @@
         <v>218</v>
       </c>
       <c r="G100" s="66" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H100" s="67"/>
       <c r="I100" s="67"/>
@@ -19178,7 +19150,7 @@
         <v>219</v>
       </c>
       <c r="G101" s="66" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H101" s="67"/>
       <c r="I101" s="67"/>
@@ -19215,7 +19187,7 @@
         <v>220</v>
       </c>
       <c r="G102" s="66" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H102" s="67"/>
       <c r="I102" s="67"/>
@@ -19256,7 +19228,7 @@
         <v>223</v>
       </c>
       <c r="G103" s="66" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H103" s="67"/>
       <c r="I103" s="67"/>
@@ -19291,7 +19263,7 @@
         <v>224</v>
       </c>
       <c r="G104" s="66" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H104" s="67"/>
       <c r="I104" s="67"/>
@@ -19326,7 +19298,7 @@
         <v>225</v>
       </c>
       <c r="G105" s="66" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H105" s="67"/>
       <c r="I105" s="67"/>
@@ -19361,7 +19333,7 @@
         <v>226</v>
       </c>
       <c r="G106" s="66" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H106" s="67"/>
       <c r="I106" s="67"/>
@@ -19396,7 +19368,7 @@
         <v>227</v>
       </c>
       <c r="G107" s="66" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H107" s="67"/>
       <c r="I107" s="67"/>
@@ -19433,7 +19405,7 @@
         <v>229</v>
       </c>
       <c r="G108" s="66" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H108" s="67"/>
       <c r="I108" s="67"/>
@@ -19468,7 +19440,7 @@
         <v>230</v>
       </c>
       <c r="G109" s="66" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H109" s="67"/>
       <c r="I109" s="67"/>
@@ -19503,7 +19475,7 @@
         <v>231</v>
       </c>
       <c r="G110" s="66" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H110" s="67"/>
       <c r="I110" s="67"/>
@@ -19538,7 +19510,7 @@
         <v>232</v>
       </c>
       <c r="G111" s="66" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H111" s="67"/>
       <c r="I111" s="67"/>
@@ -19573,7 +19545,7 @@
         <v>233</v>
       </c>
       <c r="G112" s="66" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H112" s="67"/>
       <c r="I112" s="67"/>
@@ -19610,7 +19582,7 @@
         <v>234</v>
       </c>
       <c r="G113" s="66" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H113" s="67"/>
       <c r="I113" s="67"/>
@@ -19653,7 +19625,7 @@
         <v>237</v>
       </c>
       <c r="G114" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H114" s="67"/>
       <c r="I114" s="67"/>
@@ -19694,7 +19666,7 @@
         <v>239</v>
       </c>
       <c r="G115" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H115" s="67"/>
       <c r="I115" s="67"/>
@@ -19729,7 +19701,7 @@
         <v>240</v>
       </c>
       <c r="G116" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H116" s="67"/>
       <c r="I116" s="67"/>
@@ -19770,7 +19742,7 @@
         <v>242</v>
       </c>
       <c r="G117" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H117" s="67"/>
       <c r="I117" s="67"/>
@@ -19811,7 +19783,7 @@
         <v>244</v>
       </c>
       <c r="G118" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H118" s="67"/>
       <c r="I118" s="67"/>
@@ -19846,7 +19818,7 @@
         <v>245</v>
       </c>
       <c r="G119" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H119" s="67"/>
       <c r="I119" s="67"/>
@@ -19889,7 +19861,7 @@
         <v>248</v>
       </c>
       <c r="G120" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H120" s="66"/>
       <c r="I120" s="66"/>
@@ -19926,7 +19898,7 @@
         <v>250</v>
       </c>
       <c r="G121" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H121" s="66"/>
       <c r="I121" s="66"/>
@@ -19961,7 +19933,7 @@
         <v>251</v>
       </c>
       <c r="G122" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H122" s="66"/>
       <c r="I122" s="66"/>
@@ -19996,7 +19968,7 @@
         <v>252</v>
       </c>
       <c r="G123" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H123" s="66"/>
       <c r="I123" s="66"/>
@@ -20033,7 +20005,7 @@
         <v>253</v>
       </c>
       <c r="G124" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H124" s="66"/>
       <c r="I124" s="66"/>
@@ -20068,7 +20040,7 @@
         <v>254</v>
       </c>
       <c r="G125" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H125" s="66"/>
       <c r="I125" s="66"/>
@@ -20103,7 +20075,7 @@
         <v>255</v>
       </c>
       <c r="G126" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H126" s="66"/>
       <c r="I126" s="66"/>
@@ -20138,7 +20110,7 @@
         <v>256</v>
       </c>
       <c r="G127" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H127" s="66"/>
       <c r="I127" s="66"/>
@@ -20173,7 +20145,7 @@
         <v>257</v>
       </c>
       <c r="G128" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H128" s="66"/>
       <c r="I128" s="66"/>
@@ -20210,7 +20182,7 @@
         <v>260</v>
       </c>
       <c r="G129" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H129" s="66"/>
       <c r="I129" s="66"/>
@@ -20245,7 +20217,7 @@
         <v>261</v>
       </c>
       <c r="G130" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H130" s="66"/>
       <c r="I130" s="66"/>
@@ -20280,7 +20252,7 @@
         <v>262</v>
       </c>
       <c r="G131" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H131" s="66"/>
       <c r="I131" s="66"/>
@@ -20315,7 +20287,7 @@
         <v>263</v>
       </c>
       <c r="G132" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H132" s="66"/>
       <c r="I132" s="66"/>
@@ -20350,7 +20322,7 @@
         <v>264</v>
       </c>
       <c r="G133" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H133" s="66"/>
       <c r="I133" s="66"/>
@@ -20387,7 +20359,7 @@
         <v>266</v>
       </c>
       <c r="G134" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H134" s="66"/>
       <c r="I134" s="66"/>
@@ -20426,7 +20398,7 @@
         <v>267</v>
       </c>
       <c r="G135" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H135" s="66"/>
       <c r="I135" s="66"/>
@@ -20467,7 +20439,7 @@
         <v>270</v>
       </c>
       <c r="G136" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H136" s="66"/>
       <c r="I136" s="66"/>
@@ -20504,7 +20476,7 @@
         <v>272</v>
       </c>
       <c r="G137" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H137" s="66"/>
       <c r="I137" s="66"/>
@@ -20539,7 +20511,7 @@
         <v>273</v>
       </c>
       <c r="G138" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H138" s="66"/>
       <c r="I138" s="66"/>
@@ -20574,7 +20546,7 @@
         <v>274</v>
       </c>
       <c r="G139" s="66" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H139" s="66"/>
       <c r="I139" s="66"/>
@@ -20617,7 +20589,7 @@
         <v>276</v>
       </c>
       <c r="G140" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H140" s="66"/>
       <c r="I140" s="66"/>
@@ -20654,7 +20626,7 @@
         <v>278</v>
       </c>
       <c r="G141" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H141" s="66"/>
       <c r="I141" s="66"/>
@@ -20689,7 +20661,7 @@
         <v>279</v>
       </c>
       <c r="G142" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H142" s="66"/>
       <c r="I142" s="66"/>
@@ -20724,7 +20696,7 @@
         <v>280</v>
       </c>
       <c r="G143" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H143" s="66"/>
       <c r="I143" s="66"/>
@@ -20761,7 +20733,7 @@
         <v>282</v>
       </c>
       <c r="G144" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H144" s="66"/>
       <c r="I144" s="66"/>
@@ -20796,7 +20768,7 @@
         <v>283</v>
       </c>
       <c r="G145" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H145" s="66"/>
       <c r="I145" s="66"/>
@@ -20835,7 +20807,7 @@
         <v>284</v>
       </c>
       <c r="G146" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H146" s="66"/>
       <c r="I146" s="66"/>
@@ -20876,7 +20848,7 @@
         <v>287</v>
       </c>
       <c r="G147" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H147" s="66"/>
       <c r="I147" s="66"/>
@@ -20913,7 +20885,7 @@
         <v>289</v>
       </c>
       <c r="G148" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H148" s="66"/>
       <c r="I148" s="66"/>
@@ -20950,7 +20922,7 @@
         <v>291</v>
       </c>
       <c r="G149" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H149" s="66"/>
       <c r="I149" s="66"/>
@@ -20987,7 +20959,7 @@
         <v>292</v>
       </c>
       <c r="G150" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H150" s="66"/>
       <c r="I150" s="66"/>
@@ -21024,7 +20996,7 @@
         <v>294</v>
       </c>
       <c r="G151" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H151" s="66"/>
       <c r="I151" s="66"/>
@@ -21061,7 +21033,7 @@
         <v>296</v>
       </c>
       <c r="G152" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H152" s="66"/>
       <c r="I152" s="66"/>
@@ -21096,7 +21068,7 @@
         <v>297</v>
       </c>
       <c r="G153" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H153" s="66"/>
       <c r="I153" s="66"/>
@@ -21131,7 +21103,7 @@
         <v>298</v>
       </c>
       <c r="G154" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H154" s="66"/>
       <c r="I154" s="66"/>
@@ -21166,7 +21138,7 @@
         <v>299</v>
       </c>
       <c r="G155" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H155" s="66"/>
       <c r="I155" s="66"/>
@@ -21201,7 +21173,7 @@
         <v>300</v>
       </c>
       <c r="G156" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H156" s="66"/>
       <c r="I156" s="66"/>
@@ -21236,7 +21208,7 @@
         <v>301</v>
       </c>
       <c r="G157" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H157" s="66"/>
       <c r="I157" s="66"/>
@@ -21275,7 +21247,7 @@
         <v>303</v>
       </c>
       <c r="G158" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H158" s="66"/>
       <c r="I158" s="66"/>
@@ -21310,7 +21282,7 @@
         <v>304</v>
       </c>
       <c r="G159" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H159" s="66"/>
       <c r="I159" s="66"/>
@@ -21347,7 +21319,7 @@
         <v>305</v>
       </c>
       <c r="G160" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H160" s="66"/>
       <c r="I160" s="66"/>
@@ -21382,7 +21354,7 @@
         <v>306</v>
       </c>
       <c r="G161" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H161" s="66"/>
       <c r="I161" s="66"/>
@@ -21417,7 +21389,7 @@
         <v>307</v>
       </c>
       <c r="G162" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H162" s="66"/>
       <c r="I162" s="66"/>
@@ -21452,7 +21424,7 @@
         <v>308</v>
       </c>
       <c r="G163" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H163" s="66"/>
       <c r="I163" s="66"/>
@@ -21487,7 +21459,7 @@
         <v>309</v>
       </c>
       <c r="G164" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H164" s="66"/>
       <c r="I164" s="66"/>
@@ -21522,7 +21494,7 @@
         <v>310</v>
       </c>
       <c r="G165" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H165" s="66"/>
       <c r="I165" s="66"/>
@@ -21557,7 +21529,7 @@
         <v>311</v>
       </c>
       <c r="G166" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H166" s="66"/>
       <c r="I166" s="66"/>
@@ -21592,7 +21564,7 @@
         <v>312</v>
       </c>
       <c r="G167" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H167" s="66"/>
       <c r="I167" s="66"/>
@@ -21627,7 +21599,7 @@
         <v>313</v>
       </c>
       <c r="G168" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H168" s="66"/>
       <c r="I168" s="66"/>
@@ -21662,7 +21634,7 @@
         <v>314</v>
       </c>
       <c r="G169" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H169" s="66"/>
       <c r="I169" s="66"/>
@@ -21697,7 +21669,7 @@
         <v>315</v>
       </c>
       <c r="G170" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H170" s="66"/>
       <c r="I170" s="66"/>
@@ -21734,7 +21706,7 @@
         <v>316</v>
       </c>
       <c r="G171" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H171" s="66"/>
       <c r="I171" s="66"/>
@@ -21769,7 +21741,7 @@
         <v>317</v>
       </c>
       <c r="G172" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H172" s="66"/>
       <c r="I172" s="66"/>
@@ -21804,7 +21776,7 @@
         <v>318</v>
       </c>
       <c r="G173" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H173" s="66"/>
       <c r="I173" s="66"/>
@@ -21839,7 +21811,7 @@
         <v>319</v>
       </c>
       <c r="G174" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H174" s="66"/>
       <c r="I174" s="66"/>
@@ -21874,7 +21846,7 @@
         <v>320</v>
       </c>
       <c r="G175" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H175" s="66"/>
       <c r="I175" s="66"/>
@@ -21909,7 +21881,7 @@
         <v>321</v>
       </c>
       <c r="G176" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H176" s="66"/>
       <c r="I176" s="66"/>
@@ -21944,7 +21916,7 @@
         <v>322</v>
       </c>
       <c r="G177" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H177" s="66"/>
       <c r="I177" s="66"/>
@@ -21981,7 +21953,7 @@
         <v>323</v>
       </c>
       <c r="G178" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H178" s="66"/>
       <c r="I178" s="66"/>
@@ -22016,7 +21988,7 @@
         <v>324</v>
       </c>
       <c r="G179" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H179" s="66"/>
       <c r="I179" s="66"/>
@@ -22051,7 +22023,7 @@
         <v>325</v>
       </c>
       <c r="G180" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H180" s="66"/>
       <c r="I180" s="66"/>
@@ -22086,7 +22058,7 @@
         <v>326</v>
       </c>
       <c r="G181" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H181" s="66"/>
       <c r="I181" s="66"/>
@@ -22121,7 +22093,7 @@
         <v>327</v>
       </c>
       <c r="G182" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H182" s="66"/>
       <c r="I182" s="66"/>
@@ -22156,7 +22128,7 @@
         <v>328</v>
       </c>
       <c r="G183" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H183" s="66"/>
       <c r="I183" s="66"/>
@@ -22191,7 +22163,7 @@
         <v>329</v>
       </c>
       <c r="G184" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H184" s="66"/>
       <c r="I184" s="66"/>
@@ -22226,7 +22198,7 @@
         <v>330</v>
       </c>
       <c r="G185" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H185" s="66"/>
       <c r="I185" s="66"/>
@@ -22261,7 +22233,7 @@
         <v>331</v>
       </c>
       <c r="G186" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H186" s="66"/>
       <c r="I186" s="66"/>
@@ -22298,7 +22270,7 @@
         <v>332</v>
       </c>
       <c r="G187" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H187" s="66"/>
       <c r="I187" s="66"/>
@@ -22335,7 +22307,7 @@
         <v>334</v>
       </c>
       <c r="G188" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H188" s="66"/>
       <c r="I188" s="66"/>
@@ -22378,7 +22350,7 @@
         <v>337</v>
       </c>
       <c r="G189" s="67" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H189" s="67"/>
       <c r="I189" s="67"/>
@@ -22417,7 +22389,7 @@
         <v>339</v>
       </c>
       <c r="G190" s="67" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H190" s="67"/>
       <c r="I190" s="67"/>
@@ -22456,7 +22428,7 @@
         <v>341</v>
       </c>
       <c r="G191" s="67" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H191" s="67"/>
       <c r="I191" s="67"/>
@@ -22499,7 +22471,7 @@
         <v>344</v>
       </c>
       <c r="G192" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H192" s="67"/>
       <c r="I192" s="67"/>
@@ -22536,7 +22508,7 @@
         <v>345</v>
       </c>
       <c r="G193" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H193" s="67"/>
       <c r="I193" s="67"/>
@@ -22571,7 +22543,7 @@
         <v>346</v>
       </c>
       <c r="G194" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H194" s="67"/>
       <c r="I194" s="67"/>
@@ -22608,7 +22580,7 @@
         <v>348</v>
       </c>
       <c r="G195" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H195" s="67"/>
       <c r="I195" s="67"/>
@@ -22643,7 +22615,7 @@
         <v>349</v>
       </c>
       <c r="G196" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H196" s="67"/>
       <c r="I196" s="67"/>
@@ -22682,7 +22654,7 @@
         <v>350</v>
       </c>
       <c r="G197" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H197" s="67"/>
       <c r="I197" s="67"/>
@@ -22723,7 +22695,7 @@
         <v>354</v>
       </c>
       <c r="G198" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H198" s="67"/>
       <c r="I198" s="67"/>
@@ -22758,7 +22730,7 @@
         <v>355</v>
       </c>
       <c r="G199" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H199" s="67"/>
       <c r="I199" s="67"/>
@@ -22793,7 +22765,7 @@
         <v>356</v>
       </c>
       <c r="G200" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H200" s="67"/>
       <c r="I200" s="67"/>
@@ -22828,7 +22800,7 @@
         <v>357</v>
       </c>
       <c r="G201" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H201" s="67"/>
       <c r="I201" s="67"/>
@@ -22863,7 +22835,7 @@
         <v>358</v>
       </c>
       <c r="G202" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H202" s="67"/>
       <c r="I202" s="67"/>
@@ -22898,7 +22870,7 @@
         <v>359</v>
       </c>
       <c r="G203" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H203" s="67"/>
       <c r="I203" s="67"/>
@@ -22933,7 +22905,7 @@
         <v>360</v>
       </c>
       <c r="G204" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H204" s="67"/>
       <c r="I204" s="67"/>
@@ -22970,7 +22942,7 @@
         <v>362</v>
       </c>
       <c r="G205" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H205" s="67"/>
       <c r="I205" s="67"/>
@@ -23009,7 +22981,7 @@
         <v>364</v>
       </c>
       <c r="G206" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H206" s="67"/>
       <c r="I206" s="67"/>
@@ -23044,7 +23016,7 @@
         <v>365</v>
       </c>
       <c r="G207" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H207" s="67"/>
       <c r="I207" s="67"/>
@@ -23079,7 +23051,7 @@
         <v>366</v>
       </c>
       <c r="G208" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H208" s="67"/>
       <c r="I208" s="67"/>
@@ -23114,7 +23086,7 @@
         <v>367</v>
       </c>
       <c r="G209" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H209" s="67"/>
       <c r="I209" s="67"/>
@@ -23149,7 +23121,7 @@
         <v>368</v>
       </c>
       <c r="G210" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H210" s="67"/>
       <c r="I210" s="67"/>
@@ -23184,7 +23156,7 @@
         <v>369</v>
       </c>
       <c r="G211" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H211" s="67"/>
       <c r="I211" s="67"/>
@@ -23219,7 +23191,7 @@
         <v>370</v>
       </c>
       <c r="G212" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H212" s="67"/>
       <c r="I212" s="67"/>
@@ -23254,7 +23226,7 @@
         <v>371</v>
       </c>
       <c r="G213" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H213" s="67"/>
       <c r="I213" s="67"/>
@@ -23289,7 +23261,7 @@
         <v>372</v>
       </c>
       <c r="G214" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H214" s="67"/>
       <c r="I214" s="67"/>
@@ -23324,7 +23296,7 @@
         <v>373</v>
       </c>
       <c r="G215" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H215" s="67"/>
       <c r="I215" s="67"/>
@@ -23359,7 +23331,7 @@
         <v>374</v>
       </c>
       <c r="G216" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H216" s="67"/>
       <c r="I216" s="67"/>
@@ -23394,7 +23366,7 @@
         <v>375</v>
       </c>
       <c r="G217" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H217" s="67"/>
       <c r="I217" s="67"/>
@@ -23429,7 +23401,7 @@
         <v>376</v>
       </c>
       <c r="G218" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H218" s="67"/>
       <c r="I218" s="67"/>
@@ -23468,7 +23440,7 @@
         <v>378</v>
       </c>
       <c r="G219" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H219" s="67"/>
       <c r="I219" s="67"/>
@@ -23503,7 +23475,7 @@
         <v>379</v>
       </c>
       <c r="G220" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H220" s="67"/>
       <c r="I220" s="67"/>
@@ -23538,7 +23510,7 @@
         <v>380</v>
       </c>
       <c r="G221" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H221" s="67"/>
       <c r="I221" s="67"/>
@@ -23573,7 +23545,7 @@
         <v>366</v>
       </c>
       <c r="G222" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H222" s="67"/>
       <c r="I222" s="67"/>
@@ -23608,7 +23580,7 @@
         <v>367</v>
       </c>
       <c r="G223" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H223" s="67"/>
       <c r="I223" s="67"/>
@@ -23643,7 +23615,7 @@
         <v>381</v>
       </c>
       <c r="G224" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H224" s="67"/>
       <c r="I224" s="67"/>
@@ -23678,7 +23650,7 @@
         <v>382</v>
       </c>
       <c r="G225" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H225" s="67"/>
       <c r="I225" s="67"/>
@@ -23713,7 +23685,7 @@
         <v>383</v>
       </c>
       <c r="G226" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H226" s="67"/>
       <c r="I226" s="67"/>
@@ -23748,7 +23720,7 @@
         <v>384</v>
       </c>
       <c r="G227" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H227" s="67"/>
       <c r="I227" s="67"/>
@@ -23783,7 +23755,7 @@
         <v>385</v>
       </c>
       <c r="G228" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H228" s="67"/>
       <c r="I228" s="67"/>
@@ -23818,7 +23790,7 @@
         <v>386</v>
       </c>
       <c r="G229" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H229" s="67"/>
       <c r="I229" s="67"/>
@@ -23853,7 +23825,7 @@
         <v>387</v>
       </c>
       <c r="G230" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H230" s="67"/>
       <c r="I230" s="67"/>
@@ -23888,7 +23860,7 @@
         <v>388</v>
       </c>
       <c r="G231" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H231" s="67"/>
       <c r="I231" s="67"/>
@@ -23923,7 +23895,7 @@
         <v>389</v>
       </c>
       <c r="G232" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H232" s="67"/>
       <c r="I232" s="67"/>
@@ -23958,7 +23930,7 @@
         <v>376</v>
       </c>
       <c r="G233" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H233" s="67"/>
       <c r="I233" s="67"/>
@@ -23995,7 +23967,7 @@
         <v>391</v>
       </c>
       <c r="G234" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H234" s="67"/>
       <c r="I234" s="67"/>
@@ -24030,7 +24002,7 @@
         <v>392</v>
       </c>
       <c r="G235" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H235" s="67"/>
       <c r="I235" s="67"/>
@@ -24065,7 +24037,7 @@
         <v>393</v>
       </c>
       <c r="G236" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H236" s="67"/>
       <c r="I236" s="67"/>
@@ -24102,7 +24074,7 @@
         <v>394</v>
       </c>
       <c r="G237" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H237" s="67"/>
       <c r="I237" s="67"/>
@@ -24139,7 +24111,7 @@
         <v>396</v>
       </c>
       <c r="G238" s="67" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H238" s="67"/>
       <c r="I238" s="67"/>
@@ -24182,7 +24154,7 @@
         <v>398</v>
       </c>
       <c r="G239" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H239" s="67"/>
       <c r="I239" s="67"/>
@@ -24219,7 +24191,7 @@
         <v>399</v>
       </c>
       <c r="G240" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H240" s="67"/>
       <c r="I240" s="67"/>
@@ -24254,7 +24226,7 @@
         <v>400</v>
       </c>
       <c r="G241" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H241" s="67"/>
       <c r="I241" s="67"/>
@@ -24289,7 +24261,7 @@
         <v>401</v>
       </c>
       <c r="G242" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H242" s="67"/>
       <c r="I242" s="67"/>
@@ -24324,7 +24296,7 @@
         <v>402</v>
       </c>
       <c r="G243" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H243" s="67"/>
       <c r="I243" s="67"/>
@@ -24359,7 +24331,7 @@
         <v>403</v>
       </c>
       <c r="G244" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H244" s="67"/>
       <c r="I244" s="67"/>
@@ -24396,7 +24368,7 @@
         <v>404</v>
       </c>
       <c r="G245" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H245" s="67"/>
       <c r="I245" s="67"/>
@@ -24431,7 +24403,7 @@
         <v>405</v>
       </c>
       <c r="G246" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H246" s="67"/>
       <c r="I246" s="67"/>
@@ -24466,7 +24438,7 @@
         <v>406</v>
       </c>
       <c r="G247" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H247" s="67"/>
       <c r="I247" s="67"/>
@@ -24501,7 +24473,7 @@
         <v>407</v>
       </c>
       <c r="G248" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H248" s="67"/>
       <c r="I248" s="67"/>
@@ -24536,7 +24508,7 @@
         <v>408</v>
       </c>
       <c r="G249" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H249" s="67"/>
       <c r="I249" s="67"/>
@@ -24573,7 +24545,7 @@
         <v>409</v>
       </c>
       <c r="G250" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H250" s="67"/>
       <c r="I250" s="67"/>
@@ -24614,7 +24586,7 @@
         <v>410</v>
       </c>
       <c r="G251" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H251" s="67"/>
       <c r="I251" s="67"/>
@@ -24657,7 +24629,7 @@
         <v>413</v>
       </c>
       <c r="G252" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H252" s="67"/>
       <c r="I252" s="67"/>
@@ -24692,7 +24664,7 @@
         <v>414</v>
       </c>
       <c r="G253" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H253" s="67"/>
       <c r="I253" s="67"/>
@@ -24731,7 +24703,7 @@
         <v>415</v>
       </c>
       <c r="G254" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H254" s="67"/>
       <c r="I254" s="67"/>
@@ -24766,7 +24738,7 @@
         <v>416</v>
       </c>
       <c r="G255" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H255" s="67"/>
       <c r="I255" s="67"/>
@@ -24807,7 +24779,7 @@
         <v>418</v>
       </c>
       <c r="G256" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H256" s="67"/>
       <c r="I256" s="67"/>
@@ -24844,7 +24816,7 @@
         <v>419</v>
       </c>
       <c r="G257" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H257" s="67"/>
       <c r="I257" s="67"/>
@@ -24881,7 +24853,7 @@
         <v>420</v>
       </c>
       <c r="G258" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H258" s="67"/>
       <c r="I258" s="67"/>
@@ -24918,7 +24890,7 @@
         <v>421</v>
       </c>
       <c r="G259" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H259" s="67"/>
       <c r="I259" s="67"/>
@@ -24957,7 +24929,7 @@
         <v>422</v>
       </c>
       <c r="G260" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H260" s="67"/>
       <c r="I260" s="67"/>
@@ -24992,7 +24964,7 @@
         <v>423</v>
       </c>
       <c r="G261" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H261" s="67"/>
       <c r="I261" s="67"/>
@@ -25029,7 +25001,7 @@
         <v>424</v>
       </c>
       <c r="G262" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H262" s="67"/>
       <c r="I262" s="67"/>
@@ -25064,7 +25036,7 @@
         <v>425</v>
       </c>
       <c r="G263" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H263" s="67"/>
       <c r="I263" s="67"/>
@@ -25099,7 +25071,7 @@
         <v>426</v>
       </c>
       <c r="G264" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H264" s="67"/>
       <c r="I264" s="67"/>
@@ -25134,7 +25106,7 @@
         <v>427</v>
       </c>
       <c r="G265" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H265" s="67"/>
       <c r="I265" s="67"/>
@@ -25169,7 +25141,7 @@
         <v>428</v>
       </c>
       <c r="G266" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H266" s="67"/>
       <c r="I266" s="67"/>
@@ -25204,7 +25176,7 @@
         <v>429</v>
       </c>
       <c r="G267" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H267" s="67"/>
       <c r="I267" s="67"/>
@@ -25239,7 +25211,7 @@
         <v>430</v>
       </c>
       <c r="G268" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H268" s="67"/>
       <c r="I268" s="67"/>
@@ -25274,7 +25246,7 @@
         <v>431</v>
       </c>
       <c r="G269" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H269" s="67"/>
       <c r="I269" s="67"/>
@@ -25309,7 +25281,7 @@
         <v>432</v>
       </c>
       <c r="G270" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H270" s="67"/>
       <c r="I270" s="67"/>
@@ -25344,7 +25316,7 @@
         <v>433</v>
       </c>
       <c r="G271" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H271" s="67"/>
       <c r="I271" s="67"/>
@@ -25379,7 +25351,7 @@
         <v>434</v>
       </c>
       <c r="G272" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H272" s="67"/>
       <c r="I272" s="67"/>
@@ -25416,7 +25388,7 @@
         <v>435</v>
       </c>
       <c r="G273" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H273" s="67"/>
       <c r="I273" s="67"/>
@@ -25451,7 +25423,7 @@
         <v>436</v>
       </c>
       <c r="G274" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H274" s="67"/>
       <c r="I274" s="67"/>
@@ -25486,7 +25458,7 @@
         <v>437</v>
       </c>
       <c r="G275" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H275" s="67"/>
       <c r="I275" s="67"/>
@@ -25521,7 +25493,7 @@
         <v>438</v>
       </c>
       <c r="G276" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H276" s="67"/>
       <c r="I276" s="67"/>
@@ -25556,7 +25528,7 @@
         <v>439</v>
       </c>
       <c r="G277" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H277" s="67"/>
       <c r="I277" s="67"/>
@@ -25591,7 +25563,7 @@
         <v>440</v>
       </c>
       <c r="G278" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H278" s="67"/>
       <c r="I278" s="67"/>
@@ -25628,7 +25600,7 @@
         <v>441</v>
       </c>
       <c r="G279" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H279" s="67"/>
       <c r="I279" s="67"/>
@@ -25663,7 +25635,7 @@
         <v>442</v>
       </c>
       <c r="G280" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H280" s="67"/>
       <c r="I280" s="67"/>
@@ -25698,7 +25670,7 @@
         <v>443</v>
       </c>
       <c r="G281" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H281" s="67"/>
       <c r="I281" s="67"/>
@@ -25733,7 +25705,7 @@
         <v>444</v>
       </c>
       <c r="G282" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H282" s="67"/>
       <c r="I282" s="67"/>
@@ -25768,7 +25740,7 @@
         <v>445</v>
       </c>
       <c r="G283" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H283" s="67"/>
       <c r="I283" s="67"/>
@@ -25803,7 +25775,7 @@
         <v>446</v>
       </c>
       <c r="G284" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H284" s="67"/>
       <c r="I284" s="67"/>
@@ -25838,7 +25810,7 @@
         <v>447</v>
       </c>
       <c r="G285" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H285" s="67"/>
       <c r="I285" s="67"/>
@@ -25873,7 +25845,7 @@
         <v>448</v>
       </c>
       <c r="G286" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H286" s="67"/>
       <c r="I286" s="67"/>
@@ -25910,7 +25882,7 @@
         <v>449</v>
       </c>
       <c r="G287" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H287" s="67"/>
       <c r="I287" s="67"/>
@@ -25953,7 +25925,7 @@
         <v>452</v>
       </c>
       <c r="G288" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H288" s="66"/>
       <c r="I288" s="66"/>
@@ -25988,7 +25960,7 @@
         <v>453</v>
       </c>
       <c r="G289" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H289" s="66"/>
       <c r="I289" s="66"/>
@@ -26023,7 +25995,7 @@
         <v>454</v>
       </c>
       <c r="G290" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H290" s="66"/>
       <c r="I290" s="66"/>
@@ -26058,7 +26030,7 @@
         <v>455</v>
       </c>
       <c r="G291" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H291" s="66"/>
       <c r="I291" s="66"/>
@@ -26099,7 +26071,7 @@
         <v>457</v>
       </c>
       <c r="G292" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H292" s="66"/>
       <c r="I292" s="66"/>
@@ -26136,7 +26108,7 @@
         <v>458</v>
       </c>
       <c r="G293" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H293" s="66"/>
       <c r="I293" s="66"/>
@@ -26173,7 +26145,7 @@
         <v>459</v>
       </c>
       <c r="G294" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H294" s="66"/>
       <c r="I294" s="66"/>
@@ -26210,7 +26182,7 @@
         <v>460</v>
       </c>
       <c r="G295" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H295" s="66"/>
       <c r="I295" s="66"/>
@@ -26249,7 +26221,7 @@
         <v>463</v>
       </c>
       <c r="G296" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H296" s="66"/>
       <c r="I296" s="66"/>
@@ -26284,7 +26256,7 @@
         <v>464</v>
       </c>
       <c r="G297" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H297" s="66"/>
       <c r="I297" s="66"/>
@@ -26319,7 +26291,7 @@
         <v>465</v>
       </c>
       <c r="G298" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H298" s="66"/>
       <c r="I298" s="66"/>
@@ -26354,7 +26326,7 @@
         <v>306</v>
       </c>
       <c r="G299" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H299" s="66"/>
       <c r="I299" s="66"/>
@@ -26389,7 +26361,7 @@
         <v>307</v>
       </c>
       <c r="G300" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H300" s="66"/>
       <c r="I300" s="66"/>
@@ -26424,7 +26396,7 @@
         <v>308</v>
       </c>
       <c r="G301" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H301" s="66"/>
       <c r="I301" s="66"/>
@@ -26459,7 +26431,7 @@
         <v>466</v>
       </c>
       <c r="G302" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H302" s="66"/>
       <c r="I302" s="66"/>
@@ -26494,7 +26466,7 @@
         <v>467</v>
       </c>
       <c r="G303" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H303" s="66"/>
       <c r="I303" s="66"/>
@@ -26529,7 +26501,7 @@
         <v>468</v>
       </c>
       <c r="G304" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H304" s="66"/>
       <c r="I304" s="66"/>
@@ -26621,7 +26593,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="28" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="O7" s="28" t="s">
         <v>23</v>
@@ -26736,7 +26708,7 @@
         <v>102</v>
       </c>
       <c r="G11" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H11" s="79"/>
       <c r="I11" s="79"/>
@@ -26773,7 +26745,7 @@
         <v>104</v>
       </c>
       <c r="G12" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H12" s="79"/>
       <c r="I12" s="79"/>
@@ -26812,7 +26784,7 @@
         <v>106</v>
       </c>
       <c r="G13" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H13" s="79"/>
       <c r="I13" s="79"/>
@@ -26847,7 +26819,7 @@
         <v>107</v>
       </c>
       <c r="G14" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H14" s="79"/>
       <c r="I14" s="79"/>
@@ -26882,7 +26854,7 @@
         <v>108</v>
       </c>
       <c r="G15" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H15" s="79"/>
       <c r="I15" s="79"/>
@@ -26917,7 +26889,7 @@
         <v>109</v>
       </c>
       <c r="G16" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H16" s="79"/>
       <c r="I16" s="79"/>
@@ -26952,7 +26924,7 @@
         <v>110</v>
       </c>
       <c r="G17" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H17" s="79"/>
       <c r="I17" s="79"/>
@@ -26991,7 +26963,7 @@
         <v>113</v>
       </c>
       <c r="G18" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H18" s="79"/>
       <c r="I18" s="79"/>
@@ -27026,7 +26998,7 @@
         <v>114</v>
       </c>
       <c r="G19" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H19" s="79"/>
       <c r="I19" s="79"/>
@@ -27061,7 +27033,7 @@
         <v>115</v>
       </c>
       <c r="G20" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H20" s="79"/>
       <c r="I20" s="79"/>
@@ -27098,7 +27070,7 @@
         <v>117</v>
       </c>
       <c r="G21" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H21" s="79"/>
       <c r="I21" s="79"/>
@@ -27133,7 +27105,7 @@
         <v>118</v>
       </c>
       <c r="G22" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H22" s="79"/>
       <c r="I22" s="79"/>
@@ -27168,7 +27140,7 @@
         <v>470</v>
       </c>
       <c r="G23" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H23" s="79"/>
       <c r="I23" s="79"/>
@@ -27199,11 +27171,11 @@
       <c r="C24" s="142"/>
       <c r="D24" s="139"/>
       <c r="E24" s="138"/>
-      <c r="F24" s="134" t="s">
-        <v>471</v>
+      <c r="F24" s="58" t="s">
+        <v>120</v>
       </c>
       <c r="G24" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H24" s="79"/>
       <c r="I24" s="79"/>
@@ -27242,7 +27214,7 @@
         <v>122</v>
       </c>
       <c r="G25" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H25" s="79"/>
       <c r="I25" s="79"/>
@@ -27277,7 +27249,7 @@
         <v>123</v>
       </c>
       <c r="G26" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H26" s="79"/>
       <c r="I26" s="79"/>
@@ -27316,7 +27288,7 @@
         <v>126</v>
       </c>
       <c r="G27" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H27" s="79"/>
       <c r="I27" s="79"/>
@@ -27351,7 +27323,7 @@
         <v>127</v>
       </c>
       <c r="G28" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H28" s="79"/>
       <c r="I28" s="79"/>
@@ -27388,7 +27360,7 @@
         <v>129</v>
       </c>
       <c r="G29" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H29" s="79"/>
       <c r="I29" s="79"/>
@@ -27423,7 +27395,7 @@
         <v>130</v>
       </c>
       <c r="G30" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H30" s="79"/>
       <c r="I30" s="79"/>
@@ -27458,7 +27430,7 @@
         <v>131</v>
       </c>
       <c r="G31" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H31" s="79"/>
       <c r="I31" s="79"/>
@@ -27493,7 +27465,7 @@
         <v>132</v>
       </c>
       <c r="G32" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H32" s="79"/>
       <c r="I32" s="79"/>
@@ -27524,13 +27496,13 @@
       <c r="C33" s="142"/>
       <c r="D33" s="136"/>
       <c r="E33" s="136" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F33" s="134" t="s">
         <v>134</v>
       </c>
       <c r="G33" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H33" s="79"/>
       <c r="I33" s="79"/>
@@ -27565,7 +27537,7 @@
         <v>135</v>
       </c>
       <c r="G34" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H34" s="79"/>
       <c r="I34" s="79"/>
@@ -27599,10 +27571,10 @@
         <v>136</v>
       </c>
       <c r="F35" s="134" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G35" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H35" s="66"/>
       <c r="I35" s="66"/>
@@ -27634,16 +27606,16 @@
         <v>138</v>
       </c>
       <c r="D36" s="141" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E36" s="132" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F36" s="138" t="s">
         <v>139</v>
       </c>
       <c r="G36" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H36" s="79"/>
       <c r="I36" s="79"/>
@@ -27675,10 +27647,10 @@
       <c r="D37" s="136"/>
       <c r="E37" s="137"/>
       <c r="F37" s="134" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G37" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H37" s="79"/>
       <c r="I37" s="79"/>
@@ -27713,7 +27685,7 @@
         <v>141</v>
       </c>
       <c r="G38" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H38" s="79"/>
       <c r="I38" s="79"/>
@@ -27748,7 +27720,7 @@
         <v>142</v>
       </c>
       <c r="G39" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H39" s="79"/>
       <c r="I39" s="79"/>
@@ -27784,10 +27756,10 @@
         <v>32</v>
       </c>
       <c r="F40" s="134" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G40" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H40" s="79"/>
       <c r="I40" s="79"/>
@@ -27819,10 +27791,10 @@
       <c r="D41" s="139"/>
       <c r="E41" s="138"/>
       <c r="F41" s="134" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G41" s="77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H41" s="79"/>
       <c r="I41" s="79"/>
@@ -27865,7 +27837,7 @@
         <v>150</v>
       </c>
       <c r="G42" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H42" s="66"/>
       <c r="I42" s="66"/>
@@ -27900,7 +27872,7 @@
         <v>151</v>
       </c>
       <c r="G43" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H43" s="58"/>
       <c r="I43" s="66"/>
@@ -27935,7 +27907,7 @@
         <v>152</v>
       </c>
       <c r="G44" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H44" s="58"/>
       <c r="I44" s="66"/>
@@ -27972,7 +27944,7 @@
         <v>154</v>
       </c>
       <c r="G45" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H45" s="79"/>
       <c r="I45" s="79"/>
@@ -28007,7 +27979,7 @@
         <v>155</v>
       </c>
       <c r="G46" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H46" s="79"/>
       <c r="I46" s="79"/>
@@ -28042,7 +28014,7 @@
         <v>152</v>
       </c>
       <c r="G47" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H47" s="79"/>
       <c r="I47" s="79"/>
@@ -28079,7 +28051,7 @@
         <v>157</v>
       </c>
       <c r="G48" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H48" s="66"/>
       <c r="I48" s="66"/>
@@ -28114,7 +28086,7 @@
         <v>158</v>
       </c>
       <c r="G49" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H49" s="66"/>
       <c r="I49" s="66"/>
@@ -28151,7 +28123,7 @@
         <v>160</v>
       </c>
       <c r="G50" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H50" s="79"/>
       <c r="I50" s="79"/>
@@ -28186,7 +28158,7 @@
         <v>161</v>
       </c>
       <c r="G51" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H51" s="79"/>
       <c r="I51" s="79"/>
@@ -28221,7 +28193,7 @@
         <v>162</v>
       </c>
       <c r="G52" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H52" s="79"/>
       <c r="I52" s="79"/>
@@ -28256,7 +28228,7 @@
         <v>163</v>
       </c>
       <c r="G53" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H53" s="79"/>
       <c r="I53" s="79"/>
@@ -28291,7 +28263,7 @@
         <v>164</v>
       </c>
       <c r="G54" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H54" s="79"/>
       <c r="I54" s="79"/>
@@ -28326,7 +28298,7 @@
         <v>165</v>
       </c>
       <c r="G55" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H55" s="79"/>
       <c r="I55" s="79"/>
@@ -28363,7 +28335,7 @@
         <v>167</v>
       </c>
       <c r="G56" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H56" s="66"/>
       <c r="I56" s="66"/>
@@ -28394,13 +28366,13 @@
       <c r="C57" s="137"/>
       <c r="D57" s="137"/>
       <c r="E57" s="134" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F57" s="134" t="s">
         <v>169</v>
       </c>
       <c r="G57" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H57" s="79"/>
       <c r="I57" s="79"/>
@@ -28437,7 +28409,7 @@
         <v>171</v>
       </c>
       <c r="G58" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H58" s="79"/>
       <c r="I58" s="79"/>
@@ -28470,13 +28442,13 @@
         <v>172</v>
       </c>
       <c r="E59" s="136" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F59" s="134" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G59" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H59" s="79"/>
       <c r="I59" s="79"/>
@@ -28508,10 +28480,10 @@
       <c r="D60" s="137"/>
       <c r="E60" s="136"/>
       <c r="F60" s="132" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G60" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H60" s="66"/>
       <c r="I60" s="66"/>
@@ -28543,10 +28515,10 @@
       <c r="D61" s="137"/>
       <c r="E61" s="136"/>
       <c r="F61" s="134" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G61" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H61" s="79"/>
       <c r="I61" s="79"/>
@@ -28578,10 +28550,10 @@
       <c r="D62" s="137"/>
       <c r="E62" s="136"/>
       <c r="F62" s="134" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G62" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H62" s="79"/>
       <c r="I62" s="79"/>
@@ -28616,7 +28588,7 @@
         <v>177</v>
       </c>
       <c r="G63" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H63" s="79"/>
       <c r="I63" s="79"/>
@@ -28653,7 +28625,7 @@
         <v>179</v>
       </c>
       <c r="G64" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H64" s="79"/>
       <c r="I64" s="79"/>
@@ -28688,7 +28660,7 @@
         <v>180</v>
       </c>
       <c r="G65" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H65" s="79"/>
       <c r="I65" s="79"/>
@@ -28723,7 +28695,7 @@
         <v>181</v>
       </c>
       <c r="G66" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H66" s="79"/>
       <c r="I66" s="79"/>
@@ -28758,7 +28730,7 @@
         <v>182</v>
       </c>
       <c r="G67" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H67" s="79"/>
       <c r="I67" s="79"/>
@@ -28793,7 +28765,7 @@
         <v>183</v>
       </c>
       <c r="G68" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H68" s="79"/>
       <c r="I68" s="79"/>
@@ -28828,7 +28800,7 @@
         <v>184</v>
       </c>
       <c r="G69" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H69" s="79"/>
       <c r="I69" s="79"/>
@@ -28863,7 +28835,7 @@
         <v>185</v>
       </c>
       <c r="G70" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H70" s="79"/>
       <c r="I70" s="79"/>
@@ -28898,7 +28870,7 @@
         <v>186</v>
       </c>
       <c r="G71" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H71" s="79"/>
       <c r="I71" s="79"/>
@@ -28935,7 +28907,7 @@
         <v>188</v>
       </c>
       <c r="G72" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H72" s="66"/>
       <c r="I72" s="66"/>
@@ -28972,7 +28944,7 @@
         <v>190</v>
       </c>
       <c r="G73" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H73" s="79"/>
       <c r="I73" s="79"/>
@@ -29007,7 +28979,7 @@
         <v>191</v>
       </c>
       <c r="G74" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H74" s="79"/>
       <c r="I74" s="79"/>
@@ -29042,7 +29014,7 @@
         <v>192</v>
       </c>
       <c r="G75" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H75" s="79"/>
       <c r="I75" s="79"/>
@@ -29077,7 +29049,7 @@
         <v>193</v>
       </c>
       <c r="G76" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H76" s="79"/>
       <c r="I76" s="79"/>
@@ -29112,7 +29084,7 @@
         <v>194</v>
       </c>
       <c r="G77" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H77" s="79"/>
       <c r="I77" s="79"/>
@@ -29153,7 +29125,7 @@
         <v>198</v>
       </c>
       <c r="G78" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H78" s="66"/>
       <c r="I78" s="66"/>
@@ -29188,7 +29160,7 @@
         <v>199</v>
       </c>
       <c r="G79" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H79" s="66"/>
       <c r="I79" s="66"/>
@@ -29225,7 +29197,7 @@
         <v>201</v>
       </c>
       <c r="G80" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H80" s="79"/>
       <c r="I80" s="79"/>
@@ -29262,7 +29234,7 @@
         <v>203</v>
       </c>
       <c r="G81" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H81" s="79"/>
       <c r="I81" s="79"/>
@@ -29297,7 +29269,7 @@
         <v>204</v>
       </c>
       <c r="G82" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H82" s="79"/>
       <c r="I82" s="79"/>
@@ -29334,7 +29306,7 @@
         <v>206</v>
       </c>
       <c r="G83" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H83" s="79"/>
       <c r="I83" s="79"/>
@@ -29371,7 +29343,7 @@
         <v>208</v>
       </c>
       <c r="G84" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H84" s="79"/>
       <c r="I84" s="79"/>
@@ -29406,13 +29378,13 @@
         <v>197</v>
       </c>
       <c r="E85" s="134" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F85" s="134" t="s">
         <v>210</v>
       </c>
       <c r="G85" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H85" s="79"/>
       <c r="I85" s="79"/>
@@ -29449,7 +29421,7 @@
         <v>211</v>
       </c>
       <c r="G86" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H86" s="79"/>
       <c r="I86" s="79"/>
@@ -29480,13 +29452,13 @@
       <c r="C87" s="138"/>
       <c r="D87" s="138"/>
       <c r="E87" s="138" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F87" s="134" t="s">
         <v>213</v>
       </c>
       <c r="G87" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H87" s="79"/>
       <c r="I87" s="79"/>
@@ -29521,13 +29493,13 @@
         <v>197</v>
       </c>
       <c r="E88" s="136" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F88" s="132" t="s">
         <v>215</v>
       </c>
       <c r="G88" s="77" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H88" s="66"/>
       <c r="I88" s="66"/>
@@ -29562,7 +29534,7 @@
         <v>216</v>
       </c>
       <c r="G89" s="77" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H89" s="79"/>
       <c r="I89" s="79"/>
@@ -29599,7 +29571,7 @@
         <v>217</v>
       </c>
       <c r="G90" s="77" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H90" s="79"/>
       <c r="I90" s="79"/>
@@ -29636,7 +29608,7 @@
         <v>218</v>
       </c>
       <c r="G91" s="77" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H91" s="79"/>
       <c r="I91" s="79"/>
@@ -29671,7 +29643,7 @@
         <v>219</v>
       </c>
       <c r="G92" s="77" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H92" s="79"/>
       <c r="I92" s="79"/>
@@ -29702,13 +29674,13 @@
       <c r="C93" s="138"/>
       <c r="D93" s="138"/>
       <c r="E93" s="138" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F93" s="134" t="s">
         <v>220</v>
       </c>
       <c r="G93" s="77" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H93" s="79"/>
       <c r="I93" s="79"/>
@@ -29749,7 +29721,7 @@
         <v>223</v>
       </c>
       <c r="G94" s="77" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H94" s="79"/>
       <c r="I94" s="79"/>
@@ -29784,7 +29756,7 @@
         <v>224</v>
       </c>
       <c r="G95" s="77" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H95" s="79"/>
       <c r="I95" s="79"/>
@@ -29819,7 +29791,7 @@
         <v>225</v>
       </c>
       <c r="G96" s="77" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H96" s="79"/>
       <c r="I96" s="79"/>
@@ -29854,7 +29826,7 @@
         <v>226</v>
       </c>
       <c r="G97" s="77" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H97" s="79"/>
       <c r="I97" s="79"/>
@@ -29889,7 +29861,7 @@
         <v>227</v>
       </c>
       <c r="G98" s="77" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H98" s="79"/>
       <c r="I98" s="79"/>
@@ -29926,7 +29898,7 @@
         <v>229</v>
       </c>
       <c r="G99" s="77" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H99" s="79"/>
       <c r="I99" s="79"/>
@@ -29961,7 +29933,7 @@
         <v>230</v>
       </c>
       <c r="G100" s="77" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H100" s="79"/>
       <c r="I100" s="79"/>
@@ -29996,7 +29968,7 @@
         <v>231</v>
       </c>
       <c r="G101" s="77" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H101" s="79"/>
       <c r="I101" s="79"/>
@@ -30031,7 +30003,7 @@
         <v>232</v>
       </c>
       <c r="G102" s="77" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H102" s="79"/>
       <c r="I102" s="79"/>
@@ -30066,7 +30038,7 @@
         <v>233</v>
       </c>
       <c r="G103" s="77" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H103" s="79"/>
       <c r="I103" s="79"/>
@@ -30097,13 +30069,13 @@
       <c r="C104" s="138"/>
       <c r="D104" s="137"/>
       <c r="E104" s="139" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F104" s="134" t="s">
         <v>234</v>
       </c>
       <c r="G104" s="77" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H104" s="79"/>
       <c r="I104" s="79"/>
@@ -30146,7 +30118,7 @@
         <v>237</v>
       </c>
       <c r="G105" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H105" s="79"/>
       <c r="I105" s="79"/>
@@ -30187,7 +30159,7 @@
         <v>239</v>
       </c>
       <c r="G106" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H106" s="79"/>
       <c r="I106" s="79"/>
@@ -30222,7 +30194,7 @@
         <v>240</v>
       </c>
       <c r="G107" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H107" s="79"/>
       <c r="I107" s="79"/>
@@ -30251,7 +30223,7 @@
       </c>
       <c r="B108" s="137"/>
       <c r="C108" s="134" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D108" s="134" t="s">
         <v>32</v>
@@ -30263,7 +30235,7 @@
         <v>242</v>
       </c>
       <c r="G108" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H108" s="79"/>
       <c r="I108" s="79"/>
@@ -30292,7 +30264,7 @@
       </c>
       <c r="B109" s="137"/>
       <c r="C109" s="137" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="D109" s="137" t="s">
         <v>32</v>
@@ -30304,7 +30276,7 @@
         <v>244</v>
       </c>
       <c r="G109" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H109" s="79"/>
       <c r="I109" s="79"/>
@@ -30339,7 +30311,7 @@
         <v>245</v>
       </c>
       <c r="G110" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H110" s="79"/>
       <c r="I110" s="79"/>
@@ -30373,16 +30345,16 @@
         <v>247</v>
       </c>
       <c r="D111" s="43" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E111" s="133" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F111" s="134" t="s">
         <v>248</v>
       </c>
       <c r="G111" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H111" s="79"/>
       <c r="I111" s="79"/>
@@ -30410,7 +30382,7 @@
         <v>43-2-1</v>
       </c>
       <c r="B112" s="223" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C112" s="112"/>
       <c r="D112" s="118"/>
@@ -30419,7 +30391,7 @@
         <v>250</v>
       </c>
       <c r="G112" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H112" s="79"/>
       <c r="I112" s="79"/>
@@ -30454,7 +30426,7 @@
         <v>251</v>
       </c>
       <c r="G113" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H113" s="79"/>
       <c r="I113" s="79"/>
@@ -30489,7 +30461,7 @@
         <v>252</v>
       </c>
       <c r="G114" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H114" s="79"/>
       <c r="I114" s="79"/>
@@ -30530,13 +30502,13 @@
         <v>19</v>
       </c>
       <c r="I115" s="110" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J115" s="109" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K115" s="109" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L115" s="110" t="s">
         <v>51</v>
@@ -30571,7 +30543,7 @@
         <v>254</v>
       </c>
       <c r="G116" s="77" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H116" s="79"/>
       <c r="I116" s="79"/>
@@ -30606,7 +30578,7 @@
         <v>255</v>
       </c>
       <c r="G117" s="66" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H117" s="79"/>
       <c r="I117" s="79"/>
@@ -30641,7 +30613,7 @@
         <v>256</v>
       </c>
       <c r="G118" s="66" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H118" s="79"/>
       <c r="I118" s="79"/>
@@ -30717,10 +30689,10 @@
         <v>19</v>
       </c>
       <c r="I120" s="110" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J120" s="109" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="K120" s="109" t="s">
         <v>30</v>
@@ -30762,10 +30734,10 @@
         <v>19</v>
       </c>
       <c r="I121" s="110" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J121" s="109" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K121" s="109" t="s">
         <v>29</v>
@@ -30807,10 +30779,10 @@
         <v>19</v>
       </c>
       <c r="I122" s="110" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J122" s="109" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="K122" s="109" t="s">
         <v>31</v>
@@ -30852,10 +30824,10 @@
         <v>19</v>
       </c>
       <c r="I123" s="110" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J123" s="109" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="K123" s="109" t="s">
         <v>29</v>
@@ -30897,10 +30869,10 @@
         <v>19</v>
       </c>
       <c r="I124" s="110" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J124" s="109" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K124" s="109" t="s">
         <v>30</v>
@@ -30934,13 +30906,13 @@
       <c r="C125" s="112"/>
       <c r="D125" s="45"/>
       <c r="E125" s="138" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F125" s="134" t="s">
         <v>266</v>
       </c>
       <c r="G125" s="77" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H125" s="79"/>
       <c r="I125" s="79"/>
@@ -30970,16 +30942,16 @@
       <c r="B126" s="118"/>
       <c r="C126" s="157"/>
       <c r="D126" s="138" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E126" s="138" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F126" s="134" t="s">
         <v>267</v>
       </c>
       <c r="G126" s="77" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H126" s="79"/>
       <c r="I126" s="79"/>
@@ -31024,10 +30996,10 @@
         <v>19</v>
       </c>
       <c r="I127" s="110" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J127" s="109" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="K127" s="109" t="s">
         <v>42</v>
@@ -31067,10 +31039,10 @@
         <v>19</v>
       </c>
       <c r="I128" s="110" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J128" s="109" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="K128" s="109" t="s">
         <v>42</v>
@@ -31110,10 +31082,10 @@
         <v>19</v>
       </c>
       <c r="I129" s="110" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J129" s="109" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="K129" s="109" t="s">
         <v>43</v>
@@ -31153,10 +31125,10 @@
         <v>19</v>
       </c>
       <c r="I130" s="110" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J130" s="109" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="K130" s="109" t="s">
         <v>43</v>
@@ -31196,10 +31168,10 @@
         <v>19</v>
       </c>
       <c r="I131" s="110" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J131" s="109" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="K131" s="109" t="s">
         <v>44</v>
@@ -31239,10 +31211,10 @@
         <v>19</v>
       </c>
       <c r="I132" s="110" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J132" s="109" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="K132" s="109" t="s">
         <v>45</v>
@@ -31282,10 +31254,10 @@
         <v>19</v>
       </c>
       <c r="I133" s="110" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J133" s="109" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="K133" s="109" t="s">
         <v>46</v>
@@ -31325,10 +31297,10 @@
         <v>19</v>
       </c>
       <c r="I134" s="110" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J134" s="109" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K134" s="109" t="s">
         <v>46</v>
@@ -31362,13 +31334,13 @@
       <c r="C135" s="118"/>
       <c r="D135" s="118"/>
       <c r="E135" s="136" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F135" s="134" t="s">
         <v>272</v>
       </c>
       <c r="G135" s="77" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H135" s="79"/>
       <c r="I135" s="79"/>
@@ -31403,7 +31375,7 @@
         <v>273</v>
       </c>
       <c r="G136" s="77" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H136" s="79"/>
       <c r="I136" s="79"/>
@@ -31438,7 +31410,7 @@
         <v>274</v>
       </c>
       <c r="G137" s="77" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H137" s="79"/>
       <c r="I137" s="79"/>
@@ -31472,16 +31444,16 @@
         <v>247</v>
       </c>
       <c r="D138" s="132" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E138" s="133" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F138" s="134" t="s">
         <v>276</v>
       </c>
       <c r="G138" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H138" s="79"/>
       <c r="I138" s="79"/>
@@ -31518,7 +31490,7 @@
         <v>278</v>
       </c>
       <c r="G139" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H139" s="79"/>
       <c r="I139" s="79"/>
@@ -31553,7 +31525,7 @@
         <v>279</v>
       </c>
       <c r="G140" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H140" s="79"/>
       <c r="I140" s="79"/>
@@ -31588,7 +31560,7 @@
         <v>280</v>
       </c>
       <c r="G141" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H141" s="79"/>
       <c r="I141" s="79"/>
@@ -31625,7 +31597,7 @@
         <v>282</v>
       </c>
       <c r="G142" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H142" s="79"/>
       <c r="I142" s="79"/>
@@ -31660,7 +31632,7 @@
         <v>283</v>
       </c>
       <c r="G143" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H143" s="79"/>
       <c r="I143" s="79"/>
@@ -31690,16 +31662,16 @@
       <c r="B144" s="137"/>
       <c r="C144" s="139"/>
       <c r="D144" s="138" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E144" s="138" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F144" s="134" t="s">
         <v>284</v>
       </c>
       <c r="G144" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H144" s="79"/>
       <c r="I144" s="79"/>
@@ -31740,7 +31712,7 @@
         <v>287</v>
       </c>
       <c r="G145" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H145" s="79"/>
       <c r="I145" s="79"/>
@@ -31777,7 +31749,7 @@
         <v>289</v>
       </c>
       <c r="G146" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H146" s="79"/>
       <c r="I146" s="79"/>
@@ -31814,7 +31786,7 @@
         <v>291</v>
       </c>
       <c r="G147" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H147" s="79"/>
       <c r="I147" s="79"/>
@@ -31851,7 +31823,7 @@
         <v>292</v>
       </c>
       <c r="G148" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H148" s="79"/>
       <c r="I148" s="79"/>
@@ -31882,13 +31854,13 @@
       <c r="C149" s="136"/>
       <c r="D149" s="137"/>
       <c r="E149" s="134" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F149" s="134" t="s">
         <v>294</v>
       </c>
       <c r="G149" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H149" s="79"/>
       <c r="I149" s="79"/>
@@ -31919,13 +31891,13 @@
       <c r="C150" s="136"/>
       <c r="D150" s="137"/>
       <c r="E150" s="140" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F150" s="134" t="s">
         <v>296</v>
       </c>
       <c r="G150" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H150" s="79"/>
       <c r="I150" s="79"/>
@@ -31960,7 +31932,7 @@
         <v>297</v>
       </c>
       <c r="G151" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H151" s="79"/>
       <c r="I151" s="79"/>
@@ -31995,7 +31967,7 @@
         <v>298</v>
       </c>
       <c r="G152" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H152" s="79"/>
       <c r="I152" s="79"/>
@@ -32030,7 +32002,7 @@
         <v>299</v>
       </c>
       <c r="G153" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H153" s="79"/>
       <c r="I153" s="79"/>
@@ -32065,7 +32037,7 @@
         <v>300</v>
       </c>
       <c r="G154" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H154" s="79"/>
       <c r="I154" s="79"/>
@@ -32100,7 +32072,7 @@
         <v>301</v>
       </c>
       <c r="G155" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H155" s="79"/>
       <c r="I155" s="79"/>
@@ -32133,13 +32105,13 @@
         <v>302</v>
       </c>
       <c r="E156" s="132" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F156" s="134" t="s">
         <v>303</v>
       </c>
       <c r="G156" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H156" s="79"/>
       <c r="I156" s="79"/>
@@ -32174,7 +32146,7 @@
         <v>304</v>
       </c>
       <c r="G157" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H157" s="79"/>
       <c r="I157" s="79"/>
@@ -32211,7 +32183,7 @@
         <v>305</v>
       </c>
       <c r="G158" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H158" s="79"/>
       <c r="I158" s="79"/>
@@ -32246,7 +32218,7 @@
         <v>306</v>
       </c>
       <c r="G159" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H159" s="79"/>
       <c r="I159" s="79"/>
@@ -32278,10 +32250,10 @@
       <c r="D160" s="137"/>
       <c r="E160" s="140"/>
       <c r="F160" s="134" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G160" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H160" s="79"/>
       <c r="I160" s="79"/>
@@ -32313,10 +32285,10 @@
       <c r="D161" s="137"/>
       <c r="E161" s="140"/>
       <c r="F161" s="134" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G161" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H161" s="79"/>
       <c r="I161" s="79"/>
@@ -32351,7 +32323,7 @@
         <v>309</v>
       </c>
       <c r="G162" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H162" s="79"/>
       <c r="I162" s="79"/>
@@ -32386,7 +32358,7 @@
         <v>310</v>
       </c>
       <c r="G163" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H163" s="79"/>
       <c r="I163" s="79"/>
@@ -32421,7 +32393,7 @@
         <v>311</v>
       </c>
       <c r="G164" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H164" s="79"/>
       <c r="I164" s="79"/>
@@ -32456,7 +32428,7 @@
         <v>312</v>
       </c>
       <c r="G165" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H165" s="79"/>
       <c r="I165" s="79"/>
@@ -32491,7 +32463,7 @@
         <v>313</v>
       </c>
       <c r="G166" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H166" s="79"/>
       <c r="I166" s="79"/>
@@ -32526,7 +32498,7 @@
         <v>314</v>
       </c>
       <c r="G167" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H167" s="79"/>
       <c r="I167" s="79"/>
@@ -32561,7 +32533,7 @@
         <v>315</v>
       </c>
       <c r="G168" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H168" s="79"/>
       <c r="I168" s="79"/>
@@ -32598,7 +32570,7 @@
         <v>316</v>
       </c>
       <c r="G169" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H169" s="79"/>
       <c r="I169" s="79"/>
@@ -32633,7 +32605,7 @@
         <v>317</v>
       </c>
       <c r="G170" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H170" s="79"/>
       <c r="I170" s="79"/>
@@ -32668,7 +32640,7 @@
         <v>318</v>
       </c>
       <c r="G171" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H171" s="79"/>
       <c r="I171" s="79"/>
@@ -32703,7 +32675,7 @@
         <v>319</v>
       </c>
       <c r="G172" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H172" s="79"/>
       <c r="I172" s="79"/>
@@ -32738,7 +32710,7 @@
         <v>320</v>
       </c>
       <c r="G173" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H173" s="79"/>
       <c r="I173" s="79"/>
@@ -32773,7 +32745,7 @@
         <v>321</v>
       </c>
       <c r="G174" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H174" s="79"/>
       <c r="I174" s="79"/>
@@ -32808,7 +32780,7 @@
         <v>322</v>
       </c>
       <c r="G175" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H175" s="79"/>
       <c r="I175" s="79"/>
@@ -32845,7 +32817,7 @@
         <v>323</v>
       </c>
       <c r="G176" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H176" s="79"/>
       <c r="I176" s="79"/>
@@ -32880,7 +32852,7 @@
         <v>324</v>
       </c>
       <c r="G177" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H177" s="79"/>
       <c r="I177" s="79"/>
@@ -32915,7 +32887,7 @@
         <v>325</v>
       </c>
       <c r="G178" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H178" s="79"/>
       <c r="I178" s="79"/>
@@ -32950,7 +32922,7 @@
         <v>326</v>
       </c>
       <c r="G179" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H179" s="79"/>
       <c r="I179" s="79"/>
@@ -32985,7 +32957,7 @@
         <v>327</v>
       </c>
       <c r="G180" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H180" s="79"/>
       <c r="I180" s="79"/>
@@ -33020,7 +32992,7 @@
         <v>328</v>
       </c>
       <c r="G181" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H181" s="79"/>
       <c r="I181" s="79"/>
@@ -33055,7 +33027,7 @@
         <v>329</v>
       </c>
       <c r="G182" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H182" s="79"/>
       <c r="I182" s="79"/>
@@ -33090,7 +33062,7 @@
         <v>330</v>
       </c>
       <c r="G183" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H183" s="79"/>
       <c r="I183" s="79"/>
@@ -33125,7 +33097,7 @@
         <v>331</v>
       </c>
       <c r="G184" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H184" s="79"/>
       <c r="I184" s="79"/>
@@ -33162,7 +33134,7 @@
         <v>332</v>
       </c>
       <c r="G185" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H185" s="79"/>
       <c r="I185" s="79"/>
@@ -33199,7 +33171,7 @@
         <v>334</v>
       </c>
       <c r="G186" s="66" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H186" s="79"/>
       <c r="I186" s="79"/>
@@ -33242,7 +33214,7 @@
         <v>337</v>
       </c>
       <c r="G187" s="66" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H187" s="79"/>
       <c r="I187" s="79"/>
@@ -33281,7 +33253,7 @@
         <v>339</v>
       </c>
       <c r="G188" s="66" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H188" s="79"/>
       <c r="I188" s="79"/>
@@ -33311,7 +33283,7 @@
       <c r="B189" s="138"/>
       <c r="C189" s="139"/>
       <c r="D189" s="139" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E189" s="139" t="s">
         <v>32</v>
@@ -33320,7 +33292,7 @@
         <v>341</v>
       </c>
       <c r="G189" s="66" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H189" s="79"/>
       <c r="I189" s="79"/>
@@ -33354,7 +33326,7 @@
         <v>247</v>
       </c>
       <c r="D190" s="132" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E190" s="134" t="s">
         <v>343</v>
@@ -33363,7 +33335,7 @@
         <v>344</v>
       </c>
       <c r="G190" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H190" s="79"/>
       <c r="I190" s="79"/>
@@ -33400,7 +33372,7 @@
         <v>345</v>
       </c>
       <c r="G191" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H191" s="79"/>
       <c r="I191" s="79"/>
@@ -33435,7 +33407,7 @@
         <v>346</v>
       </c>
       <c r="G192" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H192" s="79"/>
       <c r="I192" s="79"/>
@@ -33472,7 +33444,7 @@
         <v>348</v>
       </c>
       <c r="G193" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H193" s="79"/>
       <c r="I193" s="79"/>
@@ -33507,7 +33479,7 @@
         <v>349</v>
       </c>
       <c r="G194" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H194" s="79"/>
       <c r="I194" s="79"/>
@@ -33537,16 +33509,16 @@
       <c r="B195" s="137"/>
       <c r="C195" s="138"/>
       <c r="D195" s="138" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E195" s="138" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F195" s="134" t="s">
         <v>350</v>
       </c>
       <c r="G195" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H195" s="79"/>
       <c r="I195" s="79"/>
@@ -33578,7 +33550,7 @@
         <v>351</v>
       </c>
       <c r="D196" s="137" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E196" s="136" t="s">
         <v>353</v>
@@ -33587,7 +33559,7 @@
         <v>354</v>
       </c>
       <c r="G196" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H196" s="79"/>
       <c r="I196" s="79"/>
@@ -33622,7 +33594,7 @@
         <v>355</v>
       </c>
       <c r="G197" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H197" s="79"/>
       <c r="I197" s="79"/>
@@ -33657,7 +33629,7 @@
         <v>356</v>
       </c>
       <c r="G198" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H198" s="79"/>
       <c r="I198" s="79"/>
@@ -33692,7 +33664,7 @@
         <v>357</v>
       </c>
       <c r="G199" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H199" s="79"/>
       <c r="I199" s="79"/>
@@ -33727,7 +33699,7 @@
         <v>358</v>
       </c>
       <c r="G200" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H200" s="79"/>
       <c r="I200" s="79"/>
@@ -33762,7 +33734,7 @@
         <v>359</v>
       </c>
       <c r="G201" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H201" s="79"/>
       <c r="I201" s="79"/>
@@ -33797,7 +33769,7 @@
         <v>360</v>
       </c>
       <c r="G202" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H202" s="79"/>
       <c r="I202" s="79"/>
@@ -33831,10 +33803,10 @@
         <v>361</v>
       </c>
       <c r="F203" s="134" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G203" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H203" s="79"/>
       <c r="I203" s="79"/>
@@ -33873,7 +33845,7 @@
         <v>364</v>
       </c>
       <c r="G204" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H204" s="79"/>
       <c r="I204" s="79"/>
@@ -33908,7 +33880,7 @@
         <v>365</v>
       </c>
       <c r="G205" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H205" s="79"/>
       <c r="I205" s="79"/>
@@ -33943,7 +33915,7 @@
         <v>366</v>
       </c>
       <c r="G206" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H206" s="79"/>
       <c r="I206" s="79"/>
@@ -33978,7 +33950,7 @@
         <v>367</v>
       </c>
       <c r="G207" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H207" s="79"/>
       <c r="I207" s="79"/>
@@ -34013,7 +33985,7 @@
         <v>368</v>
       </c>
       <c r="G208" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H208" s="79"/>
       <c r="I208" s="79"/>
@@ -34048,7 +34020,7 @@
         <v>369</v>
       </c>
       <c r="G209" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H209" s="79"/>
       <c r="I209" s="79"/>
@@ -34080,10 +34052,10 @@
       <c r="D210" s="137"/>
       <c r="E210" s="136"/>
       <c r="F210" s="134" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G210" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H210" s="79"/>
       <c r="I210" s="79"/>
@@ -34118,7 +34090,7 @@
         <v>371</v>
       </c>
       <c r="G211" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H211" s="79"/>
       <c r="I211" s="79"/>
@@ -34153,7 +34125,7 @@
         <v>372</v>
       </c>
       <c r="G212" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H212" s="79"/>
       <c r="I212" s="79"/>
@@ -34188,7 +34160,7 @@
         <v>373</v>
       </c>
       <c r="G213" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H213" s="79"/>
       <c r="I213" s="79"/>
@@ -34223,7 +34195,7 @@
         <v>374</v>
       </c>
       <c r="G214" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H214" s="79"/>
       <c r="I214" s="79"/>
@@ -34258,7 +34230,7 @@
         <v>375</v>
       </c>
       <c r="G215" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H215" s="79"/>
       <c r="I215" s="79"/>
@@ -34293,7 +34265,7 @@
         <v>376</v>
       </c>
       <c r="G216" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H216" s="79"/>
       <c r="I216" s="79"/>
@@ -34323,7 +34295,7 @@
       <c r="B217" s="137"/>
       <c r="C217" s="142"/>
       <c r="D217" s="132" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E217" s="141" t="s">
         <v>178</v>
@@ -34332,7 +34304,7 @@
         <v>378</v>
       </c>
       <c r="G217" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H217" s="79"/>
       <c r="I217" s="79"/>
@@ -34367,7 +34339,7 @@
         <v>379</v>
       </c>
       <c r="G218" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H218" s="79"/>
       <c r="I218" s="79"/>
@@ -34402,7 +34374,7 @@
         <v>380</v>
       </c>
       <c r="G219" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H219" s="79"/>
       <c r="I219" s="79"/>
@@ -34437,7 +34409,7 @@
         <v>366</v>
       </c>
       <c r="G220" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H220" s="79"/>
       <c r="I220" s="79"/>
@@ -34472,7 +34444,7 @@
         <v>367</v>
       </c>
       <c r="G221" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H221" s="79"/>
       <c r="I221" s="79"/>
@@ -34507,7 +34479,7 @@
         <v>381</v>
       </c>
       <c r="G222" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H222" s="79"/>
       <c r="I222" s="79"/>
@@ -34542,7 +34514,7 @@
         <v>382</v>
       </c>
       <c r="G223" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H223" s="79"/>
       <c r="I223" s="79"/>
@@ -34574,10 +34546,10 @@
       <c r="D224" s="137"/>
       <c r="E224" s="136"/>
       <c r="F224" s="134" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G224" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H224" s="79"/>
       <c r="I224" s="79"/>
@@ -34609,10 +34581,10 @@
       <c r="D225" s="137"/>
       <c r="E225" s="136"/>
       <c r="F225" s="134" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G225" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H225" s="79"/>
       <c r="I225" s="79"/>
@@ -34647,7 +34619,7 @@
         <v>385</v>
       </c>
       <c r="G226" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H226" s="79"/>
       <c r="I226" s="79"/>
@@ -34682,7 +34654,7 @@
         <v>386</v>
       </c>
       <c r="G227" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H227" s="79"/>
       <c r="I227" s="79"/>
@@ -34717,7 +34689,7 @@
         <v>387</v>
       </c>
       <c r="G228" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H228" s="79"/>
       <c r="I228" s="79"/>
@@ -34752,7 +34724,7 @@
         <v>388</v>
       </c>
       <c r="G229" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H229" s="79"/>
       <c r="I229" s="79"/>
@@ -34787,7 +34759,7 @@
         <v>389</v>
       </c>
       <c r="G230" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H230" s="79"/>
       <c r="I230" s="79"/>
@@ -34822,7 +34794,7 @@
         <v>376</v>
       </c>
       <c r="G231" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H231" s="79"/>
       <c r="I231" s="79"/>
@@ -34859,7 +34831,7 @@
         <v>391</v>
       </c>
       <c r="G232" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H232" s="79"/>
       <c r="I232" s="79"/>
@@ -34894,7 +34866,7 @@
         <v>392</v>
       </c>
       <c r="G233" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H233" s="79"/>
       <c r="I233" s="79"/>
@@ -34929,7 +34901,7 @@
         <v>393</v>
       </c>
       <c r="G234" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H234" s="79"/>
       <c r="I234" s="79"/>
@@ -34963,10 +34935,10 @@
         <v>205</v>
       </c>
       <c r="F235" s="134" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G235" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H235" s="79"/>
       <c r="I235" s="79"/>
@@ -35003,7 +34975,7 @@
         <v>396</v>
       </c>
       <c r="G236" s="66" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H236" s="79"/>
       <c r="I236" s="79"/>
@@ -35037,16 +35009,16 @@
         <v>247</v>
       </c>
       <c r="D237" s="132" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E237" s="134" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F237" s="134" t="s">
         <v>398</v>
       </c>
       <c r="G237" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H237" s="79"/>
       <c r="I237" s="79"/>
@@ -35083,7 +35055,7 @@
         <v>399</v>
       </c>
       <c r="G238" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H238" s="79"/>
       <c r="I238" s="79"/>
@@ -35118,7 +35090,7 @@
         <v>400</v>
       </c>
       <c r="G239" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H239" s="79"/>
       <c r="I239" s="79"/>
@@ -35153,7 +35125,7 @@
         <v>401</v>
       </c>
       <c r="G240" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H240" s="79"/>
       <c r="I240" s="79"/>
@@ -35188,7 +35160,7 @@
         <v>402</v>
       </c>
       <c r="G241" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H241" s="79"/>
       <c r="I241" s="79"/>
@@ -35223,7 +35195,7 @@
         <v>403</v>
       </c>
       <c r="G242" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H242" s="79"/>
       <c r="I242" s="79"/>
@@ -35260,7 +35232,7 @@
         <v>404</v>
       </c>
       <c r="G243" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H243" s="79"/>
       <c r="I243" s="79"/>
@@ -35295,7 +35267,7 @@
         <v>405</v>
       </c>
       <c r="G244" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H244" s="79"/>
       <c r="I244" s="79"/>
@@ -35330,7 +35302,7 @@
         <v>406</v>
       </c>
       <c r="G245" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H245" s="79"/>
       <c r="I245" s="79"/>
@@ -35365,7 +35337,7 @@
         <v>407</v>
       </c>
       <c r="G246" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H246" s="79"/>
       <c r="I246" s="79"/>
@@ -35400,7 +35372,7 @@
         <v>408</v>
       </c>
       <c r="G247" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H247" s="79"/>
       <c r="I247" s="79"/>
@@ -35431,13 +35403,13 @@
       <c r="C248" s="138"/>
       <c r="D248" s="138"/>
       <c r="E248" s="138" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F248" s="134" t="s">
         <v>409</v>
       </c>
       <c r="G248" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H248" s="79"/>
       <c r="I248" s="79"/>
@@ -35478,7 +35450,7 @@
         <v>410</v>
       </c>
       <c r="G249" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H249" s="79"/>
       <c r="I249" s="79"/>
@@ -35512,16 +35484,16 @@
         <v>412</v>
       </c>
       <c r="D250" s="132" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E250" s="141" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F250" s="134" t="s">
         <v>413</v>
       </c>
       <c r="G250" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H250" s="79"/>
       <c r="I250" s="79"/>
@@ -35556,7 +35528,7 @@
         <v>414</v>
       </c>
       <c r="G251" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H251" s="79"/>
       <c r="I251" s="79"/>
@@ -35586,16 +35558,16 @@
       <c r="B252" s="137"/>
       <c r="C252" s="137"/>
       <c r="D252" s="137" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E252" s="136" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F252" s="134" t="s">
         <v>415</v>
       </c>
       <c r="G252" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H252" s="79"/>
       <c r="I252" s="79"/>
@@ -35630,7 +35602,7 @@
         <v>416</v>
       </c>
       <c r="G253" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H253" s="79"/>
       <c r="I253" s="79"/>
@@ -35671,7 +35643,7 @@
         <v>418</v>
       </c>
       <c r="G254" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H254" s="79"/>
       <c r="I254" s="79"/>
@@ -35708,7 +35680,7 @@
         <v>419</v>
       </c>
       <c r="G255" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H255" s="79"/>
       <c r="I255" s="79"/>
@@ -35745,7 +35717,7 @@
         <v>420</v>
       </c>
       <c r="G256" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H256" s="79"/>
       <c r="I256" s="79"/>
@@ -35782,7 +35754,7 @@
         <v>421</v>
       </c>
       <c r="G257" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H257" s="79"/>
       <c r="I257" s="79"/>
@@ -35815,13 +35787,13 @@
         <v>302</v>
       </c>
       <c r="E258" s="140" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F258" s="134" t="s">
         <v>422</v>
       </c>
       <c r="G258" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H258" s="79"/>
       <c r="I258" s="79"/>
@@ -35856,7 +35828,7 @@
         <v>423</v>
       </c>
       <c r="G259" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H259" s="79"/>
       <c r="I259" s="79"/>
@@ -35893,7 +35865,7 @@
         <v>424</v>
       </c>
       <c r="G260" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H260" s="79"/>
       <c r="I260" s="79"/>
@@ -35928,7 +35900,7 @@
         <v>425</v>
       </c>
       <c r="G261" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H261" s="79"/>
       <c r="I261" s="79"/>
@@ -35960,10 +35932,10 @@
       <c r="D262" s="136"/>
       <c r="E262" s="136"/>
       <c r="F262" s="134" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G262" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H262" s="79"/>
       <c r="I262" s="79"/>
@@ -35998,7 +35970,7 @@
         <v>427</v>
       </c>
       <c r="G263" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H263" s="79"/>
       <c r="I263" s="79"/>
@@ -36033,7 +36005,7 @@
         <v>428</v>
       </c>
       <c r="G264" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H264" s="79"/>
       <c r="I264" s="79"/>
@@ -36068,7 +36040,7 @@
         <v>429</v>
       </c>
       <c r="G265" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H265" s="79"/>
       <c r="I265" s="79"/>
@@ -36103,7 +36075,7 @@
         <v>430</v>
       </c>
       <c r="G266" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H266" s="79"/>
       <c r="I266" s="79"/>
@@ -36138,7 +36110,7 @@
         <v>431</v>
       </c>
       <c r="G267" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H267" s="79"/>
       <c r="I267" s="79"/>
@@ -36173,7 +36145,7 @@
         <v>432</v>
       </c>
       <c r="G268" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H268" s="79"/>
       <c r="I268" s="79"/>
@@ -36208,7 +36180,7 @@
         <v>433</v>
       </c>
       <c r="G269" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H269" s="79"/>
       <c r="I269" s="79"/>
@@ -36243,7 +36215,7 @@
         <v>434</v>
       </c>
       <c r="G270" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H270" s="79"/>
       <c r="I270" s="79"/>
@@ -36280,7 +36252,7 @@
         <v>435</v>
       </c>
       <c r="G271" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H271" s="79"/>
       <c r="I271" s="79"/>
@@ -36315,7 +36287,7 @@
         <v>436</v>
       </c>
       <c r="G272" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H272" s="79"/>
       <c r="I272" s="79"/>
@@ -36350,7 +36322,7 @@
         <v>437</v>
       </c>
       <c r="G273" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H273" s="79"/>
       <c r="I273" s="79"/>
@@ -36385,7 +36357,7 @@
         <v>438</v>
       </c>
       <c r="G274" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H274" s="79"/>
       <c r="I274" s="79"/>
@@ -36420,7 +36392,7 @@
         <v>439</v>
       </c>
       <c r="G275" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H275" s="79"/>
       <c r="I275" s="79"/>
@@ -36455,7 +36427,7 @@
         <v>440</v>
       </c>
       <c r="G276" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H276" s="79"/>
       <c r="I276" s="79"/>
@@ -36492,7 +36464,7 @@
         <v>441</v>
       </c>
       <c r="G277" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H277" s="79"/>
       <c r="I277" s="79"/>
@@ -36527,7 +36499,7 @@
         <v>442</v>
       </c>
       <c r="G278" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H278" s="79"/>
       <c r="I278" s="79"/>
@@ -36562,7 +36534,7 @@
         <v>443</v>
       </c>
       <c r="G279" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H279" s="79"/>
       <c r="I279" s="79"/>
@@ -36597,7 +36569,7 @@
         <v>444</v>
       </c>
       <c r="G280" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H280" s="79"/>
       <c r="I280" s="79"/>
@@ -36632,7 +36604,7 @@
         <v>445</v>
       </c>
       <c r="G281" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H281" s="79"/>
       <c r="I281" s="79"/>
@@ -36667,7 +36639,7 @@
         <v>446</v>
       </c>
       <c r="G282" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H282" s="79"/>
       <c r="I282" s="79"/>
@@ -36702,7 +36674,7 @@
         <v>447</v>
       </c>
       <c r="G283" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H283" s="79"/>
       <c r="I283" s="79"/>
@@ -36737,7 +36709,7 @@
         <v>448</v>
       </c>
       <c r="G284" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H284" s="79"/>
       <c r="I284" s="79"/>
@@ -36774,7 +36746,7 @@
         <v>449</v>
       </c>
       <c r="G285" s="77" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H285" s="79"/>
       <c r="I285" s="79"/>
@@ -36808,16 +36780,16 @@
         <v>451</v>
       </c>
       <c r="D286" s="132" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E286" s="141" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F286" s="134" t="s">
         <v>452</v>
       </c>
       <c r="G286" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H286" s="79"/>
       <c r="I286" s="79"/>
@@ -36852,7 +36824,7 @@
         <v>453</v>
       </c>
       <c r="G287" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H287" s="79"/>
       <c r="I287" s="79"/>
@@ -36887,7 +36859,7 @@
         <v>454</v>
       </c>
       <c r="G288" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H288" s="79"/>
       <c r="I288" s="79"/>
@@ -36922,7 +36894,7 @@
         <v>455</v>
       </c>
       <c r="G289" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H289" s="79"/>
       <c r="I289" s="79"/>
@@ -36963,7 +36935,7 @@
         <v>457</v>
       </c>
       <c r="G290" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H290" s="79"/>
       <c r="I290" s="79"/>
@@ -37000,7 +36972,7 @@
         <v>458</v>
       </c>
       <c r="G291" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H291" s="79"/>
       <c r="I291" s="79"/>
@@ -37037,7 +37009,7 @@
         <v>459</v>
       </c>
       <c r="G292" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H292" s="79"/>
       <c r="I292" s="79"/>
@@ -37074,7 +37046,7 @@
         <v>460</v>
       </c>
       <c r="G293" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H293" s="79"/>
       <c r="I293" s="79"/>
@@ -37113,7 +37085,7 @@
         <v>463</v>
       </c>
       <c r="G294" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H294" s="79"/>
       <c r="I294" s="79"/>
@@ -37148,7 +37120,7 @@
         <v>464</v>
       </c>
       <c r="G295" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H295" s="79"/>
       <c r="I295" s="79"/>
@@ -37183,7 +37155,7 @@
         <v>465</v>
       </c>
       <c r="G296" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H296" s="79"/>
       <c r="I296" s="79"/>
@@ -37215,10 +37187,10 @@
       <c r="D297" s="136"/>
       <c r="E297" s="136"/>
       <c r="F297" s="134" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G297" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H297" s="79"/>
       <c r="I297" s="79"/>
@@ -37250,10 +37222,10 @@
       <c r="D298" s="136"/>
       <c r="E298" s="136"/>
       <c r="F298" s="134" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="G298" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H298" s="79"/>
       <c r="I298" s="79"/>
@@ -37285,10 +37257,10 @@
       <c r="D299" s="136"/>
       <c r="E299" s="136"/>
       <c r="F299" s="134" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="G299" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H299" s="79"/>
       <c r="I299" s="79"/>
@@ -37320,10 +37292,10 @@
       <c r="D300" s="136"/>
       <c r="E300" s="136"/>
       <c r="F300" s="134" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G300" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H300" s="79"/>
       <c r="I300" s="79"/>
@@ -37358,7 +37330,7 @@
         <v>467</v>
       </c>
       <c r="G301" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H301" s="79"/>
       <c r="I301" s="79"/>
@@ -37393,7 +37365,7 @@
         <v>468</v>
       </c>
       <c r="G302" s="66" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H302" s="79"/>
       <c r="I302" s="79"/>
@@ -37421,7 +37393,7 @@
         <v>101-1-1</v>
       </c>
       <c r="B303" s="50" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C303" s="50" t="s">
         <v>196</v>
@@ -37430,23 +37402,23 @@
         <v>32</v>
       </c>
       <c r="E303" s="105" t="s">
+        <v>504</v>
+      </c>
+      <c r="F303" s="74" t="s">
         <v>505</v>
-      </c>
-      <c r="F303" s="74" t="s">
-        <v>506</v>
       </c>
       <c r="G303" s="74"/>
       <c r="H303" s="47" t="s">
+        <v>538</v>
+      </c>
+      <c r="I303" s="47" t="s">
+        <v>634</v>
+      </c>
+      <c r="J303" s="47" t="s">
+        <v>611</v>
+      </c>
+      <c r="K303" s="47" t="s">
         <v>539</v>
-      </c>
-      <c r="I303" s="47" t="s">
-        <v>635</v>
-      </c>
-      <c r="J303" s="47" t="s">
-        <v>612</v>
-      </c>
-      <c r="K303" s="47" t="s">
-        <v>540</v>
       </c>
       <c r="L303" s="47" t="s">
         <v>47</v>
@@ -37478,20 +37450,20 @@
       <c r="D304" s="106"/>
       <c r="E304" s="106"/>
       <c r="F304" s="74" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G304" s="74"/>
       <c r="H304" s="47" t="s">
+        <v>538</v>
+      </c>
+      <c r="I304" s="47" t="s">
+        <v>634</v>
+      </c>
+      <c r="J304" s="47" t="s">
+        <v>610</v>
+      </c>
+      <c r="K304" s="47" t="s">
         <v>539</v>
-      </c>
-      <c r="I304" s="47" t="s">
-        <v>635</v>
-      </c>
-      <c r="J304" s="47" t="s">
-        <v>611</v>
-      </c>
-      <c r="K304" s="47" t="s">
-        <v>540</v>
       </c>
       <c r="L304" s="47" t="s">
         <v>39</v>
@@ -37523,20 +37495,20 @@
       <c r="D305" s="106"/>
       <c r="E305" s="106"/>
       <c r="F305" s="74" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G305" s="74"/>
       <c r="H305" s="47" t="s">
+        <v>538</v>
+      </c>
+      <c r="I305" s="47" t="s">
+        <v>634</v>
+      </c>
+      <c r="J305" s="47" t="s">
+        <v>612</v>
+      </c>
+      <c r="K305" s="47" t="s">
         <v>539</v>
-      </c>
-      <c r="I305" s="47" t="s">
-        <v>635</v>
-      </c>
-      <c r="J305" s="47" t="s">
-        <v>613</v>
-      </c>
-      <c r="K305" s="47" t="s">
-        <v>540</v>
       </c>
       <c r="L305" s="47" t="s">
         <v>39</v>
@@ -37568,20 +37540,20 @@
       <c r="D306" s="106"/>
       <c r="E306" s="107"/>
       <c r="F306" s="74" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G306" s="74"/>
       <c r="H306" s="47" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I306" s="47" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="J306" s="47" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="K306" s="49" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L306" s="47" t="s">
         <v>39</v>
@@ -37612,10 +37584,10 @@
       <c r="C307" s="48"/>
       <c r="D307" s="106"/>
       <c r="E307" s="74" t="s">
+        <v>509</v>
+      </c>
+      <c r="F307" s="74" t="s">
         <v>510</v>
-      </c>
-      <c r="F307" s="74" t="s">
-        <v>511</v>
       </c>
       <c r="G307" s="74"/>
       <c r="H307" s="47" t="s">
@@ -37625,13 +37597,13 @@
         <v>21</v>
       </c>
       <c r="J307" s="47" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="K307" s="47" t="s">
         <v>33</v>
       </c>
       <c r="L307" s="47" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="M307" s="47"/>
       <c r="N307" s="47"/>
@@ -37657,13 +37629,13 @@
       <c r="C308" s="158"/>
       <c r="D308" s="159"/>
       <c r="E308" s="77" t="s">
+        <v>511</v>
+      </c>
+      <c r="F308" s="77" t="s">
         <v>512</v>
       </c>
-      <c r="F308" s="77" t="s">
-        <v>513</v>
-      </c>
       <c r="G308" s="77" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H308" s="79"/>
       <c r="I308" s="79"/>
@@ -37694,13 +37666,13 @@
       <c r="C309" s="158"/>
       <c r="D309" s="159"/>
       <c r="E309" s="77" t="s">
+        <v>513</v>
+      </c>
+      <c r="F309" s="77" t="s">
         <v>514</v>
       </c>
-      <c r="F309" s="77" t="s">
-        <v>515</v>
-      </c>
       <c r="G309" s="77" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H309" s="79"/>
       <c r="I309" s="79"/>
@@ -37731,13 +37703,13 @@
       <c r="C310" s="158"/>
       <c r="D310" s="160"/>
       <c r="E310" s="77" t="s">
+        <v>515</v>
+      </c>
+      <c r="F310" s="77" t="s">
         <v>516</v>
       </c>
-      <c r="F310" s="77" t="s">
-        <v>517</v>
-      </c>
       <c r="G310" s="77" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H310" s="79"/>
       <c r="I310" s="79"/>
@@ -37767,26 +37739,26 @@
       <c r="B311" s="48"/>
       <c r="C311" s="48"/>
       <c r="D311" s="105" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E311" s="105" t="s">
         <v>32</v>
       </c>
       <c r="F311" s="74" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G311" s="74"/>
       <c r="H311" s="47" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="I311" s="47" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="J311" s="47" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="K311" s="47" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="L311" s="47" t="s">
         <v>51</v>
@@ -37818,17 +37790,17 @@
       <c r="D312" s="106"/>
       <c r="E312" s="106"/>
       <c r="F312" s="105" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G312" s="105"/>
       <c r="H312" s="47" t="s">
         <v>19</v>
       </c>
       <c r="I312" s="47" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="J312" s="47" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K312" s="47" t="s">
         <v>35</v>
@@ -37868,10 +37840,10 @@
         <v>19</v>
       </c>
       <c r="I313" s="47" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="J313" s="47" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="K313" s="47" t="s">
         <v>36</v>
@@ -37911,10 +37883,10 @@
         <v>19</v>
       </c>
       <c r="I314" s="47" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="J314" s="47" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="K314" s="47" t="s">
         <v>37</v>
@@ -37954,10 +37926,10 @@
         <v>19</v>
       </c>
       <c r="I315" s="47" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="J315" s="47" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="K315" s="47" t="s">
         <v>38</v>
@@ -37992,10 +37964,10 @@
       <c r="D316" s="160"/>
       <c r="E316" s="160"/>
       <c r="F316" s="77" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G316" s="77" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H316" s="79"/>
       <c r="I316" s="79"/>
@@ -38025,26 +37997,26 @@
       <c r="B317" s="48"/>
       <c r="C317" s="48"/>
       <c r="D317" s="105" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E317" s="105" t="s">
         <v>32</v>
       </c>
       <c r="F317" s="74" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G317" s="74"/>
       <c r="H317" s="47" t="s">
         <v>19</v>
       </c>
       <c r="I317" s="47" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J317" s="47" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="K317" s="47" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="L317" s="47" t="s">
         <v>51</v>
@@ -38076,10 +38048,10 @@
       <c r="D318" s="159"/>
       <c r="E318" s="159"/>
       <c r="F318" s="77" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G318" s="77" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H318" s="79"/>
       <c r="I318" s="79"/>
@@ -38111,20 +38083,20 @@
       <c r="D319" s="107"/>
       <c r="E319" s="107"/>
       <c r="F319" s="74" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G319" s="74"/>
       <c r="H319" s="47" t="s">
         <v>19</v>
       </c>
       <c r="I319" s="47" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="J319" s="47" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="K319" s="47" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="L319" s="47" t="s">
         <v>47</v>
@@ -38160,17 +38132,17 @@
         <v>32</v>
       </c>
       <c r="F320" s="74" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G320" s="74"/>
       <c r="H320" s="47" t="s">
         <v>19</v>
       </c>
       <c r="I320" s="47" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="J320" s="47" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="K320" s="47" t="s">
         <v>48</v>
@@ -38205,10 +38177,10 @@
       <c r="D321" s="159"/>
       <c r="E321" s="159"/>
       <c r="F321" s="77" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G321" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H321" s="79"/>
       <c r="I321" s="79"/>
@@ -38240,10 +38212,10 @@
       <c r="D322" s="159"/>
       <c r="E322" s="159"/>
       <c r="F322" s="77" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G322" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H322" s="79"/>
       <c r="I322" s="79"/>
@@ -38275,10 +38247,10 @@
       <c r="D323" s="159"/>
       <c r="E323" s="159"/>
       <c r="F323" s="77" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G323" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H323" s="79"/>
       <c r="I323" s="79"/>
@@ -38310,10 +38282,10 @@
       <c r="D324" s="159"/>
       <c r="E324" s="159"/>
       <c r="F324" s="77" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G324" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H324" s="79"/>
       <c r="I324" s="79"/>
@@ -38345,10 +38317,10 @@
       <c r="D325" s="159"/>
       <c r="E325" s="159"/>
       <c r="F325" s="77" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G325" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H325" s="79"/>
       <c r="I325" s="79"/>
@@ -38380,10 +38352,10 @@
       <c r="D326" s="159"/>
       <c r="E326" s="159"/>
       <c r="F326" s="77" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G326" s="77" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H326" s="79"/>
       <c r="I326" s="79"/>
@@ -38415,10 +38387,10 @@
       <c r="D327" s="160"/>
       <c r="E327" s="160"/>
       <c r="F327" s="77" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G327" s="77" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H327" s="79"/>
       <c r="I327" s="79"/>
@@ -38446,10 +38418,10 @@
         <v>109-1-1</v>
       </c>
       <c r="B328" s="47" t="s">
+        <v>533</v>
+      </c>
+      <c r="C328" s="47" t="s">
         <v>534</v>
-      </c>
-      <c r="C328" s="47" t="s">
-        <v>535</v>
       </c>
       <c r="D328" s="74" t="s">
         <v>32</v>
@@ -38458,20 +38430,20 @@
         <v>32</v>
       </c>
       <c r="F328" s="74" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="G328" s="74"/>
       <c r="H328" s="47" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I328" s="47" t="s">
+        <v>542</v>
+      </c>
+      <c r="J328" s="47" t="s">
+        <v>632</v>
+      </c>
+      <c r="K328" s="49" t="s">
         <v>543</v>
-      </c>
-      <c r="J328" s="47" t="s">
-        <v>633</v>
-      </c>
-      <c r="K328" s="49" t="s">
-        <v>544</v>
       </c>
       <c r="L328" s="47" t="s">
         <v>47</v>
@@ -38499,10 +38471,10 @@
         <v>110-1-1</v>
       </c>
       <c r="B329" s="79" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C329" s="79" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D329" s="77" t="s">
         <v>32</v>
@@ -38511,10 +38483,10 @@
         <v>32</v>
       </c>
       <c r="F329" s="77" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G329" s="77" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H329" s="79"/>
       <c r="I329" s="79"/>
@@ -38720,13 +38692,13 @@
       </c>
       <c r="G11" s="105"/>
       <c r="H11" s="36" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="I11" s="36" t="s">
         <v>55</v>
       </c>
       <c r="J11" s="39" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="K11" s="40">
         <v>1</v>
@@ -38758,13 +38730,13 @@
       <c r="F12" s="42"/>
       <c r="G12" s="106"/>
       <c r="H12" s="36" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="I12" s="36" t="s">
         <v>56</v>
       </c>
       <c r="J12" s="39" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="K12" s="40">
         <v>2</v>
@@ -38802,7 +38774,7 @@
       </c>
       <c r="G13" s="105"/>
       <c r="H13" s="36" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="I13" s="36" t="s">
         <v>58</v>
@@ -38840,7 +38812,7 @@
       <c r="F14" s="41"/>
       <c r="G14" s="106"/>
       <c r="H14" s="36" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="I14" s="36" t="s">
         <v>59</v>
@@ -38878,7 +38850,7 @@
       <c r="F15" s="42"/>
       <c r="G15" s="107"/>
       <c r="H15" s="36" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I15" s="36" t="s">
         <v>60</v>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(バッチ)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(バッチ)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA4DF45E-3DAA-4252-A493-57EE5DCF4117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E42944C-2EAF-4AB2-BE55-38A9F0E9A7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="619" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9861,72 +9861,6 @@
     <xf numFmtId="31" fontId="13" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="6" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -10033,6 +9967,72 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -14204,57 +14204,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="192" t="s">
+      <c r="A1" s="170" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="194"/>
-      <c r="E1" s="195" t="s">
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="172"/>
+      <c r="E1" s="173" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="196"/>
-      <c r="G1" s="196"/>
-      <c r="H1" s="196"/>
-      <c r="I1" s="196"/>
-      <c r="J1" s="196"/>
-      <c r="K1" s="196"/>
-      <c r="L1" s="196"/>
-      <c r="M1" s="196"/>
-      <c r="N1" s="197"/>
-      <c r="O1" s="201" t="s">
+      <c r="F1" s="174"/>
+      <c r="G1" s="174"/>
+      <c r="H1" s="174"/>
+      <c r="I1" s="174"/>
+      <c r="J1" s="174"/>
+      <c r="K1" s="174"/>
+      <c r="L1" s="174"/>
+      <c r="M1" s="174"/>
+      <c r="N1" s="175"/>
+      <c r="O1" s="179" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="202"/>
-      <c r="Q1" s="202"/>
-      <c r="R1" s="203"/>
-      <c r="S1" s="210" t="s">
+      <c r="P1" s="180"/>
+      <c r="Q1" s="180"/>
+      <c r="R1" s="181"/>
+      <c r="S1" s="188" t="s">
         <v>641</v>
       </c>
-      <c r="T1" s="211"/>
-      <c r="U1" s="211"/>
-      <c r="V1" s="211"/>
-      <c r="W1" s="211"/>
-      <c r="X1" s="211"/>
-      <c r="Y1" s="211"/>
-      <c r="Z1" s="212"/>
-      <c r="AA1" s="192" t="s">
+      <c r="T1" s="189"/>
+      <c r="U1" s="189"/>
+      <c r="V1" s="189"/>
+      <c r="W1" s="189"/>
+      <c r="X1" s="189"/>
+      <c r="Y1" s="189"/>
+      <c r="Z1" s="190"/>
+      <c r="AA1" s="170" t="s">
         <v>65</v>
       </c>
-      <c r="AB1" s="194"/>
-      <c r="AC1" s="219" t="str">
+      <c r="AB1" s="172"/>
+      <c r="AC1" s="197" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="220"/>
-      <c r="AE1" s="220"/>
-      <c r="AF1" s="221"/>
-      <c r="AG1" s="186">
+      <c r="AD1" s="198"/>
+      <c r="AE1" s="198"/>
+      <c r="AF1" s="199"/>
+      <c r="AG1" s="164">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="187"/>
-      <c r="AI1" s="188"/>
+      <c r="AH1" s="165"/>
+      <c r="AI1" s="166"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -14262,53 +14262,53 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="192" t="s">
+      <c r="A2" s="170" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="193"/>
-      <c r="C2" s="193"/>
-      <c r="D2" s="194"/>
-      <c r="E2" s="195" t="s">
+      <c r="B2" s="171"/>
+      <c r="C2" s="171"/>
+      <c r="D2" s="172"/>
+      <c r="E2" s="173" t="s">
         <v>84</v>
       </c>
-      <c r="F2" s="196"/>
-      <c r="G2" s="196"/>
-      <c r="H2" s="196"/>
-      <c r="I2" s="196"/>
-      <c r="J2" s="196"/>
-      <c r="K2" s="196"/>
-      <c r="L2" s="196"/>
-      <c r="M2" s="196"/>
-      <c r="N2" s="197"/>
-      <c r="O2" s="204"/>
-      <c r="P2" s="205"/>
-      <c r="Q2" s="205"/>
-      <c r="R2" s="206"/>
-      <c r="S2" s="213"/>
-      <c r="T2" s="214"/>
-      <c r="U2" s="214"/>
-      <c r="V2" s="214"/>
-      <c r="W2" s="214"/>
-      <c r="X2" s="214"/>
-      <c r="Y2" s="214"/>
-      <c r="Z2" s="215"/>
-      <c r="AA2" s="192" t="s">
+      <c r="F2" s="174"/>
+      <c r="G2" s="174"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="174"/>
+      <c r="J2" s="174"/>
+      <c r="K2" s="174"/>
+      <c r="L2" s="174"/>
+      <c r="M2" s="174"/>
+      <c r="N2" s="175"/>
+      <c r="O2" s="182"/>
+      <c r="P2" s="183"/>
+      <c r="Q2" s="183"/>
+      <c r="R2" s="184"/>
+      <c r="S2" s="191"/>
+      <c r="T2" s="192"/>
+      <c r="U2" s="192"/>
+      <c r="V2" s="192"/>
+      <c r="W2" s="192"/>
+      <c r="X2" s="192"/>
+      <c r="Y2" s="192"/>
+      <c r="Z2" s="193"/>
+      <c r="AA2" s="170" t="s">
         <v>67</v>
       </c>
-      <c r="AB2" s="194"/>
-      <c r="AC2" s="198" t="str">
+      <c r="AB2" s="172"/>
+      <c r="AC2" s="176" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="199"/>
-      <c r="AE2" s="199"/>
-      <c r="AF2" s="200"/>
-      <c r="AG2" s="186">
+      <c r="AD2" s="177"/>
+      <c r="AE2" s="177"/>
+      <c r="AF2" s="178"/>
+      <c r="AG2" s="164">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44852</v>
       </c>
-      <c r="AH2" s="187"/>
-      <c r="AI2" s="188"/>
+      <c r="AH2" s="165"/>
+      <c r="AI2" s="166"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -14316,45 +14316,45 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="192" t="s">
+      <c r="A3" s="170" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="193"/>
-      <c r="C3" s="193"/>
-      <c r="D3" s="194"/>
-      <c r="E3" s="195" t="s">
+      <c r="B3" s="171"/>
+      <c r="C3" s="171"/>
+      <c r="D3" s="172"/>
+      <c r="E3" s="173" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="196"/>
-      <c r="G3" s="196"/>
-      <c r="H3" s="196"/>
-      <c r="I3" s="196"/>
-      <c r="J3" s="196"/>
-      <c r="K3" s="196"/>
-      <c r="L3" s="196"/>
-      <c r="M3" s="196"/>
-      <c r="N3" s="197"/>
-      <c r="O3" s="207"/>
-      <c r="P3" s="208"/>
-      <c r="Q3" s="208"/>
-      <c r="R3" s="209"/>
-      <c r="S3" s="216"/>
-      <c r="T3" s="217"/>
-      <c r="U3" s="217"/>
-      <c r="V3" s="217"/>
-      <c r="W3" s="217"/>
-      <c r="X3" s="217"/>
-      <c r="Y3" s="217"/>
-      <c r="Z3" s="218"/>
-      <c r="AA3" s="192"/>
-      <c r="AB3" s="194"/>
-      <c r="AC3" s="219"/>
-      <c r="AD3" s="220"/>
-      <c r="AE3" s="220"/>
-      <c r="AF3" s="221"/>
-      <c r="AG3" s="186"/>
-      <c r="AH3" s="187"/>
-      <c r="AI3" s="188"/>
+      <c r="F3" s="174"/>
+      <c r="G3" s="174"/>
+      <c r="H3" s="174"/>
+      <c r="I3" s="174"/>
+      <c r="J3" s="174"/>
+      <c r="K3" s="174"/>
+      <c r="L3" s="174"/>
+      <c r="M3" s="174"/>
+      <c r="N3" s="175"/>
+      <c r="O3" s="185"/>
+      <c r="P3" s="186"/>
+      <c r="Q3" s="186"/>
+      <c r="R3" s="187"/>
+      <c r="S3" s="194"/>
+      <c r="T3" s="195"/>
+      <c r="U3" s="195"/>
+      <c r="V3" s="195"/>
+      <c r="W3" s="195"/>
+      <c r="X3" s="195"/>
+      <c r="Y3" s="195"/>
+      <c r="Z3" s="196"/>
+      <c r="AA3" s="170"/>
+      <c r="AB3" s="172"/>
+      <c r="AC3" s="197"/>
+      <c r="AD3" s="198"/>
+      <c r="AE3" s="198"/>
+      <c r="AF3" s="199"/>
+      <c r="AG3" s="164"/>
+      <c r="AH3" s="165"/>
+      <c r="AI3" s="166"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -14391,97 +14391,97 @@
       <c r="A7" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="189" t="s">
+      <c r="B7" s="167" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="190"/>
-      <c r="D7" s="189" t="s">
+      <c r="C7" s="168"/>
+      <c r="D7" s="167" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="191"/>
-      <c r="F7" s="190"/>
-      <c r="G7" s="189" t="s">
+      <c r="E7" s="169"/>
+      <c r="F7" s="168"/>
+      <c r="G7" s="167" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="191"/>
-      <c r="I7" s="190"/>
-      <c r="J7" s="189" t="s">
+      <c r="H7" s="169"/>
+      <c r="I7" s="168"/>
+      <c r="J7" s="167" t="s">
         <v>73</v>
       </c>
-      <c r="K7" s="191"/>
-      <c r="L7" s="191"/>
-      <c r="M7" s="191"/>
-      <c r="N7" s="191"/>
-      <c r="O7" s="191"/>
-      <c r="P7" s="190"/>
-      <c r="Q7" s="189" t="s">
+      <c r="K7" s="169"/>
+      <c r="L7" s="169"/>
+      <c r="M7" s="169"/>
+      <c r="N7" s="169"/>
+      <c r="O7" s="169"/>
+      <c r="P7" s="168"/>
+      <c r="Q7" s="167" t="s">
         <v>74</v>
       </c>
-      <c r="R7" s="191"/>
-      <c r="S7" s="191"/>
-      <c r="T7" s="191"/>
-      <c r="U7" s="191"/>
-      <c r="V7" s="191"/>
-      <c r="W7" s="191"/>
-      <c r="X7" s="191"/>
-      <c r="Y7" s="191"/>
-      <c r="Z7" s="191"/>
-      <c r="AA7" s="191"/>
-      <c r="AB7" s="191"/>
-      <c r="AC7" s="191"/>
-      <c r="AD7" s="191"/>
-      <c r="AE7" s="190"/>
-      <c r="AF7" s="189" t="s">
+      <c r="R7" s="169"/>
+      <c r="S7" s="169"/>
+      <c r="T7" s="169"/>
+      <c r="U7" s="169"/>
+      <c r="V7" s="169"/>
+      <c r="W7" s="169"/>
+      <c r="X7" s="169"/>
+      <c r="Y7" s="169"/>
+      <c r="Z7" s="169"/>
+      <c r="AA7" s="169"/>
+      <c r="AB7" s="169"/>
+      <c r="AC7" s="169"/>
+      <c r="AD7" s="169"/>
+      <c r="AE7" s="168"/>
+      <c r="AF7" s="167" t="s">
         <v>75</v>
       </c>
-      <c r="AG7" s="191"/>
-      <c r="AH7" s="191"/>
-      <c r="AI7" s="190"/>
+      <c r="AG7" s="169"/>
+      <c r="AH7" s="169"/>
+      <c r="AI7" s="168"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="24">
         <v>1</v>
       </c>
-      <c r="B8" s="177" t="s">
+      <c r="B8" s="212" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="178"/>
-      <c r="D8" s="179">
+      <c r="C8" s="213"/>
+      <c r="D8" s="214">
         <v>43336</v>
       </c>
-      <c r="E8" s="180"/>
-      <c r="F8" s="181"/>
-      <c r="G8" s="177" t="s">
+      <c r="E8" s="215"/>
+      <c r="F8" s="216"/>
+      <c r="G8" s="212" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="182"/>
-      <c r="I8" s="178"/>
-      <c r="J8" s="183" t="s">
+      <c r="H8" s="217"/>
+      <c r="I8" s="213"/>
+      <c r="J8" s="218" t="s">
         <v>78</v>
       </c>
-      <c r="K8" s="184"/>
-      <c r="L8" s="184"/>
-      <c r="M8" s="184"/>
-      <c r="N8" s="184"/>
-      <c r="O8" s="184"/>
-      <c r="P8" s="185"/>
-      <c r="Q8" s="183" t="s">
+      <c r="K8" s="219"/>
+      <c r="L8" s="219"/>
+      <c r="M8" s="219"/>
+      <c r="N8" s="219"/>
+      <c r="O8" s="219"/>
+      <c r="P8" s="220"/>
+      <c r="Q8" s="218" t="s">
         <v>79</v>
       </c>
-      <c r="R8" s="184"/>
-      <c r="S8" s="184"/>
-      <c r="T8" s="184"/>
-      <c r="U8" s="184"/>
-      <c r="V8" s="184"/>
-      <c r="W8" s="184"/>
-      <c r="X8" s="184"/>
-      <c r="Y8" s="184"/>
-      <c r="Z8" s="184"/>
-      <c r="AA8" s="184"/>
-      <c r="AB8" s="184"/>
-      <c r="AC8" s="184"/>
-      <c r="AD8" s="184"/>
-      <c r="AE8" s="185"/>
+      <c r="R8" s="219"/>
+      <c r="S8" s="219"/>
+      <c r="T8" s="219"/>
+      <c r="U8" s="219"/>
+      <c r="V8" s="219"/>
+      <c r="W8" s="219"/>
+      <c r="X8" s="219"/>
+      <c r="Y8" s="219"/>
+      <c r="Z8" s="219"/>
+      <c r="AA8" s="219"/>
+      <c r="AB8" s="219"/>
+      <c r="AC8" s="219"/>
+      <c r="AD8" s="219"/>
+      <c r="AE8" s="220"/>
       <c r="AF8" s="25" t="s">
         <v>80</v>
       </c>
@@ -14493,946 +14493,1101 @@
       <c r="A9" s="24">
         <v>2</v>
       </c>
-      <c r="B9" s="164" t="s">
+      <c r="B9" s="200" t="s">
         <v>546</v>
       </c>
-      <c r="C9" s="165"/>
-      <c r="D9" s="166">
+      <c r="C9" s="201"/>
+      <c r="D9" s="202">
         <v>44852</v>
       </c>
-      <c r="E9" s="167"/>
-      <c r="F9" s="168"/>
-      <c r="G9" s="166" t="s">
+      <c r="E9" s="203"/>
+      <c r="F9" s="204"/>
+      <c r="G9" s="202" t="s">
         <v>547</v>
       </c>
-      <c r="H9" s="169"/>
-      <c r="I9" s="165"/>
-      <c r="J9" s="173" t="s">
+      <c r="H9" s="205"/>
+      <c r="I9" s="201"/>
+      <c r="J9" s="206" t="s">
         <v>549</v>
       </c>
-      <c r="K9" s="171"/>
-      <c r="L9" s="171"/>
-      <c r="M9" s="171"/>
-      <c r="N9" s="171"/>
-      <c r="O9" s="171"/>
-      <c r="P9" s="172"/>
-      <c r="Q9" s="173" t="s">
+      <c r="K9" s="207"/>
+      <c r="L9" s="207"/>
+      <c r="M9" s="207"/>
+      <c r="N9" s="207"/>
+      <c r="O9" s="207"/>
+      <c r="P9" s="208"/>
+      <c r="Q9" s="206" t="s">
         <v>548</v>
       </c>
-      <c r="R9" s="174"/>
-      <c r="S9" s="174"/>
-      <c r="T9" s="174"/>
-      <c r="U9" s="174"/>
-      <c r="V9" s="174"/>
-      <c r="W9" s="174"/>
-      <c r="X9" s="174"/>
-      <c r="Y9" s="174"/>
-      <c r="Z9" s="174"/>
-      <c r="AA9" s="174"/>
-      <c r="AB9" s="174"/>
-      <c r="AC9" s="174"/>
-      <c r="AD9" s="174"/>
-      <c r="AE9" s="175"/>
-      <c r="AF9" s="170" t="s">
+      <c r="R9" s="209"/>
+      <c r="S9" s="209"/>
+      <c r="T9" s="209"/>
+      <c r="U9" s="209"/>
+      <c r="V9" s="209"/>
+      <c r="W9" s="209"/>
+      <c r="X9" s="209"/>
+      <c r="Y9" s="209"/>
+      <c r="Z9" s="209"/>
+      <c r="AA9" s="209"/>
+      <c r="AB9" s="209"/>
+      <c r="AC9" s="209"/>
+      <c r="AD9" s="209"/>
+      <c r="AE9" s="210"/>
+      <c r="AF9" s="211" t="s">
         <v>80</v>
       </c>
-      <c r="AG9" s="171"/>
-      <c r="AH9" s="171"/>
-      <c r="AI9" s="172"/>
+      <c r="AG9" s="207"/>
+      <c r="AH9" s="207"/>
+      <c r="AI9" s="208"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="21"/>
-      <c r="B10" s="164"/>
-      <c r="C10" s="165"/>
-      <c r="D10" s="166"/>
-      <c r="E10" s="167"/>
-      <c r="F10" s="168"/>
-      <c r="G10" s="164"/>
-      <c r="H10" s="169"/>
-      <c r="I10" s="165"/>
-      <c r="J10" s="170"/>
-      <c r="K10" s="171"/>
-      <c r="L10" s="171"/>
-      <c r="M10" s="171"/>
-      <c r="N10" s="171"/>
-      <c r="O10" s="171"/>
-      <c r="P10" s="172"/>
-      <c r="Q10" s="173"/>
-      <c r="R10" s="174"/>
-      <c r="S10" s="174"/>
-      <c r="T10" s="174"/>
-      <c r="U10" s="174"/>
-      <c r="V10" s="174"/>
-      <c r="W10" s="174"/>
-      <c r="X10" s="174"/>
-      <c r="Y10" s="174"/>
-      <c r="Z10" s="174"/>
-      <c r="AA10" s="174"/>
-      <c r="AB10" s="174"/>
-      <c r="AC10" s="174"/>
-      <c r="AD10" s="174"/>
-      <c r="AE10" s="175"/>
-      <c r="AF10" s="170"/>
-      <c r="AG10" s="171"/>
-      <c r="AH10" s="171"/>
-      <c r="AI10" s="172"/>
+      <c r="B10" s="200"/>
+      <c r="C10" s="201"/>
+      <c r="D10" s="202"/>
+      <c r="E10" s="203"/>
+      <c r="F10" s="204"/>
+      <c r="G10" s="200"/>
+      <c r="H10" s="205"/>
+      <c r="I10" s="201"/>
+      <c r="J10" s="211"/>
+      <c r="K10" s="207"/>
+      <c r="L10" s="207"/>
+      <c r="M10" s="207"/>
+      <c r="N10" s="207"/>
+      <c r="O10" s="207"/>
+      <c r="P10" s="208"/>
+      <c r="Q10" s="206"/>
+      <c r="R10" s="209"/>
+      <c r="S10" s="209"/>
+      <c r="T10" s="209"/>
+      <c r="U10" s="209"/>
+      <c r="V10" s="209"/>
+      <c r="W10" s="209"/>
+      <c r="X10" s="209"/>
+      <c r="Y10" s="209"/>
+      <c r="Z10" s="209"/>
+      <c r="AA10" s="209"/>
+      <c r="AB10" s="209"/>
+      <c r="AC10" s="209"/>
+      <c r="AD10" s="209"/>
+      <c r="AE10" s="210"/>
+      <c r="AF10" s="211"/>
+      <c r="AG10" s="207"/>
+      <c r="AH10" s="207"/>
+      <c r="AI10" s="208"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="21"/>
-      <c r="B11" s="164"/>
-      <c r="C11" s="165"/>
-      <c r="D11" s="166"/>
-      <c r="E11" s="167"/>
-      <c r="F11" s="168"/>
-      <c r="G11" s="164"/>
-      <c r="H11" s="169"/>
-      <c r="I11" s="165"/>
-      <c r="J11" s="170"/>
-      <c r="K11" s="171"/>
-      <c r="L11" s="171"/>
-      <c r="M11" s="171"/>
-      <c r="N11" s="171"/>
-      <c r="O11" s="171"/>
-      <c r="P11" s="172"/>
-      <c r="Q11" s="173"/>
-      <c r="R11" s="174"/>
-      <c r="S11" s="174"/>
-      <c r="T11" s="174"/>
-      <c r="U11" s="174"/>
-      <c r="V11" s="174"/>
-      <c r="W11" s="174"/>
-      <c r="X11" s="174"/>
-      <c r="Y11" s="174"/>
-      <c r="Z11" s="174"/>
-      <c r="AA11" s="174"/>
-      <c r="AB11" s="174"/>
-      <c r="AC11" s="174"/>
-      <c r="AD11" s="174"/>
-      <c r="AE11" s="175"/>
-      <c r="AF11" s="170"/>
-      <c r="AG11" s="171"/>
-      <c r="AH11" s="171"/>
-      <c r="AI11" s="172"/>
+      <c r="B11" s="200"/>
+      <c r="C11" s="201"/>
+      <c r="D11" s="202"/>
+      <c r="E11" s="203"/>
+      <c r="F11" s="204"/>
+      <c r="G11" s="200"/>
+      <c r="H11" s="205"/>
+      <c r="I11" s="201"/>
+      <c r="J11" s="211"/>
+      <c r="K11" s="207"/>
+      <c r="L11" s="207"/>
+      <c r="M11" s="207"/>
+      <c r="N11" s="207"/>
+      <c r="O11" s="207"/>
+      <c r="P11" s="208"/>
+      <c r="Q11" s="206"/>
+      <c r="R11" s="209"/>
+      <c r="S11" s="209"/>
+      <c r="T11" s="209"/>
+      <c r="U11" s="209"/>
+      <c r="V11" s="209"/>
+      <c r="W11" s="209"/>
+      <c r="X11" s="209"/>
+      <c r="Y11" s="209"/>
+      <c r="Z11" s="209"/>
+      <c r="AA11" s="209"/>
+      <c r="AB11" s="209"/>
+      <c r="AC11" s="209"/>
+      <c r="AD11" s="209"/>
+      <c r="AE11" s="210"/>
+      <c r="AF11" s="211"/>
+      <c r="AG11" s="207"/>
+      <c r="AH11" s="207"/>
+      <c r="AI11" s="208"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="21"/>
-      <c r="B12" s="164"/>
-      <c r="C12" s="165"/>
-      <c r="D12" s="166"/>
-      <c r="E12" s="167"/>
-      <c r="F12" s="168"/>
-      <c r="G12" s="164"/>
-      <c r="H12" s="169"/>
-      <c r="I12" s="165"/>
-      <c r="J12" s="170"/>
-      <c r="K12" s="171"/>
-      <c r="L12" s="171"/>
-      <c r="M12" s="171"/>
-      <c r="N12" s="171"/>
-      <c r="O12" s="171"/>
-      <c r="P12" s="172"/>
-      <c r="Q12" s="173"/>
-      <c r="R12" s="174"/>
-      <c r="S12" s="174"/>
-      <c r="T12" s="174"/>
-      <c r="U12" s="174"/>
-      <c r="V12" s="174"/>
-      <c r="W12" s="174"/>
-      <c r="X12" s="174"/>
-      <c r="Y12" s="174"/>
-      <c r="Z12" s="174"/>
-      <c r="AA12" s="174"/>
-      <c r="AB12" s="174"/>
-      <c r="AC12" s="174"/>
-      <c r="AD12" s="174"/>
-      <c r="AE12" s="175"/>
-      <c r="AF12" s="170"/>
-      <c r="AG12" s="171"/>
-      <c r="AH12" s="171"/>
-      <c r="AI12" s="172"/>
+      <c r="B12" s="200"/>
+      <c r="C12" s="201"/>
+      <c r="D12" s="202"/>
+      <c r="E12" s="203"/>
+      <c r="F12" s="204"/>
+      <c r="G12" s="200"/>
+      <c r="H12" s="205"/>
+      <c r="I12" s="201"/>
+      <c r="J12" s="211"/>
+      <c r="K12" s="207"/>
+      <c r="L12" s="207"/>
+      <c r="M12" s="207"/>
+      <c r="N12" s="207"/>
+      <c r="O12" s="207"/>
+      <c r="P12" s="208"/>
+      <c r="Q12" s="206"/>
+      <c r="R12" s="209"/>
+      <c r="S12" s="209"/>
+      <c r="T12" s="209"/>
+      <c r="U12" s="209"/>
+      <c r="V12" s="209"/>
+      <c r="W12" s="209"/>
+      <c r="X12" s="209"/>
+      <c r="Y12" s="209"/>
+      <c r="Z12" s="209"/>
+      <c r="AA12" s="209"/>
+      <c r="AB12" s="209"/>
+      <c r="AC12" s="209"/>
+      <c r="AD12" s="209"/>
+      <c r="AE12" s="210"/>
+      <c r="AF12" s="211"/>
+      <c r="AG12" s="207"/>
+      <c r="AH12" s="207"/>
+      <c r="AI12" s="208"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="21"/>
-      <c r="B13" s="164"/>
-      <c r="C13" s="165"/>
-      <c r="D13" s="166"/>
-      <c r="E13" s="167"/>
-      <c r="F13" s="168"/>
-      <c r="G13" s="164"/>
-      <c r="H13" s="169"/>
-      <c r="I13" s="165"/>
-      <c r="J13" s="170"/>
-      <c r="K13" s="171"/>
-      <c r="L13" s="171"/>
-      <c r="M13" s="171"/>
-      <c r="N13" s="171"/>
-      <c r="O13" s="171"/>
-      <c r="P13" s="172"/>
-      <c r="Q13" s="173"/>
-      <c r="R13" s="174"/>
-      <c r="S13" s="174"/>
-      <c r="T13" s="174"/>
-      <c r="U13" s="174"/>
-      <c r="V13" s="174"/>
-      <c r="W13" s="174"/>
-      <c r="X13" s="174"/>
-      <c r="Y13" s="174"/>
-      <c r="Z13" s="174"/>
-      <c r="AA13" s="174"/>
-      <c r="AB13" s="174"/>
-      <c r="AC13" s="174"/>
-      <c r="AD13" s="174"/>
-      <c r="AE13" s="175"/>
-      <c r="AF13" s="170"/>
-      <c r="AG13" s="171"/>
-      <c r="AH13" s="171"/>
-      <c r="AI13" s="172"/>
+      <c r="B13" s="200"/>
+      <c r="C13" s="201"/>
+      <c r="D13" s="202"/>
+      <c r="E13" s="203"/>
+      <c r="F13" s="204"/>
+      <c r="G13" s="200"/>
+      <c r="H13" s="205"/>
+      <c r="I13" s="201"/>
+      <c r="J13" s="211"/>
+      <c r="K13" s="207"/>
+      <c r="L13" s="207"/>
+      <c r="M13" s="207"/>
+      <c r="N13" s="207"/>
+      <c r="O13" s="207"/>
+      <c r="P13" s="208"/>
+      <c r="Q13" s="206"/>
+      <c r="R13" s="209"/>
+      <c r="S13" s="209"/>
+      <c r="T13" s="209"/>
+      <c r="U13" s="209"/>
+      <c r="V13" s="209"/>
+      <c r="W13" s="209"/>
+      <c r="X13" s="209"/>
+      <c r="Y13" s="209"/>
+      <c r="Z13" s="209"/>
+      <c r="AA13" s="209"/>
+      <c r="AB13" s="209"/>
+      <c r="AC13" s="209"/>
+      <c r="AD13" s="209"/>
+      <c r="AE13" s="210"/>
+      <c r="AF13" s="211"/>
+      <c r="AG13" s="207"/>
+      <c r="AH13" s="207"/>
+      <c r="AI13" s="208"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="164"/>
-      <c r="C14" s="165"/>
-      <c r="D14" s="166"/>
-      <c r="E14" s="167"/>
-      <c r="F14" s="168"/>
-      <c r="G14" s="164"/>
-      <c r="H14" s="169"/>
-      <c r="I14" s="165"/>
-      <c r="J14" s="170"/>
-      <c r="K14" s="171"/>
-      <c r="L14" s="171"/>
-      <c r="M14" s="171"/>
-      <c r="N14" s="171"/>
-      <c r="O14" s="171"/>
-      <c r="P14" s="172"/>
-      <c r="Q14" s="173"/>
-      <c r="R14" s="174"/>
-      <c r="S14" s="174"/>
-      <c r="T14" s="174"/>
-      <c r="U14" s="174"/>
-      <c r="V14" s="174"/>
-      <c r="W14" s="174"/>
-      <c r="X14" s="174"/>
-      <c r="Y14" s="174"/>
-      <c r="Z14" s="174"/>
-      <c r="AA14" s="174"/>
-      <c r="AB14" s="174"/>
-      <c r="AC14" s="174"/>
-      <c r="AD14" s="174"/>
-      <c r="AE14" s="175"/>
-      <c r="AF14" s="170"/>
-      <c r="AG14" s="171"/>
-      <c r="AH14" s="171"/>
-      <c r="AI14" s="172"/>
+      <c r="B14" s="200"/>
+      <c r="C14" s="201"/>
+      <c r="D14" s="202"/>
+      <c r="E14" s="203"/>
+      <c r="F14" s="204"/>
+      <c r="G14" s="200"/>
+      <c r="H14" s="205"/>
+      <c r="I14" s="201"/>
+      <c r="J14" s="211"/>
+      <c r="K14" s="207"/>
+      <c r="L14" s="207"/>
+      <c r="M14" s="207"/>
+      <c r="N14" s="207"/>
+      <c r="O14" s="207"/>
+      <c r="P14" s="208"/>
+      <c r="Q14" s="206"/>
+      <c r="R14" s="209"/>
+      <c r="S14" s="209"/>
+      <c r="T14" s="209"/>
+      <c r="U14" s="209"/>
+      <c r="V14" s="209"/>
+      <c r="W14" s="209"/>
+      <c r="X14" s="209"/>
+      <c r="Y14" s="209"/>
+      <c r="Z14" s="209"/>
+      <c r="AA14" s="209"/>
+      <c r="AB14" s="209"/>
+      <c r="AC14" s="209"/>
+      <c r="AD14" s="209"/>
+      <c r="AE14" s="210"/>
+      <c r="AF14" s="211"/>
+      <c r="AG14" s="207"/>
+      <c r="AH14" s="207"/>
+      <c r="AI14" s="208"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="21"/>
-      <c r="B15" s="164"/>
-      <c r="C15" s="165"/>
-      <c r="D15" s="166"/>
-      <c r="E15" s="167"/>
-      <c r="F15" s="168"/>
-      <c r="G15" s="164"/>
-      <c r="H15" s="169"/>
-      <c r="I15" s="165"/>
-      <c r="J15" s="170"/>
-      <c r="K15" s="171"/>
-      <c r="L15" s="171"/>
-      <c r="M15" s="171"/>
-      <c r="N15" s="171"/>
-      <c r="O15" s="171"/>
-      <c r="P15" s="172"/>
-      <c r="Q15" s="173"/>
-      <c r="R15" s="174"/>
-      <c r="S15" s="174"/>
-      <c r="T15" s="174"/>
-      <c r="U15" s="174"/>
-      <c r="V15" s="174"/>
-      <c r="W15" s="174"/>
-      <c r="X15" s="174"/>
-      <c r="Y15" s="174"/>
-      <c r="Z15" s="174"/>
-      <c r="AA15" s="174"/>
-      <c r="AB15" s="174"/>
-      <c r="AC15" s="174"/>
-      <c r="AD15" s="174"/>
-      <c r="AE15" s="175"/>
-      <c r="AF15" s="170"/>
-      <c r="AG15" s="171"/>
-      <c r="AH15" s="171"/>
-      <c r="AI15" s="172"/>
+      <c r="B15" s="200"/>
+      <c r="C15" s="201"/>
+      <c r="D15" s="202"/>
+      <c r="E15" s="203"/>
+      <c r="F15" s="204"/>
+      <c r="G15" s="200"/>
+      <c r="H15" s="205"/>
+      <c r="I15" s="201"/>
+      <c r="J15" s="211"/>
+      <c r="K15" s="207"/>
+      <c r="L15" s="207"/>
+      <c r="M15" s="207"/>
+      <c r="N15" s="207"/>
+      <c r="O15" s="207"/>
+      <c r="P15" s="208"/>
+      <c r="Q15" s="206"/>
+      <c r="R15" s="209"/>
+      <c r="S15" s="209"/>
+      <c r="T15" s="209"/>
+      <c r="U15" s="209"/>
+      <c r="V15" s="209"/>
+      <c r="W15" s="209"/>
+      <c r="X15" s="209"/>
+      <c r="Y15" s="209"/>
+      <c r="Z15" s="209"/>
+      <c r="AA15" s="209"/>
+      <c r="AB15" s="209"/>
+      <c r="AC15" s="209"/>
+      <c r="AD15" s="209"/>
+      <c r="AE15" s="210"/>
+      <c r="AF15" s="211"/>
+      <c r="AG15" s="207"/>
+      <c r="AH15" s="207"/>
+      <c r="AI15" s="208"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="21"/>
-      <c r="B16" s="164"/>
-      <c r="C16" s="165"/>
-      <c r="D16" s="166"/>
-      <c r="E16" s="167"/>
-      <c r="F16" s="168"/>
-      <c r="G16" s="164"/>
-      <c r="H16" s="169"/>
-      <c r="I16" s="165"/>
-      <c r="J16" s="170"/>
-      <c r="K16" s="171"/>
-      <c r="L16" s="171"/>
-      <c r="M16" s="171"/>
-      <c r="N16" s="171"/>
-      <c r="O16" s="171"/>
-      <c r="P16" s="172"/>
-      <c r="Q16" s="173"/>
-      <c r="R16" s="174"/>
-      <c r="S16" s="174"/>
-      <c r="T16" s="174"/>
-      <c r="U16" s="174"/>
-      <c r="V16" s="174"/>
-      <c r="W16" s="174"/>
-      <c r="X16" s="174"/>
-      <c r="Y16" s="174"/>
-      <c r="Z16" s="174"/>
-      <c r="AA16" s="174"/>
-      <c r="AB16" s="174"/>
-      <c r="AC16" s="174"/>
-      <c r="AD16" s="174"/>
-      <c r="AE16" s="175"/>
-      <c r="AF16" s="170"/>
-      <c r="AG16" s="171"/>
-      <c r="AH16" s="171"/>
-      <c r="AI16" s="172"/>
+      <c r="B16" s="200"/>
+      <c r="C16" s="201"/>
+      <c r="D16" s="202"/>
+      <c r="E16" s="203"/>
+      <c r="F16" s="204"/>
+      <c r="G16" s="200"/>
+      <c r="H16" s="205"/>
+      <c r="I16" s="201"/>
+      <c r="J16" s="211"/>
+      <c r="K16" s="207"/>
+      <c r="L16" s="207"/>
+      <c r="M16" s="207"/>
+      <c r="N16" s="207"/>
+      <c r="O16" s="207"/>
+      <c r="P16" s="208"/>
+      <c r="Q16" s="206"/>
+      <c r="R16" s="209"/>
+      <c r="S16" s="209"/>
+      <c r="T16" s="209"/>
+      <c r="U16" s="209"/>
+      <c r="V16" s="209"/>
+      <c r="W16" s="209"/>
+      <c r="X16" s="209"/>
+      <c r="Y16" s="209"/>
+      <c r="Z16" s="209"/>
+      <c r="AA16" s="209"/>
+      <c r="AB16" s="209"/>
+      <c r="AC16" s="209"/>
+      <c r="AD16" s="209"/>
+      <c r="AE16" s="210"/>
+      <c r="AF16" s="211"/>
+      <c r="AG16" s="207"/>
+      <c r="AH16" s="207"/>
+      <c r="AI16" s="208"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="21"/>
-      <c r="B17" s="164"/>
-      <c r="C17" s="165"/>
-      <c r="D17" s="166"/>
-      <c r="E17" s="167"/>
-      <c r="F17" s="168"/>
-      <c r="G17" s="164"/>
-      <c r="H17" s="169"/>
-      <c r="I17" s="165"/>
-      <c r="J17" s="170"/>
-      <c r="K17" s="171"/>
-      <c r="L17" s="171"/>
-      <c r="M17" s="171"/>
-      <c r="N17" s="171"/>
-      <c r="O17" s="171"/>
-      <c r="P17" s="172"/>
-      <c r="Q17" s="173"/>
-      <c r="R17" s="174"/>
-      <c r="S17" s="174"/>
-      <c r="T17" s="174"/>
-      <c r="U17" s="174"/>
-      <c r="V17" s="174"/>
-      <c r="W17" s="174"/>
-      <c r="X17" s="174"/>
-      <c r="Y17" s="174"/>
-      <c r="Z17" s="174"/>
-      <c r="AA17" s="174"/>
-      <c r="AB17" s="174"/>
-      <c r="AC17" s="174"/>
-      <c r="AD17" s="174"/>
-      <c r="AE17" s="175"/>
-      <c r="AF17" s="170"/>
-      <c r="AG17" s="171"/>
-      <c r="AH17" s="171"/>
-      <c r="AI17" s="172"/>
+      <c r="B17" s="200"/>
+      <c r="C17" s="201"/>
+      <c r="D17" s="202"/>
+      <c r="E17" s="203"/>
+      <c r="F17" s="204"/>
+      <c r="G17" s="200"/>
+      <c r="H17" s="205"/>
+      <c r="I17" s="201"/>
+      <c r="J17" s="211"/>
+      <c r="K17" s="207"/>
+      <c r="L17" s="207"/>
+      <c r="M17" s="207"/>
+      <c r="N17" s="207"/>
+      <c r="O17" s="207"/>
+      <c r="P17" s="208"/>
+      <c r="Q17" s="206"/>
+      <c r="R17" s="209"/>
+      <c r="S17" s="209"/>
+      <c r="T17" s="209"/>
+      <c r="U17" s="209"/>
+      <c r="V17" s="209"/>
+      <c r="W17" s="209"/>
+      <c r="X17" s="209"/>
+      <c r="Y17" s="209"/>
+      <c r="Z17" s="209"/>
+      <c r="AA17" s="209"/>
+      <c r="AB17" s="209"/>
+      <c r="AC17" s="209"/>
+      <c r="AD17" s="209"/>
+      <c r="AE17" s="210"/>
+      <c r="AF17" s="211"/>
+      <c r="AG17" s="207"/>
+      <c r="AH17" s="207"/>
+      <c r="AI17" s="208"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="21"/>
-      <c r="B18" s="164"/>
-      <c r="C18" s="165"/>
-      <c r="D18" s="166"/>
-      <c r="E18" s="167"/>
-      <c r="F18" s="168"/>
-      <c r="G18" s="164"/>
-      <c r="H18" s="169"/>
-      <c r="I18" s="165"/>
-      <c r="J18" s="170"/>
-      <c r="K18" s="171"/>
-      <c r="L18" s="171"/>
-      <c r="M18" s="171"/>
-      <c r="N18" s="171"/>
-      <c r="O18" s="171"/>
-      <c r="P18" s="172"/>
-      <c r="Q18" s="173"/>
-      <c r="R18" s="174"/>
-      <c r="S18" s="174"/>
-      <c r="T18" s="174"/>
-      <c r="U18" s="174"/>
-      <c r="V18" s="174"/>
-      <c r="W18" s="174"/>
-      <c r="X18" s="174"/>
-      <c r="Y18" s="174"/>
-      <c r="Z18" s="174"/>
-      <c r="AA18" s="174"/>
-      <c r="AB18" s="174"/>
-      <c r="AC18" s="174"/>
-      <c r="AD18" s="174"/>
-      <c r="AE18" s="175"/>
-      <c r="AF18" s="170"/>
-      <c r="AG18" s="171"/>
-      <c r="AH18" s="171"/>
-      <c r="AI18" s="172"/>
+      <c r="B18" s="200"/>
+      <c r="C18" s="201"/>
+      <c r="D18" s="202"/>
+      <c r="E18" s="203"/>
+      <c r="F18" s="204"/>
+      <c r="G18" s="200"/>
+      <c r="H18" s="205"/>
+      <c r="I18" s="201"/>
+      <c r="J18" s="211"/>
+      <c r="K18" s="207"/>
+      <c r="L18" s="207"/>
+      <c r="M18" s="207"/>
+      <c r="N18" s="207"/>
+      <c r="O18" s="207"/>
+      <c r="P18" s="208"/>
+      <c r="Q18" s="206"/>
+      <c r="R18" s="209"/>
+      <c r="S18" s="209"/>
+      <c r="T18" s="209"/>
+      <c r="U18" s="209"/>
+      <c r="V18" s="209"/>
+      <c r="W18" s="209"/>
+      <c r="X18" s="209"/>
+      <c r="Y18" s="209"/>
+      <c r="Z18" s="209"/>
+      <c r="AA18" s="209"/>
+      <c r="AB18" s="209"/>
+      <c r="AC18" s="209"/>
+      <c r="AD18" s="209"/>
+      <c r="AE18" s="210"/>
+      <c r="AF18" s="211"/>
+      <c r="AG18" s="207"/>
+      <c r="AH18" s="207"/>
+      <c r="AI18" s="208"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="21"/>
-      <c r="B19" s="164"/>
-      <c r="C19" s="165"/>
-      <c r="D19" s="166"/>
-      <c r="E19" s="167"/>
-      <c r="F19" s="168"/>
-      <c r="G19" s="164"/>
-      <c r="H19" s="169"/>
-      <c r="I19" s="165"/>
-      <c r="J19" s="170"/>
-      <c r="K19" s="171"/>
-      <c r="L19" s="171"/>
-      <c r="M19" s="171"/>
-      <c r="N19" s="171"/>
-      <c r="O19" s="171"/>
-      <c r="P19" s="172"/>
-      <c r="Q19" s="173"/>
-      <c r="R19" s="174"/>
-      <c r="S19" s="174"/>
-      <c r="T19" s="174"/>
-      <c r="U19" s="174"/>
-      <c r="V19" s="174"/>
-      <c r="W19" s="174"/>
-      <c r="X19" s="174"/>
-      <c r="Y19" s="174"/>
-      <c r="Z19" s="174"/>
-      <c r="AA19" s="174"/>
-      <c r="AB19" s="174"/>
-      <c r="AC19" s="174"/>
-      <c r="AD19" s="174"/>
-      <c r="AE19" s="175"/>
-      <c r="AF19" s="170"/>
-      <c r="AG19" s="171"/>
-      <c r="AH19" s="171"/>
-      <c r="AI19" s="172"/>
+      <c r="B19" s="200"/>
+      <c r="C19" s="201"/>
+      <c r="D19" s="202"/>
+      <c r="E19" s="203"/>
+      <c r="F19" s="204"/>
+      <c r="G19" s="200"/>
+      <c r="H19" s="205"/>
+      <c r="I19" s="201"/>
+      <c r="J19" s="211"/>
+      <c r="K19" s="207"/>
+      <c r="L19" s="207"/>
+      <c r="M19" s="207"/>
+      <c r="N19" s="207"/>
+      <c r="O19" s="207"/>
+      <c r="P19" s="208"/>
+      <c r="Q19" s="206"/>
+      <c r="R19" s="209"/>
+      <c r="S19" s="209"/>
+      <c r="T19" s="209"/>
+      <c r="U19" s="209"/>
+      <c r="V19" s="209"/>
+      <c r="W19" s="209"/>
+      <c r="X19" s="209"/>
+      <c r="Y19" s="209"/>
+      <c r="Z19" s="209"/>
+      <c r="AA19" s="209"/>
+      <c r="AB19" s="209"/>
+      <c r="AC19" s="209"/>
+      <c r="AD19" s="209"/>
+      <c r="AE19" s="210"/>
+      <c r="AF19" s="211"/>
+      <c r="AG19" s="207"/>
+      <c r="AH19" s="207"/>
+      <c r="AI19" s="208"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="21"/>
-      <c r="B20" s="164"/>
-      <c r="C20" s="165"/>
-      <c r="D20" s="166"/>
-      <c r="E20" s="167"/>
-      <c r="F20" s="168"/>
-      <c r="G20" s="164"/>
-      <c r="H20" s="169"/>
-      <c r="I20" s="165"/>
-      <c r="J20" s="170"/>
-      <c r="K20" s="171"/>
-      <c r="L20" s="171"/>
-      <c r="M20" s="171"/>
-      <c r="N20" s="171"/>
-      <c r="O20" s="171"/>
-      <c r="P20" s="172"/>
-      <c r="Q20" s="173"/>
-      <c r="R20" s="174"/>
-      <c r="S20" s="174"/>
-      <c r="T20" s="174"/>
-      <c r="U20" s="174"/>
-      <c r="V20" s="174"/>
-      <c r="W20" s="174"/>
-      <c r="X20" s="174"/>
-      <c r="Y20" s="174"/>
-      <c r="Z20" s="174"/>
-      <c r="AA20" s="174"/>
-      <c r="AB20" s="174"/>
-      <c r="AC20" s="174"/>
-      <c r="AD20" s="174"/>
-      <c r="AE20" s="175"/>
-      <c r="AF20" s="170"/>
-      <c r="AG20" s="171"/>
-      <c r="AH20" s="171"/>
-      <c r="AI20" s="172"/>
+      <c r="B20" s="200"/>
+      <c r="C20" s="201"/>
+      <c r="D20" s="202"/>
+      <c r="E20" s="203"/>
+      <c r="F20" s="204"/>
+      <c r="G20" s="200"/>
+      <c r="H20" s="205"/>
+      <c r="I20" s="201"/>
+      <c r="J20" s="211"/>
+      <c r="K20" s="207"/>
+      <c r="L20" s="207"/>
+      <c r="M20" s="207"/>
+      <c r="N20" s="207"/>
+      <c r="O20" s="207"/>
+      <c r="P20" s="208"/>
+      <c r="Q20" s="206"/>
+      <c r="R20" s="209"/>
+      <c r="S20" s="209"/>
+      <c r="T20" s="209"/>
+      <c r="U20" s="209"/>
+      <c r="V20" s="209"/>
+      <c r="W20" s="209"/>
+      <c r="X20" s="209"/>
+      <c r="Y20" s="209"/>
+      <c r="Z20" s="209"/>
+      <c r="AA20" s="209"/>
+      <c r="AB20" s="209"/>
+      <c r="AC20" s="209"/>
+      <c r="AD20" s="209"/>
+      <c r="AE20" s="210"/>
+      <c r="AF20" s="211"/>
+      <c r="AG20" s="207"/>
+      <c r="AH20" s="207"/>
+      <c r="AI20" s="208"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="21"/>
-      <c r="B21" s="164"/>
-      <c r="C21" s="165"/>
-      <c r="D21" s="166"/>
-      <c r="E21" s="167"/>
-      <c r="F21" s="168"/>
-      <c r="G21" s="164"/>
-      <c r="H21" s="169"/>
-      <c r="I21" s="165"/>
-      <c r="J21" s="170"/>
-      <c r="K21" s="171"/>
-      <c r="L21" s="171"/>
-      <c r="M21" s="171"/>
-      <c r="N21" s="171"/>
-      <c r="O21" s="171"/>
-      <c r="P21" s="172"/>
-      <c r="Q21" s="173"/>
-      <c r="R21" s="174"/>
-      <c r="S21" s="174"/>
-      <c r="T21" s="174"/>
-      <c r="U21" s="174"/>
-      <c r="V21" s="174"/>
-      <c r="W21" s="174"/>
-      <c r="X21" s="174"/>
-      <c r="Y21" s="174"/>
-      <c r="Z21" s="174"/>
-      <c r="AA21" s="174"/>
-      <c r="AB21" s="174"/>
-      <c r="AC21" s="174"/>
-      <c r="AD21" s="174"/>
-      <c r="AE21" s="175"/>
-      <c r="AF21" s="170"/>
-      <c r="AG21" s="171"/>
-      <c r="AH21" s="171"/>
-      <c r="AI21" s="172"/>
+      <c r="B21" s="200"/>
+      <c r="C21" s="201"/>
+      <c r="D21" s="202"/>
+      <c r="E21" s="203"/>
+      <c r="F21" s="204"/>
+      <c r="G21" s="200"/>
+      <c r="H21" s="205"/>
+      <c r="I21" s="201"/>
+      <c r="J21" s="211"/>
+      <c r="K21" s="207"/>
+      <c r="L21" s="207"/>
+      <c r="M21" s="207"/>
+      <c r="N21" s="207"/>
+      <c r="O21" s="207"/>
+      <c r="P21" s="208"/>
+      <c r="Q21" s="206"/>
+      <c r="R21" s="209"/>
+      <c r="S21" s="209"/>
+      <c r="T21" s="209"/>
+      <c r="U21" s="209"/>
+      <c r="V21" s="209"/>
+      <c r="W21" s="209"/>
+      <c r="X21" s="209"/>
+      <c r="Y21" s="209"/>
+      <c r="Z21" s="209"/>
+      <c r="AA21" s="209"/>
+      <c r="AB21" s="209"/>
+      <c r="AC21" s="209"/>
+      <c r="AD21" s="209"/>
+      <c r="AE21" s="210"/>
+      <c r="AF21" s="211"/>
+      <c r="AG21" s="207"/>
+      <c r="AH21" s="207"/>
+      <c r="AI21" s="208"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="21"/>
-      <c r="B22" s="164"/>
-      <c r="C22" s="165"/>
-      <c r="D22" s="166"/>
-      <c r="E22" s="167"/>
-      <c r="F22" s="168"/>
-      <c r="G22" s="164"/>
-      <c r="H22" s="169"/>
-      <c r="I22" s="165"/>
-      <c r="J22" s="170"/>
-      <c r="K22" s="171"/>
-      <c r="L22" s="171"/>
-      <c r="M22" s="171"/>
-      <c r="N22" s="171"/>
-      <c r="O22" s="171"/>
-      <c r="P22" s="172"/>
-      <c r="Q22" s="173"/>
-      <c r="R22" s="174"/>
-      <c r="S22" s="174"/>
-      <c r="T22" s="174"/>
-      <c r="U22" s="174"/>
-      <c r="V22" s="174"/>
-      <c r="W22" s="174"/>
-      <c r="X22" s="174"/>
-      <c r="Y22" s="174"/>
-      <c r="Z22" s="174"/>
-      <c r="AA22" s="174"/>
-      <c r="AB22" s="174"/>
-      <c r="AC22" s="174"/>
-      <c r="AD22" s="174"/>
-      <c r="AE22" s="175"/>
-      <c r="AF22" s="170"/>
-      <c r="AG22" s="171"/>
-      <c r="AH22" s="171"/>
-      <c r="AI22" s="172"/>
+      <c r="B22" s="200"/>
+      <c r="C22" s="201"/>
+      <c r="D22" s="202"/>
+      <c r="E22" s="203"/>
+      <c r="F22" s="204"/>
+      <c r="G22" s="200"/>
+      <c r="H22" s="205"/>
+      <c r="I22" s="201"/>
+      <c r="J22" s="211"/>
+      <c r="K22" s="207"/>
+      <c r="L22" s="207"/>
+      <c r="M22" s="207"/>
+      <c r="N22" s="207"/>
+      <c r="O22" s="207"/>
+      <c r="P22" s="208"/>
+      <c r="Q22" s="206"/>
+      <c r="R22" s="209"/>
+      <c r="S22" s="209"/>
+      <c r="T22" s="209"/>
+      <c r="U22" s="209"/>
+      <c r="V22" s="209"/>
+      <c r="W22" s="209"/>
+      <c r="X22" s="209"/>
+      <c r="Y22" s="209"/>
+      <c r="Z22" s="209"/>
+      <c r="AA22" s="209"/>
+      <c r="AB22" s="209"/>
+      <c r="AC22" s="209"/>
+      <c r="AD22" s="209"/>
+      <c r="AE22" s="210"/>
+      <c r="AF22" s="211"/>
+      <c r="AG22" s="207"/>
+      <c r="AH22" s="207"/>
+      <c r="AI22" s="208"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="21"/>
-      <c r="B23" s="164"/>
-      <c r="C23" s="165"/>
-      <c r="D23" s="166"/>
-      <c r="E23" s="167"/>
-      <c r="F23" s="168"/>
-      <c r="G23" s="164"/>
-      <c r="H23" s="169"/>
-      <c r="I23" s="165"/>
-      <c r="J23" s="170"/>
-      <c r="K23" s="171"/>
-      <c r="L23" s="171"/>
-      <c r="M23" s="171"/>
-      <c r="N23" s="171"/>
-      <c r="O23" s="171"/>
-      <c r="P23" s="172"/>
-      <c r="Q23" s="173"/>
-      <c r="R23" s="174"/>
-      <c r="S23" s="174"/>
-      <c r="T23" s="174"/>
-      <c r="U23" s="174"/>
-      <c r="V23" s="174"/>
-      <c r="W23" s="174"/>
-      <c r="X23" s="174"/>
-      <c r="Y23" s="174"/>
-      <c r="Z23" s="174"/>
-      <c r="AA23" s="174"/>
-      <c r="AB23" s="174"/>
-      <c r="AC23" s="174"/>
-      <c r="AD23" s="174"/>
-      <c r="AE23" s="175"/>
-      <c r="AF23" s="170"/>
-      <c r="AG23" s="171"/>
-      <c r="AH23" s="171"/>
-      <c r="AI23" s="172"/>
+      <c r="B23" s="200"/>
+      <c r="C23" s="201"/>
+      <c r="D23" s="202"/>
+      <c r="E23" s="203"/>
+      <c r="F23" s="204"/>
+      <c r="G23" s="200"/>
+      <c r="H23" s="205"/>
+      <c r="I23" s="201"/>
+      <c r="J23" s="211"/>
+      <c r="K23" s="207"/>
+      <c r="L23" s="207"/>
+      <c r="M23" s="207"/>
+      <c r="N23" s="207"/>
+      <c r="O23" s="207"/>
+      <c r="P23" s="208"/>
+      <c r="Q23" s="206"/>
+      <c r="R23" s="209"/>
+      <c r="S23" s="209"/>
+      <c r="T23" s="209"/>
+      <c r="U23" s="209"/>
+      <c r="V23" s="209"/>
+      <c r="W23" s="209"/>
+      <c r="X23" s="209"/>
+      <c r="Y23" s="209"/>
+      <c r="Z23" s="209"/>
+      <c r="AA23" s="209"/>
+      <c r="AB23" s="209"/>
+      <c r="AC23" s="209"/>
+      <c r="AD23" s="209"/>
+      <c r="AE23" s="210"/>
+      <c r="AF23" s="211"/>
+      <c r="AG23" s="207"/>
+      <c r="AH23" s="207"/>
+      <c r="AI23" s="208"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="21"/>
-      <c r="B24" s="164"/>
-      <c r="C24" s="165"/>
-      <c r="D24" s="166"/>
-      <c r="E24" s="167"/>
-      <c r="F24" s="168"/>
-      <c r="G24" s="164"/>
-      <c r="H24" s="169"/>
-      <c r="I24" s="165"/>
-      <c r="J24" s="170"/>
-      <c r="K24" s="171"/>
-      <c r="L24" s="171"/>
-      <c r="M24" s="171"/>
-      <c r="N24" s="171"/>
-      <c r="O24" s="171"/>
-      <c r="P24" s="172"/>
-      <c r="Q24" s="173"/>
-      <c r="R24" s="174"/>
-      <c r="S24" s="174"/>
-      <c r="T24" s="174"/>
-      <c r="U24" s="174"/>
-      <c r="V24" s="174"/>
-      <c r="W24" s="174"/>
-      <c r="X24" s="174"/>
-      <c r="Y24" s="174"/>
-      <c r="Z24" s="174"/>
-      <c r="AA24" s="174"/>
-      <c r="AB24" s="174"/>
-      <c r="AC24" s="174"/>
-      <c r="AD24" s="174"/>
-      <c r="AE24" s="175"/>
-      <c r="AF24" s="170"/>
-      <c r="AG24" s="171"/>
-      <c r="AH24" s="171"/>
-      <c r="AI24" s="172"/>
+      <c r="B24" s="200"/>
+      <c r="C24" s="201"/>
+      <c r="D24" s="202"/>
+      <c r="E24" s="203"/>
+      <c r="F24" s="204"/>
+      <c r="G24" s="200"/>
+      <c r="H24" s="205"/>
+      <c r="I24" s="201"/>
+      <c r="J24" s="211"/>
+      <c r="K24" s="207"/>
+      <c r="L24" s="207"/>
+      <c r="M24" s="207"/>
+      <c r="N24" s="207"/>
+      <c r="O24" s="207"/>
+      <c r="P24" s="208"/>
+      <c r="Q24" s="206"/>
+      <c r="R24" s="209"/>
+      <c r="S24" s="209"/>
+      <c r="T24" s="209"/>
+      <c r="U24" s="209"/>
+      <c r="V24" s="209"/>
+      <c r="W24" s="209"/>
+      <c r="X24" s="209"/>
+      <c r="Y24" s="209"/>
+      <c r="Z24" s="209"/>
+      <c r="AA24" s="209"/>
+      <c r="AB24" s="209"/>
+      <c r="AC24" s="209"/>
+      <c r="AD24" s="209"/>
+      <c r="AE24" s="210"/>
+      <c r="AF24" s="211"/>
+      <c r="AG24" s="207"/>
+      <c r="AH24" s="207"/>
+      <c r="AI24" s="208"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="21"/>
-      <c r="B25" s="164"/>
-      <c r="C25" s="165"/>
-      <c r="D25" s="166"/>
-      <c r="E25" s="167"/>
-      <c r="F25" s="168"/>
-      <c r="G25" s="164"/>
-      <c r="H25" s="169"/>
-      <c r="I25" s="165"/>
-      <c r="J25" s="170"/>
-      <c r="K25" s="171"/>
-      <c r="L25" s="171"/>
-      <c r="M25" s="171"/>
-      <c r="N25" s="171"/>
-      <c r="O25" s="171"/>
-      <c r="P25" s="172"/>
-      <c r="Q25" s="173"/>
-      <c r="R25" s="174"/>
-      <c r="S25" s="174"/>
-      <c r="T25" s="174"/>
-      <c r="U25" s="174"/>
-      <c r="V25" s="174"/>
-      <c r="W25" s="174"/>
-      <c r="X25" s="174"/>
-      <c r="Y25" s="174"/>
-      <c r="Z25" s="174"/>
-      <c r="AA25" s="174"/>
-      <c r="AB25" s="174"/>
-      <c r="AC25" s="174"/>
-      <c r="AD25" s="174"/>
-      <c r="AE25" s="175"/>
-      <c r="AF25" s="170"/>
-      <c r="AG25" s="171"/>
-      <c r="AH25" s="171"/>
-      <c r="AI25" s="172"/>
+      <c r="B25" s="200"/>
+      <c r="C25" s="201"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="203"/>
+      <c r="F25" s="204"/>
+      <c r="G25" s="200"/>
+      <c r="H25" s="205"/>
+      <c r="I25" s="201"/>
+      <c r="J25" s="211"/>
+      <c r="K25" s="207"/>
+      <c r="L25" s="207"/>
+      <c r="M25" s="207"/>
+      <c r="N25" s="207"/>
+      <c r="O25" s="207"/>
+      <c r="P25" s="208"/>
+      <c r="Q25" s="206"/>
+      <c r="R25" s="209"/>
+      <c r="S25" s="209"/>
+      <c r="T25" s="209"/>
+      <c r="U25" s="209"/>
+      <c r="V25" s="209"/>
+      <c r="W25" s="209"/>
+      <c r="X25" s="209"/>
+      <c r="Y25" s="209"/>
+      <c r="Z25" s="209"/>
+      <c r="AA25" s="209"/>
+      <c r="AB25" s="209"/>
+      <c r="AC25" s="209"/>
+      <c r="AD25" s="209"/>
+      <c r="AE25" s="210"/>
+      <c r="AF25" s="211"/>
+      <c r="AG25" s="207"/>
+      <c r="AH25" s="207"/>
+      <c r="AI25" s="208"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="21"/>
-      <c r="B26" s="164"/>
-      <c r="C26" s="165"/>
-      <c r="D26" s="166"/>
-      <c r="E26" s="167"/>
-      <c r="F26" s="168"/>
-      <c r="G26" s="164"/>
-      <c r="H26" s="169"/>
-      <c r="I26" s="165"/>
-      <c r="J26" s="170"/>
-      <c r="K26" s="171"/>
-      <c r="L26" s="171"/>
-      <c r="M26" s="171"/>
-      <c r="N26" s="171"/>
-      <c r="O26" s="171"/>
-      <c r="P26" s="172"/>
-      <c r="Q26" s="173"/>
-      <c r="R26" s="174"/>
-      <c r="S26" s="174"/>
-      <c r="T26" s="174"/>
-      <c r="U26" s="174"/>
-      <c r="V26" s="174"/>
-      <c r="W26" s="174"/>
-      <c r="X26" s="174"/>
-      <c r="Y26" s="174"/>
-      <c r="Z26" s="174"/>
-      <c r="AA26" s="174"/>
-      <c r="AB26" s="174"/>
-      <c r="AC26" s="174"/>
-      <c r="AD26" s="174"/>
-      <c r="AE26" s="175"/>
-      <c r="AF26" s="170"/>
-      <c r="AG26" s="171"/>
-      <c r="AH26" s="171"/>
-      <c r="AI26" s="172"/>
+      <c r="B26" s="200"/>
+      <c r="C26" s="201"/>
+      <c r="D26" s="202"/>
+      <c r="E26" s="203"/>
+      <c r="F26" s="204"/>
+      <c r="G26" s="200"/>
+      <c r="H26" s="205"/>
+      <c r="I26" s="201"/>
+      <c r="J26" s="211"/>
+      <c r="K26" s="207"/>
+      <c r="L26" s="207"/>
+      <c r="M26" s="207"/>
+      <c r="N26" s="207"/>
+      <c r="O26" s="207"/>
+      <c r="P26" s="208"/>
+      <c r="Q26" s="206"/>
+      <c r="R26" s="209"/>
+      <c r="S26" s="209"/>
+      <c r="T26" s="209"/>
+      <c r="U26" s="209"/>
+      <c r="V26" s="209"/>
+      <c r="W26" s="209"/>
+      <c r="X26" s="209"/>
+      <c r="Y26" s="209"/>
+      <c r="Z26" s="209"/>
+      <c r="AA26" s="209"/>
+      <c r="AB26" s="209"/>
+      <c r="AC26" s="209"/>
+      <c r="AD26" s="209"/>
+      <c r="AE26" s="210"/>
+      <c r="AF26" s="211"/>
+      <c r="AG26" s="207"/>
+      <c r="AH26" s="207"/>
+      <c r="AI26" s="208"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="21"/>
-      <c r="B27" s="164"/>
-      <c r="C27" s="165"/>
-      <c r="D27" s="166"/>
-      <c r="E27" s="167"/>
-      <c r="F27" s="168"/>
-      <c r="G27" s="164"/>
-      <c r="H27" s="169"/>
-      <c r="I27" s="165"/>
-      <c r="J27" s="170"/>
-      <c r="K27" s="171"/>
-      <c r="L27" s="171"/>
-      <c r="M27" s="171"/>
-      <c r="N27" s="171"/>
-      <c r="O27" s="171"/>
-      <c r="P27" s="172"/>
-      <c r="Q27" s="173"/>
-      <c r="R27" s="174"/>
-      <c r="S27" s="174"/>
-      <c r="T27" s="174"/>
-      <c r="U27" s="174"/>
-      <c r="V27" s="174"/>
-      <c r="W27" s="174"/>
-      <c r="X27" s="174"/>
-      <c r="Y27" s="174"/>
-      <c r="Z27" s="174"/>
-      <c r="AA27" s="174"/>
-      <c r="AB27" s="174"/>
-      <c r="AC27" s="174"/>
-      <c r="AD27" s="174"/>
-      <c r="AE27" s="175"/>
-      <c r="AF27" s="170"/>
-      <c r="AG27" s="171"/>
-      <c r="AH27" s="171"/>
-      <c r="AI27" s="172"/>
+      <c r="B27" s="200"/>
+      <c r="C27" s="201"/>
+      <c r="D27" s="202"/>
+      <c r="E27" s="203"/>
+      <c r="F27" s="204"/>
+      <c r="G27" s="200"/>
+      <c r="H27" s="205"/>
+      <c r="I27" s="201"/>
+      <c r="J27" s="211"/>
+      <c r="K27" s="207"/>
+      <c r="L27" s="207"/>
+      <c r="M27" s="207"/>
+      <c r="N27" s="207"/>
+      <c r="O27" s="207"/>
+      <c r="P27" s="208"/>
+      <c r="Q27" s="206"/>
+      <c r="R27" s="209"/>
+      <c r="S27" s="209"/>
+      <c r="T27" s="209"/>
+      <c r="U27" s="209"/>
+      <c r="V27" s="209"/>
+      <c r="W27" s="209"/>
+      <c r="X27" s="209"/>
+      <c r="Y27" s="209"/>
+      <c r="Z27" s="209"/>
+      <c r="AA27" s="209"/>
+      <c r="AB27" s="209"/>
+      <c r="AC27" s="209"/>
+      <c r="AD27" s="209"/>
+      <c r="AE27" s="210"/>
+      <c r="AF27" s="211"/>
+      <c r="AG27" s="207"/>
+      <c r="AH27" s="207"/>
+      <c r="AI27" s="208"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="21"/>
-      <c r="B28" s="164"/>
-      <c r="C28" s="165"/>
-      <c r="D28" s="166"/>
-      <c r="E28" s="167"/>
-      <c r="F28" s="168"/>
-      <c r="G28" s="164"/>
-      <c r="H28" s="169"/>
-      <c r="I28" s="165"/>
-      <c r="J28" s="170"/>
-      <c r="K28" s="171"/>
-      <c r="L28" s="171"/>
-      <c r="M28" s="171"/>
-      <c r="N28" s="171"/>
-      <c r="O28" s="171"/>
-      <c r="P28" s="172"/>
-      <c r="Q28" s="173"/>
-      <c r="R28" s="174"/>
-      <c r="S28" s="174"/>
-      <c r="T28" s="174"/>
-      <c r="U28" s="174"/>
-      <c r="V28" s="174"/>
-      <c r="W28" s="174"/>
-      <c r="X28" s="174"/>
-      <c r="Y28" s="174"/>
-      <c r="Z28" s="174"/>
-      <c r="AA28" s="174"/>
-      <c r="AB28" s="174"/>
-      <c r="AC28" s="174"/>
-      <c r="AD28" s="174"/>
-      <c r="AE28" s="175"/>
-      <c r="AF28" s="170"/>
-      <c r="AG28" s="171"/>
-      <c r="AH28" s="171"/>
-      <c r="AI28" s="172"/>
+      <c r="B28" s="200"/>
+      <c r="C28" s="201"/>
+      <c r="D28" s="202"/>
+      <c r="E28" s="203"/>
+      <c r="F28" s="204"/>
+      <c r="G28" s="200"/>
+      <c r="H28" s="205"/>
+      <c r="I28" s="201"/>
+      <c r="J28" s="211"/>
+      <c r="K28" s="207"/>
+      <c r="L28" s="207"/>
+      <c r="M28" s="207"/>
+      <c r="N28" s="207"/>
+      <c r="O28" s="207"/>
+      <c r="P28" s="208"/>
+      <c r="Q28" s="206"/>
+      <c r="R28" s="209"/>
+      <c r="S28" s="209"/>
+      <c r="T28" s="209"/>
+      <c r="U28" s="209"/>
+      <c r="V28" s="209"/>
+      <c r="W28" s="209"/>
+      <c r="X28" s="209"/>
+      <c r="Y28" s="209"/>
+      <c r="Z28" s="209"/>
+      <c r="AA28" s="209"/>
+      <c r="AB28" s="209"/>
+      <c r="AC28" s="209"/>
+      <c r="AD28" s="209"/>
+      <c r="AE28" s="210"/>
+      <c r="AF28" s="211"/>
+      <c r="AG28" s="207"/>
+      <c r="AH28" s="207"/>
+      <c r="AI28" s="208"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="21"/>
-      <c r="B29" s="164"/>
-      <c r="C29" s="165"/>
-      <c r="D29" s="166"/>
-      <c r="E29" s="167"/>
-      <c r="F29" s="168"/>
-      <c r="G29" s="164"/>
-      <c r="H29" s="169"/>
-      <c r="I29" s="165"/>
-      <c r="J29" s="170"/>
-      <c r="K29" s="171"/>
-      <c r="L29" s="171"/>
-      <c r="M29" s="171"/>
-      <c r="N29" s="171"/>
-      <c r="O29" s="171"/>
-      <c r="P29" s="172"/>
-      <c r="Q29" s="173"/>
-      <c r="R29" s="174"/>
-      <c r="S29" s="174"/>
-      <c r="T29" s="174"/>
-      <c r="U29" s="174"/>
-      <c r="V29" s="174"/>
-      <c r="W29" s="174"/>
-      <c r="X29" s="174"/>
-      <c r="Y29" s="174"/>
-      <c r="Z29" s="174"/>
-      <c r="AA29" s="174"/>
-      <c r="AB29" s="174"/>
-      <c r="AC29" s="174"/>
-      <c r="AD29" s="174"/>
-      <c r="AE29" s="175"/>
-      <c r="AF29" s="170"/>
-      <c r="AG29" s="171"/>
-      <c r="AH29" s="171"/>
-      <c r="AI29" s="172"/>
+      <c r="B29" s="200"/>
+      <c r="C29" s="201"/>
+      <c r="D29" s="202"/>
+      <c r="E29" s="203"/>
+      <c r="F29" s="204"/>
+      <c r="G29" s="200"/>
+      <c r="H29" s="205"/>
+      <c r="I29" s="201"/>
+      <c r="J29" s="211"/>
+      <c r="K29" s="207"/>
+      <c r="L29" s="207"/>
+      <c r="M29" s="207"/>
+      <c r="N29" s="207"/>
+      <c r="O29" s="207"/>
+      <c r="P29" s="208"/>
+      <c r="Q29" s="206"/>
+      <c r="R29" s="209"/>
+      <c r="S29" s="209"/>
+      <c r="T29" s="209"/>
+      <c r="U29" s="209"/>
+      <c r="V29" s="209"/>
+      <c r="W29" s="209"/>
+      <c r="X29" s="209"/>
+      <c r="Y29" s="209"/>
+      <c r="Z29" s="209"/>
+      <c r="AA29" s="209"/>
+      <c r="AB29" s="209"/>
+      <c r="AC29" s="209"/>
+      <c r="AD29" s="209"/>
+      <c r="AE29" s="210"/>
+      <c r="AF29" s="211"/>
+      <c r="AG29" s="207"/>
+      <c r="AH29" s="207"/>
+      <c r="AI29" s="208"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="21"/>
-      <c r="B30" s="164"/>
-      <c r="C30" s="165"/>
-      <c r="D30" s="166"/>
-      <c r="E30" s="167"/>
-      <c r="F30" s="168"/>
-      <c r="G30" s="164"/>
-      <c r="H30" s="169"/>
-      <c r="I30" s="165"/>
-      <c r="J30" s="170"/>
-      <c r="K30" s="171"/>
-      <c r="L30" s="171"/>
-      <c r="M30" s="171"/>
-      <c r="N30" s="171"/>
-      <c r="O30" s="171"/>
-      <c r="P30" s="172"/>
-      <c r="Q30" s="173"/>
-      <c r="R30" s="174"/>
-      <c r="S30" s="174"/>
-      <c r="T30" s="174"/>
-      <c r="U30" s="174"/>
-      <c r="V30" s="174"/>
-      <c r="W30" s="174"/>
-      <c r="X30" s="174"/>
-      <c r="Y30" s="174"/>
-      <c r="Z30" s="174"/>
-      <c r="AA30" s="174"/>
-      <c r="AB30" s="174"/>
-      <c r="AC30" s="174"/>
-      <c r="AD30" s="174"/>
-      <c r="AE30" s="175"/>
-      <c r="AF30" s="170"/>
-      <c r="AG30" s="171"/>
-      <c r="AH30" s="171"/>
-      <c r="AI30" s="172"/>
+      <c r="B30" s="200"/>
+      <c r="C30" s="201"/>
+      <c r="D30" s="202"/>
+      <c r="E30" s="203"/>
+      <c r="F30" s="204"/>
+      <c r="G30" s="200"/>
+      <c r="H30" s="205"/>
+      <c r="I30" s="201"/>
+      <c r="J30" s="211"/>
+      <c r="K30" s="207"/>
+      <c r="L30" s="207"/>
+      <c r="M30" s="207"/>
+      <c r="N30" s="207"/>
+      <c r="O30" s="207"/>
+      <c r="P30" s="208"/>
+      <c r="Q30" s="206"/>
+      <c r="R30" s="209"/>
+      <c r="S30" s="209"/>
+      <c r="T30" s="209"/>
+      <c r="U30" s="209"/>
+      <c r="V30" s="209"/>
+      <c r="W30" s="209"/>
+      <c r="X30" s="209"/>
+      <c r="Y30" s="209"/>
+      <c r="Z30" s="209"/>
+      <c r="AA30" s="209"/>
+      <c r="AB30" s="209"/>
+      <c r="AC30" s="209"/>
+      <c r="AD30" s="209"/>
+      <c r="AE30" s="210"/>
+      <c r="AF30" s="211"/>
+      <c r="AG30" s="207"/>
+      <c r="AH30" s="207"/>
+      <c r="AI30" s="208"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="164"/>
-      <c r="C31" s="165"/>
-      <c r="D31" s="166"/>
-      <c r="E31" s="167"/>
-      <c r="F31" s="168"/>
-      <c r="G31" s="164"/>
-      <c r="H31" s="169"/>
-      <c r="I31" s="165"/>
-      <c r="J31" s="170"/>
-      <c r="K31" s="171"/>
-      <c r="L31" s="171"/>
-      <c r="M31" s="171"/>
-      <c r="N31" s="171"/>
-      <c r="O31" s="171"/>
-      <c r="P31" s="172"/>
-      <c r="Q31" s="173"/>
-      <c r="R31" s="174"/>
-      <c r="S31" s="174"/>
-      <c r="T31" s="174"/>
-      <c r="U31" s="174"/>
-      <c r="V31" s="174"/>
-      <c r="W31" s="174"/>
-      <c r="X31" s="174"/>
-      <c r="Y31" s="174"/>
-      <c r="Z31" s="174"/>
-      <c r="AA31" s="174"/>
-      <c r="AB31" s="174"/>
-      <c r="AC31" s="174"/>
-      <c r="AD31" s="174"/>
-      <c r="AE31" s="175"/>
-      <c r="AF31" s="170"/>
-      <c r="AG31" s="171"/>
-      <c r="AH31" s="171"/>
-      <c r="AI31" s="172"/>
+      <c r="B31" s="200"/>
+      <c r="C31" s="201"/>
+      <c r="D31" s="202"/>
+      <c r="E31" s="203"/>
+      <c r="F31" s="204"/>
+      <c r="G31" s="200"/>
+      <c r="H31" s="205"/>
+      <c r="I31" s="201"/>
+      <c r="J31" s="211"/>
+      <c r="K31" s="207"/>
+      <c r="L31" s="207"/>
+      <c r="M31" s="207"/>
+      <c r="N31" s="207"/>
+      <c r="O31" s="207"/>
+      <c r="P31" s="208"/>
+      <c r="Q31" s="206"/>
+      <c r="R31" s="209"/>
+      <c r="S31" s="209"/>
+      <c r="T31" s="209"/>
+      <c r="U31" s="209"/>
+      <c r="V31" s="209"/>
+      <c r="W31" s="209"/>
+      <c r="X31" s="209"/>
+      <c r="Y31" s="209"/>
+      <c r="Z31" s="209"/>
+      <c r="AA31" s="209"/>
+      <c r="AB31" s="209"/>
+      <c r="AC31" s="209"/>
+      <c r="AD31" s="209"/>
+      <c r="AE31" s="210"/>
+      <c r="AF31" s="211"/>
+      <c r="AG31" s="207"/>
+      <c r="AH31" s="207"/>
+      <c r="AI31" s="208"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="21"/>
-      <c r="B32" s="164"/>
-      <c r="C32" s="165"/>
-      <c r="D32" s="166"/>
-      <c r="E32" s="167"/>
-      <c r="F32" s="168"/>
-      <c r="G32" s="164"/>
-      <c r="H32" s="169"/>
-      <c r="I32" s="165"/>
-      <c r="J32" s="170"/>
-      <c r="K32" s="176"/>
-      <c r="L32" s="171"/>
-      <c r="M32" s="171"/>
-      <c r="N32" s="171"/>
-      <c r="O32" s="171"/>
-      <c r="P32" s="172"/>
-      <c r="Q32" s="173"/>
-      <c r="R32" s="174"/>
-      <c r="S32" s="174"/>
-      <c r="T32" s="174"/>
-      <c r="U32" s="174"/>
-      <c r="V32" s="174"/>
-      <c r="W32" s="174"/>
-      <c r="X32" s="174"/>
-      <c r="Y32" s="174"/>
-      <c r="Z32" s="174"/>
-      <c r="AA32" s="174"/>
-      <c r="AB32" s="174"/>
-      <c r="AC32" s="174"/>
-      <c r="AD32" s="174"/>
-      <c r="AE32" s="175"/>
-      <c r="AF32" s="170"/>
-      <c r="AG32" s="171"/>
-      <c r="AH32" s="171"/>
-      <c r="AI32" s="172"/>
+      <c r="B32" s="200"/>
+      <c r="C32" s="201"/>
+      <c r="D32" s="202"/>
+      <c r="E32" s="203"/>
+      <c r="F32" s="204"/>
+      <c r="G32" s="200"/>
+      <c r="H32" s="205"/>
+      <c r="I32" s="201"/>
+      <c r="J32" s="211"/>
+      <c r="K32" s="221"/>
+      <c r="L32" s="207"/>
+      <c r="M32" s="207"/>
+      <c r="N32" s="207"/>
+      <c r="O32" s="207"/>
+      <c r="P32" s="208"/>
+      <c r="Q32" s="206"/>
+      <c r="R32" s="209"/>
+      <c r="S32" s="209"/>
+      <c r="T32" s="209"/>
+      <c r="U32" s="209"/>
+      <c r="V32" s="209"/>
+      <c r="W32" s="209"/>
+      <c r="X32" s="209"/>
+      <c r="Y32" s="209"/>
+      <c r="Z32" s="209"/>
+      <c r="AA32" s="209"/>
+      <c r="AB32" s="209"/>
+      <c r="AC32" s="209"/>
+      <c r="AD32" s="209"/>
+      <c r="AE32" s="210"/>
+      <c r="AF32" s="211"/>
+      <c r="AG32" s="207"/>
+      <c r="AH32" s="207"/>
+      <c r="AI32" s="208"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="21"/>
-      <c r="B33" s="164"/>
-      <c r="C33" s="165"/>
-      <c r="D33" s="166"/>
-      <c r="E33" s="167"/>
-      <c r="F33" s="168"/>
-      <c r="G33" s="164"/>
-      <c r="H33" s="169"/>
-      <c r="I33" s="165"/>
-      <c r="J33" s="170"/>
-      <c r="K33" s="171"/>
-      <c r="L33" s="171"/>
-      <c r="M33" s="171"/>
-      <c r="N33" s="171"/>
-      <c r="O33" s="171"/>
-      <c r="P33" s="172"/>
-      <c r="Q33" s="173"/>
-      <c r="R33" s="174"/>
-      <c r="S33" s="174"/>
-      <c r="T33" s="174"/>
-      <c r="U33" s="174"/>
-      <c r="V33" s="174"/>
-      <c r="W33" s="174"/>
-      <c r="X33" s="174"/>
-      <c r="Y33" s="174"/>
-      <c r="Z33" s="174"/>
-      <c r="AA33" s="174"/>
-      <c r="AB33" s="174"/>
-      <c r="AC33" s="174"/>
-      <c r="AD33" s="174"/>
-      <c r="AE33" s="175"/>
-      <c r="AF33" s="170"/>
-      <c r="AG33" s="171"/>
-      <c r="AH33" s="171"/>
-      <c r="AI33" s="172"/>
+      <c r="B33" s="200"/>
+      <c r="C33" s="201"/>
+      <c r="D33" s="202"/>
+      <c r="E33" s="203"/>
+      <c r="F33" s="204"/>
+      <c r="G33" s="200"/>
+      <c r="H33" s="205"/>
+      <c r="I33" s="201"/>
+      <c r="J33" s="211"/>
+      <c r="K33" s="207"/>
+      <c r="L33" s="207"/>
+      <c r="M33" s="207"/>
+      <c r="N33" s="207"/>
+      <c r="O33" s="207"/>
+      <c r="P33" s="208"/>
+      <c r="Q33" s="206"/>
+      <c r="R33" s="209"/>
+      <c r="S33" s="209"/>
+      <c r="T33" s="209"/>
+      <c r="U33" s="209"/>
+      <c r="V33" s="209"/>
+      <c r="W33" s="209"/>
+      <c r="X33" s="209"/>
+      <c r="Y33" s="209"/>
+      <c r="Z33" s="209"/>
+      <c r="AA33" s="209"/>
+      <c r="AB33" s="209"/>
+      <c r="AC33" s="209"/>
+      <c r="AD33" s="209"/>
+      <c r="AE33" s="210"/>
+      <c r="AF33" s="211"/>
+      <c r="AG33" s="207"/>
+      <c r="AH33" s="207"/>
+      <c r="AI33" s="208"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -15456,161 +15611,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -38668,7 +38668,7 @@
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C11)&gt;0)*ROW($C$11:C11),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D11),
 _xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
-_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0)),
+_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H11),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -38716,7 +38716,7 @@
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C12)&gt;0)*ROW($C$11:C12),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D12),
 _xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
-_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0)),
+_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H12),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -38754,7 +38754,7 @@
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C13)&gt;0)*ROW($C$11:C13),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D13),
 _xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
-_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D13)&gt;0)*ROW($D$11:D13),0)),
+_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D13)&gt;0)*ROW($D$11:D13),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H13),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -38798,7 +38798,7 @@
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C14)&gt;0)*ROW($C$11:C14),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D14),
 _xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
-_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D14)&gt;0)*ROW($D$11:D14),0)),
+_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D14)&gt;0)*ROW($D$11:D14),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H14),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -38836,7 +38836,7 @@
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C15)&gt;0)*ROW($C$11:C15),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D15),
 _xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
-_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D15)&gt;0)*ROW($D$11:D15),0)),
+_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D15)&gt;0)*ROW($D$11:D15),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H15),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(バッチ)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(バッチ)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E42944C-2EAF-4AB2-BE55-38A9F0E9A7AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676F63A6-511A-4325-B4C1-98BA5FA542C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="619" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,19 +11,19 @@
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
     <sheet name="XxxAction_クラス単体" sheetId="25" r:id="rId3"/>
-    <sheet name="RBxxxxxxxx_リクエスト単体" sheetId="26" r:id="rId4"/>
+    <sheet name="XxxAction_リクエスト単体" sheetId="26" r:id="rId4"/>
     <sheet name="取引単体" sheetId="17" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RBxxxxxxxx_リクエスト単体!$A$10:$R$329</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">XxxAction_クラス単体!$A$10:$R$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">RBxxxxxxxx_リクエスト単体!$A$1:$R$329</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">XxxAction_リクエスト単体!$A$10:$R$329</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">XxxAction_クラス単体!$A$1:$R$304</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">XxxAction_リクエスト単体!$A$1:$R$329</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$P$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">RBxxxxxxxx_リクエスト単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">XxxAction_クラス単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">XxxAction_リクエスト単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1892" uniqueCount="643">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1893" uniqueCount="643">
   <si>
     <t>正常取引</t>
     <rPh sb="0" eb="2">
@@ -8914,9 +8914,9 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>テストターゲット名：RBxxxxxxxx</t>
-    <rPh sb="8" eb="9">
-      <t>メイ</t>
+    <t>バッチ処理ID：XXX</t>
+    <rPh sb="3" eb="5">
+      <t>ショリ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -26593,7 +26593,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="28" t="s">
-        <v>642</v>
+        <v>577</v>
       </c>
       <c r="O7" s="28" t="s">
         <v>23</v>
@@ -26603,7 +26603,9 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="11.5" thickBot="1">
-      <c r="A8" s="30"/>
+      <c r="A8" s="30" t="s">
+        <v>642</v>
+      </c>
       <c r="B8" s="30"/>
       <c r="C8" s="30"/>
       <c r="D8" s="31"/>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(バッチ)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(バッチ)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{676F63A6-511A-4325-B4C1-98BA5FA542C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC8F6337-0531-45D1-A70C-D961653051D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="619" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,19 +11,19 @@
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
     <sheet name="XxxAction_クラス単体" sheetId="25" r:id="rId3"/>
-    <sheet name="XxxAction_リクエスト単体" sheetId="26" r:id="rId4"/>
+    <sheet name="XXX_リクエスト単体" sheetId="26" r:id="rId4"/>
     <sheet name="取引単体" sheetId="17" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">XXX_リクエスト単体!$A$10:$R$329</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">XxxAction_クラス単体!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">XxxAction_リクエスト単体!$A$10:$R$329</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">XXX_リクエスト単体!$A$1:$R$329</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">XxxAction_クラス単体!$A$1:$R$304</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">XxxAction_リクエスト単体!$A$1:$R$329</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$P$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">XXX_リクエスト単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">XxxAction_クラス単体!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">XxxAction_リクエスト単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
@@ -8914,10 +8914,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>バッチ処理ID：XXX</t>
-    <rPh sb="3" eb="5">
-      <t>ショリ</t>
-    </rPh>
+    <t>リクエストID：XXX</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -9861,6 +9858,72 @@
     <xf numFmtId="31" fontId="13" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="6" fillId="0" borderId="10" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -9967,72 +10030,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="21" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -14204,57 +14201,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="192" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="173" t="s">
+      <c r="B1" s="193"/>
+      <c r="C1" s="193"/>
+      <c r="D1" s="194"/>
+      <c r="E1" s="195" t="s">
         <v>83</v>
       </c>
-      <c r="F1" s="174"/>
-      <c r="G1" s="174"/>
-      <c r="H1" s="174"/>
-      <c r="I1" s="174"/>
-      <c r="J1" s="174"/>
-      <c r="K1" s="174"/>
-      <c r="L1" s="174"/>
-      <c r="M1" s="174"/>
-      <c r="N1" s="175"/>
-      <c r="O1" s="179" t="s">
+      <c r="F1" s="196"/>
+      <c r="G1" s="196"/>
+      <c r="H1" s="196"/>
+      <c r="I1" s="196"/>
+      <c r="J1" s="196"/>
+      <c r="K1" s="196"/>
+      <c r="L1" s="196"/>
+      <c r="M1" s="196"/>
+      <c r="N1" s="197"/>
+      <c r="O1" s="201" t="s">
         <v>64</v>
       </c>
-      <c r="P1" s="180"/>
-      <c r="Q1" s="180"/>
-      <c r="R1" s="181"/>
-      <c r="S1" s="188" t="s">
+      <c r="P1" s="202"/>
+      <c r="Q1" s="202"/>
+      <c r="R1" s="203"/>
+      <c r="S1" s="210" t="s">
         <v>641</v>
       </c>
-      <c r="T1" s="189"/>
-      <c r="U1" s="189"/>
-      <c r="V1" s="189"/>
-      <c r="W1" s="189"/>
-      <c r="X1" s="189"/>
-      <c r="Y1" s="189"/>
-      <c r="Z1" s="190"/>
-      <c r="AA1" s="170" t="s">
+      <c r="T1" s="211"/>
+      <c r="U1" s="211"/>
+      <c r="V1" s="211"/>
+      <c r="W1" s="211"/>
+      <c r="X1" s="211"/>
+      <c r="Y1" s="211"/>
+      <c r="Z1" s="212"/>
+      <c r="AA1" s="192" t="s">
         <v>65</v>
       </c>
-      <c r="AB1" s="172"/>
-      <c r="AC1" s="197" t="str">
+      <c r="AB1" s="194"/>
+      <c r="AC1" s="219" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="198"/>
-      <c r="AE1" s="198"/>
-      <c r="AF1" s="199"/>
-      <c r="AG1" s="164">
+      <c r="AD1" s="220"/>
+      <c r="AE1" s="220"/>
+      <c r="AF1" s="221"/>
+      <c r="AG1" s="186">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="165"/>
-      <c r="AI1" s="166"/>
+      <c r="AH1" s="187"/>
+      <c r="AI1" s="188"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -14262,53 +14259,53 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="170" t="s">
+      <c r="A2" s="192" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="171"/>
-      <c r="C2" s="171"/>
-      <c r="D2" s="172"/>
-      <c r="E2" s="173" t="s">
+      <c r="B2" s="193"/>
+      <c r="C2" s="193"/>
+      <c r="D2" s="194"/>
+      <c r="E2" s="195" t="s">
         <v>84</v>
       </c>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
-      <c r="J2" s="174"/>
-      <c r="K2" s="174"/>
-      <c r="L2" s="174"/>
-      <c r="M2" s="174"/>
-      <c r="N2" s="175"/>
-      <c r="O2" s="182"/>
-      <c r="P2" s="183"/>
-      <c r="Q2" s="183"/>
-      <c r="R2" s="184"/>
-      <c r="S2" s="191"/>
-      <c r="T2" s="192"/>
-      <c r="U2" s="192"/>
-      <c r="V2" s="192"/>
-      <c r="W2" s="192"/>
-      <c r="X2" s="192"/>
-      <c r="Y2" s="192"/>
-      <c r="Z2" s="193"/>
-      <c r="AA2" s="170" t="s">
+      <c r="F2" s="196"/>
+      <c r="G2" s="196"/>
+      <c r="H2" s="196"/>
+      <c r="I2" s="196"/>
+      <c r="J2" s="196"/>
+      <c r="K2" s="196"/>
+      <c r="L2" s="196"/>
+      <c r="M2" s="196"/>
+      <c r="N2" s="197"/>
+      <c r="O2" s="204"/>
+      <c r="P2" s="205"/>
+      <c r="Q2" s="205"/>
+      <c r="R2" s="206"/>
+      <c r="S2" s="213"/>
+      <c r="T2" s="214"/>
+      <c r="U2" s="214"/>
+      <c r="V2" s="214"/>
+      <c r="W2" s="214"/>
+      <c r="X2" s="214"/>
+      <c r="Y2" s="214"/>
+      <c r="Z2" s="215"/>
+      <c r="AA2" s="192" t="s">
         <v>67</v>
       </c>
-      <c r="AB2" s="172"/>
-      <c r="AC2" s="176" t="str">
+      <c r="AB2" s="194"/>
+      <c r="AC2" s="198" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="177"/>
-      <c r="AE2" s="177"/>
-      <c r="AF2" s="178"/>
-      <c r="AG2" s="164">
+      <c r="AD2" s="199"/>
+      <c r="AE2" s="199"/>
+      <c r="AF2" s="200"/>
+      <c r="AG2" s="186">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44852</v>
       </c>
-      <c r="AH2" s="165"/>
-      <c r="AI2" s="166"/>
+      <c r="AH2" s="187"/>
+      <c r="AI2" s="188"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -14316,45 +14313,45 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="170" t="s">
+      <c r="A3" s="192" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="171"/>
-      <c r="C3" s="171"/>
-      <c r="D3" s="172"/>
-      <c r="E3" s="173" t="s">
+      <c r="B3" s="193"/>
+      <c r="C3" s="193"/>
+      <c r="D3" s="194"/>
+      <c r="E3" s="195" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="174"/>
-      <c r="G3" s="174"/>
-      <c r="H3" s="174"/>
-      <c r="I3" s="174"/>
-      <c r="J3" s="174"/>
-      <c r="K3" s="174"/>
-      <c r="L3" s="174"/>
-      <c r="M3" s="174"/>
-      <c r="N3" s="175"/>
-      <c r="O3" s="185"/>
-      <c r="P3" s="186"/>
-      <c r="Q3" s="186"/>
-      <c r="R3" s="187"/>
-      <c r="S3" s="194"/>
-      <c r="T3" s="195"/>
-      <c r="U3" s="195"/>
-      <c r="V3" s="195"/>
-      <c r="W3" s="195"/>
-      <c r="X3" s="195"/>
-      <c r="Y3" s="195"/>
-      <c r="Z3" s="196"/>
-      <c r="AA3" s="170"/>
-      <c r="AB3" s="172"/>
-      <c r="AC3" s="197"/>
-      <c r="AD3" s="198"/>
-      <c r="AE3" s="198"/>
-      <c r="AF3" s="199"/>
-      <c r="AG3" s="164"/>
-      <c r="AH3" s="165"/>
-      <c r="AI3" s="166"/>
+      <c r="F3" s="196"/>
+      <c r="G3" s="196"/>
+      <c r="H3" s="196"/>
+      <c r="I3" s="196"/>
+      <c r="J3" s="196"/>
+      <c r="K3" s="196"/>
+      <c r="L3" s="196"/>
+      <c r="M3" s="196"/>
+      <c r="N3" s="197"/>
+      <c r="O3" s="207"/>
+      <c r="P3" s="208"/>
+      <c r="Q3" s="208"/>
+      <c r="R3" s="209"/>
+      <c r="S3" s="216"/>
+      <c r="T3" s="217"/>
+      <c r="U3" s="217"/>
+      <c r="V3" s="217"/>
+      <c r="W3" s="217"/>
+      <c r="X3" s="217"/>
+      <c r="Y3" s="217"/>
+      <c r="Z3" s="218"/>
+      <c r="AA3" s="192"/>
+      <c r="AB3" s="194"/>
+      <c r="AC3" s="219"/>
+      <c r="AD3" s="220"/>
+      <c r="AE3" s="220"/>
+      <c r="AF3" s="221"/>
+      <c r="AG3" s="186"/>
+      <c r="AH3" s="187"/>
+      <c r="AI3" s="188"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -14391,97 +14388,97 @@
       <c r="A7" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="167" t="s">
+      <c r="B7" s="189" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="168"/>
-      <c r="D7" s="167" t="s">
+      <c r="C7" s="190"/>
+      <c r="D7" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="E7" s="169"/>
-      <c r="F7" s="168"/>
-      <c r="G7" s="167" t="s">
+      <c r="E7" s="191"/>
+      <c r="F7" s="190"/>
+      <c r="G7" s="189" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="169"/>
-      <c r="I7" s="168"/>
-      <c r="J7" s="167" t="s">
+      <c r="H7" s="191"/>
+      <c r="I7" s="190"/>
+      <c r="J7" s="189" t="s">
         <v>73</v>
       </c>
-      <c r="K7" s="169"/>
-      <c r="L7" s="169"/>
-      <c r="M7" s="169"/>
-      <c r="N7" s="169"/>
-      <c r="O7" s="169"/>
-      <c r="P7" s="168"/>
-      <c r="Q7" s="167" t="s">
+      <c r="K7" s="191"/>
+      <c r="L7" s="191"/>
+      <c r="M7" s="191"/>
+      <c r="N7" s="191"/>
+      <c r="O7" s="191"/>
+      <c r="P7" s="190"/>
+      <c r="Q7" s="189" t="s">
         <v>74</v>
       </c>
-      <c r="R7" s="169"/>
-      <c r="S7" s="169"/>
-      <c r="T7" s="169"/>
-      <c r="U7" s="169"/>
-      <c r="V7" s="169"/>
-      <c r="W7" s="169"/>
-      <c r="X7" s="169"/>
-      <c r="Y7" s="169"/>
-      <c r="Z7" s="169"/>
-      <c r="AA7" s="169"/>
-      <c r="AB7" s="169"/>
-      <c r="AC7" s="169"/>
-      <c r="AD7" s="169"/>
-      <c r="AE7" s="168"/>
-      <c r="AF7" s="167" t="s">
+      <c r="R7" s="191"/>
+      <c r="S7" s="191"/>
+      <c r="T7" s="191"/>
+      <c r="U7" s="191"/>
+      <c r="V7" s="191"/>
+      <c r="W7" s="191"/>
+      <c r="X7" s="191"/>
+      <c r="Y7" s="191"/>
+      <c r="Z7" s="191"/>
+      <c r="AA7" s="191"/>
+      <c r="AB7" s="191"/>
+      <c r="AC7" s="191"/>
+      <c r="AD7" s="191"/>
+      <c r="AE7" s="190"/>
+      <c r="AF7" s="189" t="s">
         <v>75</v>
       </c>
-      <c r="AG7" s="169"/>
-      <c r="AH7" s="169"/>
-      <c r="AI7" s="168"/>
+      <c r="AG7" s="191"/>
+      <c r="AH7" s="191"/>
+      <c r="AI7" s="190"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="24">
         <v>1</v>
       </c>
-      <c r="B8" s="212" t="s">
+      <c r="B8" s="177" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="213"/>
-      <c r="D8" s="214">
+      <c r="C8" s="178"/>
+      <c r="D8" s="179">
         <v>43336</v>
       </c>
-      <c r="E8" s="215"/>
-      <c r="F8" s="216"/>
-      <c r="G8" s="212" t="s">
+      <c r="E8" s="180"/>
+      <c r="F8" s="181"/>
+      <c r="G8" s="177" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="217"/>
-      <c r="I8" s="213"/>
-      <c r="J8" s="218" t="s">
+      <c r="H8" s="182"/>
+      <c r="I8" s="178"/>
+      <c r="J8" s="183" t="s">
         <v>78</v>
       </c>
-      <c r="K8" s="219"/>
-      <c r="L8" s="219"/>
-      <c r="M8" s="219"/>
-      <c r="N8" s="219"/>
-      <c r="O8" s="219"/>
-      <c r="P8" s="220"/>
-      <c r="Q8" s="218" t="s">
+      <c r="K8" s="184"/>
+      <c r="L8" s="184"/>
+      <c r="M8" s="184"/>
+      <c r="N8" s="184"/>
+      <c r="O8" s="184"/>
+      <c r="P8" s="185"/>
+      <c r="Q8" s="183" t="s">
         <v>79</v>
       </c>
-      <c r="R8" s="219"/>
-      <c r="S8" s="219"/>
-      <c r="T8" s="219"/>
-      <c r="U8" s="219"/>
-      <c r="V8" s="219"/>
-      <c r="W8" s="219"/>
-      <c r="X8" s="219"/>
-      <c r="Y8" s="219"/>
-      <c r="Z8" s="219"/>
-      <c r="AA8" s="219"/>
-      <c r="AB8" s="219"/>
-      <c r="AC8" s="219"/>
-      <c r="AD8" s="219"/>
-      <c r="AE8" s="220"/>
+      <c r="R8" s="184"/>
+      <c r="S8" s="184"/>
+      <c r="T8" s="184"/>
+      <c r="U8" s="184"/>
+      <c r="V8" s="184"/>
+      <c r="W8" s="184"/>
+      <c r="X8" s="184"/>
+      <c r="Y8" s="184"/>
+      <c r="Z8" s="184"/>
+      <c r="AA8" s="184"/>
+      <c r="AB8" s="184"/>
+      <c r="AC8" s="184"/>
+      <c r="AD8" s="184"/>
+      <c r="AE8" s="185"/>
       <c r="AF8" s="25" t="s">
         <v>80</v>
       </c>
@@ -14493,1101 +14490,946 @@
       <c r="A9" s="24">
         <v>2</v>
       </c>
-      <c r="B9" s="200" t="s">
+      <c r="B9" s="164" t="s">
         <v>546</v>
       </c>
-      <c r="C9" s="201"/>
-      <c r="D9" s="202">
+      <c r="C9" s="165"/>
+      <c r="D9" s="166">
         <v>44852</v>
       </c>
-      <c r="E9" s="203"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="202" t="s">
+      <c r="E9" s="167"/>
+      <c r="F9" s="168"/>
+      <c r="G9" s="166" t="s">
         <v>547</v>
       </c>
-      <c r="H9" s="205"/>
-      <c r="I9" s="201"/>
-      <c r="J9" s="206" t="s">
+      <c r="H9" s="169"/>
+      <c r="I9" s="165"/>
+      <c r="J9" s="173" t="s">
         <v>549</v>
       </c>
-      <c r="K9" s="207"/>
-      <c r="L9" s="207"/>
-      <c r="M9" s="207"/>
-      <c r="N9" s="207"/>
-      <c r="O9" s="207"/>
-      <c r="P9" s="208"/>
-      <c r="Q9" s="206" t="s">
+      <c r="K9" s="171"/>
+      <c r="L9" s="171"/>
+      <c r="M9" s="171"/>
+      <c r="N9" s="171"/>
+      <c r="O9" s="171"/>
+      <c r="P9" s="172"/>
+      <c r="Q9" s="173" t="s">
         <v>548</v>
       </c>
-      <c r="R9" s="209"/>
-      <c r="S9" s="209"/>
-      <c r="T9" s="209"/>
-      <c r="U9" s="209"/>
-      <c r="V9" s="209"/>
-      <c r="W9" s="209"/>
-      <c r="X9" s="209"/>
-      <c r="Y9" s="209"/>
-      <c r="Z9" s="209"/>
-      <c r="AA9" s="209"/>
-      <c r="AB9" s="209"/>
-      <c r="AC9" s="209"/>
-      <c r="AD9" s="209"/>
-      <c r="AE9" s="210"/>
-      <c r="AF9" s="211" t="s">
+      <c r="R9" s="174"/>
+      <c r="S9" s="174"/>
+      <c r="T9" s="174"/>
+      <c r="U9" s="174"/>
+      <c r="V9" s="174"/>
+      <c r="W9" s="174"/>
+      <c r="X9" s="174"/>
+      <c r="Y9" s="174"/>
+      <c r="Z9" s="174"/>
+      <c r="AA9" s="174"/>
+      <c r="AB9" s="174"/>
+      <c r="AC9" s="174"/>
+      <c r="AD9" s="174"/>
+      <c r="AE9" s="175"/>
+      <c r="AF9" s="170" t="s">
         <v>80</v>
       </c>
-      <c r="AG9" s="207"/>
-      <c r="AH9" s="207"/>
-      <c r="AI9" s="208"/>
+      <c r="AG9" s="171"/>
+      <c r="AH9" s="171"/>
+      <c r="AI9" s="172"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="21"/>
-      <c r="B10" s="200"/>
-      <c r="C10" s="201"/>
-      <c r="D10" s="202"/>
-      <c r="E10" s="203"/>
-      <c r="F10" s="204"/>
-      <c r="G10" s="200"/>
-      <c r="H10" s="205"/>
-      <c r="I10" s="201"/>
-      <c r="J10" s="211"/>
-      <c r="K10" s="207"/>
-      <c r="L10" s="207"/>
-      <c r="M10" s="207"/>
-      <c r="N10" s="207"/>
-      <c r="O10" s="207"/>
-      <c r="P10" s="208"/>
-      <c r="Q10" s="206"/>
-      <c r="R10" s="209"/>
-      <c r="S10" s="209"/>
-      <c r="T10" s="209"/>
-      <c r="U10" s="209"/>
-      <c r="V10" s="209"/>
-      <c r="W10" s="209"/>
-      <c r="X10" s="209"/>
-      <c r="Y10" s="209"/>
-      <c r="Z10" s="209"/>
-      <c r="AA10" s="209"/>
-      <c r="AB10" s="209"/>
-      <c r="AC10" s="209"/>
-      <c r="AD10" s="209"/>
-      <c r="AE10" s="210"/>
-      <c r="AF10" s="211"/>
-      <c r="AG10" s="207"/>
-      <c r="AH10" s="207"/>
-      <c r="AI10" s="208"/>
+      <c r="B10" s="164"/>
+      <c r="C10" s="165"/>
+      <c r="D10" s="166"/>
+      <c r="E10" s="167"/>
+      <c r="F10" s="168"/>
+      <c r="G10" s="164"/>
+      <c r="H10" s="169"/>
+      <c r="I10" s="165"/>
+      <c r="J10" s="170"/>
+      <c r="K10" s="171"/>
+      <c r="L10" s="171"/>
+      <c r="M10" s="171"/>
+      <c r="N10" s="171"/>
+      <c r="O10" s="171"/>
+      <c r="P10" s="172"/>
+      <c r="Q10" s="173"/>
+      <c r="R10" s="174"/>
+      <c r="S10" s="174"/>
+      <c r="T10" s="174"/>
+      <c r="U10" s="174"/>
+      <c r="V10" s="174"/>
+      <c r="W10" s="174"/>
+      <c r="X10" s="174"/>
+      <c r="Y10" s="174"/>
+      <c r="Z10" s="174"/>
+      <c r="AA10" s="174"/>
+      <c r="AB10" s="174"/>
+      <c r="AC10" s="174"/>
+      <c r="AD10" s="174"/>
+      <c r="AE10" s="175"/>
+      <c r="AF10" s="170"/>
+      <c r="AG10" s="171"/>
+      <c r="AH10" s="171"/>
+      <c r="AI10" s="172"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="21"/>
-      <c r="B11" s="200"/>
-      <c r="C11" s="201"/>
-      <c r="D11" s="202"/>
-      <c r="E11" s="203"/>
-      <c r="F11" s="204"/>
-      <c r="G11" s="200"/>
-      <c r="H11" s="205"/>
-      <c r="I11" s="201"/>
-      <c r="J11" s="211"/>
-      <c r="K11" s="207"/>
-      <c r="L11" s="207"/>
-      <c r="M11" s="207"/>
-      <c r="N11" s="207"/>
-      <c r="O11" s="207"/>
-      <c r="P11" s="208"/>
-      <c r="Q11" s="206"/>
-      <c r="R11" s="209"/>
-      <c r="S11" s="209"/>
-      <c r="T11" s="209"/>
-      <c r="U11" s="209"/>
-      <c r="V11" s="209"/>
-      <c r="W11" s="209"/>
-      <c r="X11" s="209"/>
-      <c r="Y11" s="209"/>
-      <c r="Z11" s="209"/>
-      <c r="AA11" s="209"/>
-      <c r="AB11" s="209"/>
-      <c r="AC11" s="209"/>
-      <c r="AD11" s="209"/>
-      <c r="AE11" s="210"/>
-      <c r="AF11" s="211"/>
-      <c r="AG11" s="207"/>
-      <c r="AH11" s="207"/>
-      <c r="AI11" s="208"/>
+      <c r="B11" s="164"/>
+      <c r="C11" s="165"/>
+      <c r="D11" s="166"/>
+      <c r="E11" s="167"/>
+      <c r="F11" s="168"/>
+      <c r="G11" s="164"/>
+      <c r="H11" s="169"/>
+      <c r="I11" s="165"/>
+      <c r="J11" s="170"/>
+      <c r="K11" s="171"/>
+      <c r="L11" s="171"/>
+      <c r="M11" s="171"/>
+      <c r="N11" s="171"/>
+      <c r="O11" s="171"/>
+      <c r="P11" s="172"/>
+      <c r="Q11" s="173"/>
+      <c r="R11" s="174"/>
+      <c r="S11" s="174"/>
+      <c r="T11" s="174"/>
+      <c r="U11" s="174"/>
+      <c r="V11" s="174"/>
+      <c r="W11" s="174"/>
+      <c r="X11" s="174"/>
+      <c r="Y11" s="174"/>
+      <c r="Z11" s="174"/>
+      <c r="AA11" s="174"/>
+      <c r="AB11" s="174"/>
+      <c r="AC11" s="174"/>
+      <c r="AD11" s="174"/>
+      <c r="AE11" s="175"/>
+      <c r="AF11" s="170"/>
+      <c r="AG11" s="171"/>
+      <c r="AH11" s="171"/>
+      <c r="AI11" s="172"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="21"/>
-      <c r="B12" s="200"/>
-      <c r="C12" s="201"/>
-      <c r="D12" s="202"/>
-      <c r="E12" s="203"/>
-      <c r="F12" s="204"/>
-      <c r="G12" s="200"/>
-      <c r="H12" s="205"/>
-      <c r="I12" s="201"/>
-      <c r="J12" s="211"/>
-      <c r="K12" s="207"/>
-      <c r="L12" s="207"/>
-      <c r="M12" s="207"/>
-      <c r="N12" s="207"/>
-      <c r="O12" s="207"/>
-      <c r="P12" s="208"/>
-      <c r="Q12" s="206"/>
-      <c r="R12" s="209"/>
-      <c r="S12" s="209"/>
-      <c r="T12" s="209"/>
-      <c r="U12" s="209"/>
-      <c r="V12" s="209"/>
-      <c r="W12" s="209"/>
-      <c r="X12" s="209"/>
-      <c r="Y12" s="209"/>
-      <c r="Z12" s="209"/>
-      <c r="AA12" s="209"/>
-      <c r="AB12" s="209"/>
-      <c r="AC12" s="209"/>
-      <c r="AD12" s="209"/>
-      <c r="AE12" s="210"/>
-      <c r="AF12" s="211"/>
-      <c r="AG12" s="207"/>
-      <c r="AH12" s="207"/>
-      <c r="AI12" s="208"/>
+      <c r="B12" s="164"/>
+      <c r="C12" s="165"/>
+      <c r="D12" s="166"/>
+      <c r="E12" s="167"/>
+      <c r="F12" s="168"/>
+      <c r="G12" s="164"/>
+      <c r="H12" s="169"/>
+      <c r="I12" s="165"/>
+      <c r="J12" s="170"/>
+      <c r="K12" s="171"/>
+      <c r="L12" s="171"/>
+      <c r="M12" s="171"/>
+      <c r="N12" s="171"/>
+      <c r="O12" s="171"/>
+      <c r="P12" s="172"/>
+      <c r="Q12" s="173"/>
+      <c r="R12" s="174"/>
+      <c r="S12" s="174"/>
+      <c r="T12" s="174"/>
+      <c r="U12" s="174"/>
+      <c r="V12" s="174"/>
+      <c r="W12" s="174"/>
+      <c r="X12" s="174"/>
+      <c r="Y12" s="174"/>
+      <c r="Z12" s="174"/>
+      <c r="AA12" s="174"/>
+      <c r="AB12" s="174"/>
+      <c r="AC12" s="174"/>
+      <c r="AD12" s="174"/>
+      <c r="AE12" s="175"/>
+      <c r="AF12" s="170"/>
+      <c r="AG12" s="171"/>
+      <c r="AH12" s="171"/>
+      <c r="AI12" s="172"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="21"/>
-      <c r="B13" s="200"/>
-      <c r="C13" s="201"/>
-      <c r="D13" s="202"/>
-      <c r="E13" s="203"/>
-      <c r="F13" s="204"/>
-      <c r="G13" s="200"/>
-      <c r="H13" s="205"/>
-      <c r="I13" s="201"/>
-      <c r="J13" s="211"/>
-      <c r="K13" s="207"/>
-      <c r="L13" s="207"/>
-      <c r="M13" s="207"/>
-      <c r="N13" s="207"/>
-      <c r="O13" s="207"/>
-      <c r="P13" s="208"/>
-      <c r="Q13" s="206"/>
-      <c r="R13" s="209"/>
-      <c r="S13" s="209"/>
-      <c r="T13" s="209"/>
-      <c r="U13" s="209"/>
-      <c r="V13" s="209"/>
-      <c r="W13" s="209"/>
-      <c r="X13" s="209"/>
-      <c r="Y13" s="209"/>
-      <c r="Z13" s="209"/>
-      <c r="AA13" s="209"/>
-      <c r="AB13" s="209"/>
-      <c r="AC13" s="209"/>
-      <c r="AD13" s="209"/>
-      <c r="AE13" s="210"/>
-      <c r="AF13" s="211"/>
-      <c r="AG13" s="207"/>
-      <c r="AH13" s="207"/>
-      <c r="AI13" s="208"/>
+      <c r="B13" s="164"/>
+      <c r="C13" s="165"/>
+      <c r="D13" s="166"/>
+      <c r="E13" s="167"/>
+      <c r="F13" s="168"/>
+      <c r="G13" s="164"/>
+      <c r="H13" s="169"/>
+      <c r="I13" s="165"/>
+      <c r="J13" s="170"/>
+      <c r="K13" s="171"/>
+      <c r="L13" s="171"/>
+      <c r="M13" s="171"/>
+      <c r="N13" s="171"/>
+      <c r="O13" s="171"/>
+      <c r="P13" s="172"/>
+      <c r="Q13" s="173"/>
+      <c r="R13" s="174"/>
+      <c r="S13" s="174"/>
+      <c r="T13" s="174"/>
+      <c r="U13" s="174"/>
+      <c r="V13" s="174"/>
+      <c r="W13" s="174"/>
+      <c r="X13" s="174"/>
+      <c r="Y13" s="174"/>
+      <c r="Z13" s="174"/>
+      <c r="AA13" s="174"/>
+      <c r="AB13" s="174"/>
+      <c r="AC13" s="174"/>
+      <c r="AD13" s="174"/>
+      <c r="AE13" s="175"/>
+      <c r="AF13" s="170"/>
+      <c r="AG13" s="171"/>
+      <c r="AH13" s="171"/>
+      <c r="AI13" s="172"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="200"/>
-      <c r="C14" s="201"/>
-      <c r="D14" s="202"/>
-      <c r="E14" s="203"/>
-      <c r="F14" s="204"/>
-      <c r="G14" s="200"/>
-      <c r="H14" s="205"/>
-      <c r="I14" s="201"/>
-      <c r="J14" s="211"/>
-      <c r="K14" s="207"/>
-      <c r="L14" s="207"/>
-      <c r="M14" s="207"/>
-      <c r="N14" s="207"/>
-      <c r="O14" s="207"/>
-      <c r="P14" s="208"/>
-      <c r="Q14" s="206"/>
-      <c r="R14" s="209"/>
-      <c r="S14" s="209"/>
-      <c r="T14" s="209"/>
-      <c r="U14" s="209"/>
-      <c r="V14" s="209"/>
-      <c r="W14" s="209"/>
-      <c r="X14" s="209"/>
-      <c r="Y14" s="209"/>
-      <c r="Z14" s="209"/>
-      <c r="AA14" s="209"/>
-      <c r="AB14" s="209"/>
-      <c r="AC14" s="209"/>
-      <c r="AD14" s="209"/>
-      <c r="AE14" s="210"/>
-      <c r="AF14" s="211"/>
-      <c r="AG14" s="207"/>
-      <c r="AH14" s="207"/>
-      <c r="AI14" s="208"/>
+      <c r="B14" s="164"/>
+      <c r="C14" s="165"/>
+      <c r="D14" s="166"/>
+      <c r="E14" s="167"/>
+      <c r="F14" s="168"/>
+      <c r="G14" s="164"/>
+      <c r="H14" s="169"/>
+      <c r="I14" s="165"/>
+      <c r="J14" s="170"/>
+      <c r="K14" s="171"/>
+      <c r="L14" s="171"/>
+      <c r="M14" s="171"/>
+      <c r="N14" s="171"/>
+      <c r="O14" s="171"/>
+      <c r="P14" s="172"/>
+      <c r="Q14" s="173"/>
+      <c r="R14" s="174"/>
+      <c r="S14" s="174"/>
+      <c r="T14" s="174"/>
+      <c r="U14" s="174"/>
+      <c r="V14" s="174"/>
+      <c r="W14" s="174"/>
+      <c r="X14" s="174"/>
+      <c r="Y14" s="174"/>
+      <c r="Z14" s="174"/>
+      <c r="AA14" s="174"/>
+      <c r="AB14" s="174"/>
+      <c r="AC14" s="174"/>
+      <c r="AD14" s="174"/>
+      <c r="AE14" s="175"/>
+      <c r="AF14" s="170"/>
+      <c r="AG14" s="171"/>
+      <c r="AH14" s="171"/>
+      <c r="AI14" s="172"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="21"/>
-      <c r="B15" s="200"/>
-      <c r="C15" s="201"/>
-      <c r="D15" s="202"/>
-      <c r="E15" s="203"/>
-      <c r="F15" s="204"/>
-      <c r="G15" s="200"/>
-      <c r="H15" s="205"/>
-      <c r="I15" s="201"/>
-      <c r="J15" s="211"/>
-      <c r="K15" s="207"/>
-      <c r="L15" s="207"/>
-      <c r="M15" s="207"/>
-      <c r="N15" s="207"/>
-      <c r="O15" s="207"/>
-      <c r="P15" s="208"/>
-      <c r="Q15" s="206"/>
-      <c r="R15" s="209"/>
-      <c r="S15" s="209"/>
-      <c r="T15" s="209"/>
-      <c r="U15" s="209"/>
-      <c r="V15" s="209"/>
-      <c r="W15" s="209"/>
-      <c r="X15" s="209"/>
-      <c r="Y15" s="209"/>
-      <c r="Z15" s="209"/>
-      <c r="AA15" s="209"/>
-      <c r="AB15" s="209"/>
-      <c r="AC15" s="209"/>
-      <c r="AD15" s="209"/>
-      <c r="AE15" s="210"/>
-      <c r="AF15" s="211"/>
-      <c r="AG15" s="207"/>
-      <c r="AH15" s="207"/>
-      <c r="AI15" s="208"/>
+      <c r="B15" s="164"/>
+      <c r="C15" s="165"/>
+      <c r="D15" s="166"/>
+      <c r="E15" s="167"/>
+      <c r="F15" s="168"/>
+      <c r="G15" s="164"/>
+      <c r="H15" s="169"/>
+      <c r="I15" s="165"/>
+      <c r="J15" s="170"/>
+      <c r="K15" s="171"/>
+      <c r="L15" s="171"/>
+      <c r="M15" s="171"/>
+      <c r="N15" s="171"/>
+      <c r="O15" s="171"/>
+      <c r="P15" s="172"/>
+      <c r="Q15" s="173"/>
+      <c r="R15" s="174"/>
+      <c r="S15" s="174"/>
+      <c r="T15" s="174"/>
+      <c r="U15" s="174"/>
+      <c r="V15" s="174"/>
+      <c r="W15" s="174"/>
+      <c r="X15" s="174"/>
+      <c r="Y15" s="174"/>
+      <c r="Z15" s="174"/>
+      <c r="AA15" s="174"/>
+      <c r="AB15" s="174"/>
+      <c r="AC15" s="174"/>
+      <c r="AD15" s="174"/>
+      <c r="AE15" s="175"/>
+      <c r="AF15" s="170"/>
+      <c r="AG15" s="171"/>
+      <c r="AH15" s="171"/>
+      <c r="AI15" s="172"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="21"/>
-      <c r="B16" s="200"/>
-      <c r="C16" s="201"/>
-      <c r="D16" s="202"/>
-      <c r="E16" s="203"/>
-      <c r="F16" s="204"/>
-      <c r="G16" s="200"/>
-      <c r="H16" s="205"/>
-      <c r="I16" s="201"/>
-      <c r="J16" s="211"/>
-      <c r="K16" s="207"/>
-      <c r="L16" s="207"/>
-      <c r="M16" s="207"/>
-      <c r="N16" s="207"/>
-      <c r="O16" s="207"/>
-      <c r="P16" s="208"/>
-      <c r="Q16" s="206"/>
-      <c r="R16" s="209"/>
-      <c r="S16" s="209"/>
-      <c r="T16" s="209"/>
-      <c r="U16" s="209"/>
-      <c r="V16" s="209"/>
-      <c r="W16" s="209"/>
-      <c r="X16" s="209"/>
-      <c r="Y16" s="209"/>
-      <c r="Z16" s="209"/>
-      <c r="AA16" s="209"/>
-      <c r="AB16" s="209"/>
-      <c r="AC16" s="209"/>
-      <c r="AD16" s="209"/>
-      <c r="AE16" s="210"/>
-      <c r="AF16" s="211"/>
-      <c r="AG16" s="207"/>
-      <c r="AH16" s="207"/>
-      <c r="AI16" s="208"/>
+      <c r="B16" s="164"/>
+      <c r="C16" s="165"/>
+      <c r="D16" s="166"/>
+      <c r="E16" s="167"/>
+      <c r="F16" s="168"/>
+      <c r="G16" s="164"/>
+      <c r="H16" s="169"/>
+      <c r="I16" s="165"/>
+      <c r="J16" s="170"/>
+      <c r="K16" s="171"/>
+      <c r="L16" s="171"/>
+      <c r="M16" s="171"/>
+      <c r="N16" s="171"/>
+      <c r="O16" s="171"/>
+      <c r="P16" s="172"/>
+      <c r="Q16" s="173"/>
+      <c r="R16" s="174"/>
+      <c r="S16" s="174"/>
+      <c r="T16" s="174"/>
+      <c r="U16" s="174"/>
+      <c r="V16" s="174"/>
+      <c r="W16" s="174"/>
+      <c r="X16" s="174"/>
+      <c r="Y16" s="174"/>
+      <c r="Z16" s="174"/>
+      <c r="AA16" s="174"/>
+      <c r="AB16" s="174"/>
+      <c r="AC16" s="174"/>
+      <c r="AD16" s="174"/>
+      <c r="AE16" s="175"/>
+      <c r="AF16" s="170"/>
+      <c r="AG16" s="171"/>
+      <c r="AH16" s="171"/>
+      <c r="AI16" s="172"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="21"/>
-      <c r="B17" s="200"/>
-      <c r="C17" s="201"/>
-      <c r="D17" s="202"/>
-      <c r="E17" s="203"/>
-      <c r="F17" s="204"/>
-      <c r="G17" s="200"/>
-      <c r="H17" s="205"/>
-      <c r="I17" s="201"/>
-      <c r="J17" s="211"/>
-      <c r="K17" s="207"/>
-      <c r="L17" s="207"/>
-      <c r="M17" s="207"/>
-      <c r="N17" s="207"/>
-      <c r="O17" s="207"/>
-      <c r="P17" s="208"/>
-      <c r="Q17" s="206"/>
-      <c r="R17" s="209"/>
-      <c r="S17" s="209"/>
-      <c r="T17" s="209"/>
-      <c r="U17" s="209"/>
-      <c r="V17" s="209"/>
-      <c r="W17" s="209"/>
-      <c r="X17" s="209"/>
-      <c r="Y17" s="209"/>
-      <c r="Z17" s="209"/>
-      <c r="AA17" s="209"/>
-      <c r="AB17" s="209"/>
-      <c r="AC17" s="209"/>
-      <c r="AD17" s="209"/>
-      <c r="AE17" s="210"/>
-      <c r="AF17" s="211"/>
-      <c r="AG17" s="207"/>
-      <c r="AH17" s="207"/>
-      <c r="AI17" s="208"/>
+      <c r="B17" s="164"/>
+      <c r="C17" s="165"/>
+      <c r="D17" s="166"/>
+      <c r="E17" s="167"/>
+      <c r="F17" s="168"/>
+      <c r="G17" s="164"/>
+      <c r="H17" s="169"/>
+      <c r="I17" s="165"/>
+      <c r="J17" s="170"/>
+      <c r="K17" s="171"/>
+      <c r="L17" s="171"/>
+      <c r="M17" s="171"/>
+      <c r="N17" s="171"/>
+      <c r="O17" s="171"/>
+      <c r="P17" s="172"/>
+      <c r="Q17" s="173"/>
+      <c r="R17" s="174"/>
+      <c r="S17" s="174"/>
+      <c r="T17" s="174"/>
+      <c r="U17" s="174"/>
+      <c r="V17" s="174"/>
+      <c r="W17" s="174"/>
+      <c r="X17" s="174"/>
+      <c r="Y17" s="174"/>
+      <c r="Z17" s="174"/>
+      <c r="AA17" s="174"/>
+      <c r="AB17" s="174"/>
+      <c r="AC17" s="174"/>
+      <c r="AD17" s="174"/>
+      <c r="AE17" s="175"/>
+      <c r="AF17" s="170"/>
+      <c r="AG17" s="171"/>
+      <c r="AH17" s="171"/>
+      <c r="AI17" s="172"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="21"/>
-      <c r="B18" s="200"/>
-      <c r="C18" s="201"/>
-      <c r="D18" s="202"/>
-      <c r="E18" s="203"/>
-      <c r="F18" s="204"/>
-      <c r="G18" s="200"/>
-      <c r="H18" s="205"/>
-      <c r="I18" s="201"/>
-      <c r="J18" s="211"/>
-      <c r="K18" s="207"/>
-      <c r="L18" s="207"/>
-      <c r="M18" s="207"/>
-      <c r="N18" s="207"/>
-      <c r="O18" s="207"/>
-      <c r="P18" s="208"/>
-      <c r="Q18" s="206"/>
-      <c r="R18" s="209"/>
-      <c r="S18" s="209"/>
-      <c r="T18" s="209"/>
-      <c r="U18" s="209"/>
-      <c r="V18" s="209"/>
-      <c r="W18" s="209"/>
-      <c r="X18" s="209"/>
-      <c r="Y18" s="209"/>
-      <c r="Z18" s="209"/>
-      <c r="AA18" s="209"/>
-      <c r="AB18" s="209"/>
-      <c r="AC18" s="209"/>
-      <c r="AD18" s="209"/>
-      <c r="AE18" s="210"/>
-      <c r="AF18" s="211"/>
-      <c r="AG18" s="207"/>
-      <c r="AH18" s="207"/>
-      <c r="AI18" s="208"/>
+      <c r="B18" s="164"/>
+      <c r="C18" s="165"/>
+      <c r="D18" s="166"/>
+      <c r="E18" s="167"/>
+      <c r="F18" s="168"/>
+      <c r="G18" s="164"/>
+      <c r="H18" s="169"/>
+      <c r="I18" s="165"/>
+      <c r="J18" s="170"/>
+      <c r="K18" s="171"/>
+      <c r="L18" s="171"/>
+      <c r="M18" s="171"/>
+      <c r="N18" s="171"/>
+      <c r="O18" s="171"/>
+      <c r="P18" s="172"/>
+      <c r="Q18" s="173"/>
+      <c r="R18" s="174"/>
+      <c r="S18" s="174"/>
+      <c r="T18" s="174"/>
+      <c r="U18" s="174"/>
+      <c r="V18" s="174"/>
+      <c r="W18" s="174"/>
+      <c r="X18" s="174"/>
+      <c r="Y18" s="174"/>
+      <c r="Z18" s="174"/>
+      <c r="AA18" s="174"/>
+      <c r="AB18" s="174"/>
+      <c r="AC18" s="174"/>
+      <c r="AD18" s="174"/>
+      <c r="AE18" s="175"/>
+      <c r="AF18" s="170"/>
+      <c r="AG18" s="171"/>
+      <c r="AH18" s="171"/>
+      <c r="AI18" s="172"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="21"/>
-      <c r="B19" s="200"/>
-      <c r="C19" s="201"/>
-      <c r="D19" s="202"/>
-      <c r="E19" s="203"/>
-      <c r="F19" s="204"/>
-      <c r="G19" s="200"/>
-      <c r="H19" s="205"/>
-      <c r="I19" s="201"/>
-      <c r="J19" s="211"/>
-      <c r="K19" s="207"/>
-      <c r="L19" s="207"/>
-      <c r="M19" s="207"/>
-      <c r="N19" s="207"/>
-      <c r="O19" s="207"/>
-      <c r="P19" s="208"/>
-      <c r="Q19" s="206"/>
-      <c r="R19" s="209"/>
-      <c r="S19" s="209"/>
-      <c r="T19" s="209"/>
-      <c r="U19" s="209"/>
-      <c r="V19" s="209"/>
-      <c r="W19" s="209"/>
-      <c r="X19" s="209"/>
-      <c r="Y19" s="209"/>
-      <c r="Z19" s="209"/>
-      <c r="AA19" s="209"/>
-      <c r="AB19" s="209"/>
-      <c r="AC19" s="209"/>
-      <c r="AD19" s="209"/>
-      <c r="AE19" s="210"/>
-      <c r="AF19" s="211"/>
-      <c r="AG19" s="207"/>
-      <c r="AH19" s="207"/>
-      <c r="AI19" s="208"/>
+      <c r="B19" s="164"/>
+      <c r="C19" s="165"/>
+      <c r="D19" s="166"/>
+      <c r="E19" s="167"/>
+      <c r="F19" s="168"/>
+      <c r="G19" s="164"/>
+      <c r="H19" s="169"/>
+      <c r="I19" s="165"/>
+      <c r="J19" s="170"/>
+      <c r="K19" s="171"/>
+      <c r="L19" s="171"/>
+      <c r="M19" s="171"/>
+      <c r="N19" s="171"/>
+      <c r="O19" s="171"/>
+      <c r="P19" s="172"/>
+      <c r="Q19" s="173"/>
+      <c r="R19" s="174"/>
+      <c r="S19" s="174"/>
+      <c r="T19" s="174"/>
+      <c r="U19" s="174"/>
+      <c r="V19" s="174"/>
+      <c r="W19" s="174"/>
+      <c r="X19" s="174"/>
+      <c r="Y19" s="174"/>
+      <c r="Z19" s="174"/>
+      <c r="AA19" s="174"/>
+      <c r="AB19" s="174"/>
+      <c r="AC19" s="174"/>
+      <c r="AD19" s="174"/>
+      <c r="AE19" s="175"/>
+      <c r="AF19" s="170"/>
+      <c r="AG19" s="171"/>
+      <c r="AH19" s="171"/>
+      <c r="AI19" s="172"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="21"/>
-      <c r="B20" s="200"/>
-      <c r="C20" s="201"/>
-      <c r="D20" s="202"/>
-      <c r="E20" s="203"/>
-      <c r="F20" s="204"/>
-      <c r="G20" s="200"/>
-      <c r="H20" s="205"/>
-      <c r="I20" s="201"/>
-      <c r="J20" s="211"/>
-      <c r="K20" s="207"/>
-      <c r="L20" s="207"/>
-      <c r="M20" s="207"/>
-      <c r="N20" s="207"/>
-      <c r="O20" s="207"/>
-      <c r="P20" s="208"/>
-      <c r="Q20" s="206"/>
-      <c r="R20" s="209"/>
-      <c r="S20" s="209"/>
-      <c r="T20" s="209"/>
-      <c r="U20" s="209"/>
-      <c r="V20" s="209"/>
-      <c r="W20" s="209"/>
-      <c r="X20" s="209"/>
-      <c r="Y20" s="209"/>
-      <c r="Z20" s="209"/>
-      <c r="AA20" s="209"/>
-      <c r="AB20" s="209"/>
-      <c r="AC20" s="209"/>
-      <c r="AD20" s="209"/>
-      <c r="AE20" s="210"/>
-      <c r="AF20" s="211"/>
-      <c r="AG20" s="207"/>
-      <c r="AH20" s="207"/>
-      <c r="AI20" s="208"/>
+      <c r="B20" s="164"/>
+      <c r="C20" s="165"/>
+      <c r="D20" s="166"/>
+      <c r="E20" s="167"/>
+      <c r="F20" s="168"/>
+      <c r="G20" s="164"/>
+      <c r="H20" s="169"/>
+      <c r="I20" s="165"/>
+      <c r="J20" s="170"/>
+      <c r="K20" s="171"/>
+      <c r="L20" s="171"/>
+      <c r="M20" s="171"/>
+      <c r="N20" s="171"/>
+      <c r="O20" s="171"/>
+      <c r="P20" s="172"/>
+      <c r="Q20" s="173"/>
+      <c r="R20" s="174"/>
+      <c r="S20" s="174"/>
+      <c r="T20" s="174"/>
+      <c r="U20" s="174"/>
+      <c r="V20" s="174"/>
+      <c r="W20" s="174"/>
+      <c r="X20" s="174"/>
+      <c r="Y20" s="174"/>
+      <c r="Z20" s="174"/>
+      <c r="AA20" s="174"/>
+      <c r="AB20" s="174"/>
+      <c r="AC20" s="174"/>
+      <c r="AD20" s="174"/>
+      <c r="AE20" s="175"/>
+      <c r="AF20" s="170"/>
+      <c r="AG20" s="171"/>
+      <c r="AH20" s="171"/>
+      <c r="AI20" s="172"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="21"/>
-      <c r="B21" s="200"/>
-      <c r="C21" s="201"/>
-      <c r="D21" s="202"/>
-      <c r="E21" s="203"/>
-      <c r="F21" s="204"/>
-      <c r="G21" s="200"/>
-      <c r="H21" s="205"/>
-      <c r="I21" s="201"/>
-      <c r="J21" s="211"/>
-      <c r="K21" s="207"/>
-      <c r="L21" s="207"/>
-      <c r="M21" s="207"/>
-      <c r="N21" s="207"/>
-      <c r="O21" s="207"/>
-      <c r="P21" s="208"/>
-      <c r="Q21" s="206"/>
-      <c r="R21" s="209"/>
-      <c r="S21" s="209"/>
-      <c r="T21" s="209"/>
-      <c r="U21" s="209"/>
-      <c r="V21" s="209"/>
-      <c r="W21" s="209"/>
-      <c r="X21" s="209"/>
-      <c r="Y21" s="209"/>
-      <c r="Z21" s="209"/>
-      <c r="AA21" s="209"/>
-      <c r="AB21" s="209"/>
-      <c r="AC21" s="209"/>
-      <c r="AD21" s="209"/>
-      <c r="AE21" s="210"/>
-      <c r="AF21" s="211"/>
-      <c r="AG21" s="207"/>
-      <c r="AH21" s="207"/>
-      <c r="AI21" s="208"/>
+      <c r="B21" s="164"/>
+      <c r="C21" s="165"/>
+      <c r="D21" s="166"/>
+      <c r="E21" s="167"/>
+      <c r="F21" s="168"/>
+      <c r="G21" s="164"/>
+      <c r="H21" s="169"/>
+      <c r="I21" s="165"/>
+      <c r="J21" s="170"/>
+      <c r="K21" s="171"/>
+      <c r="L21" s="171"/>
+      <c r="M21" s="171"/>
+      <c r="N21" s="171"/>
+      <c r="O21" s="171"/>
+      <c r="P21" s="172"/>
+      <c r="Q21" s="173"/>
+      <c r="R21" s="174"/>
+      <c r="S21" s="174"/>
+      <c r="T21" s="174"/>
+      <c r="U21" s="174"/>
+      <c r="V21" s="174"/>
+      <c r="W21" s="174"/>
+      <c r="X21" s="174"/>
+      <c r="Y21" s="174"/>
+      <c r="Z21" s="174"/>
+      <c r="AA21" s="174"/>
+      <c r="AB21" s="174"/>
+      <c r="AC21" s="174"/>
+      <c r="AD21" s="174"/>
+      <c r="AE21" s="175"/>
+      <c r="AF21" s="170"/>
+      <c r="AG21" s="171"/>
+      <c r="AH21" s="171"/>
+      <c r="AI21" s="172"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="21"/>
-      <c r="B22" s="200"/>
-      <c r="C22" s="201"/>
-      <c r="D22" s="202"/>
-      <c r="E22" s="203"/>
-      <c r="F22" s="204"/>
-      <c r="G22" s="200"/>
-      <c r="H22" s="205"/>
-      <c r="I22" s="201"/>
-      <c r="J22" s="211"/>
-      <c r="K22" s="207"/>
-      <c r="L22" s="207"/>
-      <c r="M22" s="207"/>
-      <c r="N22" s="207"/>
-      <c r="O22" s="207"/>
-      <c r="P22" s="208"/>
-      <c r="Q22" s="206"/>
-      <c r="R22" s="209"/>
-      <c r="S22" s="209"/>
-      <c r="T22" s="209"/>
-      <c r="U22" s="209"/>
-      <c r="V22" s="209"/>
-      <c r="W22" s="209"/>
-      <c r="X22" s="209"/>
-      <c r="Y22" s="209"/>
-      <c r="Z22" s="209"/>
-      <c r="AA22" s="209"/>
-      <c r="AB22" s="209"/>
-      <c r="AC22" s="209"/>
-      <c r="AD22" s="209"/>
-      <c r="AE22" s="210"/>
-      <c r="AF22" s="211"/>
-      <c r="AG22" s="207"/>
-      <c r="AH22" s="207"/>
-      <c r="AI22" s="208"/>
+      <c r="B22" s="164"/>
+      <c r="C22" s="165"/>
+      <c r="D22" s="166"/>
+      <c r="E22" s="167"/>
+      <c r="F22" s="168"/>
+      <c r="G22" s="164"/>
+      <c r="H22" s="169"/>
+      <c r="I22" s="165"/>
+      <c r="J22" s="170"/>
+      <c r="K22" s="171"/>
+      <c r="L22" s="171"/>
+      <c r="M22" s="171"/>
+      <c r="N22" s="171"/>
+      <c r="O22" s="171"/>
+      <c r="P22" s="172"/>
+      <c r="Q22" s="173"/>
+      <c r="R22" s="174"/>
+      <c r="S22" s="174"/>
+      <c r="T22" s="174"/>
+      <c r="U22" s="174"/>
+      <c r="V22" s="174"/>
+      <c r="W22" s="174"/>
+      <c r="X22" s="174"/>
+      <c r="Y22" s="174"/>
+      <c r="Z22" s="174"/>
+      <c r="AA22" s="174"/>
+      <c r="AB22" s="174"/>
+      <c r="AC22" s="174"/>
+      <c r="AD22" s="174"/>
+      <c r="AE22" s="175"/>
+      <c r="AF22" s="170"/>
+      <c r="AG22" s="171"/>
+      <c r="AH22" s="171"/>
+      <c r="AI22" s="172"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="21"/>
-      <c r="B23" s="200"/>
-      <c r="C23" s="201"/>
-      <c r="D23" s="202"/>
-      <c r="E23" s="203"/>
-      <c r="F23" s="204"/>
-      <c r="G23" s="200"/>
-      <c r="H23" s="205"/>
-      <c r="I23" s="201"/>
-      <c r="J23" s="211"/>
-      <c r="K23" s="207"/>
-      <c r="L23" s="207"/>
-      <c r="M23" s="207"/>
-      <c r="N23" s="207"/>
-      <c r="O23" s="207"/>
-      <c r="P23" s="208"/>
-      <c r="Q23" s="206"/>
-      <c r="R23" s="209"/>
-      <c r="S23" s="209"/>
-      <c r="T23" s="209"/>
-      <c r="U23" s="209"/>
-      <c r="V23" s="209"/>
-      <c r="W23" s="209"/>
-      <c r="X23" s="209"/>
-      <c r="Y23" s="209"/>
-      <c r="Z23" s="209"/>
-      <c r="AA23" s="209"/>
-      <c r="AB23" s="209"/>
-      <c r="AC23" s="209"/>
-      <c r="AD23" s="209"/>
-      <c r="AE23" s="210"/>
-      <c r="AF23" s="211"/>
-      <c r="AG23" s="207"/>
-      <c r="AH23" s="207"/>
-      <c r="AI23" s="208"/>
+      <c r="B23" s="164"/>
+      <c r="C23" s="165"/>
+      <c r="D23" s="166"/>
+      <c r="E23" s="167"/>
+      <c r="F23" s="168"/>
+      <c r="G23" s="164"/>
+      <c r="H23" s="169"/>
+      <c r="I23" s="165"/>
+      <c r="J23" s="170"/>
+      <c r="K23" s="171"/>
+      <c r="L23" s="171"/>
+      <c r="M23" s="171"/>
+      <c r="N23" s="171"/>
+      <c r="O23" s="171"/>
+      <c r="P23" s="172"/>
+      <c r="Q23" s="173"/>
+      <c r="R23" s="174"/>
+      <c r="S23" s="174"/>
+      <c r="T23" s="174"/>
+      <c r="U23" s="174"/>
+      <c r="V23" s="174"/>
+      <c r="W23" s="174"/>
+      <c r="X23" s="174"/>
+      <c r="Y23" s="174"/>
+      <c r="Z23" s="174"/>
+      <c r="AA23" s="174"/>
+      <c r="AB23" s="174"/>
+      <c r="AC23" s="174"/>
+      <c r="AD23" s="174"/>
+      <c r="AE23" s="175"/>
+      <c r="AF23" s="170"/>
+      <c r="AG23" s="171"/>
+      <c r="AH23" s="171"/>
+      <c r="AI23" s="172"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="21"/>
-      <c r="B24" s="200"/>
-      <c r="C24" s="201"/>
-      <c r="D24" s="202"/>
-      <c r="E24" s="203"/>
-      <c r="F24" s="204"/>
-      <c r="G24" s="200"/>
-      <c r="H24" s="205"/>
-      <c r="I24" s="201"/>
-      <c r="J24" s="211"/>
-      <c r="K24" s="207"/>
-      <c r="L24" s="207"/>
-      <c r="M24" s="207"/>
-      <c r="N24" s="207"/>
-      <c r="O24" s="207"/>
-      <c r="P24" s="208"/>
-      <c r="Q24" s="206"/>
-      <c r="R24" s="209"/>
-      <c r="S24" s="209"/>
-      <c r="T24" s="209"/>
-      <c r="U24" s="209"/>
-      <c r="V24" s="209"/>
-      <c r="W24" s="209"/>
-      <c r="X24" s="209"/>
-      <c r="Y24" s="209"/>
-      <c r="Z24" s="209"/>
-      <c r="AA24" s="209"/>
-      <c r="AB24" s="209"/>
-      <c r="AC24" s="209"/>
-      <c r="AD24" s="209"/>
-      <c r="AE24" s="210"/>
-      <c r="AF24" s="211"/>
-      <c r="AG24" s="207"/>
-      <c r="AH24" s="207"/>
-      <c r="AI24" s="208"/>
+      <c r="B24" s="164"/>
+      <c r="C24" s="165"/>
+      <c r="D24" s="166"/>
+      <c r="E24" s="167"/>
+      <c r="F24" s="168"/>
+      <c r="G24" s="164"/>
+      <c r="H24" s="169"/>
+      <c r="I24" s="165"/>
+      <c r="J24" s="170"/>
+      <c r="K24" s="171"/>
+      <c r="L24" s="171"/>
+      <c r="M24" s="171"/>
+      <c r="N24" s="171"/>
+      <c r="O24" s="171"/>
+      <c r="P24" s="172"/>
+      <c r="Q24" s="173"/>
+      <c r="R24" s="174"/>
+      <c r="S24" s="174"/>
+      <c r="T24" s="174"/>
+      <c r="U24" s="174"/>
+      <c r="V24" s="174"/>
+      <c r="W24" s="174"/>
+      <c r="X24" s="174"/>
+      <c r="Y24" s="174"/>
+      <c r="Z24" s="174"/>
+      <c r="AA24" s="174"/>
+      <c r="AB24" s="174"/>
+      <c r="AC24" s="174"/>
+      <c r="AD24" s="174"/>
+      <c r="AE24" s="175"/>
+      <c r="AF24" s="170"/>
+      <c r="AG24" s="171"/>
+      <c r="AH24" s="171"/>
+      <c r="AI24" s="172"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="21"/>
-      <c r="B25" s="200"/>
-      <c r="C25" s="201"/>
-      <c r="D25" s="202"/>
-      <c r="E25" s="203"/>
-      <c r="F25" s="204"/>
-      <c r="G25" s="200"/>
-      <c r="H25" s="205"/>
-      <c r="I25" s="201"/>
-      <c r="J25" s="211"/>
-      <c r="K25" s="207"/>
-      <c r="L25" s="207"/>
-      <c r="M25" s="207"/>
-      <c r="N25" s="207"/>
-      <c r="O25" s="207"/>
-      <c r="P25" s="208"/>
-      <c r="Q25" s="206"/>
-      <c r="R25" s="209"/>
-      <c r="S25" s="209"/>
-      <c r="T25" s="209"/>
-      <c r="U25" s="209"/>
-      <c r="V25" s="209"/>
-      <c r="W25" s="209"/>
-      <c r="X25" s="209"/>
-      <c r="Y25" s="209"/>
-      <c r="Z25" s="209"/>
-      <c r="AA25" s="209"/>
-      <c r="AB25" s="209"/>
-      <c r="AC25" s="209"/>
-      <c r="AD25" s="209"/>
-      <c r="AE25" s="210"/>
-      <c r="AF25" s="211"/>
-      <c r="AG25" s="207"/>
-      <c r="AH25" s="207"/>
-      <c r="AI25" s="208"/>
+      <c r="B25" s="164"/>
+      <c r="C25" s="165"/>
+      <c r="D25" s="166"/>
+      <c r="E25" s="167"/>
+      <c r="F25" s="168"/>
+      <c r="G25" s="164"/>
+      <c r="H25" s="169"/>
+      <c r="I25" s="165"/>
+      <c r="J25" s="170"/>
+      <c r="K25" s="171"/>
+      <c r="L25" s="171"/>
+      <c r="M25" s="171"/>
+      <c r="N25" s="171"/>
+      <c r="O25" s="171"/>
+      <c r="P25" s="172"/>
+      <c r="Q25" s="173"/>
+      <c r="R25" s="174"/>
+      <c r="S25" s="174"/>
+      <c r="T25" s="174"/>
+      <c r="U25" s="174"/>
+      <c r="V25" s="174"/>
+      <c r="W25" s="174"/>
+      <c r="X25" s="174"/>
+      <c r="Y25" s="174"/>
+      <c r="Z25" s="174"/>
+      <c r="AA25" s="174"/>
+      <c r="AB25" s="174"/>
+      <c r="AC25" s="174"/>
+      <c r="AD25" s="174"/>
+      <c r="AE25" s="175"/>
+      <c r="AF25" s="170"/>
+      <c r="AG25" s="171"/>
+      <c r="AH25" s="171"/>
+      <c r="AI25" s="172"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="21"/>
-      <c r="B26" s="200"/>
-      <c r="C26" s="201"/>
-      <c r="D26" s="202"/>
-      <c r="E26" s="203"/>
-      <c r="F26" s="204"/>
-      <c r="G26" s="200"/>
-      <c r="H26" s="205"/>
-      <c r="I26" s="201"/>
-      <c r="J26" s="211"/>
-      <c r="K26" s="207"/>
-      <c r="L26" s="207"/>
-      <c r="M26" s="207"/>
-      <c r="N26" s="207"/>
-      <c r="O26" s="207"/>
-      <c r="P26" s="208"/>
-      <c r="Q26" s="206"/>
-      <c r="R26" s="209"/>
-      <c r="S26" s="209"/>
-      <c r="T26" s="209"/>
-      <c r="U26" s="209"/>
-      <c r="V26" s="209"/>
-      <c r="W26" s="209"/>
-      <c r="X26" s="209"/>
-      <c r="Y26" s="209"/>
-      <c r="Z26" s="209"/>
-      <c r="AA26" s="209"/>
-      <c r="AB26" s="209"/>
-      <c r="AC26" s="209"/>
-      <c r="AD26" s="209"/>
-      <c r="AE26" s="210"/>
-      <c r="AF26" s="211"/>
-      <c r="AG26" s="207"/>
-      <c r="AH26" s="207"/>
-      <c r="AI26" s="208"/>
+      <c r="B26" s="164"/>
+      <c r="C26" s="165"/>
+      <c r="D26" s="166"/>
+      <c r="E26" s="167"/>
+      <c r="F26" s="168"/>
+      <c r="G26" s="164"/>
+      <c r="H26" s="169"/>
+      <c r="I26" s="165"/>
+      <c r="J26" s="170"/>
+      <c r="K26" s="171"/>
+      <c r="L26" s="171"/>
+      <c r="M26" s="171"/>
+      <c r="N26" s="171"/>
+      <c r="O26" s="171"/>
+      <c r="P26" s="172"/>
+      <c r="Q26" s="173"/>
+      <c r="R26" s="174"/>
+      <c r="S26" s="174"/>
+      <c r="T26" s="174"/>
+      <c r="U26" s="174"/>
+      <c r="V26" s="174"/>
+      <c r="W26" s="174"/>
+      <c r="X26" s="174"/>
+      <c r="Y26" s="174"/>
+      <c r="Z26" s="174"/>
+      <c r="AA26" s="174"/>
+      <c r="AB26" s="174"/>
+      <c r="AC26" s="174"/>
+      <c r="AD26" s="174"/>
+      <c r="AE26" s="175"/>
+      <c r="AF26" s="170"/>
+      <c r="AG26" s="171"/>
+      <c r="AH26" s="171"/>
+      <c r="AI26" s="172"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="21"/>
-      <c r="B27" s="200"/>
-      <c r="C27" s="201"/>
-      <c r="D27" s="202"/>
-      <c r="E27" s="203"/>
-      <c r="F27" s="204"/>
-      <c r="G27" s="200"/>
-      <c r="H27" s="205"/>
-      <c r="I27" s="201"/>
-      <c r="J27" s="211"/>
-      <c r="K27" s="207"/>
-      <c r="L27" s="207"/>
-      <c r="M27" s="207"/>
-      <c r="N27" s="207"/>
-      <c r="O27" s="207"/>
-      <c r="P27" s="208"/>
-      <c r="Q27" s="206"/>
-      <c r="R27" s="209"/>
-      <c r="S27" s="209"/>
-      <c r="T27" s="209"/>
-      <c r="U27" s="209"/>
-      <c r="V27" s="209"/>
-      <c r="W27" s="209"/>
-      <c r="X27" s="209"/>
-      <c r="Y27" s="209"/>
-      <c r="Z27" s="209"/>
-      <c r="AA27" s="209"/>
-      <c r="AB27" s="209"/>
-      <c r="AC27" s="209"/>
-      <c r="AD27" s="209"/>
-      <c r="AE27" s="210"/>
-      <c r="AF27" s="211"/>
-      <c r="AG27" s="207"/>
-      <c r="AH27" s="207"/>
-      <c r="AI27" s="208"/>
+      <c r="B27" s="164"/>
+      <c r="C27" s="165"/>
+      <c r="D27" s="166"/>
+      <c r="E27" s="167"/>
+      <c r="F27" s="168"/>
+      <c r="G27" s="164"/>
+      <c r="H27" s="169"/>
+      <c r="I27" s="165"/>
+      <c r="J27" s="170"/>
+      <c r="K27" s="171"/>
+      <c r="L27" s="171"/>
+      <c r="M27" s="171"/>
+      <c r="N27" s="171"/>
+      <c r="O27" s="171"/>
+      <c r="P27" s="172"/>
+      <c r="Q27" s="173"/>
+      <c r="R27" s="174"/>
+      <c r="S27" s="174"/>
+      <c r="T27" s="174"/>
+      <c r="U27" s="174"/>
+      <c r="V27" s="174"/>
+      <c r="W27" s="174"/>
+      <c r="X27" s="174"/>
+      <c r="Y27" s="174"/>
+      <c r="Z27" s="174"/>
+      <c r="AA27" s="174"/>
+      <c r="AB27" s="174"/>
+      <c r="AC27" s="174"/>
+      <c r="AD27" s="174"/>
+      <c r="AE27" s="175"/>
+      <c r="AF27" s="170"/>
+      <c r="AG27" s="171"/>
+      <c r="AH27" s="171"/>
+      <c r="AI27" s="172"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="21"/>
-      <c r="B28" s="200"/>
-      <c r="C28" s="201"/>
-      <c r="D28" s="202"/>
-      <c r="E28" s="203"/>
-      <c r="F28" s="204"/>
-      <c r="G28" s="200"/>
-      <c r="H28" s="205"/>
-      <c r="I28" s="201"/>
-      <c r="J28" s="211"/>
-      <c r="K28" s="207"/>
-      <c r="L28" s="207"/>
-      <c r="M28" s="207"/>
-      <c r="N28" s="207"/>
-      <c r="O28" s="207"/>
-      <c r="P28" s="208"/>
-      <c r="Q28" s="206"/>
-      <c r="R28" s="209"/>
-      <c r="S28" s="209"/>
-      <c r="T28" s="209"/>
-      <c r="U28" s="209"/>
-      <c r="V28" s="209"/>
-      <c r="W28" s="209"/>
-      <c r="X28" s="209"/>
-      <c r="Y28" s="209"/>
-      <c r="Z28" s="209"/>
-      <c r="AA28" s="209"/>
-      <c r="AB28" s="209"/>
-      <c r="AC28" s="209"/>
-      <c r="AD28" s="209"/>
-      <c r="AE28" s="210"/>
-      <c r="AF28" s="211"/>
-      <c r="AG28" s="207"/>
-      <c r="AH28" s="207"/>
-      <c r="AI28" s="208"/>
+      <c r="B28" s="164"/>
+      <c r="C28" s="165"/>
+      <c r="D28" s="166"/>
+      <c r="E28" s="167"/>
+      <c r="F28" s="168"/>
+      <c r="G28" s="164"/>
+      <c r="H28" s="169"/>
+      <c r="I28" s="165"/>
+      <c r="J28" s="170"/>
+      <c r="K28" s="171"/>
+      <c r="L28" s="171"/>
+      <c r="M28" s="171"/>
+      <c r="N28" s="171"/>
+      <c r="O28" s="171"/>
+      <c r="P28" s="172"/>
+      <c r="Q28" s="173"/>
+      <c r="R28" s="174"/>
+      <c r="S28" s="174"/>
+      <c r="T28" s="174"/>
+      <c r="U28" s="174"/>
+      <c r="V28" s="174"/>
+      <c r="W28" s="174"/>
+      <c r="X28" s="174"/>
+      <c r="Y28" s="174"/>
+      <c r="Z28" s="174"/>
+      <c r="AA28" s="174"/>
+      <c r="AB28" s="174"/>
+      <c r="AC28" s="174"/>
+      <c r="AD28" s="174"/>
+      <c r="AE28" s="175"/>
+      <c r="AF28" s="170"/>
+      <c r="AG28" s="171"/>
+      <c r="AH28" s="171"/>
+      <c r="AI28" s="172"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="21"/>
-      <c r="B29" s="200"/>
-      <c r="C29" s="201"/>
-      <c r="D29" s="202"/>
-      <c r="E29" s="203"/>
-      <c r="F29" s="204"/>
-      <c r="G29" s="200"/>
-      <c r="H29" s="205"/>
-      <c r="I29" s="201"/>
-      <c r="J29" s="211"/>
-      <c r="K29" s="207"/>
-      <c r="L29" s="207"/>
-      <c r="M29" s="207"/>
-      <c r="N29" s="207"/>
-      <c r="O29" s="207"/>
-      <c r="P29" s="208"/>
-      <c r="Q29" s="206"/>
-      <c r="R29" s="209"/>
-      <c r="S29" s="209"/>
-      <c r="T29" s="209"/>
-      <c r="U29" s="209"/>
-      <c r="V29" s="209"/>
-      <c r="W29" s="209"/>
-      <c r="X29" s="209"/>
-      <c r="Y29" s="209"/>
-      <c r="Z29" s="209"/>
-      <c r="AA29" s="209"/>
-      <c r="AB29" s="209"/>
-      <c r="AC29" s="209"/>
-      <c r="AD29" s="209"/>
-      <c r="AE29" s="210"/>
-      <c r="AF29" s="211"/>
-      <c r="AG29" s="207"/>
-      <c r="AH29" s="207"/>
-      <c r="AI29" s="208"/>
+      <c r="B29" s="164"/>
+      <c r="C29" s="165"/>
+      <c r="D29" s="166"/>
+      <c r="E29" s="167"/>
+      <c r="F29" s="168"/>
+      <c r="G29" s="164"/>
+      <c r="H29" s="169"/>
+      <c r="I29" s="165"/>
+      <c r="J29" s="170"/>
+      <c r="K29" s="171"/>
+      <c r="L29" s="171"/>
+      <c r="M29" s="171"/>
+      <c r="N29" s="171"/>
+      <c r="O29" s="171"/>
+      <c r="P29" s="172"/>
+      <c r="Q29" s="173"/>
+      <c r="R29" s="174"/>
+      <c r="S29" s="174"/>
+      <c r="T29" s="174"/>
+      <c r="U29" s="174"/>
+      <c r="V29" s="174"/>
+      <c r="W29" s="174"/>
+      <c r="X29" s="174"/>
+      <c r="Y29" s="174"/>
+      <c r="Z29" s="174"/>
+      <c r="AA29" s="174"/>
+      <c r="AB29" s="174"/>
+      <c r="AC29" s="174"/>
+      <c r="AD29" s="174"/>
+      <c r="AE29" s="175"/>
+      <c r="AF29" s="170"/>
+      <c r="AG29" s="171"/>
+      <c r="AH29" s="171"/>
+      <c r="AI29" s="172"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="21"/>
-      <c r="B30" s="200"/>
-      <c r="C30" s="201"/>
-      <c r="D30" s="202"/>
-      <c r="E30" s="203"/>
-      <c r="F30" s="204"/>
-      <c r="G30" s="200"/>
-      <c r="H30" s="205"/>
-      <c r="I30" s="201"/>
-      <c r="J30" s="211"/>
-      <c r="K30" s="207"/>
-      <c r="L30" s="207"/>
-      <c r="M30" s="207"/>
-      <c r="N30" s="207"/>
-      <c r="O30" s="207"/>
-      <c r="P30" s="208"/>
-      <c r="Q30" s="206"/>
-      <c r="R30" s="209"/>
-      <c r="S30" s="209"/>
-      <c r="T30" s="209"/>
-      <c r="U30" s="209"/>
-      <c r="V30" s="209"/>
-      <c r="W30" s="209"/>
-      <c r="X30" s="209"/>
-      <c r="Y30" s="209"/>
-      <c r="Z30" s="209"/>
-      <c r="AA30" s="209"/>
-      <c r="AB30" s="209"/>
-      <c r="AC30" s="209"/>
-      <c r="AD30" s="209"/>
-      <c r="AE30" s="210"/>
-      <c r="AF30" s="211"/>
-      <c r="AG30" s="207"/>
-      <c r="AH30" s="207"/>
-      <c r="AI30" s="208"/>
+      <c r="B30" s="164"/>
+      <c r="C30" s="165"/>
+      <c r="D30" s="166"/>
+      <c r="E30" s="167"/>
+      <c r="F30" s="168"/>
+      <c r="G30" s="164"/>
+      <c r="H30" s="169"/>
+      <c r="I30" s="165"/>
+      <c r="J30" s="170"/>
+      <c r="K30" s="171"/>
+      <c r="L30" s="171"/>
+      <c r="M30" s="171"/>
+      <c r="N30" s="171"/>
+      <c r="O30" s="171"/>
+      <c r="P30" s="172"/>
+      <c r="Q30" s="173"/>
+      <c r="R30" s="174"/>
+      <c r="S30" s="174"/>
+      <c r="T30" s="174"/>
+      <c r="U30" s="174"/>
+      <c r="V30" s="174"/>
+      <c r="W30" s="174"/>
+      <c r="X30" s="174"/>
+      <c r="Y30" s="174"/>
+      <c r="Z30" s="174"/>
+      <c r="AA30" s="174"/>
+      <c r="AB30" s="174"/>
+      <c r="AC30" s="174"/>
+      <c r="AD30" s="174"/>
+      <c r="AE30" s="175"/>
+      <c r="AF30" s="170"/>
+      <c r="AG30" s="171"/>
+      <c r="AH30" s="171"/>
+      <c r="AI30" s="172"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="200"/>
-      <c r="C31" s="201"/>
-      <c r="D31" s="202"/>
-      <c r="E31" s="203"/>
-      <c r="F31" s="204"/>
-      <c r="G31" s="200"/>
-      <c r="H31" s="205"/>
-      <c r="I31" s="201"/>
-      <c r="J31" s="211"/>
-      <c r="K31" s="207"/>
-      <c r="L31" s="207"/>
-      <c r="M31" s="207"/>
-      <c r="N31" s="207"/>
-      <c r="O31" s="207"/>
-      <c r="P31" s="208"/>
-      <c r="Q31" s="206"/>
-      <c r="R31" s="209"/>
-      <c r="S31" s="209"/>
-      <c r="T31" s="209"/>
-      <c r="U31" s="209"/>
-      <c r="V31" s="209"/>
-      <c r="W31" s="209"/>
-      <c r="X31" s="209"/>
-      <c r="Y31" s="209"/>
-      <c r="Z31" s="209"/>
-      <c r="AA31" s="209"/>
-      <c r="AB31" s="209"/>
-      <c r="AC31" s="209"/>
-      <c r="AD31" s="209"/>
-      <c r="AE31" s="210"/>
-      <c r="AF31" s="211"/>
-      <c r="AG31" s="207"/>
-      <c r="AH31" s="207"/>
-      <c r="AI31" s="208"/>
+      <c r="B31" s="164"/>
+      <c r="C31" s="165"/>
+      <c r="D31" s="166"/>
+      <c r="E31" s="167"/>
+      <c r="F31" s="168"/>
+      <c r="G31" s="164"/>
+      <c r="H31" s="169"/>
+      <c r="I31" s="165"/>
+      <c r="J31" s="170"/>
+      <c r="K31" s="171"/>
+      <c r="L31" s="171"/>
+      <c r="M31" s="171"/>
+      <c r="N31" s="171"/>
+      <c r="O31" s="171"/>
+      <c r="P31" s="172"/>
+      <c r="Q31" s="173"/>
+      <c r="R31" s="174"/>
+      <c r="S31" s="174"/>
+      <c r="T31" s="174"/>
+      <c r="U31" s="174"/>
+      <c r="V31" s="174"/>
+      <c r="W31" s="174"/>
+      <c r="X31" s="174"/>
+      <c r="Y31" s="174"/>
+      <c r="Z31" s="174"/>
+      <c r="AA31" s="174"/>
+      <c r="AB31" s="174"/>
+      <c r="AC31" s="174"/>
+      <c r="AD31" s="174"/>
+      <c r="AE31" s="175"/>
+      <c r="AF31" s="170"/>
+      <c r="AG31" s="171"/>
+      <c r="AH31" s="171"/>
+      <c r="AI31" s="172"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="21"/>
-      <c r="B32" s="200"/>
-      <c r="C32" s="201"/>
-      <c r="D32" s="202"/>
-      <c r="E32" s="203"/>
-      <c r="F32" s="204"/>
-      <c r="G32" s="200"/>
-      <c r="H32" s="205"/>
-      <c r="I32" s="201"/>
-      <c r="J32" s="211"/>
-      <c r="K32" s="221"/>
-      <c r="L32" s="207"/>
-      <c r="M32" s="207"/>
-      <c r="N32" s="207"/>
-      <c r="O32" s="207"/>
-      <c r="P32" s="208"/>
-      <c r="Q32" s="206"/>
-      <c r="R32" s="209"/>
-      <c r="S32" s="209"/>
-      <c r="T32" s="209"/>
-      <c r="U32" s="209"/>
-      <c r="V32" s="209"/>
-      <c r="W32" s="209"/>
-      <c r="X32" s="209"/>
-      <c r="Y32" s="209"/>
-      <c r="Z32" s="209"/>
-      <c r="AA32" s="209"/>
-      <c r="AB32" s="209"/>
-      <c r="AC32" s="209"/>
-      <c r="AD32" s="209"/>
-      <c r="AE32" s="210"/>
-      <c r="AF32" s="211"/>
-      <c r="AG32" s="207"/>
-      <c r="AH32" s="207"/>
-      <c r="AI32" s="208"/>
+      <c r="B32" s="164"/>
+      <c r="C32" s="165"/>
+      <c r="D32" s="166"/>
+      <c r="E32" s="167"/>
+      <c r="F32" s="168"/>
+      <c r="G32" s="164"/>
+      <c r="H32" s="169"/>
+      <c r="I32" s="165"/>
+      <c r="J32" s="170"/>
+      <c r="K32" s="176"/>
+      <c r="L32" s="171"/>
+      <c r="M32" s="171"/>
+      <c r="N32" s="171"/>
+      <c r="O32" s="171"/>
+      <c r="P32" s="172"/>
+      <c r="Q32" s="173"/>
+      <c r="R32" s="174"/>
+      <c r="S32" s="174"/>
+      <c r="T32" s="174"/>
+      <c r="U32" s="174"/>
+      <c r="V32" s="174"/>
+      <c r="W32" s="174"/>
+      <c r="X32" s="174"/>
+      <c r="Y32" s="174"/>
+      <c r="Z32" s="174"/>
+      <c r="AA32" s="174"/>
+      <c r="AB32" s="174"/>
+      <c r="AC32" s="174"/>
+      <c r="AD32" s="174"/>
+      <c r="AE32" s="175"/>
+      <c r="AF32" s="170"/>
+      <c r="AG32" s="171"/>
+      <c r="AH32" s="171"/>
+      <c r="AI32" s="172"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="21"/>
-      <c r="B33" s="200"/>
-      <c r="C33" s="201"/>
-      <c r="D33" s="202"/>
-      <c r="E33" s="203"/>
-      <c r="F33" s="204"/>
-      <c r="G33" s="200"/>
-      <c r="H33" s="205"/>
-      <c r="I33" s="201"/>
-      <c r="J33" s="211"/>
-      <c r="K33" s="207"/>
-      <c r="L33" s="207"/>
-      <c r="M33" s="207"/>
-      <c r="N33" s="207"/>
-      <c r="O33" s="207"/>
-      <c r="P33" s="208"/>
-      <c r="Q33" s="206"/>
-      <c r="R33" s="209"/>
-      <c r="S33" s="209"/>
-      <c r="T33" s="209"/>
-      <c r="U33" s="209"/>
-      <c r="V33" s="209"/>
-      <c r="W33" s="209"/>
-      <c r="X33" s="209"/>
-      <c r="Y33" s="209"/>
-      <c r="Z33" s="209"/>
-      <c r="AA33" s="209"/>
-      <c r="AB33" s="209"/>
-      <c r="AC33" s="209"/>
-      <c r="AD33" s="209"/>
-      <c r="AE33" s="210"/>
-      <c r="AF33" s="211"/>
-      <c r="AG33" s="207"/>
-      <c r="AH33" s="207"/>
-      <c r="AI33" s="208"/>
+      <c r="B33" s="164"/>
+      <c r="C33" s="165"/>
+      <c r="D33" s="166"/>
+      <c r="E33" s="167"/>
+      <c r="F33" s="168"/>
+      <c r="G33" s="164"/>
+      <c r="H33" s="169"/>
+      <c r="I33" s="165"/>
+      <c r="J33" s="170"/>
+      <c r="K33" s="171"/>
+      <c r="L33" s="171"/>
+      <c r="M33" s="171"/>
+      <c r="N33" s="171"/>
+      <c r="O33" s="171"/>
+      <c r="P33" s="172"/>
+      <c r="Q33" s="173"/>
+      <c r="R33" s="174"/>
+      <c r="S33" s="174"/>
+      <c r="T33" s="174"/>
+      <c r="U33" s="174"/>
+      <c r="V33" s="174"/>
+      <c r="W33" s="174"/>
+      <c r="X33" s="174"/>
+      <c r="Y33" s="174"/>
+      <c r="Z33" s="174"/>
+      <c r="AA33" s="174"/>
+      <c r="AB33" s="174"/>
+      <c r="AC33" s="174"/>
+      <c r="AD33" s="174"/>
+      <c r="AE33" s="175"/>
+      <c r="AF33" s="170"/>
+      <c r="AG33" s="171"/>
+      <c r="AH33" s="171"/>
+      <c r="AI33" s="172"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="178">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -15611,6 +15453,161 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(バッチ)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(バッチ)_サンプル.xlsx
@@ -15766,8 +15766,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -15809,8 +15809,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -15846,8 +15846,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -15885,8 +15885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -15920,8 +15920,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -15955,8 +15955,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -15990,8 +15990,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -16025,8 +16025,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -16064,8 +16064,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -16099,8 +16099,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -16134,8 +16134,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -16171,8 +16171,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -16206,8 +16206,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -16241,8 +16241,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -16276,8 +16276,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -16315,8 +16315,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -16350,8 +16350,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -16389,8 +16389,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -16424,8 +16424,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -16461,8 +16461,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -16496,8 +16496,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -16531,8 +16531,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -16566,8 +16566,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -16603,8 +16603,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -16638,8 +16638,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -16675,8 +16675,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -16716,8 +16716,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -16751,8 +16751,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -16786,8 +16786,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -16821,8 +16821,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -16860,8 +16860,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -16895,8 +16895,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -16938,8 +16938,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -16973,8 +16973,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -17008,8 +17008,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -17045,8 +17045,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -17080,8 +17080,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -17115,8 +17115,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -17152,8 +17152,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -17187,8 +17187,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -17224,8 +17224,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -17259,8 +17259,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -17294,8 +17294,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -17329,8 +17329,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -17364,8 +17364,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -17399,8 +17399,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -17436,8 +17436,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -17473,8 +17473,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -17510,8 +17510,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -17559,8 +17559,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -17594,8 +17594,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -17629,8 +17629,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -17664,8 +17664,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -17699,8 +17699,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -17746,8 +17746,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -17791,8 +17791,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-2</v>
       </c>
@@ -17834,8 +17834,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -17869,8 +17869,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -17904,8 +17904,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -17939,8 +17939,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -17974,8 +17974,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -18009,8 +18009,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -18044,8 +18044,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -18091,8 +18091,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-2</v>
       </c>
@@ -18130,8 +18130,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-3</v>
       </c>
@@ -18169,8 +18169,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-4</v>
       </c>
@@ -18208,8 +18208,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-5</v>
       </c>
@@ -18247,8 +18247,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -18294,8 +18294,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-2</v>
       </c>
@@ -18333,8 +18333,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-3</v>
       </c>
@@ -18372,8 +18372,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-4</v>
       </c>
@@ -18411,8 +18411,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-5</v>
       </c>
@@ -18450,8 +18450,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -18485,8 +18485,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -18520,8 +18520,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -18555,8 +18555,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -18590,8 +18590,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -18631,8 +18631,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -18666,8 +18666,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -18703,8 +18703,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -18740,8 +18740,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -18775,8 +18775,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -18812,8 +18812,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -18849,8 +18849,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -18900,8 +18900,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -18947,8 +18947,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -18984,8 +18984,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -19025,8 +19025,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -19060,8 +19060,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -19097,8 +19097,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -19134,8 +19134,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -19169,8 +19169,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -19206,8 +19206,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -19247,8 +19247,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -19282,8 +19282,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -19317,8 +19317,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -19352,8 +19352,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -19387,8 +19387,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -19424,8 +19424,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -19459,8 +19459,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -19494,8 +19494,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -19529,8 +19529,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -19564,8 +19564,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -19601,8 +19601,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -19644,8 +19644,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -19685,8 +19685,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -19720,8 +19720,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -19761,8 +19761,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -19802,8 +19802,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -19837,8 +19837,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -19880,8 +19880,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -19917,8 +19917,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -19952,8 +19952,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -19987,8 +19987,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -20024,8 +20024,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -20059,8 +20059,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -20094,8 +20094,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -20129,8 +20129,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -20164,8 +20164,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -20201,8 +20201,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -20236,8 +20236,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -20271,8 +20271,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -20306,8 +20306,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -20341,8 +20341,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -20378,8 +20378,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -20417,8 +20417,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -20458,8 +20458,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -20495,8 +20495,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -20530,8 +20530,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -20565,8 +20565,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -20608,8 +20608,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -20645,8 +20645,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -20680,8 +20680,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -20715,8 +20715,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -20752,8 +20752,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -20787,8 +20787,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -20826,8 +20826,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -20867,8 +20867,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -20904,8 +20904,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -20941,8 +20941,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -20978,8 +20978,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -21015,8 +21015,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -21052,8 +21052,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -21087,8 +21087,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -21122,8 +21122,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -21157,8 +21157,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -21192,8 +21192,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -21227,8 +21227,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -21266,8 +21266,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -21301,8 +21301,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -21338,8 +21338,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -21373,8 +21373,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -21408,8 +21408,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -21443,8 +21443,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -21478,8 +21478,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -21513,8 +21513,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -21548,8 +21548,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -21583,8 +21583,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -21618,8 +21618,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -21653,8 +21653,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -21688,8 +21688,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -21725,8 +21725,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -21760,8 +21760,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -21795,8 +21795,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -21830,8 +21830,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -21865,8 +21865,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -21900,8 +21900,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -21935,8 +21935,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -21972,8 +21972,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -22007,8 +22007,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -22042,8 +22042,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -22077,8 +22077,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -22112,8 +22112,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -22147,8 +22147,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -22182,8 +22182,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -22217,8 +22217,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -22252,8 +22252,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -22289,8 +22289,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -22326,8 +22326,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -22369,8 +22369,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -22408,8 +22408,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -22447,8 +22447,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -22490,8 +22490,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -22527,8 +22527,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -22562,8 +22562,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -22599,8 +22599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -22634,8 +22634,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -22673,8 +22673,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -22714,8 +22714,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -22749,8 +22749,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -22784,8 +22784,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -22819,8 +22819,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -22854,8 +22854,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -22889,8 +22889,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -22924,8 +22924,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -22961,8 +22961,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -23000,8 +23000,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -23035,8 +23035,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -23070,8 +23070,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -23105,8 +23105,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -23140,8 +23140,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -23175,8 +23175,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -23210,8 +23210,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -23245,8 +23245,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -23280,8 +23280,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -23315,8 +23315,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -23350,8 +23350,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -23385,8 +23385,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -23420,8 +23420,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -23459,8 +23459,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -23494,8 +23494,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -23529,8 +23529,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -23564,8 +23564,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -23599,8 +23599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -23634,8 +23634,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -23669,8 +23669,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -23704,8 +23704,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -23739,8 +23739,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -23774,8 +23774,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -23809,8 +23809,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -23844,8 +23844,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -23879,8 +23879,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -23914,8 +23914,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -23949,8 +23949,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -23986,8 +23986,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -24021,8 +24021,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -24056,8 +24056,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -24093,8 +24093,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -24130,8 +24130,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -24173,8 +24173,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -24210,8 +24210,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -24245,8 +24245,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -24280,8 +24280,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -24315,8 +24315,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -24350,8 +24350,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -24387,8 +24387,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -24422,8 +24422,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -24457,8 +24457,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -24492,8 +24492,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -24527,8 +24527,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -24564,8 +24564,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -24605,8 +24605,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -24648,8 +24648,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -24683,8 +24683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -24722,8 +24722,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -24757,8 +24757,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -24798,8 +24798,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -24835,8 +24835,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -24872,8 +24872,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -24909,8 +24909,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -24948,8 +24948,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -24983,8 +24983,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -25020,8 +25020,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -25055,8 +25055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -25090,8 +25090,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -25125,8 +25125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -25160,8 +25160,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -25195,8 +25195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -25230,8 +25230,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -25265,8 +25265,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -25300,8 +25300,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -25335,8 +25335,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -25370,8 +25370,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -25407,8 +25407,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -25442,8 +25442,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -25477,8 +25477,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -25512,8 +25512,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -25547,8 +25547,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -25582,8 +25582,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -25619,8 +25619,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -25654,8 +25654,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -25689,8 +25689,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -25724,8 +25724,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -25759,8 +25759,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -25794,8 +25794,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -25829,8 +25829,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -25864,8 +25864,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -25901,8 +25901,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -25944,8 +25944,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -25979,8 +25979,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -26014,8 +26014,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -26049,8 +26049,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -26090,8 +26090,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -26127,8 +26127,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -26164,8 +26164,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -26201,8 +26201,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -26240,8 +26240,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -26275,8 +26275,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F298),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F298)&gt;0)*ROW($F$11:F298),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J298),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -26310,8 +26310,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F299),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F299)&gt;0)*ROW($F$11:F299),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J299),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -26345,8 +26345,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F300),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F300)&gt;0)*ROW($F$11:F300),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J300),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -26380,8 +26380,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F301),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F301)&gt;0)*ROW($F$11:F301),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J301),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -26415,8 +26415,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F302),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F302)&gt;0)*ROW($F$11:F302),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J302),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -26450,8 +26450,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F303),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F303)&gt;0)*ROW($F$11:F303),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J303),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -26485,8 +26485,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F304),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F304)&gt;0)*ROW($F$11:F304),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J304),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -26686,8 +26686,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -26729,8 +26729,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -26766,8 +26766,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -26805,8 +26805,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -26840,8 +26840,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -26875,8 +26875,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -26910,8 +26910,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -26945,8 +26945,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -26984,8 +26984,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -27019,8 +27019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -27054,8 +27054,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -27091,8 +27091,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -27126,8 +27126,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -27161,8 +27161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -27196,8 +27196,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -27235,8 +27235,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -27270,8 +27270,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -27309,8 +27309,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -27344,8 +27344,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -27381,8 +27381,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -27416,8 +27416,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -27451,8 +27451,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -27486,8 +27486,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -27523,8 +27523,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -27558,8 +27558,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -27595,8 +27595,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -27636,8 +27636,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -27671,8 +27671,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -27706,8 +27706,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -27741,8 +27741,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -27780,8 +27780,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -27815,8 +27815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -27858,8 +27858,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -27893,8 +27893,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -27928,8 +27928,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -27965,8 +27965,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -28000,8 +28000,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -28035,8 +28035,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -28072,8 +28072,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -28107,8 +28107,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -28144,8 +28144,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -28179,8 +28179,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -28214,8 +28214,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -28249,8 +28249,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -28284,8 +28284,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -28319,8 +28319,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -28356,8 +28356,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -28393,8 +28393,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -28430,8 +28430,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -28469,8 +28469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -28504,8 +28504,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -28539,8 +28539,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -28574,8 +28574,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -28609,8 +28609,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -28646,8 +28646,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -28681,8 +28681,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -28716,8 +28716,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -28751,8 +28751,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -28786,8 +28786,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -28821,8 +28821,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -28856,8 +28856,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -28891,8 +28891,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -28928,8 +28928,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -28965,8 +28965,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -29000,8 +29000,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -29035,8 +29035,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -29070,8 +29070,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -29105,8 +29105,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -29146,8 +29146,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -29181,8 +29181,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -29218,8 +29218,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -29255,8 +29255,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -29290,8 +29290,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -29327,8 +29327,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -29364,8 +29364,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -29405,8 +29405,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -29442,8 +29442,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -29479,8 +29479,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -29520,8 +29520,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -29555,8 +29555,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -29592,8 +29592,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -29629,8 +29629,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -29664,8 +29664,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -29701,8 +29701,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -29742,8 +29742,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -29777,8 +29777,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -29812,8 +29812,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -29847,8 +29847,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -29882,8 +29882,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -29919,8 +29919,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -29954,8 +29954,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -29989,8 +29989,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -30024,8 +30024,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -30059,8 +30059,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -30096,8 +30096,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -30139,8 +30139,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -30180,8 +30180,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -30215,8 +30215,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -30256,8 +30256,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -30297,8 +30297,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -30332,8 +30332,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -30375,8 +30375,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -30412,8 +30412,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -30447,8 +30447,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -30482,8 +30482,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -30529,8 +30529,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -30564,8 +30564,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -30599,8 +30599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -30634,8 +30634,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -30669,8 +30669,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -30716,8 +30716,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -30761,8 +30761,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -30806,8 +30806,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -30851,8 +30851,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -30896,8 +30896,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -30933,8 +30933,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -30972,8 +30972,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -31023,8 +31023,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-2</v>
       </c>
@@ -31066,8 +31066,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-3</v>
       </c>
@@ -31109,8 +31109,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-4</v>
       </c>
@@ -31152,8 +31152,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-5</v>
       </c>
@@ -31195,8 +31195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-6</v>
       </c>
@@ -31238,8 +31238,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-7</v>
       </c>
@@ -31281,8 +31281,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-8</v>
       </c>
@@ -31324,8 +31324,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -31361,8 +31361,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -31396,8 +31396,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -31431,8 +31431,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -31474,8 +31474,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -31511,8 +31511,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -31546,8 +31546,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -31581,8 +31581,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -31618,8 +31618,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -31653,8 +31653,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -31692,8 +31692,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -31733,8 +31733,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -31770,8 +31770,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -31807,8 +31807,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -31844,8 +31844,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -31881,8 +31881,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -31918,8 +31918,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -31953,8 +31953,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -31988,8 +31988,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -32023,8 +32023,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -32058,8 +32058,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -32093,8 +32093,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -32132,8 +32132,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -32167,8 +32167,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -32204,8 +32204,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -32239,8 +32239,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -32274,8 +32274,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -32309,8 +32309,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -32344,8 +32344,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -32379,8 +32379,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -32414,8 +32414,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -32449,8 +32449,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -32484,8 +32484,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -32519,8 +32519,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -32554,8 +32554,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -32591,8 +32591,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -32626,8 +32626,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -32661,8 +32661,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -32696,8 +32696,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -32731,8 +32731,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -32766,8 +32766,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -32801,8 +32801,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -32838,8 +32838,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -32873,8 +32873,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -32908,8 +32908,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -32943,8 +32943,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -32978,8 +32978,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -33013,8 +33013,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -33048,8 +33048,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -33083,8 +33083,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -33118,8 +33118,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -33155,8 +33155,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -33192,8 +33192,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -33235,8 +33235,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -33274,8 +33274,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -33313,8 +33313,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -33356,8 +33356,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -33393,8 +33393,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -33428,8 +33428,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -33465,8 +33465,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -33500,8 +33500,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -33539,8 +33539,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -33580,8 +33580,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -33615,8 +33615,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -33650,8 +33650,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -33685,8 +33685,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -33720,8 +33720,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -33755,8 +33755,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -33790,8 +33790,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -33827,8 +33827,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -33866,8 +33866,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -33901,8 +33901,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -33936,8 +33936,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -33971,8 +33971,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -34006,8 +34006,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -34041,8 +34041,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -34076,8 +34076,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -34111,8 +34111,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -34146,8 +34146,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -34181,8 +34181,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -34216,8 +34216,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -34251,8 +34251,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -34286,8 +34286,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -34325,8 +34325,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -34360,8 +34360,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -34395,8 +34395,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -34430,8 +34430,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -34465,8 +34465,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -34500,8 +34500,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -34535,8 +34535,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -34570,8 +34570,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -34605,8 +34605,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -34640,8 +34640,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -34675,8 +34675,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -34710,8 +34710,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -34745,8 +34745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -34780,8 +34780,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -34815,8 +34815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -34852,8 +34852,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -34887,8 +34887,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -34922,8 +34922,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -34959,8 +34959,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -34996,8 +34996,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -35039,8 +35039,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -35076,8 +35076,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -35111,8 +35111,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -35146,8 +35146,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -35181,8 +35181,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -35216,8 +35216,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -35253,8 +35253,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -35288,8 +35288,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -35323,8 +35323,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -35358,8 +35358,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -35393,8 +35393,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -35430,8 +35430,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -35471,8 +35471,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -35514,8 +35514,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -35549,8 +35549,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -35588,8 +35588,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -35623,8 +35623,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -35664,8 +35664,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -35701,8 +35701,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -35738,8 +35738,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -35775,8 +35775,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -35814,8 +35814,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -35849,8 +35849,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -35886,8 +35886,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -35921,8 +35921,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -35956,8 +35956,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -35991,8 +35991,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -36026,8 +36026,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -36061,8 +36061,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -36096,8 +36096,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -36131,8 +36131,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -36166,8 +36166,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -36201,8 +36201,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -36236,8 +36236,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -36273,8 +36273,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -36308,8 +36308,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -36343,8 +36343,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -36378,8 +36378,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -36413,8 +36413,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -36448,8 +36448,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -36485,8 +36485,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -36520,8 +36520,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -36555,8 +36555,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -36590,8 +36590,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -36625,8 +36625,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -36660,8 +36660,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -36695,8 +36695,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -36730,8 +36730,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -36767,8 +36767,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -36810,8 +36810,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -36845,8 +36845,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -36880,8 +36880,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -36915,8 +36915,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -36956,8 +36956,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -36993,8 +36993,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -37030,8 +37030,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -37067,8 +37067,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -37106,8 +37106,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -37141,8 +37141,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -37176,8 +37176,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -37211,8 +37211,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F298),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F298)&gt;0)*ROW($F$11:F298),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J298),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -37246,8 +37246,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F299),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F299)&gt;0)*ROW($F$11:F299),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J299),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -37281,8 +37281,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F300),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F300)&gt;0)*ROW($F$11:F300),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J300),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -37316,8 +37316,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F301),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F301)&gt;0)*ROW($F$11:F301),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J301),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -37351,8 +37351,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F302),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F302)&gt;0)*ROW($F$11:F302),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J302),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -37386,8 +37386,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F303),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F303)&gt;0)*ROW($F$11:F303),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J303),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-1-1</v>
       </c>
@@ -37439,8 +37439,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F304),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F304)&gt;0)*ROW($F$11:F304),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J304),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-2-1</v>
       </c>
@@ -37484,8 +37484,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F305),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F305)&gt;0)*ROW($F$11:F305),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J305),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-3-1</v>
       </c>
@@ -37529,8 +37529,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F306),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F306)&gt;0)*ROW($F$11:F306),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J306),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-4-1</v>
       </c>
@@ -37574,8 +37574,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F307),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F307)&gt;0)*ROW($F$11:F307),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J307),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-1-1</v>
       </c>
@@ -37619,8 +37619,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F308),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F308)&gt;0)*ROW($F$11:F308),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J308),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-1</v>
       </c>
@@ -37656,8 +37656,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F309),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F309)&gt;0)*ROW($F$11:F309),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J309),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-1</v>
       </c>
@@ -37693,8 +37693,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F310),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F310)&gt;0)*ROW($F$11:F310),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J310),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-1-1</v>
       </c>
@@ -37730,8 +37730,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F311),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F311)&gt;0)*ROW($F$11:F311),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J311),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-1-1</v>
       </c>
@@ -37779,8 +37779,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F312),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F312)&gt;0)*ROW($F$11:F312),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J312),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-2-1</v>
       </c>
@@ -37824,8 +37824,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F313),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F313)&gt;0)*ROW($F$11:F313),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J313),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-2-2</v>
       </c>
@@ -37867,8 +37867,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F314),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F314)&gt;0)*ROW($F$11:F314),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J314),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-2-3</v>
       </c>
@@ -37910,8 +37910,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F315),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F315)&gt;0)*ROW($F$11:F315),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J315),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-2-4</v>
       </c>
@@ -37953,8 +37953,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F316),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F316)&gt;0)*ROW($F$11:F316),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J316),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>106-3-1</v>
       </c>
@@ -37988,8 +37988,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F317),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F317)&gt;0)*ROW($F$11:F317),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J317),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>107-1-1</v>
       </c>
@@ -38037,8 +38037,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F318),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F318)&gt;0)*ROW($F$11:F318),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J318),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>107-2-1</v>
       </c>
@@ -38072,8 +38072,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F319),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F319)&gt;0)*ROW($F$11:F319),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J319),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>107-3-1</v>
       </c>
@@ -38117,8 +38117,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F320),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F320)&gt;0)*ROW($F$11:F320),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J320),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-1-1</v>
       </c>
@@ -38166,8 +38166,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F321),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F321)&gt;0)*ROW($F$11:F321),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J321),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-2-1</v>
       </c>
@@ -38201,8 +38201,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F322),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F322)&gt;0)*ROW($F$11:F322),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J322),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-3-1</v>
       </c>
@@ -38236,8 +38236,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F323),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F323)&gt;0)*ROW($F$11:F323),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J323),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-4-1</v>
       </c>
@@ -38271,8 +38271,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F324),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F324)&gt;0)*ROW($F$11:F324),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J324),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-5-1</v>
       </c>
@@ -38306,8 +38306,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F325),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F325)&gt;0)*ROW($F$11:F325),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J325),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-6-1</v>
       </c>
@@ -38341,8 +38341,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F326),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F326)&gt;0)*ROW($F$11:F326),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J326),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-7-1</v>
       </c>
@@ -38376,8 +38376,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F327),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F327)&gt;0)*ROW($F$11:F327),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J327),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>108-8-1</v>
       </c>
@@ -38411,8 +38411,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F328),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F328)&gt;0)*ROW($F$11:F328),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J328),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>109-1-1</v>
       </c>
@@ -38464,8 +38464,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F329),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F329)&gt;0)*ROW($F$11:F329),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J329),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>110-1-1</v>
       </c>
@@ -38666,11 +38666,11 @@
 _xlpm.確認観点1数, COUNTA($C$11:C11),
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C11)&gt;0)*ROW($C$11:C11),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D11),
-_xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
+_xlpm.確認観点2数_空なら1,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -38714,11 +38714,11 @@
 _xlpm.確認観点1数, COUNTA($C$11:C12),
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C12)&gt;0)*ROW($C$11:C12),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D12),
-_xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
+_xlpm.確認観点2数_空なら1,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-2</v>
       </c>
@@ -38752,11 +38752,11 @@
 _xlpm.確認観点1数, COUNTA($C$11:C13),
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C13)&gt;0)*ROW($C$11:C13),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D13),
-_xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
+_xlpm.確認観点2数_空なら1,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D13)&gt;0)*ROW($D$11:D13),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-2-1</v>
       </c>
@@ -38796,11 +38796,11 @@
 _xlpm.確認観点1数, COUNTA($C$11:C14),
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C14)&gt;0)*ROW($C$11:C14),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D14),
-_xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
+_xlpm.確認観点2数_空なら1,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D14)&gt;0)*ROW($D$11:D14),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-2-2</v>
       </c>
@@ -38834,11 +38834,11 @@
 _xlpm.確認観点1数, COUNTA($C$11:C15),
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C15)&gt;0)*ROW($C$11:C15),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D15),
-_xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
+_xlpm.確認観点2数_空なら1,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D15)&gt;0)*ROW($D$11:D15),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-2-3</v>
       </c>
